--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="449">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Transport</t>
   </si>
   <si>
-    <t>Self-drive rental, FCO to FCO (Aug 24 – Sep 6) — Benz C-Class or similar, IDP in hand</t>
+    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive from Aug 29 (Florence → FCO), IDP in hand</t>
   </si>
   <si>
     <t>Chain story</t>
@@ -175,570 +175,591 @@
     <t>ITA Airways from IAH</t>
   </si>
   <si>
+    <t>12:35pm</t>
+  </si>
+  <si>
+    <t>Private driver to Hotel Trame — Pre-booked NCC, meeting you inside arrivals with a name board. Licensed cars may enter the ZTL to set down, so you are dropped at the hotel door — no garage, no walk with the bags.</t>
+  </si>
+  <si>
+    <t>Private transfer, ~45 min</t>
+  </si>
+  <si>
+    <t>2:00pm</t>
+  </si>
+  <si>
+    <t>Check in at Hotel Trame — A former Franciscan monastery a few streets off Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>Arrive</t>
+  </si>
+  <si>
+    <t>3:00pm</t>
+  </si>
+  <si>
+    <t>First walk: Pantheon → Piazza Navona → Campo de' Fiori — The Pantheon is an eight-minute walk. Go before the nap, not after.</t>
+  </si>
+  <si>
+    <t>On foot</t>
+  </si>
+  <si>
+    <t>6:00pm</t>
+  </si>
+  <si>
+    <t>Nap, deliberately — Set an alarm. This is the single best defence against day-two jet lag.</t>
+  </si>
+  <si>
+    <t>At the hotel</t>
+  </si>
+  <si>
+    <t>7:30pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Etabli — Or the Campari bar on Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>Walk, 4 min</t>
+  </si>
+  <si>
+    <t>Find -&gt;</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Armando al Pantheon — Tiny, family-run, and booked out weeks ahead. Reserve now.</t>
+  </si>
+  <si>
+    <t>Walk, 8 min</t>
+  </si>
+  <si>
+    <t>Reserve -&gt;</t>
+  </si>
+  <si>
+    <t>Tue, Aug 25</t>
+  </si>
+  <si>
+    <t>ROME — Vatican</t>
+  </si>
+  <si>
+    <t>7:45am</t>
+  </si>
+  <si>
+    <t>Vatican early-entry private tour — Into the Sistine Chapel before general admission</t>
+  </si>
+  <si>
+    <t>Taxi, ~15 min</t>
+  </si>
+  <si>
+    <t>Tickets -&gt;</t>
+  </si>
+  <si>
+    <t>1:00pm</t>
+  </si>
+  <si>
+    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
+  </si>
+  <si>
+    <t>Walk from the Vatican</t>
+  </si>
+  <si>
+    <t>2:30pm</t>
+  </si>
+  <si>
+    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>5:00pm</t>
+  </si>
+  <si>
+    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
+  </si>
+  <si>
+    <t>Taxi, ~10 min</t>
+  </si>
+  <si>
+    <t>Rooftop aperitivo near Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>8:30pm</t>
+  </si>
+  <si>
+    <t>OPERA — arias at All Saints' Anglican Church — Confirm the Aug 25 programme; Via del Babuino, off Piazza di Spagna</t>
+  </si>
+  <si>
+    <t>10:00pm</t>
+  </si>
+  <si>
+    <t>Late dinner — Pierluigi — Seafood on Piazza de' Ricci; a properly Roman hour to eat</t>
+  </si>
+  <si>
+    <t>Walk, 6 min</t>
+  </si>
+  <si>
+    <t>Wed, Aug 26</t>
+  </si>
+  <si>
+    <t>ROME — Colosseum &amp; the Forum</t>
+  </si>
+  <si>
+    <t>8:45am</t>
+  </si>
+  <si>
+    <t>Colosseum with arena floor, then Forum + Palatine — The arena-floor add-on is worth it — you stand where the sand was</t>
+  </si>
+  <si>
+    <t>Taxi, ~12 min</t>
+  </si>
+  <si>
+    <t>Lunch — Roscioli — Carbonara and cacio e pepe, and the deli counter on the way out</t>
+  </si>
+  <si>
+    <t>Walk, 5 min via Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>Siesta</t>
+  </si>
+  <si>
+    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
+  </si>
+  <si>
+    <t>Walk, ~12 min</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>[optional] Optional — Galleria Borghese — Timed entry, two-hour slots, books out early. Skip it guilt-free if the day already feels long.</t>
+  </si>
+  <si>
+    <t>Taxi, ~20 min</t>
+  </si>
+  <si>
+    <t>9:00pm</t>
+  </si>
+  <si>
+    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
+  </si>
+  <si>
+    <t>Thu, Aug 27</t>
+  </si>
+  <si>
+    <t>ROME → FLORENCE — Casa G. Firenze</t>
+  </si>
+  <si>
+    <t>TRAVEL DAY</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori. Aim to be at the platform twenty minutes before departure.</t>
+  </si>
+  <si>
+    <t>10:35am</t>
+  </si>
+  <si>
+    <t>Frecciarossa — Roma Termini → Firenze S.M.N. — Book Trenitalia or Italo well ahead; advance fares are a fraction of the walk-up price and both run the route hourly.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1h30</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>12:10pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze Santa Maria Novella — The station is a nine-minute walk from Via dei Rondinelli — no transfer needed</t>
+  </si>
+  <si>
+    <t>Walk, ~9 min</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Drop bags at Casa G. Firenze — Via dei Rondinelli, between the Duomo and Santa Maria Novella. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
+  </si>
+  <si>
+    <t>Trip.com -&gt;</t>
+  </si>
+  <si>
+    <t>1:15pm</t>
+  </si>
+  <si>
+    <t>Lunch at the Mercato Centrale — Five minutes north — the upstairs food hall, no booking, no ceremony</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>First orientation walk — The Duomo and Baptistery from the outside, then Piazza della Repubblica and down to the Arno. The ticketed interiors are all tomorrow — today is just getting your bearings.</t>
+  </si>
+  <si>
+    <t>Unpack and reset — The train bought you an afternoon the drive would have eaten</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo on the secret patio — Casa G.'s courtyard bar</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, comfortably clear now the train lands you at midday.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>1:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, ~10 min on foot and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>Info -&gt;</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and Volterra</t>
+  </si>
+  <si>
+    <t>Driver to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>10:00am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion, right on Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>Lunch + a Vernaccia tasting — San Gimignano's own DOCG white, crisp and mineral, made for a hot afternoon</t>
+  </si>
+  <si>
+    <t>Driver to Volterra — About forty-five minutes</t>
+  </si>
+  <si>
+    <t>3:30pm</t>
+  </si>
+  <si>
+    <t>Piazza dei Priori and the Roman theatre — Tuscany's most complete medieval civic square, plus a 1st-century BC theatre still being excavated</t>
+  </si>
+  <si>
+    <t>Arrive Volterra</t>
+  </si>
+  <si>
+    <t>Alabaster workshops — A carving tradition here since Etruscan times — several studios welcome walk-ins</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Drive back to Castelfalfi — About fifty minutes</t>
+  </si>
+  <si>
+    <t>Dinner at the resort — Or a quieter table down in Montaione village</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY — Montespertoli wine day</t>
+  </si>
+  <si>
+    <t>The estate's 27-hole course, or the spa — Tuscany's largest golf course, or a morning at the newly renovated spa</t>
+  </si>
+  <si>
     <t>12:00pm</t>
   </si>
   <si>
-    <t>Pick up the rental car — Benz C-Class or similar, automatic — reservation #21586310US4. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>FCO rental desk</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Drive to a garage near the hotel — Hotel Trame sits inside Rome's ZTL — park in a garage just outside it (e.g. near Largo Argentina) and walk in. The car stays there until Day 4.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~45 min</t>
-  </si>
-  <si>
-    <t>2:00pm</t>
-  </si>
-  <si>
-    <t>Check in at Hotel Trame — A former Franciscan monastery a few streets off Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Arrive</t>
-  </si>
-  <si>
-    <t>3:00pm</t>
-  </si>
-  <si>
-    <t>First walk: Pantheon → Piazza Navona → Campo de' Fiori — The Pantheon is an eight-minute walk. Go before the nap, not after.</t>
-  </si>
-  <si>
-    <t>On foot</t>
-  </si>
-  <si>
-    <t>6:00pm</t>
-  </si>
-  <si>
-    <t>Nap, deliberately — Set an alarm. This is the single best defence against day-two jet lag.</t>
-  </si>
-  <si>
-    <t>At the hotel</t>
-  </si>
-  <si>
-    <t>7:30pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Etabli — Or the Campari bar on Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Walk, 4 min</t>
-  </si>
-  <si>
-    <t>Find -&gt;</t>
-  </si>
-  <si>
-    <t>8:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Armando al Pantheon — Tiny, family-run, and booked out weeks ahead. Reserve now.</t>
-  </si>
-  <si>
-    <t>Walk, 8 min</t>
-  </si>
-  <si>
-    <t>Reserve -&gt;</t>
-  </si>
-  <si>
-    <t>Tue, Aug 25</t>
-  </si>
-  <si>
-    <t>ROME — Vatican</t>
-  </si>
-  <si>
-    <t>7:45am</t>
-  </si>
-  <si>
-    <t>Vatican early-entry private tour — Into the Sistine Chapel before general admission</t>
-  </si>
-  <si>
-    <t>Taxi, ~15 min</t>
-  </si>
-  <si>
-    <t>Tickets -&gt;</t>
-  </si>
-  <si>
-    <t>1:00pm</t>
-  </si>
-  <si>
-    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
-  </si>
-  <si>
-    <t>Walk from the Vatican</t>
-  </si>
-  <si>
-    <t>2:30pm</t>
-  </si>
-  <si>
-    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
-  </si>
-  <si>
-    <t>Taxi</t>
-  </si>
-  <si>
-    <t>5:00pm</t>
-  </si>
-  <si>
-    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
-  </si>
-  <si>
-    <t>Taxi, ~10 min</t>
-  </si>
-  <si>
-    <t>Rooftop aperitivo near Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Walk</t>
-  </si>
-  <si>
-    <t>8:30pm</t>
-  </si>
-  <si>
-    <t>OPERA — arias at All Saints' Anglican Church — Confirm the Aug 25 programme; Via del Babuino, off Piazza di Spagna</t>
-  </si>
-  <si>
-    <t>10:00pm</t>
-  </si>
-  <si>
-    <t>Late dinner — Pierluigi — Seafood on Piazza de' Ricci; a properly Roman hour to eat</t>
-  </si>
-  <si>
-    <t>Walk, 6 min</t>
-  </si>
-  <si>
-    <t>Wed, Aug 26</t>
-  </si>
-  <si>
-    <t>ROME — Colosseum &amp; the Forum</t>
-  </si>
-  <si>
-    <t>8:45am</t>
-  </si>
-  <si>
-    <t>Colosseum with arena floor, then Forum + Palatine — The arena-floor add-on is worth it — you stand where the sand was</t>
-  </si>
-  <si>
-    <t>Taxi, ~12 min</t>
-  </si>
-  <si>
-    <t>Lunch — Roscioli — Carbonara and cacio e pepe, and the deli counter on the way out</t>
-  </si>
-  <si>
-    <t>Walk, 5 min via Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Siesta</t>
-  </si>
-  <si>
-    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
-  </si>
-  <si>
-    <t>Walk, ~12 min</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>[optional] Optional — Galleria Borghese — Timed entry, two-hour slots, books out early. Skip it guilt-free if the day already feels long.</t>
-  </si>
-  <si>
-    <t>Taxi, ~20 min</t>
-  </si>
-  <si>
-    <t>9:00pm</t>
-  </si>
-  <si>
-    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
-  </si>
-  <si>
-    <t>Thu, Aug 27</t>
-  </si>
-  <si>
-    <t>ROME → FLORENCE — Casa G. Firenze</t>
-  </si>
-  <si>
-    <t>TRAVEL DAY</t>
-  </si>
-  <si>
-    <t>Watch this: Tight evening. The 8:00pm opera assumes the car reaches Florence by 4pm — hold the driver to a 2:00pm departure from Orvieto. If the drive slips, move the opera to Fri Aug 28 and pull Borgo San Jacopo forward to tonight.</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>Check out; collect the car — North on the A1</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>Orvieto — the Duomo and lunch — A hilltop Umbrian town with one of the great striped façades in Italy. Ninety minutes is enough.</t>
-  </si>
-  <si>
-    <t>Just off the A1, ~1h15 from Rome</t>
-  </si>
-  <si>
-    <t>Duomo -&gt;</t>
-  </si>
-  <si>
-    <t>Back on the road — hold this departure — Orvieto → Florence is about two hours</t>
-  </si>
-  <si>
-    <t>Driver</t>
+    <t>Driver to Montespertoli — About forty minutes</t>
+  </si>
+  <si>
+    <t>A Chianti Montespertoli estate — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper</t>
+  </si>
+  <si>
+    <t>1:30pm</t>
+  </si>
+  <si>
+    <t>Lunch among the vines</t>
+  </si>
+  <si>
+    <t>At the estate</t>
+  </si>
+  <si>
+    <t>The village and a second cellar — Small enough to see on foot between tastings</t>
+  </si>
+  <si>
+    <t>5:30pm</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About forty minutes</t>
+  </si>
+  <si>
+    <t>The pool or the spa terrace at sunset</t>
+  </si>
+  <si>
+    <t>Dinner — Giglio Blu or La Via del Sale — Something casual, or a second night at the estate's fine-dining room</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>TUSCANY → AMALFI, self-drive via Pompeii</t>
+  </si>
+  <si>
+    <t>Watch this: The longest drive of the trip — about 4.5 hours of highway before you've even reached Pompeii. Swap drivers if you can, fill the tank before you leave Castelfalfi, and expect Naples-area traffic to eat into the buffer.</t>
+  </si>
+  <si>
+    <t>6:30am</t>
+  </si>
+  <si>
+    <t>Check out; on the road early — South on the A1 — Florence's ring road, then the long autostrada stretch past Rome and Caserta</t>
+  </si>
+  <si>
+    <t>Fuel and coffee stop — An Autogrill service area north of Rome — top up the tank, swap drivers</t>
+  </si>
+  <si>
+    <t>Toward Naples and Pompeii — The A1 becomes the A2 past Rome; exit for Pompei Scavi</t>
+  </si>
+  <si>
+    <t>Pompeii, guided — Two hours is the right length in September heat. Ask for the Villa of the Mysteries. Parking is at the Pompei Scavi lot by the entrance.</t>
+  </si>
+  <si>
+    <t>Arrive; on-site parking</t>
+  </si>
+  <si>
+    <t>Snack, then onto the corniche — The coast road starts properly after Vietri — narrow, slow, spectacular. Take it easy.</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Check in — Anantara Convento di Amalfi — A 13th-century monastery on the cliff edge, with the original cloister still standing</t>
+  </si>
+  <si>
+    <t>Scenic drive, ~1.5 hrs</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo in the cloister</t>
+  </si>
+  <si>
+    <t>Dinner — Dei Cappuccini — The hotel's Michelin room, or La Locanda for pizza if the day has beaten you</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>AMALFI — Capri boat day</t>
+  </si>
+  <si>
+    <t>Private boat from the hotel jetty — Lucibello, roughly seven hours with skipper</t>
+  </si>
+  <si>
+    <t>Private boat</t>
+  </si>
+  <si>
+    <t>The Faraglioni, the grottoes, the swim coves — Blue Grotto if the sea is calm enough to enter</t>
+  </si>
+  <si>
+    <t>By boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Marina Grande, then the funicular</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
+  </si>
+  <si>
+    <t>Cruise home, prosecco at sunset — About forty minutes back along the coast</t>
+  </si>
+  <si>
+    <t>Dinner — La Conca del Sogno — Reachable by boat, in a cove near Nerano. Or stay in on the cloister terrace.</t>
+  </si>
+  <si>
+    <t>Hotel car or boat, ~30 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>AMALFI — Nerano lunch and Ravello</t>
+  </si>
+  <si>
+    <t>The beach club, by cliff lift — A slow morning at sea level before the day starts properly</t>
+  </si>
+  <si>
+    <t>Hotel cliff lift</t>
+  </si>
+  <si>
+    <t>Lunch — Lo Scoglio — Nerano. The original spaghetti alla Nerano, and worth the boat ride on its own.</t>
+  </si>
+  <si>
+    <t>Hotel car or boat, ~40 min</t>
+  </si>
+  <si>
+    <t>Up to Ravello — Forty-five minutes of switchbacks above the coast</t>
   </si>
   <si>
     <t>3:45pm</t>
   </si>
   <si>
-    <t>Check in — Casa G. Firenze — Via dei Rondinelli, between the Duomo and Santa Maria Novella</t>
-  </si>
-  <si>
-    <t>Trip.com -&gt;</t>
-  </si>
-  <si>
-    <t>Unpack and reset — You have been in a car since morning</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo on the secret patio — Casa G.'s courtyard bar</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, right after the drive from Orvieto.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>1:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>Check out; driver southwest — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>Info -&gt;</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and Volterra</t>
-  </si>
-  <si>
-    <t>Driver to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>10:00am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion, right on Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>Lunch + a Vernaccia tasting — San Gimignano's own DOCG white, crisp and mineral, made for a hot afternoon</t>
-  </si>
-  <si>
-    <t>Driver to Volterra — About forty-five minutes</t>
-  </si>
-  <si>
-    <t>3:30pm</t>
-  </si>
-  <si>
-    <t>Piazza dei Priori and the Roman theatre — Tuscany's most complete medieval civic square, plus a 1st-century BC theatre still being excavated</t>
-  </si>
-  <si>
-    <t>Arrive Volterra</t>
-  </si>
-  <si>
-    <t>Alabaster workshops — A carving tradition here since Etruscan times — several studios welcome walk-ins</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Drive back to Castelfalfi — About fifty minutes</t>
-  </si>
-  <si>
-    <t>Dinner at the resort — Or a quieter table down in Montaione village</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY — Montespertoli wine day</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>The estate's 27-hole course, or the spa — Tuscany's largest golf course, or a morning at the newly renovated spa</t>
-  </si>
-  <si>
-    <t>Driver to Montespertoli — About forty minutes</t>
-  </si>
-  <si>
-    <t>A Chianti Montespertoli estate — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper</t>
-  </si>
-  <si>
-    <t>1:30pm</t>
-  </si>
-  <si>
-    <t>Lunch among the vines</t>
-  </si>
-  <si>
-    <t>At the estate</t>
-  </si>
-  <si>
-    <t>The village and a second cellar — Small enough to see on foot between tastings</t>
-  </si>
-  <si>
-    <t>5:30pm</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About forty minutes</t>
-  </si>
-  <si>
-    <t>The pool or the spa terrace at sunset</t>
-  </si>
-  <si>
-    <t>Dinner — Giglio Blu or La Via del Sale — Something casual, or a second night at the estate's fine-dining room</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>TUSCANY → AMALFI, self-drive via Pompeii</t>
-  </si>
-  <si>
-    <t>Watch this: The longest drive of the trip — about 4.5 hours of highway before you've even reached Pompeii. Swap drivers if you can, fill the tank before you leave Castelfalfi, and expect Naples-area traffic to eat into the buffer.</t>
-  </si>
-  <si>
-    <t>6:30am</t>
-  </si>
-  <si>
-    <t>Check out; on the road early — South on the A1 — Florence's ring road, then the long autostrada stretch past Rome and Caserta</t>
-  </si>
-  <si>
-    <t>Fuel and coffee stop — An Autogrill service area north of Rome — top up the tank, swap drivers</t>
-  </si>
-  <si>
-    <t>Toward Naples and Pompeii — The A1 becomes the A2 past Rome; exit for Pompei Scavi</t>
-  </si>
-  <si>
-    <t>Pompeii, guided — Two hours is the right length in September heat. Ask for the Villa of the Mysteries. Parking is at the Pompei Scavi lot by the entrance.</t>
-  </si>
-  <si>
-    <t>Arrive; on-site parking</t>
-  </si>
-  <si>
-    <t>Snack, then onto the corniche — The coast road starts properly after Vietri — narrow, slow, spectacular. Take it easy.</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Check in — Anantara Convento di Amalfi — A 13th-century monastery on the cliff edge, with the original cloister still standing</t>
-  </si>
-  <si>
-    <t>Scenic drive, ~1.5 hrs</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo in the cloister</t>
-  </si>
-  <si>
-    <t>Dinner — Dei Cappuccini — The hotel's Michelin room, or La Locanda for pizza if the day has beaten you</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>AMALFI — Capri boat day</t>
-  </si>
-  <si>
-    <t>Private boat from the hotel jetty — Lucibello, roughly seven hours with skipper</t>
-  </si>
-  <si>
-    <t>Private boat</t>
-  </si>
-  <si>
-    <t>The Faraglioni, the grottoes, the swim coves — Blue Grotto if the sea is calm enough to enter</t>
-  </si>
-  <si>
-    <t>By boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Marina Grande, then the funicular</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
-  </si>
-  <si>
-    <t>Cruise home, prosecco at sunset — About forty minutes back along the coast</t>
-  </si>
-  <si>
-    <t>Dinner — La Conca del Sogno — Reachable by boat, in a cove near Nerano. Or stay in on the cloister terrace.</t>
-  </si>
-  <si>
-    <t>Hotel car or boat, ~30 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>AMALFI — Nerano lunch and Ravello</t>
-  </si>
-  <si>
-    <t>The beach club, by cliff lift — A slow morning at sea level before the day starts properly</t>
-  </si>
-  <si>
-    <t>Hotel cliff lift</t>
-  </si>
-  <si>
-    <t>Lunch — Lo Scoglio — Nerano. The original spaghetti alla Nerano, and worth the boat ride on its own.</t>
-  </si>
-  <si>
-    <t>Hotel car or boat, ~40 min</t>
-  </si>
-  <si>
-    <t>Up to Ravello — Forty-five minutes of switchbacks above the coast</t>
-  </si>
-  <si>
     <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
   </si>
   <si>
@@ -967,7 +988,7 @@
     <t>6 hotels, 13 nights. Trame, Castelfalfi and Convento are actual quotes.</t>
   </si>
   <si>
-    <t>Rental car $1,175 (€1,087.81, actual), plus fuel, tolls, ZTL/garage parking.</t>
+    <t>Holding the old total pending a re-quote: the rental drops from 14 days to 8 (Florence Aug 29 → FCO Sep 6), but a one-way pickup fee eats into that, and the FCO private transfer (~€70–90) and two Frecciarossa fares are new. Rome garage parking is gone entirely. Fuel and tolls now only from Aug 29.</t>
   </si>
   <si>
     <t>Excursions &amp; guides</t>
@@ -1003,10 +1024,10 @@
     <t>Aug 24</t>
   </si>
   <si>
-    <t>Pick up the car</t>
-  </si>
-  <si>
-    <t>FCO → garage near Hotel Trame, Rome  (Reservation #21586310US4 — Benz C-Class or similar)</t>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>FCO → Hotel Trame, Rome  (Pre-booked NCC, name board at arrivals — book before you fly)</t>
   </si>
   <si>
     <t>~45 min</t>
@@ -1018,60 +1039,75 @@
     <t>Aug 27</t>
   </si>
   <si>
-    <t>Rome → Orvieto (lunch stop) → Casa G. Firenze, Florence  (Florence ZTL ~€200 if you drive into the centro storico)</t>
+    <t>High-speed rail</t>
+  </si>
+  <si>
+    <t>Roma Termini → Firenze S.M.N.  (Frecciarossa or Italo, hourly — no car in Rome, nothing to park)</t>
+  </si>
+  <si>
+    <t>~1h30</t>
+  </si>
+  <si>
+    <t>Aug 29</t>
+  </si>
+  <si>
+    <t>Collect the car</t>
+  </si>
+  <si>
+    <t>Borgo Ognissanti, Florence — outside the ZTL  (Reservation #21586310US4 — needs rebooking from FCO Aug 24 to Florence Aug 29)</t>
+  </si>
+  <si>
+    <t>~30 min</t>
+  </si>
+  <si>
+    <t>Florence → Certaldo (lunch stop) → Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>~2 hrs</t>
+  </si>
+  <si>
+    <t>Aug 30</t>
+  </si>
+  <si>
+    <t>Full day</t>
+  </si>
+  <si>
+    <t>Castelfalfi → San Gimignano → Volterra → back</t>
+  </si>
+  <si>
+    <t>~8 hrs</t>
+  </si>
+  <si>
+    <t>Aug 31</t>
+  </si>
+  <si>
+    <t>Half day</t>
+  </si>
+  <si>
+    <t>Castelfalfi → Montespertoli wine estates → back</t>
+  </si>
+  <si>
+    <t>~6 hrs</t>
+  </si>
+  <si>
+    <t>Sep 1</t>
+  </si>
+  <si>
+    <t>Il Castelfalfi → Pompeii (guided) → Amalfi corniche  (The longest drive of the trip — start early and swap drivers)</t>
+  </si>
+  <si>
+    <t>~9 hrs</t>
+  </si>
+  <si>
+    <t>Sep 3</t>
+  </si>
+  <si>
+    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks — a local driver is a fine substitute for this one leg)</t>
   </si>
   <si>
     <t>~5 hrs</t>
   </si>
   <si>
-    <t>Aug 29</t>
-  </si>
-  <si>
-    <t>Florence → Certaldo (lunch stop) → Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>~2 hrs</t>
-  </si>
-  <si>
-    <t>Aug 30</t>
-  </si>
-  <si>
-    <t>Full day</t>
-  </si>
-  <si>
-    <t>Castelfalfi → San Gimignano → Volterra → back</t>
-  </si>
-  <si>
-    <t>~8 hrs</t>
-  </si>
-  <si>
-    <t>Aug 31</t>
-  </si>
-  <si>
-    <t>Half day</t>
-  </si>
-  <si>
-    <t>Castelfalfi → Montespertoli wine estates → back</t>
-  </si>
-  <si>
-    <t>~6 hrs</t>
-  </si>
-  <si>
-    <t>Sep 1</t>
-  </si>
-  <si>
-    <t>Il Castelfalfi → Pompeii (guided) → Amalfi corniche  (The longest drive of the trip — start early and swap drivers)</t>
-  </si>
-  <si>
-    <t>~9 hrs</t>
-  </si>
-  <si>
-    <t>Sep 3</t>
-  </si>
-  <si>
-    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks — a local driver is a fine substitute for this one leg)</t>
-  </si>
-  <si>
     <t>Sep 4</t>
   </si>
   <si>
@@ -1102,7 +1138,7 @@
     <t>~40 min</t>
   </si>
   <si>
-    <t>The IDP ships by Aug 3 — pack it with the physical licence, not just a photo of it. Rome and Florence's historic centres are ZTL zones: enter only to check in/out, then park in a garage just outside (Rome ~€35–45/night, Florence ~€30–35/night) and walk. Castelfalfi and the Amalfi hotel have their own parking. Budget roughly €80 in tolls for the full route and a full tank about every 2–3 driving days.</t>
+    <t>You are car-free for the first five days: a private driver in from FCO, taxis and your feet in Rome, the Frecciarossa to Florence. The car is only collected on Aug 29, on Borgo Ognissanti just outside Florence's ZTL, and runs from there to the FCO drop-off on Sep 6 — eight days rather than fourteen, and no Rome garage at all. The IDP ships by Aug 3; pack it with the physical licence, not just a photo of it. Never drive into either historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi and the Amalfi hotel have their own parking, Naples has hotel valet. Budget roughly €60 in tolls from Aug 29 on and a full tank about every 2–3 driving days.</t>
   </si>
   <si>
     <t>#</t>
@@ -1138,22 +1174,28 @@
     <t>THIS WEEK</t>
   </si>
   <si>
-    <t>Fix the rental car's drop-off time</t>
-  </si>
-  <si>
-    <t>Reservation #21586310US4 has drop-off at noon on Sep 6, but the flight leaves at 10:20am. Call and move it to around 6:00am.</t>
-  </si>
-  <si>
-    <t>Plan Rome and Florence parking before you land</t>
-  </si>
-  <si>
-    <t>Both hotels sit inside a ZTL — pick a garage just outside each one now, rather than improvising on arrival with a rental car and jet lag.</t>
+    <t>Rebook the rental car — Florence pickup, not FCO</t>
+  </si>
+  <si>
+    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → FCO Sep 6: six days shorter, but a different pickup city usually carries a one-way fee, so the €1,087.81 quote will not hold. Re-quote before cancelling. While you are on the phone, move the Sep 6 drop-off off noon — the flight leaves at 10:20am, so around 6:00am.</t>
+  </si>
+  <si>
+    <t>Book the FCO → Hotel Trame private driver</t>
+  </si>
+  <si>
+    <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
+  </si>
+  <si>
+    <t>Frecciarossa tickets — Roma Termini → Firenze S.M.N., Aug 27</t>
+  </si>
+  <si>
+    <t>Trenitalia and Italo both run the route hourly in about 1h30. Advance fares open around four months out and are a fraction of the walk-up price, so book as soon as the date is loaded. Aim for a departure around 10:35am.</t>
   </si>
   <si>
     <t>Florence opera — La Traviata at St. Mark's, Aug 27</t>
   </si>
   <si>
-    <t>Lands the same evening as the Orvieto drive north — the fallback is Aug 28 if the drive runs late.</t>
+    <t>The train lands you at midday, so the evening is no longer tight — but book it before the seats go.</t>
   </si>
   <si>
     <t>Rome opera — All Saints' Anglican, Aug 25</t>
@@ -2009,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2167,8 +2209,8 @@
       <c r="E8" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F8" t="s">
-        <v>48</v>
+      <c r="F8" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,47 +2221,47 @@
         <v>48</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="4" t="s">
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>2</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="7" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>2</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="D12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="E12" s="13" t="s">
         <v>76</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2230,16 +2272,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2258,8 +2300,8 @@
       <c r="E14" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>74</v>
+      <c r="F14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2278,8 +2320,8 @@
       <c r="E15" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="F15" t="s">
-        <v>48</v>
+      <c r="F15" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,16 +2332,16 @@
         <v>48</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>80</v>
+      <c r="F16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2310,16 +2352,16 @@
         <v>48</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>90</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2330,47 +2372,47 @@
         <v>48</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <v>3</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="C20" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="13" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>3</v>
-      </c>
-      <c r="B21" s="10" t="s">
+      <c r="D21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="E21" s="13" t="s">
         <v>98</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2381,16 +2423,16 @@
         <v>48</v>
       </c>
       <c r="C22" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="F22" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2404,13 +2446,13 @@
         <v>81</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>74</v>
+        <v>63</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2424,10 +2466,10 @@
         <v>84</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
         <v>48</v>
@@ -2441,7 +2483,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>105</v>
@@ -2449,8 +2491,8 @@
       <c r="E25" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="F25" t="s">
-        <v>48</v>
+      <c r="F25" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2467,58 +2509,64 @@
         <v>108</v>
       </c>
       <c r="E26" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>4</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="F28" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
-        <v>4</v>
-      </c>
-      <c r="B29" s="10" t="s">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="E29" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="4" t="s">
         <v>115</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2529,13 +2577,13 @@
         <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s">
         <v>48</v>
@@ -2549,16 +2597,16 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2569,13 +2617,13 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
         <v>48</v>
@@ -2589,16 +2637,16 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>126</v>
+      <c r="F34" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2609,13 +2657,13 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
         <v>48</v>
@@ -2629,16 +2677,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,16 +2697,16 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2669,16 +2717,16 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2686,10 +2734,10 @@
         <v>5</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2700,16 +2748,16 @@
         <v>48</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2720,16 +2768,16 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2740,13 +2788,13 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F43" t="s">
         <v>48</v>
@@ -2760,16 +2808,16 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2780,16 +2828,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,16 +2848,16 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2820,13 +2868,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
         <v>48</v>
@@ -2840,13 +2888,13 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
@@ -2860,16 +2908,16 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2877,13 +2925,13 @@
         <v>6</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2894,13 +2942,13 @@
         <v>48</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F52" t="s">
         <v>48</v>
@@ -2914,16 +2962,16 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="F53" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2934,16 +2982,16 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F54" t="s">
-        <v>48</v>
+        <v>168</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2954,13 +3002,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -2974,13 +3022,13 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="F56" t="s">
         <v>48</v>
@@ -2994,16 +3042,16 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
+      </c>
+      <c r="F57" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3014,16 +3062,16 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3034,13 +3082,13 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F59" t="s">
         <v>48</v>
@@ -3054,47 +3102,47 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F60" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="10">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" t="s">
+        <v>48</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
         <v>7</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>48</v>
-      </c>
-      <c r="B63" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F63" t="s">
-        <v>48</v>
+      <c r="B63" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3105,13 +3153,13 @@
         <v>48</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="F64" t="s">
         <v>48</v>
@@ -3125,13 +3173,13 @@
         <v>48</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F65" t="s">
         <v>48</v>
@@ -3145,13 +3193,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3165,13 +3213,13 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F67" t="s">
         <v>48</v>
@@ -3185,13 +3233,13 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="F68" t="s">
         <v>48</v>
@@ -3205,13 +3253,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3225,13 +3273,13 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -3245,13 +3293,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3265,47 +3313,47 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="10">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
         <v>8</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>48</v>
-      </c>
-      <c r="B75" t="s">
-        <v>48</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F75" t="s">
-        <v>48</v>
+      <c r="B75" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3316,13 +3364,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3336,13 +3384,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3356,13 +3404,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3376,13 +3424,13 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="F79" t="s">
         <v>48</v>
@@ -3396,13 +3444,13 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="F80" t="s">
         <v>48</v>
@@ -3416,13 +3464,13 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="F81" t="s">
         <v>48</v>
@@ -3436,64 +3484,64 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F82" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="10">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>48</v>
+      </c>
+      <c r="B83" t="s">
+        <v>48</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F83" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="10">
         <v>9</v>
       </c>
-      <c r="B84" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="F84" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>48</v>
-      </c>
-      <c r="B85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C85" t="s">
-        <v>48</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B85" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>48</v>
       </c>
       <c r="B86" t="s">
         <v>48</v>
       </c>
-      <c r="C86" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F86" t="s">
-        <v>48</v>
+      <c r="C86" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3504,13 +3552,13 @@
         <v>48</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="F87" t="s">
         <v>48</v>
@@ -3524,13 +3572,13 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E88" s="13" t="s">
         <v>165</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="F88" t="s">
         <v>48</v>
@@ -3544,16 +3592,16 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>80</v>
+        <v>165</v>
+      </c>
+      <c r="F89" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3564,16 +3612,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F90" t="s">
-        <v>48</v>
+        <v>219</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3584,16 +3632,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>215</v>
+        <v>151</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>126</v>
+        <v>165</v>
+      </c>
+      <c r="F91" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3604,16 +3652,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F92" t="s">
-        <v>48</v>
+        <v>223</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3624,47 +3672,47 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+        <v>63</v>
+      </c>
+      <c r="F93" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>48</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
         <v>10</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" t="s">
-        <v>48</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>170</v>
+      <c r="B96" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3675,16 +3723,16 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F97" t="s">
-        <v>48</v>
+        <v>230</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3695,16 +3743,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>74</v>
+        <v>232</v>
+      </c>
+      <c r="F98" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3715,16 +3763,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>63</v>
+        <v>234</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,16 +3783,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F100" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,47 +3803,47 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F101" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="10">
+      <c r="F101" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" t="s">
+        <v>48</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
         <v>11</v>
       </c>
-      <c r="B103" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>48</v>
-      </c>
-      <c r="B104" t="s">
-        <v>48</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="F104" t="s">
-        <v>48</v>
+      <c r="B104" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3806,16 +3854,16 @@
         <v>48</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>74</v>
+        <v>242</v>
+      </c>
+      <c r="F105" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3826,16 +3874,16 @@
         <v>48</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F106" t="s">
-        <v>48</v>
+        <v>244</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3846,16 +3894,16 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>80</v>
+        <v>165</v>
+      </c>
+      <c r="F107" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,16 +3914,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>91</v>
+        <v>248</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3886,16 +3934,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>244</v>
+        <v>88</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>245</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3906,50 +3954,50 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="10">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>48</v>
+      </c>
+      <c r="B111" t="s">
+        <v>48</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="10">
         <v>12</v>
       </c>
-      <c r="B112" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="F112" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>48</v>
-      </c>
-      <c r="B113" t="s">
-        <v>48</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F113" t="s">
-        <v>48</v>
+      <c r="B113" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F113" s="14" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,13 +4008,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -3980,16 +4028,16 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>126</v>
+        <v>165</v>
+      </c>
+      <c r="F115" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4000,16 +4048,16 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4020,16 +4068,16 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>257</v>
+        <v>86</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>258</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4040,16 +4088,16 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>64</v>
+        <v>262</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F118" t="s">
-        <v>48</v>
+        <v>264</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4060,13 +4108,13 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F119" t="s">
         <v>48</v>
@@ -4080,50 +4128,50 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="10">
+        <v>63</v>
+      </c>
+      <c r="F120" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>48</v>
+      </c>
+      <c r="B121" t="s">
+        <v>48</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="10">
         <v>13</v>
       </c>
-      <c r="B122" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="F122" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>48</v>
-      </c>
-      <c r="B123" t="s">
-        <v>48</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>265</v>
+      <c r="B123" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4137,13 +4185,13 @@
         <v>161</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F124" t="s">
-        <v>48</v>
+        <v>134</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,16 +4202,16 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>126</v>
+        <v>165</v>
+      </c>
+      <c r="F125" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4174,16 +4222,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="F126" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4194,13 +4242,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>66</v>
+        <v>276</v>
       </c>
       <c r="F127" t="s">
         <v>48</v>
@@ -4214,61 +4262,61 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="10">
+        <v>63</v>
+      </c>
+      <c r="F128" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" t="s">
+        <v>48</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="10">
         <v>14</v>
       </c>
-      <c r="B130" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>48</v>
-      </c>
-      <c r="B131" t="s">
-        <v>48</v>
-      </c>
-      <c r="C131" t="s">
-        <v>48</v>
-      </c>
-      <c r="D131" s="15" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B131" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>48</v>
       </c>
       <c r="B132" t="s">
         <v>48</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F132" t="s">
-        <v>48</v>
+      <c r="C132" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,13 +4327,13 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="F133" t="s">
         <v>48</v>
@@ -4299,33 +4347,53 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F134" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>48</v>
+      </c>
+      <c r="B135" t="s">
+        <v>48</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="F135" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F9" r:id="rId1"/>
-    <hyperlink ref="F10" r:id="rId2"/>
-    <hyperlink ref="F13" r:id="rId3"/>
-    <hyperlink ref="F14" r:id="rId4"/>
-    <hyperlink ref="F16" r:id="rId5"/>
-    <hyperlink ref="F18" r:id="rId6"/>
-    <hyperlink ref="F19" r:id="rId7"/>
-    <hyperlink ref="F22" r:id="rId8"/>
-    <hyperlink ref="F23" r:id="rId9"/>
-    <hyperlink ref="F26" r:id="rId10"/>
-    <hyperlink ref="F27" r:id="rId11"/>
-    <hyperlink ref="F32" r:id="rId12"/>
-    <hyperlink ref="F34" r:id="rId13"/>
+    <hyperlink ref="F8" r:id="rId1"/>
+    <hyperlink ref="F9" r:id="rId2"/>
+    <hyperlink ref="F12" r:id="rId3"/>
+    <hyperlink ref="F13" r:id="rId4"/>
+    <hyperlink ref="F15" r:id="rId5"/>
+    <hyperlink ref="F17" r:id="rId6"/>
+    <hyperlink ref="F18" r:id="rId7"/>
+    <hyperlink ref="F21" r:id="rId8"/>
+    <hyperlink ref="F22" r:id="rId9"/>
+    <hyperlink ref="F25" r:id="rId10"/>
+    <hyperlink ref="F26" r:id="rId11"/>
+    <hyperlink ref="F30" r:id="rId12"/>
+    <hyperlink ref="F32" r:id="rId13"/>
     <hyperlink ref="F36" r:id="rId14"/>
     <hyperlink ref="F37" r:id="rId15"/>
     <hyperlink ref="F38" r:id="rId16"/>
@@ -4335,27 +4403,27 @@
     <hyperlink ref="F45" r:id="rId20"/>
     <hyperlink ref="F46" r:id="rId21"/>
     <hyperlink ref="F49" r:id="rId22"/>
-    <hyperlink ref="F53" r:id="rId23"/>
-    <hyperlink ref="F57" r:id="rId24"/>
-    <hyperlink ref="F89" r:id="rId25"/>
-    <hyperlink ref="F91" r:id="rId26"/>
-    <hyperlink ref="F93" r:id="rId27"/>
-    <hyperlink ref="F96" r:id="rId28"/>
-    <hyperlink ref="F98" r:id="rId29"/>
-    <hyperlink ref="F99" r:id="rId30"/>
-    <hyperlink ref="F101" r:id="rId31"/>
-    <hyperlink ref="F105" r:id="rId32"/>
-    <hyperlink ref="F107" r:id="rId33"/>
-    <hyperlink ref="F108" r:id="rId34"/>
-    <hyperlink ref="F109" r:id="rId35"/>
-    <hyperlink ref="F110" r:id="rId36"/>
-    <hyperlink ref="F115" r:id="rId37"/>
-    <hyperlink ref="F116" r:id="rId38"/>
-    <hyperlink ref="F117" r:id="rId39"/>
-    <hyperlink ref="F120" r:id="rId40"/>
-    <hyperlink ref="F123" r:id="rId41"/>
-    <hyperlink ref="F125" r:id="rId42"/>
-    <hyperlink ref="F128" r:id="rId43"/>
+    <hyperlink ref="F54" r:id="rId23"/>
+    <hyperlink ref="F58" r:id="rId24"/>
+    <hyperlink ref="F90" r:id="rId25"/>
+    <hyperlink ref="F92" r:id="rId26"/>
+    <hyperlink ref="F94" r:id="rId27"/>
+    <hyperlink ref="F97" r:id="rId28"/>
+    <hyperlink ref="F99" r:id="rId29"/>
+    <hyperlink ref="F100" r:id="rId30"/>
+    <hyperlink ref="F102" r:id="rId31"/>
+    <hyperlink ref="F106" r:id="rId32"/>
+    <hyperlink ref="F108" r:id="rId33"/>
+    <hyperlink ref="F109" r:id="rId34"/>
+    <hyperlink ref="F110" r:id="rId35"/>
+    <hyperlink ref="F111" r:id="rId36"/>
+    <hyperlink ref="F116" r:id="rId37"/>
+    <hyperlink ref="F117" r:id="rId38"/>
+    <hyperlink ref="F118" r:id="rId39"/>
+    <hyperlink ref="F121" r:id="rId40"/>
+    <hyperlink ref="F124" r:id="rId41"/>
+    <hyperlink ref="F126" r:id="rId42"/>
+    <hyperlink ref="F129" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4378,48 +4446,48 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -4431,24 +4499,24 @@
         <v>1570</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4460,24 +4528,24 @@
         <v>1470</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -4489,24 +4557,24 @@
         <v>3762.66</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -4518,24 +4586,24 @@
         <v>4500</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C6" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D6" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E6" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4547,24 +4615,24 @@
         <v>500</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C7" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -4576,7 +4644,7 @@
         <v>1000</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -4593,7 +4661,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F8" s="17">
         <v>13</v>
@@ -4631,24 +4699,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B2" s="16">
         <v>12802.66</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,51 +4727,51 @@
         <v>1775</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B4" s="16">
         <v>2100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B5" s="16">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B6" s="16">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B7" s="18">
         <v>19477.66</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4728,197 +4796,214 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>340</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>344</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D4" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="B5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="D5" t="s">
-        <v>341</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B6" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>354</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D8" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D9" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D10" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B11" t="s">
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>361</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="D12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -4933,6 +5018,7 @@
     <hyperlink ref="E9" r:id="rId8"/>
     <hyperlink ref="E10" r:id="rId9"/>
     <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4941,7 +5027,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4952,16 +5038,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -4972,16 +5058,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4989,16 +5075,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5006,16 +5092,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5023,16 +5109,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>372</v>
+        <v>388</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>380</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5040,16 +5126,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>372</v>
+        <v>390</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>380</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5057,16 +5143,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5074,16 +5160,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>381</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5091,16 +5177,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>372</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5108,16 +5194,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5125,16 +5211,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>389</v>
+        <v>400</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>384</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5142,16 +5228,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5159,35 +5245,41 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>395</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>396</v>
+      <c r="B16" s="23" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -5195,10 +5287,21 @@
         <v>48</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>398</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -5215,6 +5318,7 @@
     <hyperlink ref="E11" r:id="rId10"/>
     <hyperlink ref="E12" r:id="rId11"/>
     <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5237,158 +5341,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B2" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C2" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F2" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="C3" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="E3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="F3" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="F4" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="C5" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" t="s">
+        <v>441</v>
+      </c>
+      <c r="F5" t="s">
+        <v>442</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" s="7" t="s">
         <v>427</v>
-      </c>
-      <c r="F5" t="s">
-        <v>428</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="B6" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C6" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="F6" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,7 +5506,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="456">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Route</t>
   </si>
   <si>
-    <t>Rome (3) → Florence (2) → Tuscany (3) → Amalfi (3) → Naples (1) → Rome finale (1)</t>
+    <t>Rome (3) → Florence (2) → Tuscany (3) → Naples (2) → Amalfi (2) → Rome finale (1)</t>
   </si>
   <si>
     <t>Transport</t>
@@ -64,7 +64,7 @@
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → Casa G. Firenze (Florence, Michelin Guide) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Anantara Convento (Amalfi, Minor / GHA) → De Bonart (Naples, Hilton Curio) → The St. Regis Rome (Marriott Bonvoy)</t>
+    <t>Hotel Trame (Rome, independent) → Casa G. Firenze (Florence, Michelin Guide) → Il Castelfalfi (Tuscany, TUI Blue Selection) → De Bonart (Naples, Hilton Curio) → Anantara Convento (Amalfi, Minor / GHA) → The St. Regis Rome (Marriott Bonvoy)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -655,34 +655,124 @@
     <t>Tue, Sep 1</t>
   </si>
   <si>
-    <t>TUSCANY → AMALFI, self-drive via Pompeii</t>
-  </si>
-  <si>
-    <t>Watch this: The longest drive of the trip — about 4.5 hours of highway before you've even reached Pompeii. Swap drivers if you can, fill the tank before you leave Castelfalfi, and expect Naples-area traffic to eat into the buffer.</t>
-  </si>
-  <si>
-    <t>6:30am</t>
-  </si>
-  <si>
-    <t>Check out; on the road early — South on the A1 — Florence's ring road, then the long autostrada stretch past Rome and Caserta</t>
+    <t>TUSCANY → NAPLES — De Bonart</t>
+  </si>
+  <si>
+    <t>Watch this: The longest drive of the trip — roughly five hours of autostrada, most of it past Rome and Caserta. Fill the tank before you leave Castelfalfi, swap drivers if you can, and expect Naples traffic to eat the last half hour.</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — South on the A1 — Florence's ring road, then the long autostrada stretch past Rome and Caserta</t>
+  </si>
+  <si>
+    <t>10:45am</t>
   </si>
   <si>
     <t>Fuel and coffee stop — An Autogrill service area north of Rome — top up the tank, swap drivers</t>
   </si>
   <si>
-    <t>Toward Naples and Pompeii — The A1 becomes the A2 past Rome; exit for Pompei Scavi</t>
-  </si>
-  <si>
-    <t>Pompeii, guided — Two hours is the right length in September heat. Ask for the Villa of the Mysteries. Parking is at the Pompei Scavi lot by the entrance.</t>
+    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay. Hand the car to the hotel valet and leave it there — you won't need it again until Thursday.</t>
+  </si>
+  <si>
+    <t>Naples Archaeological Museum — The frescoes, mosaics and bronzes lifted out of Pompeii all ended up here. You see the rooms they came from on Thursday, so this is the right way round.</t>
+  </si>
+  <si>
+    <t>Spaccanapoli — The dead-straight Greek road that still splits the old city in half</t>
+  </si>
+  <si>
+    <t>Walk from the museum</t>
+  </si>
+  <si>
+    <t>Street food, standing up — Pizza fritta, zeppoline, a sfogliatella riccia straight from the oven</t>
+  </si>
+  <si>
+    <t>Rooftop aperitivo — Vesuvius on one side, the bay on the other</t>
+  </si>
+  <si>
+    <t>9:15pm</t>
+  </si>
+  <si>
+    <t>Dinner — pizza on Via dei Tribunali — Sorbillo or Di Matteo. You are in the city that invented it; do this before anything fancier.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>NAPLES — Capri day trip</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Walk down to Molo Beverello — The fast-ferry pier is fifteen minutes along the seafront from the hotel</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>9:20am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Naples → Capri — NLG, SNAV and Caremar all run it in about fifty minutes. Sailings are frequent in September but sell out at the counter — book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~50 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>The Faraglioni, the grottoes, the swim coves — Pick up a round-the-island boat at Marina Grande — Blue Grotto if the sea is calm enough to enter</t>
+  </si>
+  <si>
+    <t>Local boat from Marina Grande</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Marina Grande, then the funicular</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
+  </si>
+  <si>
+    <t>6:15pm</t>
+  </si>
+  <si>
+    <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
+  </si>
+  <si>
+    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu, back in the old city</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>NAPLES → AMALFI, via Pompeii</t>
+  </si>
+  <si>
+    <t>Check out; collect the car from the valet — First time behind the wheel since Tuesday</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Drive to Pompeii — Half an hour southeast on the A3 — exit for Pompei Scavi</t>
+  </si>
+  <si>
+    <t>Self-drive, ~30 min</t>
+  </si>
+  <si>
+    <t>Pompeii, guided — Two and a half hours is the right length in September heat. Ask for the Villa of the Mysteries. Parking is at the Pompei Scavi lot by the entrance.</t>
   </si>
   <si>
     <t>Arrive; on-site parking</t>
   </si>
   <si>
-    <t>Snack, then onto the corniche — The coast road starts properly after Vietri — narrow, slow, spectacular. Take it easy.</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
+    <t>Lunch, then onto the corniche — The coast road starts properly after Vietri — narrow, slow, spectacular. Take it easy.</t>
   </si>
   <si>
     <t>Check in — Anantara Convento di Amalfi — A 13th-century monastery on the cliff edge, with the original cloister still standing</t>
@@ -691,6 +781,12 @@
     <t>Scenic drive, ~1.5 hrs</t>
   </si>
   <si>
+    <t>The beach club, by cliff lift — Down to sea level for what's left of the afternoon</t>
+  </si>
+  <si>
+    <t>Hotel cliff lift</t>
+  </si>
+  <si>
     <t>7:45pm</t>
   </si>
   <si>
@@ -700,52 +796,13 @@
     <t>Dinner — Dei Cappuccini — The hotel's Michelin room, or La Locanda for pizza if the day has beaten you</t>
   </si>
   <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>AMALFI — Capri boat day</t>
-  </si>
-  <si>
-    <t>Private boat from the hotel jetty — Lucibello, roughly seven hours with skipper</t>
-  </si>
-  <si>
-    <t>Private boat</t>
-  </si>
-  <si>
-    <t>The Faraglioni, the grottoes, the swim coves — Blue Grotto if the sea is calm enough to enter</t>
-  </si>
-  <si>
-    <t>By boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Marina Grande, then the funicular</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
-  </si>
-  <si>
-    <t>Cruise home, prosecco at sunset — About forty minutes back along the coast</t>
-  </si>
-  <si>
-    <t>Dinner — La Conca del Sogno — Reachable by boat, in a cove near Nerano. Or stay in on the cloister terrace.</t>
-  </si>
-  <si>
-    <t>Hotel car or boat, ~30 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
+    <t>Fri, Sep 4</t>
   </si>
   <si>
     <t>AMALFI — Nerano lunch and Ravello</t>
   </si>
   <si>
-    <t>The beach club, by cliff lift — A slow morning at sea level before the day starts properly</t>
-  </si>
-  <si>
-    <t>Hotel cliff lift</t>
+    <t>A slow morning on the cloister terrace — The one unhurried morning on the coast — use it</t>
   </si>
   <si>
     <t>Lunch — Lo Scoglio — Nerano. The original spaghetti alla Nerano, and worth the boat ride on its own.</t>
@@ -769,7 +826,7 @@
     <t>Aperitivo, then Villa Rufolo's gardens</t>
   </si>
   <si>
-    <t>RAVELLO FESTIVAL — check the Sep 3 programme — Confirmed concerts run to Sep 5. The Aug 29 Mahler Youth Orchestra date falls on your Florence → Siena transfer, so it is out either way.</t>
+    <t>RAVELLO FESTIVAL — check the Sep 4 programme — Confirmed concerts run to Sep 5, so both your Amalfi nights are inside the festival window.</t>
   </si>
   <si>
     <t>Walk to Villa Rufolo</t>
@@ -787,58 +844,16 @@
     <t>Walk; drive down after</t>
   </si>
   <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>AMALFI → NAPLES — De Bonart</t>
-  </si>
-  <si>
-    <t>Check out; last look at the coast</t>
-  </si>
-  <si>
-    <t>Drive to Naples — Coast road, then the A3, ~1.5 hrs</t>
-  </si>
-  <si>
-    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay. Use the hotel's valet — Naples is not a city for a rental car to sit unattended.</t>
-  </si>
-  <si>
-    <t>Naples Archaeological Museum — Where everything good from Pompeii actually ended up. Go after seeing the site, not before.</t>
-  </si>
-  <si>
-    <t>4:30pm</t>
-  </si>
-  <si>
-    <t>Spaccanapoli — The dead-straight Greek road that still splits the old city in half</t>
-  </si>
-  <si>
-    <t>Walk from the museum</t>
-  </si>
-  <si>
-    <t>Guide -&gt;</t>
-  </si>
-  <si>
-    <t>Street food, standing up — Pizza fritta, zeppoline, a sfogliatella riccia straight from the oven</t>
-  </si>
-  <si>
-    <t>Rooftop aperitivo — Vesuvius on one side, the bay on the other</t>
-  </si>
-  <si>
-    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu</t>
-  </si>
-  <si>
     <t>Sat, Sep 5</t>
   </si>
   <si>
-    <t>NAPLES → ROME — The St. Regis</t>
-  </si>
-  <si>
-    <t>Pizza for breakfast — Sorbillo or Di Matteo on Via dei Tribunali. Yes, at 9am. It's Naples.</t>
-  </si>
-  <si>
-    <t>Sorbillo -&gt;</t>
-  </si>
-  <si>
-    <t>Collect the car; on the road — Naples → Rome is about two and a half hours on the A1</t>
+    <t>AMALFI → ROME — The St. Regis</t>
+  </si>
+  <si>
+    <t>Check out; last look at the coast — Breakfast on the cloister terrace before you give the cliff back</t>
+  </si>
+  <si>
+    <t>Down the corniche, then north — The coast road as far as Vietri, then the A3 and the A1 — Amalfi → Rome is about four hours all told</t>
   </si>
   <si>
     <t>Check in — The St. Regis Rome — The hotel is inside Rome's ZTL — use valet or a garage nearby; don't try to park at the curb.</t>
@@ -847,9 +862,6 @@
     <t>Last Roman afternoon — Piazza di Spagna and the windows along Via Condotti</t>
   </si>
   <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
     <t>Aperitivo at Lumen — The St. Regis bar — the grand-hotel version of a last night</t>
   </si>
   <si>
@@ -943,6 +955,15 @@
     <t>TUI Blue Selection</t>
   </si>
   <si>
+    <t>Naples</t>
+  </si>
+  <si>
+    <t>De Bonart Naples</t>
+  </si>
+  <si>
+    <t>Curio Collection / Hilton Honors</t>
+  </si>
+  <si>
     <t>Amalfi Coast</t>
   </si>
   <si>
@@ -952,15 +973,6 @@
     <t>Minor / GHA Discovery</t>
   </si>
   <si>
-    <t>Naples</t>
-  </si>
-  <si>
-    <t>De Bonart Naples</t>
-  </si>
-  <si>
-    <t>Curio Collection / Hilton Honors</t>
-  </si>
-  <si>
     <t>Rome (finale)</t>
   </si>
   <si>
@@ -985,7 +997,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>6 hotels, 13 nights. Trame, Castelfalfi and Convento are actual quotes.</t>
+    <t>6 hotels, 13 nights. Trame ($1,571.58), Castelfalfi ($3,764.98) and De Bonart ($1,098.27) are confirmed bookings; Convento is a quote, now 2 nights rather than 3. The St. Regis is still an estimate.</t>
   </si>
   <si>
     <t>Holding the old total pending a re-quote: the rental drops from 14 days to 8 (Florence Aug 29 → FCO Sep 6), but a one-way pickup fee eats into that, and the FCO private transfer (~€70–90) and two Frecciarossa fares are new. Rome garage parking is gone entirely. Fuel and tolls now only from Aug 29.</t>
@@ -994,7 +1006,7 @@
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Colosseum, Pompeii, Capri boat, wineries, Florence galleries, operas.</t>
+    <t>Vatican, Colosseum, Pompeii, Capri, wineries, Florence galleries, operas. Held pending a re-quote: swapping the private Lucibello charter for the Capri ferry takes a four-figure line down to about €50 of tickets for the two of you, so this should come down materially.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1093,37 +1105,46 @@
     <t>Sep 1</t>
   </si>
   <si>
-    <t>Il Castelfalfi → Pompeii (guided) → Amalfi corniche  (The longest drive of the trip — start early and swap drivers)</t>
-  </si>
-  <si>
-    <t>~9 hrs</t>
+    <t>Il Castelfalfi → De Bonart Naples  (The longest drive of the trip — then the car goes to the hotel valet until Thursday)</t>
+  </si>
+  <si>
+    <t>~5 hrs</t>
+  </si>
+  <si>
+    <t>Sep 2</t>
+  </si>
+  <si>
+    <t>Fast ferry</t>
+  </si>
+  <si>
+    <t>Molo Beverello, Naples → Capri → back  (NLG / SNAV / Caremar — book online the night before, and check the last sailing back)</t>
+  </si>
+  <si>
+    <t>~50 min each way</t>
   </si>
   <si>
     <t>Sep 3</t>
   </si>
   <si>
+    <t>Naples → Pompeii (guided) → Anantara Convento, Amalfi  (Pompeii is directly on the way — no detour at all)</t>
+  </si>
+  <si>
+    <t>~5 hrs with the site</t>
+  </si>
+  <si>
+    <t>Sep 4</t>
+  </si>
+  <si>
     <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks — a local driver is a fine substitute for this one leg)</t>
   </si>
   <si>
-    <t>~5 hrs</t>
-  </si>
-  <si>
-    <t>Sep 4</t>
-  </si>
-  <si>
-    <t>Anantara Convento → De Bonart Naples  (Use the hotel valet in Naples)</t>
-  </si>
-  <si>
-    <t>~1.5 hrs</t>
-  </si>
-  <si>
     <t>Sep 5</t>
   </si>
   <si>
-    <t>De Bonart Naples → The St. Regis Rome</t>
-  </si>
-  <si>
-    <t>~2.5 hrs</t>
+    <t>Anantara Convento → The St. Regis Rome  (Corniche as far as Vietri, then the A3 and A1)</t>
+  </si>
+  <si>
+    <t>~4 hrs</t>
   </si>
   <si>
     <t>Sep 6</t>
@@ -1216,25 +1237,25 @@
     <t>Three in one morning, in that order. Book the dome climb first; it has the fewest slots.</t>
   </si>
   <si>
-    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26), Pompeii guide (Sep 1)</t>
-  </si>
-  <si>
-    <t>All three need booking — the Vatican and Colosseum slots go first.</t>
-  </si>
-  <si>
-    <t>Capri private boat — Lucibello, Sep 2</t>
-  </si>
-  <si>
-    <t>Roughly seven hours with a skipper from the hotel jetty — book a few weeks out in peak season.</t>
+    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26), Pompeii guide (Sep 3)</t>
+  </si>
+  <si>
+    <t>All three need booking — the Vatican and Colosseum slots go first. Pompeii moved to Sep 3 with the reorder; take a morning slot, the site has almost no shade by noon.</t>
+  </si>
+  <si>
+    <t>Capri ferry — Naples → Capri return, Sep 2</t>
+  </si>
+  <si>
+    <t>Fast ferries from Molo Beverello take about fifty minutes; NLG, SNAV and Caremar all run the route. Book both legs online the night before rather than queueing at the counter, and note the last sailing back. The round-the-island boat can be picked up at Marina Grande on the day.</t>
   </si>
   <si>
     <t>BEFORE YOU GO</t>
   </si>
   <si>
-    <t>Ravello Festival — check the Sep 3 programme</t>
-  </si>
-  <si>
-    <t>Festival runs to Sep 5. The confirmed Aug 29 Mahler date falls on your Florence→Castelfalfi transfer, so it was never reachable.</t>
+    <t>Ravello Festival — check the Sep 4 programme</t>
+  </si>
+  <si>
+    <t>Festival runs to Sep 5, so both Amalfi nights now fall inside the window. The Aug 29 Mahler date still lands on your Florence→Castelfalfi transfer, so it was never reachable.</t>
   </si>
   <si>
     <t>Headline dinners on their dates</t>
@@ -1255,7 +1276,7 @@
     <t>Arena di Verona — Aida (Zeffirelli), Sep 4 &amp; 10</t>
   </si>
   <si>
-    <t>Needs a Verona overnight; Sep 4 is the Amalfi → Naples transfer.</t>
+    <t>Needs a Verona overnight, and Sep 4 is your Ravello night on the Amalfi Coast.</t>
   </si>
   <si>
     <t>Location</t>
@@ -2051,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3572,10 +3593,10 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E88" s="13" t="s">
         <v>165</v>
@@ -3592,16 +3613,16 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F89" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3612,13 +3633,13 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>77</v>
@@ -3632,13 +3653,13 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="F91" t="s">
         <v>48</v>
@@ -3652,16 +3673,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>222</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>123</v>
+        <v>88</v>
+      </c>
+      <c r="F92" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3672,10 +3693,10 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>63</v>
@@ -3692,16 +3713,16 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3709,10 +3730,10 @@
         <v>10</v>
       </c>
       <c r="B96" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C96" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3723,7 +3744,7 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>229</v>
@@ -3731,8 +3752,8 @@
       <c r="E97" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>176</v>
+      <c r="F97" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3743,16 +3764,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="F98" t="s">
-        <v>48</v>
+        <v>233</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3763,16 +3784,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>71</v>
+        <v>236</v>
+      </c>
+      <c r="F99" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3783,16 +3804,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3803,16 +3824,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="F101" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3823,47 +3844,50 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="F102" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F102" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" t="s">
+        <v>48</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F103" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="10">
+    <row r="105" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
         <v>11</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>48</v>
-      </c>
-      <c r="B105" t="s">
-        <v>48</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="F105" t="s">
-        <v>48</v>
+      <c r="B105" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,16 +3898,16 @@
         <v>48</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="F106" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,13 +3918,13 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>58</v>
+        <v>246</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="F107" t="s">
         <v>48</v>
@@ -3914,13 +3938,13 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>246</v>
+        <v>183</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>77</v>
@@ -3934,16 +3958,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>77</v>
+        <v>165</v>
+      </c>
+      <c r="F109" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3954,16 +3978,16 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>252</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,7 +3998,7 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>253</v>
+        <v>84</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>254</v>
@@ -3982,62 +4006,59 @@
       <c r="E111" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="F111" s="7" t="s">
+      <c r="F111" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" t="s">
+        <v>48</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F112" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="113" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="10">
+    <row r="115" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="10">
         <v>12</v>
       </c>
-      <c r="B113" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="F113" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>48</v>
-      </c>
-      <c r="B114" t="s">
-        <v>48</v>
-      </c>
-      <c r="C114" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F114" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>48</v>
-      </c>
-      <c r="B115" t="s">
-        <v>48</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D115" s="4" t="s">
+      <c r="B115" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E115" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F115" t="s">
-        <v>48</v>
+      <c r="C115" s="11" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4048,16 +4069,16 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>123</v>
+        <v>63</v>
+      </c>
+      <c r="F116" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4068,16 +4089,16 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>55</v>
+        <v>186</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>86</v>
+        <v>263</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4088,16 +4109,16 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>262</v>
+        <v>58</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>265</v>
+        <v>165</v>
+      </c>
+      <c r="F118" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4108,16 +4129,16 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>61</v>
+        <v>265</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>266</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F119" t="s">
-        <v>48</v>
+        <v>267</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4128,16 +4149,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F120" t="s">
-        <v>48</v>
+        <v>88</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4148,50 +4169,50 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="F121" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" t="s">
+        <v>48</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F122" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="10">
+    <row r="124" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="10">
         <v>13</v>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="F123" s="14" t="s">
+      <c r="B124" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F124" s="14" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>48</v>
-      </c>
-      <c r="B124" t="s">
-        <v>48</v>
-      </c>
-      <c r="C124" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4202,13 +4223,13 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="F125" t="s">
         <v>48</v>
@@ -4222,16 +4243,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>123</v>
+        <v>165</v>
+      </c>
+      <c r="F126" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,16 +4263,16 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>55</v>
+        <v>203</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="F127" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4262,13 +4283,13 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="F128" t="s">
         <v>48</v>
@@ -4282,61 +4303,61 @@
         <v>48</v>
       </c>
       <c r="C129" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F129" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>48</v>
+      </c>
+      <c r="B130" t="s">
+        <v>48</v>
+      </c>
+      <c r="C130" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D129" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E129" s="13" t="s">
+      <c r="D130" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E130" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F129" s="7" t="s">
+      <c r="F130" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="131" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="10">
+    <row r="132" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="10">
         <v>14</v>
       </c>
-      <c r="B131" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>48</v>
-      </c>
-      <c r="B132" t="s">
-        <v>48</v>
-      </c>
-      <c r="C132" t="s">
-        <v>48</v>
-      </c>
-      <c r="D132" s="15" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B132" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>48</v>
       </c>
       <c r="B133" t="s">
         <v>48</v>
       </c>
-      <c r="C133" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="E133" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F133" t="s">
-        <v>48</v>
+      <c r="C133" t="s">
+        <v>48</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4347,13 +4368,13 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>286</v>
+        <v>165</v>
       </c>
       <c r="F134" t="s">
         <v>48</v>
@@ -4367,15 +4388,35 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F135" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>48</v>
+      </c>
+      <c r="B136" t="s">
+        <v>48</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F136" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4405,25 +4446,23 @@
     <hyperlink ref="F49" r:id="rId22"/>
     <hyperlink ref="F54" r:id="rId23"/>
     <hyperlink ref="F58" r:id="rId24"/>
-    <hyperlink ref="F90" r:id="rId25"/>
-    <hyperlink ref="F92" r:id="rId26"/>
+    <hyperlink ref="F89" r:id="rId25"/>
+    <hyperlink ref="F90" r:id="rId26"/>
     <hyperlink ref="F94" r:id="rId27"/>
-    <hyperlink ref="F97" r:id="rId28"/>
-    <hyperlink ref="F99" r:id="rId29"/>
-    <hyperlink ref="F100" r:id="rId30"/>
-    <hyperlink ref="F102" r:id="rId31"/>
-    <hyperlink ref="F106" r:id="rId32"/>
-    <hyperlink ref="F108" r:id="rId33"/>
-    <hyperlink ref="F109" r:id="rId34"/>
-    <hyperlink ref="F110" r:id="rId35"/>
-    <hyperlink ref="F111" r:id="rId36"/>
-    <hyperlink ref="F116" r:id="rId37"/>
-    <hyperlink ref="F117" r:id="rId38"/>
-    <hyperlink ref="F118" r:id="rId39"/>
-    <hyperlink ref="F121" r:id="rId40"/>
-    <hyperlink ref="F124" r:id="rId41"/>
-    <hyperlink ref="F126" r:id="rId42"/>
-    <hyperlink ref="F129" r:id="rId43"/>
+    <hyperlink ref="F98" r:id="rId28"/>
+    <hyperlink ref="F100" r:id="rId29"/>
+    <hyperlink ref="F101" r:id="rId30"/>
+    <hyperlink ref="F103" r:id="rId31"/>
+    <hyperlink ref="F108" r:id="rId32"/>
+    <hyperlink ref="F110" r:id="rId33"/>
+    <hyperlink ref="F113" r:id="rId34"/>
+    <hyperlink ref="F117" r:id="rId35"/>
+    <hyperlink ref="F119" r:id="rId36"/>
+    <hyperlink ref="F120" r:id="rId37"/>
+    <hyperlink ref="F121" r:id="rId38"/>
+    <hyperlink ref="F122" r:id="rId39"/>
+    <hyperlink ref="F127" r:id="rId40"/>
+    <hyperlink ref="F130" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4446,42 +4485,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4493,10 +4532,10 @@
         <v>3</v>
       </c>
       <c r="G2" s="16">
-        <v>523.33</v>
+        <v>523.86</v>
       </c>
       <c r="H2" s="16">
-        <v>1570</v>
+        <v>1571.58</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>123</v>
@@ -4504,13 +4543,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
         <v>109</v>
@@ -4533,13 +4572,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
         <v>159</v>
@@ -4551,10 +4590,10 @@
         <v>3</v>
       </c>
       <c r="G4" s="16">
-        <v>1254.22</v>
+        <v>1254.99</v>
       </c>
       <c r="H4" s="16">
-        <v>3762.66</v>
+        <v>3764.98</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>123</v>
@@ -4562,28 +4601,28 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D5" t="s">
         <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="16">
-        <v>1500</v>
+        <v>549.14</v>
       </c>
       <c r="H5" s="16">
-        <v>4500</v>
+        <v>1098.27</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>123</v>
@@ -4591,28 +4630,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="16">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="H6" s="16">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>123</v>
@@ -4620,19 +4659,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C7" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -4661,7 +4700,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F8" s="17">
         <v>13</v>
@@ -4670,7 +4709,7 @@
         <v>48</v>
       </c>
       <c r="H8" s="18">
-        <v>12802.66</v>
+        <v>11904.83</v>
       </c>
     </row>
   </sheetData>
@@ -4699,24 +4738,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B2" s="16">
-        <v>12802.66</v>
+        <v>11904.83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4727,51 +4766,51 @@
         <v>1775</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" s="16">
         <v>2100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B5" s="16">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B6" s="16">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B7" s="18">
-        <v>19477.66</v>
+        <v>18579.83</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4782,7 +4821,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4796,214 +4835,231 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
         <v>165</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D6" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B7" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D7" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B8" t="s">
         <v>165</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D9" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B10" t="s">
         <v>165</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D10" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B11" t="s">
         <v>165</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D11" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>165</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D12" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>373</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="D13" t="s">
+        <v>379</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -5019,6 +5075,7 @@
     <hyperlink ref="E10" r:id="rId9"/>
     <hyperlink ref="E11" r:id="rId10"/>
     <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5038,16 +5095,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5058,16 +5115,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5075,16 +5132,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5092,16 +5149,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5109,16 +5166,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D5" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5126,16 +5183,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5143,16 +5200,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>384</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5160,16 +5217,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5177,16 +5234,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5194,16 +5251,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5211,16 +5268,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5228,16 +5285,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5245,16 +5302,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5262,16 +5319,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5279,7 +5336,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -5287,10 +5344,10 @@
         <v>48</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5298,10 +5355,10 @@
         <v>48</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5341,158 +5398,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C2" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E3" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" s="7" t="s">
         <v>434</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="E4" t="s">
-        <v>436</v>
-      </c>
-      <c r="F4" t="s">
-        <v>437</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="E5" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F5" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B6" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C6" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E6" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F6" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5506,7 +5563,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="463">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Transport</t>
   </si>
   <si>
-    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive from Aug 29 (Florence → FCO), IDP in hand</t>
+    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive Florence–Tuscany only (Aug 29 – Sep 1) · rail + private drivers from Naples on, IDP in hand</t>
   </si>
   <si>
     <t>Chain story</t>
@@ -655,133 +655,124 @@
     <t>Tue, Sep 1</t>
   </si>
   <si>
-    <t>TUSCANY → NAPLES — De Bonart</t>
-  </si>
-  <si>
-    <t>Watch this: The longest drive of the trip — roughly five hours of autostrada, most of it past Rome and Caserta. Fill the tank before you leave Castelfalfi, swap drivers if you can, and expect Naples traffic to eat the last half hour.</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — South on the A1 — Florence's ring road, then the long autostrada stretch past Rome and Caserta</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Fuel and coffee stop — An Autogrill service area north of Rome — top up the tank, swap drivers</t>
-  </si>
-  <si>
-    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay. Hand the car to the hotel valet and leave it there — you won't need it again until Thursday.</t>
-  </si>
-  <si>
-    <t>Naples Archaeological Museum — The frescoes, mosaics and bronzes lifted out of Pompeii all ended up here. You see the rooms they came from on Thursday, so this is the right way round.</t>
+    <t>TUSCANY → NAPLES — return the car in Florence, then the train</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Check out; drive to Florence — Back the way you came — about ninety minutes, less traffic than the Friday-afternoon drive in</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti, near Firenze S.M.N. — reservation #21586310US4 ends here</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Coffee, then the platform — A buffer before the train — Frecciarossa 9413 doesn't wait</t>
+  </si>
+  <si>
+    <t>12:48pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9413 to Naples — Firenze S.M.N. → Napoli Centrale, direct — 3h15. Super Economy fare, from €71.80.</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>4:03pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale</t>
+  </si>
+  <si>
+    <t>4:30pm</t>
+  </si>
+  <si>
+    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay</t>
+  </si>
+  <si>
+    <t>Rooftop aperitivo — Vesuvius on one side, the bay on the other</t>
+  </si>
+  <si>
+    <t>Dinner — pizza at Sorbillo — Via dei Tribunali. You are in the city that invented it; do this before anything fancier.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>NAPLES — Capri day trip</t>
+  </si>
+  <si>
+    <t>Walk down to Molo Beverello — The fast-ferry pier is fifteen minutes along the seafront from the hotel</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>9:20am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Naples → Capri — NLG, SNAV and Caremar all run it in about fifty minutes. Sailings are frequent in September but sell out at the counter — book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~50 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>The Faraglioni, the grottoes, the swim coves — Pick up a round-the-island boat at Marina Grande — Blue Grotto if the sea is calm enough to enter</t>
+  </si>
+  <si>
+    <t>Local boat from Marina Grande</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Marina Grande, then the funicular</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
+  </si>
+  <si>
+    <t>6:15pm</t>
+  </si>
+  <si>
+    <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
+  </si>
+  <si>
+    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu, back in the old city — the celebration dinner for the boat day</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>NAPLES → AMALFI — private driver</t>
+  </si>
+  <si>
+    <t>Pizza for breakfast — Di Matteo — Also on Via dei Tribunali, a few doors from last night's Sorbillo. Yes, at 8:30am. It's Naples.</t>
   </si>
   <si>
     <t>Spaccanapoli — The dead-straight Greek road that still splits the old city in half</t>
   </si>
   <si>
-    <t>Walk from the museum</t>
-  </si>
-  <si>
-    <t>Street food, standing up — Pizza fritta, zeppoline, a sfogliatella riccia straight from the oven</t>
-  </si>
-  <si>
-    <t>Rooftop aperitivo — Vesuvius on one side, the bay on the other</t>
-  </si>
-  <si>
-    <t>9:15pm</t>
-  </si>
-  <si>
-    <t>Dinner — pizza on Via dei Tribunali — Sorbillo or Di Matteo. You are in the city that invented it; do this before anything fancier.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>NAPLES — Capri day trip</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Walk down to Molo Beverello — The fast-ferry pier is fifteen minutes along the seafront from the hotel</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
-    <t>9:20am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Naples → Capri — NLG, SNAV and Caremar all run it in about fifty minutes. Sailings are frequent in September but sell out at the counter — book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~50 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>The Faraglioni, the grottoes, the swim coves — Pick up a round-the-island boat at Marina Grande — Blue Grotto if the sea is calm enough to enter</t>
-  </si>
-  <si>
-    <t>Local boat from Marina Grande</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Marina Grande, then the funicular</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
-  </si>
-  <si>
-    <t>6:15pm</t>
-  </si>
-  <si>
-    <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
-  </si>
-  <si>
-    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu, back in the old city</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>NAPLES → AMALFI, via Pompeii</t>
-  </si>
-  <si>
-    <t>Check out; collect the car from the valet — First time behind the wheel since Tuesday</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Drive to Pompeii — Half an hour southeast on the A3 — exit for Pompei Scavi</t>
-  </si>
-  <si>
-    <t>Self-drive, ~30 min</t>
-  </si>
-  <si>
-    <t>Pompeii, guided — Two and a half hours is the right length in September heat. Ask for the Villa of the Mysteries. Parking is at the Pompei Scavi lot by the entrance.</t>
-  </si>
-  <si>
-    <t>Arrive; on-site parking</t>
-  </si>
-  <si>
-    <t>Lunch, then onto the corniche — The coast road starts properly after Vietri — narrow, slow, spectacular. Take it easy.</t>
+    <t>Check out; last look at the bay</t>
+  </si>
+  <si>
+    <t>Private driver to Amalfi — Coast road via Vietri — narrow, slow, spectacular. Sit back, someone else is driving.</t>
+  </si>
+  <si>
+    <t>Private driver, ~1.5–2 hrs</t>
   </si>
   <si>
     <t>Check in — Anantara Convento di Amalfi — A 13th-century monastery on the cliff edge, with the original cloister still standing</t>
   </si>
   <si>
-    <t>Scenic drive, ~1.5 hrs</t>
-  </si>
-  <si>
-    <t>The beach club, by cliff lift — Down to sea level for what's left of the afternoon</t>
+    <t>The beach club, by cliff lift — A slow afternoon at sea level after the drive</t>
   </si>
   <si>
     <t>Hotel cliff lift</t>
@@ -814,6 +805,9 @@
     <t>Up to Ravello — Forty-five minutes of switchbacks above the coast</t>
   </si>
   <si>
+    <t>Private driver</t>
+  </si>
+  <si>
     <t>3:45pm</t>
   </si>
   <si>
@@ -847,13 +841,25 @@
     <t>Sat, Sep 5</t>
   </si>
   <si>
-    <t>AMALFI → ROME — The St. Regis</t>
-  </si>
-  <si>
-    <t>Check out; last look at the coast — Breakfast on the cloister terrace before you give the cliff back</t>
-  </si>
-  <si>
-    <t>Down the corniche, then north — The coast road as far as Vietri, then the A3 and the A1 — Amalfi → Rome is about four hours all told</t>
+    <t>AMALFI → NAPLES → ROME — driver, then train</t>
+  </si>
+  <si>
+    <t>Check out; last look at the coast — Breakfast on the cloister terrace before you give the room back</t>
+  </si>
+  <si>
+    <t>Private driver to Naples — Back along the coast road to Napoli Centrale</t>
+  </si>
+  <si>
+    <t>Private driver, ~1.5 hrs</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale; drop bags, coffee</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Rome — Napoli Centrale → Roma Termini, direct — about 1h10. Frequent departures; no need to book far ahead.</t>
+  </si>
+  <si>
+    <t>Arrive Roma Termini; taxi to the hotel</t>
   </si>
   <si>
     <t>Check in — The St. Regis Rome — The hotel is inside Rome's ZTL — use valet or a garage nearby; don't try to park at the curb.</t>
@@ -874,13 +880,10 @@
     <t>DEPART — FCO → IAH</t>
   </si>
   <si>
-    <t>Watch this: The rental is booked for a 12:00pm drop-off, but the flight leaves at 10:20am — the car would still be at FCO after you've taken off. Call the rental company and move the drop-off to around 6:00am.</t>
-  </si>
-  <si>
-    <t>6:00am</t>
-  </si>
-  <si>
-    <t>Drive to FCO; drop off the car — About forty minutes on an empty Sunday road — reservation #21586310US4</t>
+    <t>6:40am</t>
+  </si>
+  <si>
+    <t>Taxi to FCO — About forty minutes on an empty Sunday road. No rental to return this time — that ended in Florence on Sep 1.</t>
   </si>
   <si>
     <t>7:20am</t>
@@ -997,16 +1000,16 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>6 hotels, 13 nights. Trame ($1,571.58), Castelfalfi ($3,764.98) and De Bonart ($1,098.27) are confirmed bookings; Convento is a quote, now 2 nights rather than 3. The St. Regis is still an estimate.</t>
-  </si>
-  <si>
-    <t>Holding the old total pending a re-quote: the rental drops from 14 days to 8 (Florence Aug 29 → FCO Sep 6), but a one-way pickup fee eats into that, and the FCO private transfer (~€70–90) and two Frecciarossa fares are new. Rome garage parking is gone entirely. Fuel and tolls now only from Aug 29.</t>
+    <t>6 hotels, 13 nights. Trame ($1,571.58), Castelfalfi ($3,764.98) and De Bonart ($1,071, confirmed) are actual bookings; Convento is a quote, 2 nights rather than 3. The St. Regis is still an estimate.</t>
+  </si>
+  <si>
+    <t>Holding the old total pending a re-quote: the rental drops from 14 days to 3 (Florence Aug 29 → Florence Sep 1, both ends the same city now), but a one-way-turned-round-trip re-quote could move that either way. New costs: the FCO private transfer (~€70–90), two Frecciarossa fares, and private drivers for both Naples↔Amalfi legs. Rome and FCO parking are gone entirely.</t>
   </si>
   <si>
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Colosseum, Pompeii, Capri, wineries, Florence galleries, operas. Held pending a re-quote: swapping the private Lucibello charter for the Capri ferry takes a four-figure line down to about €50 of tickets for the two of you, so this should come down materially.</t>
+    <t>Vatican, Colosseum, Capri, wineries, Florence galleries, operas. Held pending a re-quote: swapping the private Lucibello charter for the Capri ferry takes a four-figure line down to about €50 of tickets for the two of you, and dropping Pompeii removes a guide fee, so this should come down materially.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1036,9 +1039,6 @@
     <t>Aug 24</t>
   </si>
   <si>
-    <t>Private driver</t>
-  </si>
-  <si>
     <t>FCO → Hotel Trame, Rome  (Pre-booked NCC, name board at arrivals — book before you fly)</t>
   </si>
   <si>
@@ -1105,61 +1105,70 @@
     <t>Sep 1</t>
   </si>
   <si>
-    <t>Il Castelfalfi → De Bonart Naples  (The longest drive of the trip — then the car goes to the hotel valet until Thursday)</t>
+    <t>Self-drive, then train</t>
+  </si>
+  <si>
+    <t>Il Castelfalfi → Firenze S.M.N. (drop the car) → Napoli Centrale  (Frecciarossa 9413, 12:48 → 16:03. Return the rental in Florence before the train — it does not go on to Naples.)</t>
+  </si>
+  <si>
+    <t>~1.5 hrs drive + 3h15 train</t>
+  </si>
+  <si>
+    <t>Sep 2</t>
+  </si>
+  <si>
+    <t>Fast ferry</t>
+  </si>
+  <si>
+    <t>Molo Beverello, Naples → Capri → back  (NLG / SNAV / Caremar — book online the night before, and check the last sailing back)</t>
+  </si>
+  <si>
+    <t>~50 min each way</t>
+  </si>
+  <si>
+    <t>Sep 3</t>
+  </si>
+  <si>
+    <t>De Bonart Naples → Anantara Convento, Amalfi  (No rental car for this leg, and Pompeii is dropped with it — book a car service for the coast road)</t>
+  </si>
+  <si>
+    <t>~1.5–2 hrs</t>
+  </si>
+  <si>
+    <t>Sep 4</t>
+  </si>
+  <si>
+    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks, and no rental car by this point — a local driver is the only option, not just the easy one)</t>
   </si>
   <si>
     <t>~5 hrs</t>
   </si>
   <si>
-    <t>Sep 2</t>
-  </si>
-  <si>
-    <t>Fast ferry</t>
-  </si>
-  <si>
-    <t>Molo Beverello, Naples → Capri → back  (NLG / SNAV / Caremar — book online the night before, and check the last sailing back)</t>
-  </si>
-  <si>
-    <t>~50 min each way</t>
-  </si>
-  <si>
-    <t>Sep 3</t>
-  </si>
-  <si>
-    <t>Naples → Pompeii (guided) → Anantara Convento, Amalfi  (Pompeii is directly on the way — no detour at all)</t>
-  </si>
-  <si>
-    <t>~5 hrs with the site</t>
-  </si>
-  <si>
-    <t>Sep 4</t>
-  </si>
-  <si>
-    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks — a local driver is a fine substitute for this one leg)</t>
-  </si>
-  <si>
     <t>Sep 5</t>
   </si>
   <si>
-    <t>Anantara Convento → The St. Regis Rome  (Corniche as far as Vietri, then the A3 and A1)</t>
-  </si>
-  <si>
-    <t>~4 hrs</t>
+    <t>Anantara Convento, Amalfi → Napoli Centrale</t>
+  </si>
+  <si>
+    <t>~1.5 hrs</t>
+  </si>
+  <si>
+    <t>Napoli Centrale → Roma Termini (Frecciarossa)  (Frequent departures — no need to pre-book far ahead)</t>
+  </si>
+  <si>
+    <t>~1h10</t>
   </si>
   <si>
     <t>Sep 6</t>
   </si>
   <si>
-    <t>Drop off the car</t>
-  </si>
-  <si>
-    <t>The St. Regis Rome → FCO  (Drop-off is booked for noon — move it earlier so it isn't after the flight)</t>
+    <t>The St. Regis Rome → FCO  (No rental to return — that was dropped off in Florence on Sep 1)</t>
   </si>
   <si>
     <t>~40 min</t>
   </si>
   <si>
-    <t>You are car-free for the first five days: a private driver in from FCO, taxis and your feet in Rome, the Frecciarossa to Florence. The car is only collected on Aug 29, on Borgo Ognissanti just outside Florence's ZTL, and runs from there to the FCO drop-off on Sep 6 — eight days rather than fourteen, and no Rome garage at all. The IDP ships by Aug 3; pack it with the physical licence, not just a photo of it. Never drive into either historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi and the Amalfi hotel have their own parking, Naples has hotel valet. Budget roughly €60 in tolls from Aug 29 on and a full tank about every 2–3 driving days.</t>
+    <t>You are car-free for the first five days: a private driver in from FCO, taxis and your feet in Rome, the Frecciarossa to Florence. The rental is only collected on Aug 29, on Borgo Ognissanti just outside Florence's ZTL, and returned in Florence again on Sep 1 before the Naples train — three driving days, not fourteen. Everything south of that (Naples, Capri, Amalfi, and the ride back to Rome) is ferry, private driver or train, never a car you're driving yourself. The IDP ships by Aug 3; pack it with the physical licence, not just a photo of it. Never drive into either historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking. Budget roughly €40 in tolls for the Florence–Tuscany stretch and a full tank each way.</t>
   </si>
   <si>
     <t>#</t>
@@ -1195,10 +1204,10 @@
     <t>THIS WEEK</t>
   </si>
   <si>
-    <t>Rebook the rental car — Florence pickup, not FCO</t>
-  </si>
-  <si>
-    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → FCO Sep 6: six days shorter, but a different pickup city usually carries a one-way fee, so the €1,087.81 quote will not hold. Re-quote before cancelling. While you are on the phone, move the Sep 6 drop-off off noon — the flight leaves at 10:20am, so around 6:00am.</t>
+    <t>Rebook the rental car — Florence pickup and drop-off, not FCO</t>
+  </si>
+  <si>
+    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → Florence Sep 1: three days rather than fourteen, both ends in the same city. A different pickup/drop-off city usually carries a fee, so the €1,087.81 quote will not hold — re-quote before cancelling.</t>
   </si>
   <si>
     <t>Book the FCO → Hotel Trame private driver</t>
@@ -1237,10 +1246,16 @@
     <t>Three in one morning, in that order. Book the dome climb first; it has the fewest slots.</t>
   </si>
   <si>
-    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26), Pompeii guide (Sep 3)</t>
-  </si>
-  <si>
-    <t>All three need booking — the Vatican and Colosseum slots go first. Pompeii moved to Sep 3 with the reorder; take a morning slot, the site has almost no shade by noon.</t>
+    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26)</t>
+  </si>
+  <si>
+    <t>Both need booking — the Vatican slots go first. Pompeii is dropped from the itinerary, so there's no third guide to book here.</t>
+  </si>
+  <si>
+    <t>Arrange private drivers — Naples → Amalfi (Sep 3) and Amalfi → Naples (Sep 5)</t>
+  </si>
+  <si>
+    <t>No rental car for either leg. Book a local car service for the coast road in both directions — the hotel can usually arrange this directly.</t>
   </si>
   <si>
     <t>Capri ferry — Naples → Capri return, Sep 2</t>
@@ -1258,6 +1273,12 @@
     <t>Festival runs to Sep 5, so both Amalfi nights now fall inside the window. The Aug 29 Mahler date still lands on your Florence→Castelfalfi transfer, so it was never reachable.</t>
   </si>
   <si>
+    <t>Naples → Rome train, Sep 5</t>
+  </si>
+  <si>
+    <t>Frecciarossa runs the route roughly every half hour, about 1h10 — no need to lock this in until closer to the date.</t>
+  </si>
+  <si>
     <t>Headline dinners on their dates</t>
   </si>
   <si>
@@ -1354,7 +1375,7 @@
     <t>~$425 / 60 min</t>
   </si>
   <si>
-    <t>Days 9–11</t>
+    <t>Days 11–13</t>
   </si>
   <si>
     <t>Flytographer Amalfi / Giuseppe Di Martino</t>
@@ -1394,7 +1415,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1447,11 +1468,6 @@
       <b/>
       <color rgb="FF9E4529"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF8A6D1F"/>
-      <sz val="9"/>
     </font>
     <font>
       <b/>
@@ -1507,7 +1523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1533,19 +1549,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2072,7 +2085,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3551,18 +3564,24 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>48</v>
       </c>
       <c r="B86" t="s">
         <v>48</v>
       </c>
-      <c r="C86" t="s">
-        <v>48</v>
-      </c>
-      <c r="D86" s="15" t="s">
+      <c r="C86" s="12" t="s">
         <v>213</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F86" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3573,13 +3592,13 @@
         <v>48</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>215</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="F87" t="s">
         <v>48</v>
@@ -3593,13 +3612,13 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>217</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="F88" t="s">
         <v>48</v>
@@ -3613,16 +3632,16 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3633,16 +3652,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="F90" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3653,16 +3672,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>84</v>
+        <v>223</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="F91" t="s">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,10 +3695,10 @@
         <v>194</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F92" t="s">
         <v>48</v>
@@ -3693,47 +3712,47 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F93" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>48</v>
-      </c>
-      <c r="B94" t="s">
-        <v>48</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E94" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="F93" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+    <row r="95" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
         <v>10</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C96" s="11" t="s">
+      <c r="B95" s="10" t="s">
         <v>227</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B96" t="s">
+        <v>48</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F96" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,16 +3763,16 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="F97" t="s">
-        <v>48</v>
+        <v>233</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,16 +3783,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
+      </c>
+      <c r="F98" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3784,16 +3803,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="F99" t="s">
-        <v>48</v>
+        <v>238</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3804,16 +3823,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,16 +3843,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>169</v>
+        <v>233</v>
+      </c>
+      <c r="F101" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3844,50 +3863,50 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F102" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>48</v>
-      </c>
-      <c r="B103" t="s">
-        <v>48</v>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E103" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="F102" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="105" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
+    <row r="104" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
         <v>11</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B104" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C104" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="F105" s="14" t="s">
+      <c r="F104" s="14" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>48</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F105" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,13 +3917,13 @@
         <v>48</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F106" t="s">
         <v>48</v>
@@ -3918,13 +3937,13 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="F107" t="s">
         <v>48</v>
@@ -3938,16 +3957,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="D108" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E108" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E108" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>77</v>
+      <c r="F108" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,16 +3977,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F109" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3981,13 +4000,13 @@
         <v>58</v>
       </c>
       <c r="D110" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E110" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E110" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>123</v>
+      <c r="F110" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,13 +4017,13 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>254</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>255</v>
+        <v>63</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
@@ -4018,47 +4037,47 @@
         <v>48</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F112" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>48</v>
-      </c>
-      <c r="B113" t="s">
-        <v>48</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="F112" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="10">
+        <v>12</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E115" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="10">
-        <v>12</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>260</v>
+      <c r="F115" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4069,16 +4088,16 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F116" t="s">
-        <v>48</v>
+        <v>260</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4089,16 +4108,16 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>186</v>
+        <v>58</v>
       </c>
       <c r="D117" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E117" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="E117" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>71</v>
+      <c r="F117" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4109,16 +4128,16 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>264</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F118" t="s">
-        <v>48</v>
+        <v>265</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,13 +4148,13 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>266</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>267</v>
+        <v>88</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>77</v>
@@ -4149,16 +4168,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>194</v>
+        <v>64</v>
       </c>
       <c r="D120" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E120" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="E120" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="F120" s="7" t="s">
-        <v>77</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4169,50 +4188,50 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>64</v>
+        <v>270</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>48</v>
-      </c>
-      <c r="B122" t="s">
-        <v>48</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D122" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="10">
+        <v>13</v>
+      </c>
+      <c r="B123" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="E122" s="13" t="s">
+      <c r="C123" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="10">
-        <v>13</v>
-      </c>
-      <c r="B124" s="10" t="s">
+      <c r="F123" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s">
+        <v>48</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C124" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>111</v>
+      <c r="E124" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F124" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4223,13 +4242,13 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="D125" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E125" s="13" t="s">
         <v>277</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="F125" t="s">
         <v>48</v>
@@ -4243,13 +4262,13 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>278</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="F126" t="s">
         <v>48</v>
@@ -4263,16 +4282,16 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>203</v>
+        <v>49</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>279</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4283,13 +4302,13 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>280</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>230</v>
+        <v>76</v>
       </c>
       <c r="F128" t="s">
         <v>48</v>
@@ -4303,16 +4322,16 @@
         <v>48</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>61</v>
+        <v>203</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>281</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F129" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4323,61 +4342,67 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>282</v>
       </c>
       <c r="E130" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F130" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>48</v>
+      </c>
+      <c r="B131" t="s">
+        <v>48</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F131" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>48</v>
+      </c>
+      <c r="B132" t="s">
+        <v>48</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E132" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F132" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="132" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="10">
+    <row r="134" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="10">
         <v>14</v>
       </c>
-      <c r="B132" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>48</v>
-      </c>
-      <c r="B133" t="s">
-        <v>48</v>
-      </c>
-      <c r="C133" t="s">
-        <v>48</v>
-      </c>
-      <c r="D133" s="15" t="s">
+      <c r="B134" s="10" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>48</v>
-      </c>
-      <c r="B134" t="s">
-        <v>48</v>
-      </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E134" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F134" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4388,13 +4413,13 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D135" s="4" t="s">
-        <v>289</v>
-      </c>
       <c r="E135" s="13" t="s">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="F135" t="s">
         <v>48</v>
@@ -4408,15 +4433,35 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E136" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="F136" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C137" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="E136" s="13" t="s">
+      <c r="D137" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F136" t="s">
+      <c r="E137" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="F137" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4447,22 +4492,22 @@
     <hyperlink ref="F54" r:id="rId23"/>
     <hyperlink ref="F58" r:id="rId24"/>
     <hyperlink ref="F89" r:id="rId25"/>
-    <hyperlink ref="F90" r:id="rId26"/>
-    <hyperlink ref="F94" r:id="rId27"/>
-    <hyperlink ref="F98" r:id="rId28"/>
-    <hyperlink ref="F100" r:id="rId29"/>
-    <hyperlink ref="F101" r:id="rId30"/>
-    <hyperlink ref="F103" r:id="rId31"/>
-    <hyperlink ref="F108" r:id="rId32"/>
-    <hyperlink ref="F110" r:id="rId33"/>
-    <hyperlink ref="F113" r:id="rId34"/>
-    <hyperlink ref="F117" r:id="rId35"/>
+    <hyperlink ref="F91" r:id="rId26"/>
+    <hyperlink ref="F93" r:id="rId27"/>
+    <hyperlink ref="F97" r:id="rId28"/>
+    <hyperlink ref="F99" r:id="rId29"/>
+    <hyperlink ref="F100" r:id="rId30"/>
+    <hyperlink ref="F102" r:id="rId31"/>
+    <hyperlink ref="F109" r:id="rId32"/>
+    <hyperlink ref="F112" r:id="rId33"/>
+    <hyperlink ref="F116" r:id="rId34"/>
+    <hyperlink ref="F118" r:id="rId35"/>
     <hyperlink ref="F119" r:id="rId36"/>
     <hyperlink ref="F120" r:id="rId37"/>
     <hyperlink ref="F121" r:id="rId38"/>
-    <hyperlink ref="F122" r:id="rId39"/>
-    <hyperlink ref="F127" r:id="rId40"/>
-    <hyperlink ref="F130" r:id="rId41"/>
+    <hyperlink ref="F127" r:id="rId39"/>
+    <hyperlink ref="F129" r:id="rId40"/>
+    <hyperlink ref="F132" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4485,42 +4530,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4531,10 +4576,10 @@
       <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="15">
         <v>523.86</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="15">
         <v>1571.58</v>
       </c>
       <c r="I2" s="7" t="s">
@@ -4543,13 +4588,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D3" t="s">
         <v>109</v>
@@ -4560,10 +4605,10 @@
       <c r="F3">
         <v>2</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="15">
         <v>735</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <v>1470</v>
       </c>
       <c r="I3" s="7" t="s">
@@ -4572,13 +4617,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
         <v>159</v>
@@ -4589,10 +4634,10 @@
       <c r="F4">
         <v>3</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="15">
         <v>1254.99</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="15">
         <v>3764.98</v>
       </c>
       <c r="I4" s="7" t="s">
@@ -4601,13 +4646,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D5" t="s">
         <v>211</v>
@@ -4618,11 +4663,11 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" s="16">
-        <v>549.14</v>
-      </c>
-      <c r="H5" s="16">
-        <v>1098.27</v>
+      <c r="G5" s="15">
+        <v>535.5</v>
+      </c>
+      <c r="H5" s="15">
+        <v>1071</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>123</v>
@@ -4630,27 +4675,27 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <v>1500</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>3000</v>
       </c>
       <c r="I6" s="7" t="s">
@@ -4659,57 +4704,57 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <v>1000</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>1000</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F8" s="17">
+    <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="16">
         <v>13</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="18">
-        <v>11904.83</v>
+      <c r="G8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="17">
+        <v>11877.56</v>
       </c>
     </row>
   </sheetData>
@@ -4738,79 +4783,79 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B2" s="16">
-        <v>11904.83</v>
+        <v>326</v>
+      </c>
+      <c r="B2" s="15">
+        <v>11877.56</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="15">
         <v>1775</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B4" s="16">
-        <v>2100</v>
+        <v>329</v>
+      </c>
+      <c r="B4" s="15">
+        <v>1900</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B5" s="16">
+        <v>331</v>
+      </c>
+      <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>332</v>
-      </c>
-      <c r="B6" s="16">
+        <v>333</v>
+      </c>
+      <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="B7" s="18">
-        <v>18579.83</v>
-      </c>
-      <c r="C7" s="17" t="s">
         <v>334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7" s="17">
+        <v>18352.559999999998</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4821,7 +4866,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4835,26 +4880,26 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C2" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>340</v>
       </c>
       <c r="D2" t="s">
@@ -4871,7 +4916,7 @@
       <c r="B3" t="s">
         <v>344</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>345</v>
       </c>
       <c r="D3" t="s">
@@ -4888,7 +4933,7 @@
       <c r="B4" t="s">
         <v>348</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>349</v>
       </c>
       <c r="D4" t="s">
@@ -4905,7 +4950,7 @@
       <c r="B5" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>351</v>
       </c>
       <c r="D5" t="s">
@@ -4922,7 +4967,7 @@
       <c r="B6" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>355</v>
       </c>
       <c r="D6" t="s">
@@ -4939,7 +4984,7 @@
       <c r="B7" t="s">
         <v>358</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>359</v>
       </c>
       <c r="D7" t="s">
@@ -4954,13 +4999,13 @@
         <v>361</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="19" t="s">
         <v>362</v>
       </c>
+      <c r="C8" s="18" t="s">
+        <v>363</v>
+      </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>342</v>
@@ -4968,16 +5013,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B9" t="s">
-        <v>365</v>
-      </c>
-      <c r="C9" s="19" t="s">
         <v>366</v>
       </c>
+      <c r="C9" s="18" t="s">
+        <v>367</v>
+      </c>
       <c r="D9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>342</v>
@@ -4985,16 +5030,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>369</v>
+        <v>262</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>370</v>
       </c>
       <c r="D10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>342</v>
@@ -5002,16 +5047,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>372</v>
+        <v>262</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>373</v>
       </c>
       <c r="D11" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>342</v>
@@ -5019,16 +5064,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>374</v>
+        <v>262</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>376</v>
       </c>
       <c r="D12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>342</v>
@@ -5036,12 +5081,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C13" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>378</v>
       </c>
       <c r="D13" t="s">
@@ -5051,314 +5096,32 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>380</v>
       </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="68" customWidth="1"/>
-    <col min="4" max="5" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D14" t="s">
         <v>382</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E14" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5376,6 +5139,342 @@
     <hyperlink ref="E12" r:id="rId11"/>
     <hyperlink ref="E13" r:id="rId12"/>
     <hyperlink ref="E14" r:id="rId13"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="68" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5398,158 +5497,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C2" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C3" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="E4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F4" t="s">
-        <v>444</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C5" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E5" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F5" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B6" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C6" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E6" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F6" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5563,7 +5662,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="465">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -322,237 +322,249 @@
     <t>Walk, 5 min via Campo de' Fiori</t>
   </si>
   <si>
-    <t>Siesta</t>
+    <t>Siesta — Shorter than the other days — the light at Borghese is worth trading a bit of rest for</t>
+  </si>
+  <si>
+    <t>4:00pm</t>
+  </si>
+  <si>
+    <t>Villa Borghese Gardens, in the daylight — Rome's largest park — shaded avenues, the Fontana dei Cavalli Marini, and the Pincio terrace over Piazza del Popolo with St. Peter's dome on the skyline. Soft light under the trees most of the afternoon — good ground for pictures. The Galleria itself needs a timed ticket booked weeks out; skip it unless you already have one.</t>
+  </si>
+  <si>
+    <t>Info -&gt;</t>
+  </si>
+  <si>
+    <t>5:30pm</t>
+  </si>
+  <si>
+    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
+  </si>
+  <si>
+    <t>Walk down, ~10 min</t>
+  </si>
+  <si>
+    <t>6:15pm</t>
   </si>
   <si>
     <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
   </si>
   <si>
+    <t>9:00pm</t>
+  </si>
+  <si>
+    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
+  </si>
+  <si>
     <t>Walk, ~12 min</t>
   </si>
   <si>
+    <t>Thu, Aug 27</t>
+  </si>
+  <si>
+    <t>ROME → FLORENCE — Casa G. Firenze</t>
+  </si>
+  <si>
+    <t>TRAVEL DAY</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori. Aim to be at the platform twenty minutes before departure.</t>
+  </si>
+  <si>
+    <t>10:35am</t>
+  </si>
+  <si>
+    <t>Frecciarossa — Roma Termini → Firenze S.M.N. — Book Trenitalia or Italo well ahead; advance fares are a fraction of the walk-up price and both run the route hourly.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1h30</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>12:10pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze Santa Maria Novella — The station is a nine-minute walk from Via dei Rondinelli — no transfer needed</t>
+  </si>
+  <si>
+    <t>Walk, ~9 min</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Drop bags at Casa G. Firenze — Via dei Rondinelli, between the Duomo and Santa Maria Novella. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
+  </si>
+  <si>
+    <t>Trip.com -&gt;</t>
+  </si>
+  <si>
+    <t>1:15pm</t>
+  </si>
+  <si>
+    <t>Lunch at the Mercato Centrale — Five minutes north — the upstairs food hall, no booking, no ceremony</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>First orientation walk — The Duomo and Baptistery from the outside, then Piazza della Repubblica and down to the Arno. The ticketed interiors are all tomorrow — today is just getting your bearings.</t>
+  </si>
+  <si>
+    <t>Unpack and reset — The train bought you an afternoon the drive would have eaten</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo on the secret patio — Casa G.'s courtyard bar</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, comfortably clear now the train lands you at midday.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>1:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, ~10 min on foot and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
     <t>7:00pm</t>
   </si>
   <si>
-    <t>[optional] Optional — Galleria Borghese — Timed entry, two-hour slots, books out early. Skip it guilt-free if the day already feels long.</t>
-  </si>
-  <si>
-    <t>Taxi, ~20 min</t>
-  </si>
-  <si>
-    <t>9:00pm</t>
-  </si>
-  <si>
-    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
-  </si>
-  <si>
-    <t>Thu, Aug 27</t>
-  </si>
-  <si>
-    <t>ROME → FLORENCE — Casa G. Firenze</t>
-  </si>
-  <si>
-    <t>TRAVEL DAY</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori. Aim to be at the platform twenty minutes before departure.</t>
-  </si>
-  <si>
-    <t>10:35am</t>
-  </si>
-  <si>
-    <t>Frecciarossa — Roma Termini → Firenze S.M.N. — Book Trenitalia or Italo well ahead; advance fares are a fraction of the walk-up price and both run the route hourly.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1h30</t>
-  </si>
-  <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>12:10pm</t>
-  </si>
-  <si>
-    <t>Arrive Firenze Santa Maria Novella — The station is a nine-minute walk from Via dei Rondinelli — no transfer needed</t>
-  </si>
-  <si>
-    <t>Walk, ~9 min</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Drop bags at Casa G. Firenze — Via dei Rondinelli, between the Duomo and Santa Maria Novella. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
-  </si>
-  <si>
-    <t>Trip.com -&gt;</t>
-  </si>
-  <si>
-    <t>1:15pm</t>
-  </si>
-  <si>
-    <t>Lunch at the Mercato Centrale — Five minutes north — the upstairs food hall, no booking, no ceremony</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>First orientation walk — The Duomo and Baptistery from the outside, then Piazza della Repubblica and down to the Arno. The ticketed interiors are all tomorrow — today is just getting your bearings.</t>
-  </si>
-  <si>
-    <t>Unpack and reset — The train bought you an afternoon the drive would have eaten</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo on the secret patio — Casa G.'s courtyard bar</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, comfortably clear now the train lands you at midday.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>1:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, ~10 min on foot and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>Info -&gt;</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
     <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
   </si>
   <si>
@@ -640,9 +652,6 @@
     <t>The village and a second cellar — Small enough to see on foot between tastings</t>
   </si>
   <si>
-    <t>5:30pm</t>
-  </si>
-  <si>
     <t>Back to Castelfalfi — About forty minutes</t>
   </si>
   <si>
@@ -737,9 +746,6 @@
   </si>
   <si>
     <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
-  </si>
-  <si>
-    <t>6:15pm</t>
   </si>
   <si>
     <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
@@ -2085,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2497,16 +2503,16 @@
         <v>48</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" t="s">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2517,16 +2523,16 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>77</v>
+        <v>107</v>
+      </c>
+      <c r="F25" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2537,50 +2543,50 @@
         <v>48</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+    <row r="29" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
         <v>4</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="B29" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" t="s">
-        <v>48</v>
+      <c r="C29" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2591,16 +2597,16 @@
         <v>48</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>117</v>
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2619,8 +2625,8 @@
       <c r="E31" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="F31" t="s">
-        <v>48</v>
+      <c r="F31" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2631,16 +2637,16 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="F32" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2651,16 +2657,16 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2671,13 +2677,13 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F34" t="s">
         <v>48</v>
@@ -2691,13 +2697,13 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F35" t="s">
         <v>48</v>
@@ -2711,16 +2717,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>123</v>
+      <c r="F36" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2731,16 +2737,16 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2751,47 +2757,47 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="F38" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+    <row r="41" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
         <v>5</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>77</v>
+      <c r="B41" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2802,13 +2808,13 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>77</v>
@@ -2822,16 +2828,16 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="F43" t="s">
-        <v>48</v>
+        <v>146</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2842,16 +2848,16 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>77</v>
+        <v>130</v>
+      </c>
+      <c r="F44" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,16 +2868,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,16 +2888,16 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2902,16 +2908,16 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F47" t="s">
-        <v>48</v>
+        <v>130</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2922,13 +2928,13 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
@@ -2942,50 +2948,50 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F49" s="7" t="s">
+      <c r="D50" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+    <row r="52" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="10">
         <v>6</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" t="s">
-        <v>48</v>
+      <c r="B52" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2996,13 +3002,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3016,16 +3022,16 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="F54" s="7" t="s">
         <v>169</v>
+      </c>
+      <c r="F54" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3042,10 +3048,10 @@
         <v>171</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F55" t="s">
-        <v>48</v>
+        <v>172</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,10 +3062,10 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>88</v>
@@ -3076,13 +3082,13 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3096,16 +3102,16 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="F58" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3116,16 +3122,16 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F59" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,13 +3142,13 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F60" t="s">
         <v>48</v>
@@ -3156,10 +3162,10 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>63</v>
@@ -3168,35 +3174,35 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="10">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
         <v>7</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>48</v>
-      </c>
-      <c r="B64" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F64" t="s">
-        <v>48</v>
+      <c r="B64" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3207,13 +3213,13 @@
         <v>48</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>183</v>
+        <v>116</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="F65" t="s">
         <v>48</v>
@@ -3227,13 +3233,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3247,10 +3253,10 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>88</v>
@@ -3267,10 +3273,10 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E68" s="13" t="s">
         <v>88</v>
@@ -3287,13 +3293,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3307,13 +3313,13 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -3327,13 +3333,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3347,13 +3353,13 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>194</v>
+        <v>84</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
@@ -3367,47 +3373,47 @@
         <v>48</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E73" s="13" t="s">
+      <c r="D74" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E74" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F73" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="10">
+      <c r="F74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="10">
         <v>8</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>48</v>
-      </c>
-      <c r="B76" t="s">
-        <v>48</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F76" t="s">
-        <v>48</v>
+      <c r="B76" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3418,13 +3424,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3438,13 +3444,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3458,13 +3464,13 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>205</v>
+        <v>57</v>
       </c>
       <c r="F79" t="s">
         <v>48</v>
@@ -3478,13 +3484,13 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="F80" t="s">
         <v>48</v>
@@ -3498,13 +3504,13 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="F81" t="s">
         <v>48</v>
@@ -3518,13 +3524,13 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>63</v>
+        <v>177</v>
       </c>
       <c r="F82" t="s">
         <v>48</v>
@@ -3538,10 +3544,10 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>63</v>
@@ -3550,38 +3556,38 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="10">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>48</v>
+      </c>
+      <c r="B84" t="s">
+        <v>48</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F84" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="10">
         <v>9</v>
       </c>
-      <c r="B85" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F85" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>48</v>
-      </c>
-      <c r="B86" t="s">
-        <v>48</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="B86" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="E86" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F86" t="s">
-        <v>48</v>
+      <c r="C86" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F86" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3592,13 +3598,13 @@
         <v>48</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="F87" t="s">
         <v>48</v>
@@ -3612,13 +3618,13 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="F88" t="s">
         <v>48</v>
@@ -3632,16 +3638,16 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>117</v>
+        <v>88</v>
+      </c>
+      <c r="F89" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,10 +3664,10 @@
         <v>222</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F90" t="s">
-        <v>48</v>
+        <v>223</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3672,16 +3678,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F91" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3692,16 +3698,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F92" t="s">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3712,47 +3718,47 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F93" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>48</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E93" s="13" t="s">
+      <c r="D94" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="F94" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
         <v>10</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" t="s">
-        <v>48</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E96" s="13" t="s">
+      <c r="B96" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F96" t="s">
-        <v>48</v>
+      <c r="C96" s="11" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3763,7 +3769,7 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>232</v>
@@ -3771,8 +3777,8 @@
       <c r="E97" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>234</v>
+      <c r="F97" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3783,7 +3789,7 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>235</v>
@@ -3791,8 +3797,8 @@
       <c r="E98" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="F98" t="s">
-        <v>48</v>
+      <c r="F98" s="7" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3803,16 +3809,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>71</v>
+        <v>239</v>
+      </c>
+      <c r="F99" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3823,16 +3829,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>60</v>
+        <v>241</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3843,16 +3849,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F101" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,50 +3869,50 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F102" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" t="s">
+        <v>48</v>
+      </c>
+      <c r="C103" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D102" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E102" s="13" t="s">
+      <c r="D103" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E103" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F103" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="10">
+    <row r="105" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
         <v>11</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="F104" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>48</v>
-      </c>
-      <c r="B105" t="s">
-        <v>48</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D105" s="4" t="s">
+      <c r="B105" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="E105" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F105" t="s">
-        <v>48</v>
+      <c r="C105" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3917,13 +3923,13 @@
         <v>48</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="F106" t="s">
         <v>48</v>
@@ -3937,13 +3943,13 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F107" t="s">
         <v>48</v>
@@ -3957,13 +3963,13 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>249</v>
+        <v>63</v>
       </c>
       <c r="F108" t="s">
         <v>48</v>
@@ -3977,16 +3983,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>250</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>123</v>
+        <v>251</v>
+      </c>
+      <c r="F109" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3997,16 +4003,16 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>58</v>
+        <v>207</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="F110" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4017,13 +4023,13 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="E111" s="13" t="s">
         <v>254</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
@@ -4037,47 +4043,47 @@
         <v>48</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="F112" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="114" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="10">
+    <row r="115" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="10">
         <v>12</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>48</v>
-      </c>
-      <c r="B115" t="s">
-        <v>48</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D115" s="4" t="s">
+      <c r="B115" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="E115" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F115" t="s">
-        <v>48</v>
+      <c r="C115" s="11" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4088,16 +4094,16 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="F116" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4108,7 +4114,7 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>261</v>
@@ -4116,8 +4122,8 @@
       <c r="E117" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="F117" t="s">
-        <v>48</v>
+      <c r="F117" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4128,16 +4134,16 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="E118" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="E118" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>77</v>
+      <c r="F118" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4148,13 +4154,13 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>266</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>77</v>
@@ -4168,16 +4174,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>268</v>
+        <v>88</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>269</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4188,50 +4194,50 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E121" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="F121" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="E121" s="13" t="s">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" t="s">
+        <v>48</v>
+      </c>
+      <c r="C122" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="F121" s="7" t="s">
+      <c r="D122" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F122" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="10">
+    <row r="124" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="10">
         <v>13</v>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="F123" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>48</v>
-      </c>
-      <c r="B124" t="s">
-        <v>48</v>
-      </c>
-      <c r="C124" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D124" s="4" t="s">
+      <c r="B124" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E124" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F124" t="s">
-        <v>48</v>
+      <c r="C124" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,13 +4248,13 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>277</v>
+        <v>63</v>
       </c>
       <c r="F125" t="s">
         <v>48</v>
@@ -4262,13 +4268,13 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>278</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="F126" t="s">
         <v>48</v>
@@ -4282,16 +4288,16 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>117</v>
+        <v>57</v>
+      </c>
+      <c r="F127" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4302,16 +4308,16 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F128" t="s">
-        <v>48</v>
+        <v>223</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,16 +4328,16 @@
         <v>48</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>123</v>
+        <v>76</v>
+      </c>
+      <c r="F129" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4342,16 +4348,16 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="F130" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4362,13 +4368,13 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>63</v>
+        <v>233</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4382,47 +4388,47 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F132" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>48</v>
+      </c>
+      <c r="B133" t="s">
+        <v>48</v>
+      </c>
+      <c r="C133" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D132" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E132" s="13" t="s">
+      <c r="D133" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E133" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="F133" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="10">
+    <row r="135" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="10">
         <v>14</v>
       </c>
-      <c r="B134" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="C134" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>48</v>
-      </c>
-      <c r="B135" t="s">
-        <v>48</v>
-      </c>
-      <c r="C135" s="12" t="s">
+      <c r="B135" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="C135" s="11" t="s">
         <v>288</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F135" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,7 +4445,7 @@
         <v>290</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="F136" t="s">
         <v>48</v>
@@ -4453,15 +4459,35 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="E137" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="E137" s="13" t="s">
+      <c r="F137" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>48</v>
+      </c>
+      <c r="B138" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="F137" t="s">
+      <c r="D138" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="F138" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4476,38 +4502,38 @@
     <hyperlink ref="F18" r:id="rId7"/>
     <hyperlink ref="F21" r:id="rId8"/>
     <hyperlink ref="F22" r:id="rId9"/>
-    <hyperlink ref="F25" r:id="rId10"/>
-    <hyperlink ref="F26" r:id="rId11"/>
-    <hyperlink ref="F30" r:id="rId12"/>
-    <hyperlink ref="F32" r:id="rId13"/>
-    <hyperlink ref="F36" r:id="rId14"/>
-    <hyperlink ref="F37" r:id="rId15"/>
-    <hyperlink ref="F38" r:id="rId16"/>
-    <hyperlink ref="F41" r:id="rId17"/>
-    <hyperlink ref="F42" r:id="rId18"/>
-    <hyperlink ref="F44" r:id="rId19"/>
-    <hyperlink ref="F45" r:id="rId20"/>
-    <hyperlink ref="F46" r:id="rId21"/>
-    <hyperlink ref="F49" r:id="rId22"/>
-    <hyperlink ref="F54" r:id="rId23"/>
-    <hyperlink ref="F58" r:id="rId24"/>
-    <hyperlink ref="F89" r:id="rId25"/>
-    <hyperlink ref="F91" r:id="rId26"/>
-    <hyperlink ref="F93" r:id="rId27"/>
-    <hyperlink ref="F97" r:id="rId28"/>
-    <hyperlink ref="F99" r:id="rId29"/>
-    <hyperlink ref="F100" r:id="rId30"/>
-    <hyperlink ref="F102" r:id="rId31"/>
-    <hyperlink ref="F109" r:id="rId32"/>
-    <hyperlink ref="F112" r:id="rId33"/>
-    <hyperlink ref="F116" r:id="rId34"/>
-    <hyperlink ref="F118" r:id="rId35"/>
-    <hyperlink ref="F119" r:id="rId36"/>
-    <hyperlink ref="F120" r:id="rId37"/>
-    <hyperlink ref="F121" r:id="rId38"/>
-    <hyperlink ref="F127" r:id="rId39"/>
-    <hyperlink ref="F129" r:id="rId40"/>
-    <hyperlink ref="F132" r:id="rId41"/>
+    <hyperlink ref="F24" r:id="rId10"/>
+    <hyperlink ref="F27" r:id="rId11"/>
+    <hyperlink ref="F31" r:id="rId12"/>
+    <hyperlink ref="F33" r:id="rId13"/>
+    <hyperlink ref="F37" r:id="rId14"/>
+    <hyperlink ref="F38" r:id="rId15"/>
+    <hyperlink ref="F39" r:id="rId16"/>
+    <hyperlink ref="F42" r:id="rId17"/>
+    <hyperlink ref="F43" r:id="rId18"/>
+    <hyperlink ref="F45" r:id="rId19"/>
+    <hyperlink ref="F46" r:id="rId20"/>
+    <hyperlink ref="F47" r:id="rId21"/>
+    <hyperlink ref="F50" r:id="rId22"/>
+    <hyperlink ref="F55" r:id="rId23"/>
+    <hyperlink ref="F59" r:id="rId24"/>
+    <hyperlink ref="F90" r:id="rId25"/>
+    <hyperlink ref="F92" r:id="rId26"/>
+    <hyperlink ref="F94" r:id="rId27"/>
+    <hyperlink ref="F98" r:id="rId28"/>
+    <hyperlink ref="F100" r:id="rId29"/>
+    <hyperlink ref="F101" r:id="rId30"/>
+    <hyperlink ref="F103" r:id="rId31"/>
+    <hyperlink ref="F110" r:id="rId32"/>
+    <hyperlink ref="F113" r:id="rId33"/>
+    <hyperlink ref="F117" r:id="rId34"/>
+    <hyperlink ref="F119" r:id="rId35"/>
+    <hyperlink ref="F120" r:id="rId36"/>
+    <hyperlink ref="F121" r:id="rId37"/>
+    <hyperlink ref="F122" r:id="rId38"/>
+    <hyperlink ref="F128" r:id="rId39"/>
+    <hyperlink ref="F130" r:id="rId40"/>
+    <hyperlink ref="F133" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4530,48 +4556,48 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -4583,24 +4609,24 @@
         <v>1571.58</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4612,24 +4638,24 @@
         <v>1470</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -4641,24 +4667,24 @@
         <v>3764.98</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -4670,24 +4696,24 @@
         <v>1071</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -4699,24 +4725,24 @@
         <v>3000</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -4728,7 +4754,7 @@
         <v>1000</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4745,7 +4771,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F8" s="16">
         <v>13</v>
@@ -4783,24 +4809,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B2" s="15">
         <v>11877.56</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4811,51 +4837,51 @@
         <v>1775</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B4" s="15">
         <v>1900</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B7" s="17">
         <v>18352.559999999998</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4880,237 +4906,237 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="D3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="D3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B14" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5121,7 +5147,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5158,16 +5184,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5178,16 +5204,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5195,16 +5221,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5212,16 +5238,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5229,16 +5255,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5246,16 +5272,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5263,16 +5289,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5280,16 +5306,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5297,16 +5323,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5314,16 +5340,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5331,16 +5357,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5348,16 +5374,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5365,16 +5391,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5382,16 +5408,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>417</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>415</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5399,16 +5425,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5416,16 +5442,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -5433,7 +5459,7 @@
         <v>48</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5441,10 +5467,10 @@
         <v>48</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5452,10 +5478,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -5497,158 +5523,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" s="7" t="s">
         <v>443</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="E3" t="s">
-        <v>445</v>
-      </c>
-      <c r="F3" t="s">
-        <v>439</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5662,7 +5688,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="463">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → Casa G. Firenze (Florence, Michelin Guide) → Il Castelfalfi (Tuscany, TUI Blue Selection) → De Bonart (Naples, Hilton Curio) → Anantara Convento (Amalfi, Minor / GHA) → The St. Regis Rome (Marriott Bonvoy)</t>
+    <t>Hotel Trame (Rome, independent) → Helvetia&amp;Bristol Firenze (Florence, Starhotels Collezione) → Il Castelfalfi (Tuscany, TUI Blue Selection) → De Bonart (Naples, Hilton Curio) → Anantara Convento (Amalfi, Minor / GHA) → The St. Regis Rome (Marriott Bonvoy)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -361,7 +361,7 @@
     <t>Thu, Aug 27</t>
   </si>
   <si>
-    <t>ROME → FLORENCE — Casa G. Firenze</t>
+    <t>ROME → FLORENCE — Helvetia&amp;Bristol Firenze</t>
   </si>
   <si>
     <t>TRAVEL DAY</t>
@@ -397,312 +397,312 @@
     <t>12:45pm</t>
   </si>
   <si>
-    <t>Drop bags at Casa G. Firenze — Via dei Rondinelli, between the Duomo and Santa Maria Novella. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
+    <t>Drop bags at Helvetia&amp;Bristol Firenze — Via Dei Pescioni 2, off Via de' Tornabuoni, in Santa Maria Novella. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
+  </si>
+  <si>
+    <t>1:15pm</t>
+  </si>
+  <si>
+    <t>Lunch at the Mercato Centrale — Five minutes north — the upstairs food hall, no booking, no ceremony</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>First orientation walk — The Duomo and Baptistery from the outside, then Piazza della Repubblica and down to the Arno. The ticketed interiors are all tomorrow — today is just getting your bearings.</t>
+  </si>
+  <si>
+    <t>Unpack and reset — The train bought you an afternoon the drive would have eaten</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at the hotel bar — A Belle Époque room to ease into Florence — no need to go anywhere</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, comfortably clear now the train lands you at midday.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>1:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, ~10 min on foot and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and Volterra</t>
+  </si>
+  <si>
+    <t>Driver to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>10:00am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion, right on Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>Lunch + a Vernaccia tasting — San Gimignano's own DOCG white, crisp and mineral, made for a hot afternoon</t>
+  </si>
+  <si>
+    <t>Driver to Volterra — About forty-five minutes</t>
+  </si>
+  <si>
+    <t>3:30pm</t>
+  </si>
+  <si>
+    <t>Piazza dei Priori and the Roman theatre — Tuscany's most complete medieval civic square, plus a 1st-century BC theatre still being excavated</t>
+  </si>
+  <si>
+    <t>Arrive Volterra</t>
+  </si>
+  <si>
+    <t>Alabaster workshops — A carving tradition here since Etruscan times — several studios welcome walk-ins</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Drive back to Castelfalfi — About fifty minutes</t>
+  </si>
+  <si>
+    <t>Dinner at the resort — Or a quieter table down in Montaione village</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY — Montespertoli wine day</t>
+  </si>
+  <si>
+    <t>The estate's 27-hole course, or the spa — Tuscany's largest golf course, or a morning at the newly renovated spa</t>
+  </si>
+  <si>
+    <t>12:00pm</t>
+  </si>
+  <si>
+    <t>Driver to Montespertoli — About forty minutes</t>
+  </si>
+  <si>
+    <t>A Chianti Montespertoli estate — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper</t>
+  </si>
+  <si>
+    <t>1:30pm</t>
+  </si>
+  <si>
+    <t>Lunch among the vines</t>
+  </si>
+  <si>
+    <t>At the estate</t>
+  </si>
+  <si>
+    <t>The village and a second cellar — Small enough to see on foot between tastings</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About forty minutes</t>
+  </si>
+  <si>
+    <t>The pool or the spa terrace at sunset</t>
+  </si>
+  <si>
+    <t>Dinner — Giglio Blu or La Via del Sale — Something casual, or a second night at the estate's fine-dining room</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>TUSCANY → NAPLES — return the car in Florence, then the train</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Check out; drive to Florence — Back the way you came — about ninety minutes, less traffic than the Friday-afternoon drive in</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti, near Firenze S.M.N. — reservation #21586310US4 ends here</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Coffee, then the platform — A buffer before the train — Frecciarossa 9413 doesn't wait</t>
+  </si>
+  <si>
+    <t>12:48pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9413 to Naples — Firenze S.M.N. → Napoli Centrale, direct — 3h15. Super Economy fare, from €71.80.</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>4:03pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale</t>
+  </si>
+  <si>
+    <t>4:30pm</t>
+  </si>
+  <si>
+    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay</t>
   </si>
   <si>
     <t>Trip.com -&gt;</t>
   </si>
   <si>
-    <t>1:15pm</t>
-  </si>
-  <si>
-    <t>Lunch at the Mercato Centrale — Five minutes north — the upstairs food hall, no booking, no ceremony</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>First orientation walk — The Duomo and Baptistery from the outside, then Piazza della Repubblica and down to the Arno. The ticketed interiors are all tomorrow — today is just getting your bearings.</t>
-  </si>
-  <si>
-    <t>Unpack and reset — The train bought you an afternoon the drive would have eaten</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo on the secret patio — Casa G.'s courtyard bar</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, comfortably clear now the train lands you at midday.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>1:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, ~10 min on foot and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and Volterra</t>
-  </si>
-  <si>
-    <t>Driver to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>10:00am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion, right on Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>Lunch + a Vernaccia tasting — San Gimignano's own DOCG white, crisp and mineral, made for a hot afternoon</t>
-  </si>
-  <si>
-    <t>Driver to Volterra — About forty-five minutes</t>
-  </si>
-  <si>
-    <t>3:30pm</t>
-  </si>
-  <si>
-    <t>Piazza dei Priori and the Roman theatre — Tuscany's most complete medieval civic square, plus a 1st-century BC theatre still being excavated</t>
-  </si>
-  <si>
-    <t>Arrive Volterra</t>
-  </si>
-  <si>
-    <t>Alabaster workshops — A carving tradition here since Etruscan times — several studios welcome walk-ins</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Drive back to Castelfalfi — About fifty minutes</t>
-  </si>
-  <si>
-    <t>Dinner at the resort — Or a quieter table down in Montaione village</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY — Montespertoli wine day</t>
-  </si>
-  <si>
-    <t>The estate's 27-hole course, or the spa — Tuscany's largest golf course, or a morning at the newly renovated spa</t>
-  </si>
-  <si>
-    <t>12:00pm</t>
-  </si>
-  <si>
-    <t>Driver to Montespertoli — About forty minutes</t>
-  </si>
-  <si>
-    <t>A Chianti Montespertoli estate — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper</t>
-  </si>
-  <si>
-    <t>1:30pm</t>
-  </si>
-  <si>
-    <t>Lunch among the vines</t>
-  </si>
-  <si>
-    <t>At the estate</t>
-  </si>
-  <si>
-    <t>The village and a second cellar — Small enough to see on foot between tastings</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About forty minutes</t>
-  </si>
-  <si>
-    <t>The pool or the spa terrace at sunset</t>
-  </si>
-  <si>
-    <t>Dinner — Giglio Blu or La Via del Sale — Something casual, or a second night at the estate's fine-dining room</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>TUSCANY → NAPLES — return the car in Florence, then the train</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Check out; drive to Florence — Back the way you came — about ninety minutes, less traffic than the Friday-afternoon drive in</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti, near Firenze S.M.N. — reservation #21586310US4 ends here</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Coffee, then the platform — A buffer before the train — Frecciarossa 9413 doesn't wait</t>
-  </si>
-  <si>
-    <t>12:48pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9413 to Naples — Firenze S.M.N. → Napoli Centrale, direct — 3h15. Super Economy fare, from €71.80.</t>
-  </si>
-  <si>
-    <t>Train</t>
-  </si>
-  <si>
-    <t>4:03pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale</t>
-  </si>
-  <si>
-    <t>4:30pm</t>
-  </si>
-  <si>
-    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay</t>
-  </si>
-  <si>
     <t>Rooftop aperitivo — Vesuvius on one side, the bay on the other</t>
   </si>
   <si>
@@ -949,10 +949,10 @@
     <t>Florence</t>
   </si>
   <si>
-    <t>Casa G. Firenze</t>
-  </si>
-  <si>
-    <t>Independent / Michelin Guide</t>
+    <t>Helvetia&amp;Bristol Firenze</t>
+  </si>
+  <si>
+    <t>Starhotels Collezione</t>
   </si>
   <si>
     <t>Tuscany</t>
@@ -1006,7 +1006,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>6 hotels, 13 nights. Trame ($1,571.58), Castelfalfi ($3,764.98) and De Bonart ($1,071, confirmed) are actual bookings; Convento is a quote, 2 nights rather than 3. The St. Regis is still an estimate.</t>
+    <t>6 hotels, 13 nights. Trame ($1,571.58), Helvetia&amp;Bristol ($1,486), Castelfalfi ($3,764.98) and De Bonart ($1,071) are confirmed bookings; Convento is a quote, 2 nights rather than 3. The St. Regis is still an estimate.</t>
   </si>
   <si>
     <t>Holding the old total pending a re-quote: the rental drops from 14 days to 3 (Florence Aug 29 → Florence Sep 1, both ends the same city now), but a one-way-turned-round-trip re-quote could move that either way. New costs: the FCO private transfer (~€70–90), two Frecciarossa fares, and private drivers for both Naples↔Amalfi legs. Rome and FCO parking are gone entirely.</t>
@@ -1189,31 +1189,25 @@
     <t>Urgency</t>
   </si>
   <si>
-    <t>Book Casa G. Firenze for Aug 27–29</t>
-  </si>
-  <si>
-    <t>Two nights in Florence, wedged between Rome and Tuscany — the tightest hotel window on the trip.</t>
+    <t>Reserve dinners at Il Castelfalfi — La Via del Sale, Aug 29 &amp; 31</t>
+  </si>
+  <si>
+    <t>The estate's fine-dining room. Worth booking ahead even though the room itself is already confirmed.</t>
+  </si>
+  <si>
+    <t>THIS WEEK</t>
+  </si>
+  <si>
+    <t>Open -&gt;</t>
+  </si>
+  <si>
+    <t>Rebook the rental car — Florence pickup and drop-off, not FCO</t>
+  </si>
+  <si>
+    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → Florence Sep 1: three days rather than fourteen, both ends in the same city. A different pickup/drop-off city usually carries a fee, so the €1,087.81 quote will not hold — re-quote before cancelling.</t>
   </si>
   <si>
     <t>DO NOW</t>
-  </si>
-  <si>
-    <t>Open -&gt;</t>
-  </si>
-  <si>
-    <t>Reserve dinners at Il Castelfalfi — La Via del Sale, Aug 29 &amp; 31</t>
-  </si>
-  <si>
-    <t>The estate's fine-dining room. Worth booking ahead even though the room itself is already confirmed.</t>
-  </si>
-  <si>
-    <t>THIS WEEK</t>
-  </si>
-  <si>
-    <t>Rebook the rental car — Florence pickup and drop-off, not FCO</t>
-  </si>
-  <si>
-    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → Florence Sep 1: three days rather than fourteen, both ends in the same city. A different pickup/drop-off city usually carries a fee, so the €1,087.81 quote will not hold — re-quote before cancelling.</t>
   </si>
   <si>
     <t>Book the FCO → Hotel Trame private driver</t>
@@ -1480,12 +1474,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF9E4529"/>
+      <color rgb="FF8A6D1F"/>
       <sz val="9"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF8A6D1F"/>
+      <color rgb="FF9E4529"/>
       <sz val="9"/>
     </font>
     <font>
@@ -2666,7 +2660,7 @@
         <v>57</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2677,13 +2671,13 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>130</v>
       </c>
       <c r="F34" t="s">
         <v>48</v>
@@ -2697,10 +2691,10 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>60</v>
@@ -2720,7 +2714,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>63</v>
@@ -2737,16 +2731,16 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>127</v>
+      <c r="F37" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2757,13 +2751,13 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" s="13" t="s">
         <v>137</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>77</v>
@@ -2777,10 +2771,10 @@
         <v>48</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>112</v>
@@ -2794,10 +2788,10 @@
         <v>5</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2808,13 +2802,13 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="E42" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>77</v>
@@ -2831,10 +2825,10 @@
         <v>116</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>146</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>77</v>
@@ -2848,13 +2842,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="E44" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2868,13 +2862,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="13" t="s">
         <v>150</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>151</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>77</v>
@@ -2888,13 +2882,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>154</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>71</v>
@@ -2908,13 +2902,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="E47" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>77</v>
@@ -2931,7 +2925,7 @@
         <v>84</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>88</v>
@@ -2948,13 +2942,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="13" t="s">
         <v>159</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
@@ -2971,10 +2965,10 @@
         <v>89</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>162</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>71</v>
@@ -2985,10 +2979,10 @@
         <v>6</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="F52" s="14" t="s">
         <v>115</v>
@@ -3002,13 +2996,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="E53" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3022,13 +3016,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="13" t="s">
         <v>168</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>169</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3042,13 +3036,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="13" t="s">
         <v>171</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>172</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>104</v>
@@ -3062,10 +3056,10 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>88</v>
@@ -3085,7 +3079,7 @@
         <v>78</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>88</v>
@@ -3105,10 +3099,10 @@
         <v>81</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>177</v>
       </c>
       <c r="F58" t="s">
         <v>48</v>
@@ -3125,13 +3119,13 @@
         <v>58</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3145,7 +3139,7 @@
         <v>84</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>60</v>
@@ -3162,10 +3156,10 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>63</v>
@@ -3185,7 +3179,7 @@
         <v>89</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>63</v>
@@ -3199,10 +3193,10 @@
         <v>7</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="11" t="s">
         <v>184</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3216,10 +3210,10 @@
         <v>116</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F65" t="s">
         <v>48</v>
@@ -3233,10 +3227,10 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>57</v>
@@ -3253,10 +3247,10 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>88</v>
@@ -3273,10 +3267,10 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="E68" s="13" t="s">
         <v>88</v>
@@ -3296,7 +3290,7 @@
         <v>78</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>88</v>
@@ -3316,10 +3310,10 @@
         <v>81</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -3333,13 +3327,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3356,7 +3350,7 @@
         <v>84</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>88</v>
@@ -3373,13 +3367,13 @@
         <v>48</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="E73" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F73" t="s">
         <v>48</v>
@@ -3396,7 +3390,7 @@
         <v>89</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E74" s="13" t="s">
         <v>63</v>
@@ -3410,10 +3404,10 @@
         <v>8</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" s="11" t="s">
         <v>201</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3424,10 +3418,10 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>63</v>
@@ -3444,13 +3438,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="E78" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3464,10 +3458,10 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>57</v>
@@ -3484,13 +3478,13 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>209</v>
       </c>
       <c r="F80" t="s">
         <v>48</v>
@@ -3504,10 +3498,10 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E81" s="13" t="s">
         <v>88</v>
@@ -3527,10 +3521,10 @@
         <v>105</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F82" t="s">
         <v>48</v>
@@ -3544,10 +3538,10 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>63</v>
@@ -3567,7 +3561,7 @@
         <v>89</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>63</v>
@@ -3581,10 +3575,10 @@
         <v>9</v>
       </c>
       <c r="B86" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C86" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>215</v>
       </c>
       <c r="F86" s="14" t="s">
         <v>115</v>
@@ -3598,13 +3592,13 @@
         <v>48</v>
       </c>
       <c r="C87" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>217</v>
-      </c>
       <c r="E87" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F87" t="s">
         <v>48</v>
@@ -3618,13 +3612,13 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D88" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E88" s="13" t="s">
         <v>218</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>219</v>
       </c>
       <c r="F88" t="s">
         <v>48</v>
@@ -3638,10 +3632,10 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E89" s="13" t="s">
         <v>88</v>
@@ -3658,13 +3652,13 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="13" t="s">
         <v>222</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>223</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>121</v>
@@ -3678,10 +3672,10 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>57</v>
@@ -3698,16 +3692,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="E92" s="13" t="s">
         <v>76</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,7 +3712,7 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>228</v>
@@ -3769,7 +3763,7 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>232</v>
@@ -3809,7 +3803,7 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>238</v>
@@ -3849,7 +3843,7 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>242</v>
@@ -3923,13 +3917,13 @@
         <v>48</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F106" t="s">
         <v>48</v>
@@ -3963,7 +3957,7 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>249</v>
@@ -3983,7 +3977,7 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>250</v>
@@ -4003,7 +3997,7 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>252</v>
@@ -4012,7 +4006,7 @@
         <v>57</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,7 +4088,7 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>260</v>
@@ -4114,7 +4108,7 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>261</v>
@@ -4174,7 +4168,7 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>268</v>
@@ -4248,7 +4242,7 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>277</v>
@@ -4288,7 +4282,7 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>280</v>
@@ -4314,7 +4308,7 @@
         <v>281</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>121</v>
@@ -4348,7 +4342,7 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>283</v>
@@ -4357,7 +4351,7 @@
         <v>57</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4506,34 +4500,33 @@
     <hyperlink ref="F27" r:id="rId11"/>
     <hyperlink ref="F31" r:id="rId12"/>
     <hyperlink ref="F33" r:id="rId13"/>
-    <hyperlink ref="F37" r:id="rId14"/>
-    <hyperlink ref="F38" r:id="rId15"/>
-    <hyperlink ref="F39" r:id="rId16"/>
-    <hyperlink ref="F42" r:id="rId17"/>
-    <hyperlink ref="F43" r:id="rId18"/>
-    <hyperlink ref="F45" r:id="rId19"/>
-    <hyperlink ref="F46" r:id="rId20"/>
-    <hyperlink ref="F47" r:id="rId21"/>
-    <hyperlink ref="F50" r:id="rId22"/>
-    <hyperlink ref="F55" r:id="rId23"/>
-    <hyperlink ref="F59" r:id="rId24"/>
-    <hyperlink ref="F90" r:id="rId25"/>
-    <hyperlink ref="F92" r:id="rId26"/>
-    <hyperlink ref="F94" r:id="rId27"/>
-    <hyperlink ref="F98" r:id="rId28"/>
-    <hyperlink ref="F100" r:id="rId29"/>
-    <hyperlink ref="F101" r:id="rId30"/>
-    <hyperlink ref="F103" r:id="rId31"/>
-    <hyperlink ref="F110" r:id="rId32"/>
-    <hyperlink ref="F113" r:id="rId33"/>
-    <hyperlink ref="F117" r:id="rId34"/>
-    <hyperlink ref="F119" r:id="rId35"/>
-    <hyperlink ref="F120" r:id="rId36"/>
-    <hyperlink ref="F121" r:id="rId37"/>
-    <hyperlink ref="F122" r:id="rId38"/>
-    <hyperlink ref="F128" r:id="rId39"/>
-    <hyperlink ref="F130" r:id="rId40"/>
-    <hyperlink ref="F133" r:id="rId41"/>
+    <hyperlink ref="F38" r:id="rId14"/>
+    <hyperlink ref="F39" r:id="rId15"/>
+    <hyperlink ref="F42" r:id="rId16"/>
+    <hyperlink ref="F43" r:id="rId17"/>
+    <hyperlink ref="F45" r:id="rId18"/>
+    <hyperlink ref="F46" r:id="rId19"/>
+    <hyperlink ref="F47" r:id="rId20"/>
+    <hyperlink ref="F50" r:id="rId21"/>
+    <hyperlink ref="F55" r:id="rId22"/>
+    <hyperlink ref="F59" r:id="rId23"/>
+    <hyperlink ref="F90" r:id="rId24"/>
+    <hyperlink ref="F92" r:id="rId25"/>
+    <hyperlink ref="F94" r:id="rId26"/>
+    <hyperlink ref="F98" r:id="rId27"/>
+    <hyperlink ref="F100" r:id="rId28"/>
+    <hyperlink ref="F101" r:id="rId29"/>
+    <hyperlink ref="F103" r:id="rId30"/>
+    <hyperlink ref="F110" r:id="rId31"/>
+    <hyperlink ref="F113" r:id="rId32"/>
+    <hyperlink ref="F117" r:id="rId33"/>
+    <hyperlink ref="F119" r:id="rId34"/>
+    <hyperlink ref="F120" r:id="rId35"/>
+    <hyperlink ref="F121" r:id="rId36"/>
+    <hyperlink ref="F122" r:id="rId37"/>
+    <hyperlink ref="F128" r:id="rId38"/>
+    <hyperlink ref="F130" r:id="rId39"/>
+    <hyperlink ref="F133" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4609,7 +4602,7 @@
         <v>1571.58</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -4626,19 +4619,19 @@
         <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" s="15">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="H3" s="15">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4652,10 +4645,10 @@
         <v>314</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -4667,7 +4660,7 @@
         <v>3764.98</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4681,7 +4674,7 @@
         <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E5" t="s">
         <v>245</v>
@@ -4696,7 +4689,7 @@
         <v>1071</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4725,7 +4718,7 @@
         <v>3000</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4754,7 +4747,7 @@
         <v>1000</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4780,7 +4773,7 @@
         <v>48</v>
       </c>
       <c r="H8" s="17">
-        <v>11877.56</v>
+        <v>11893.56</v>
       </c>
     </row>
   </sheetData>
@@ -4823,7 +4816,7 @@
         <v>328</v>
       </c>
       <c r="B2" s="15">
-        <v>11877.56</v>
+        <v>11893.56</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>329</v>
@@ -4878,7 +4871,7 @@
         <v>324</v>
       </c>
       <c r="B7" s="17">
-        <v>18352.559999999998</v>
+        <v>18368.559999999998</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>337</v>
@@ -4974,7 +4967,7 @@
         <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>353</v>
@@ -5110,7 +5103,7 @@
         <v>377</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>380</v>
@@ -5173,7 +5166,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5243,8 +5236,8 @@
       <c r="C4" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>392</v>
+      <c r="D4" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>393</v>
@@ -5260,8 +5253,8 @@
       <c r="C5" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>392</v>
+      <c r="D5" s="20" t="s">
+        <v>396</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>393</v>
@@ -5294,8 +5287,8 @@
       <c r="C7" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>396</v>
+      <c r="D7" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>393</v>
@@ -5311,8 +5304,8 @@
       <c r="C8" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>396</v>
+      <c r="D8" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>393</v>
@@ -5328,8 +5321,8 @@
       <c r="C9" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>396</v>
+      <c r="D9" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>393</v>
@@ -5345,8 +5338,8 @@
       <c r="C10" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>396</v>
+      <c r="D10" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>393</v>
@@ -5362,8 +5355,8 @@
       <c r="C11" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>396</v>
+      <c r="D11" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>393</v>
@@ -5379,8 +5372,8 @@
       <c r="C12" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="D12" s="20" t="s">
-        <v>396</v>
+      <c r="D12" s="21" t="s">
+        <v>415</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>393</v>
@@ -5391,13 +5384,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>415</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>417</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>393</v>
@@ -5414,7 +5407,7 @@
         <v>419</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>393</v>
@@ -5431,34 +5424,28 @@
         <v>421</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>422</v>
       </c>
-      <c r="C16" s="4" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="C18" s="2" t="s">
         <v>424</v>
       </c>
     </row>
@@ -5471,17 +5458,6 @@
       </c>
       <c r="C19" s="2" t="s">
         <v>426</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -5500,7 +5476,6 @@
     <hyperlink ref="E13" r:id="rId12"/>
     <hyperlink ref="E14" r:id="rId13"/>
     <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5523,28 +5498,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>434</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5552,25 +5527,25 @@
         <v>306</v>
       </c>
       <c r="B2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>438</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" t="s">
         <v>439</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5578,51 +5553,51 @@
         <v>309</v>
       </c>
       <c r="B3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>445</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="E3" t="s">
-        <v>447</v>
-      </c>
       <c r="F3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" t="s">
         <v>448</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>450</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" t="s">
         <v>451</v>
       </c>
-      <c r="E4" t="s">
-        <v>452</v>
-      </c>
-      <c r="F4" t="s">
-        <v>453</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -5630,51 +5605,51 @@
         <v>318</v>
       </c>
       <c r="B5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>455</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" t="s">
         <v>456</v>
       </c>
-      <c r="E5" t="s">
-        <v>457</v>
-      </c>
-      <c r="F5" t="s">
-        <v>458</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" t="s">
         <v>459</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>461</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="E6" t="s">
-        <v>463</v>
-      </c>
       <c r="F6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5688,7 +5663,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="469">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
   <si>
-    <t>Updated Mon, Jul 27</t>
+    <t>Updated Fri, Jul 31</t>
   </si>
   <si>
     <t>Travelers</t>
@@ -52,19 +52,19 @@
     <t>Route</t>
   </si>
   <si>
-    <t>Rome (3) → Florence (2) → Tuscany (3) → Naples (2) → Amalfi (2) → Rome finale (1)</t>
+    <t>Rome (3) → Naples (2) → Amalfi (2) → Florence (3) → Tuscany (2) → Rome finale (1)</t>
   </si>
   <si>
     <t>Transport</t>
   </si>
   <si>
-    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive Florence–Tuscany only (Aug 29 – Sep 1) · rail + private drivers from Naples on, IDP in hand</t>
+    <t>Private driver in from FCO · Frecciarossa to Naples · ferry to Capri and on to Amalfi via Positano · driver to Salerno, Frecciarossa to Florence · self-drive Florence–Tuscany only (Sep 3–5) · Frecciarossa back to Rome</t>
   </si>
   <si>
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → Helvetia&amp;Bristol Firenze (Florence, Starhotels Collezione) → Il Castelfalfi (Tuscany, TUI Blue Selection) → De Bonart (Naples, Hilton Curio) → Anantara Convento (Amalfi, Minor / GHA) → The St. Regis Rome (Marriott Bonvoy)</t>
+    <t>Hotel Trame (Rome, independent) → Grand Hotel Vesuvio (Naples, Leading Hotels of the World) → Anantara Convento (Amalfi, Minor / GHA) → The Hoxton Florence (independent) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Nobu Hotel Roma (Rome, Nobu Hospitality)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -361,598 +361,619 @@
     <t>Thu, Aug 27</t>
   </si>
   <si>
-    <t>ROME → FLORENCE — Helvetia&amp;Bristol Firenze</t>
+    <t>ROME → NAPLES — direct by Frecciarossa</t>
   </si>
   <si>
     <t>TRAVEL DAY</t>
   </si>
   <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Naples — Roma Termini → Napoli Centrale, direct — about 1h10. Trains run roughly every half hour; no need to book far ahead.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1h10</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Drop bags — Grand Hotel Vesuvio — Via Partenope, facing Castel dell'Ovo and the bay. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>Spaccanapoli and the old city — The dead-straight Greek road that still splits Naples in half — pizza fritta and sfogliatelle along the way</t>
+  </si>
+  <si>
+    <t>Check in and reset</t>
+  </si>
+  <si>
+    <t>Aperitivo — Sky Lounge — The hotel's rooftop bar, one floor below dinner</t>
+  </si>
+  <si>
+    <t>Dinner — Caruso Roof Garden — Ninth floor, Michelin-starred, named for Enrico Caruso, who called this hotel his Neapolitan home. Reservations open only 14 days out — call as soon as the window opens. The Bucatini alla Caruso is the dish to order.</t>
+  </si>
+  <si>
+    <t>Caruso -&gt;</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>NAPLES — Capri day trip</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Walk down to Molo Beverello — The fast-ferry pier is fifteen minutes along the seafront from the hotel</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>9:20am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Naples → Capri — NLG, SNAV and Caremar all run it in about fifty minutes. Sailings are frequent in summer but sell out at the counter — book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~50 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>The Faraglioni, the grottoes, the swim coves — Pick up a round-the-island boat at Marina Grande — Blue Grotto if the sea is calm enough to enter</t>
+  </si>
+  <si>
+    <t>Local boat from Marina Grande</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Marina Grande, then the funicular</t>
+  </si>
+  <si>
+    <t>3:30pm</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
+  </si>
+  <si>
+    <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
+  </si>
+  <si>
+    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu, back in the old city — the celebration dinner for the boat day</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>NAPLES → AMALFI — ferry via Positano</t>
+  </si>
+  <si>
+    <t>Check out — Grand Hotel Vesuvio</t>
+  </si>
+  <si>
+    <t>Walk to Molo Beverello — Fifteen minutes along the seafront</t>
+  </si>
+  <si>
     <t>9:30am</t>
   </si>
   <si>
-    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori. Aim to be at the platform twenty minutes before departure.</t>
-  </si>
-  <si>
-    <t>10:35am</t>
-  </si>
-  <si>
-    <t>Frecciarossa — Roma Termini → Firenze S.M.N. — Book Trenitalia or Italo well ahead; advance fares are a fraction of the walk-up price and both run the route hourly.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1h30</t>
-  </si>
-  <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>12:10pm</t>
-  </si>
-  <si>
-    <t>Arrive Firenze Santa Maria Novella — The station is a nine-minute walk from Via dei Rondinelli — no transfer needed</t>
-  </si>
-  <si>
-    <t>Walk, ~9 min</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Drop bags at Helvetia&amp;Bristol Firenze — Via Dei Pescioni 2, off Via de' Tornabuoni, in Santa Maria Novella. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
+    <t>Ferry to Positano and Amalfi — Positano Jet and a couple of other operators run this seasonal route — book the Amalfi-bound leg specifically, not just the Positano hop.</t>
+  </si>
+  <si>
+    <t>Ferry, ~2.5 hrs total</t>
+  </si>
+  <si>
+    <t>Positano Jet -&gt;</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Positano from the water — The pastel stairs climbing straight up from the sea — the best view of the town is from the boat, not the beach</t>
+  </si>
+  <si>
+    <t>By ferry</t>
+  </si>
+  <si>
+    <t>11:45am</t>
+  </si>
+  <si>
+    <t>Arrive Amalfi marina; lunch nearby — A table just off Piazza Duomo before checking in</t>
+  </si>
+  <si>
+    <t>1:30pm</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the old town — The striped façade of Sant'Andrea and the Cloister of Paradise, then the lemon-lined lanes behind the piazza</t>
+  </si>
+  <si>
+    <t>Check in — Anantara Convento di Amalfi — Deluxe Sea View Room. A 13th-century monastery on the cliff edge, with the original cloister still standing.</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo in the cloister</t>
+  </si>
+  <si>
+    <t>Dinner — Dei Cappuccini — The hotel's Michelin room, or La Locanda for pizza if the day has beaten you</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>AMALFI — Nerano lunch and Ravello</t>
+  </si>
+  <si>
+    <t>The beach club, by cliff lift — A slow morning at sea level before the day starts properly</t>
+  </si>
+  <si>
+    <t>Hotel cliff lift</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Lunch — Lo Scoglio — Nerano. The original spaghetti alla Nerano, and worth the boat ride on its own.</t>
+  </si>
+  <si>
+    <t>Hotel car or boat, ~40 min</t>
+  </si>
+  <si>
+    <t>Up to Ravello — Forty-five minutes of switchbacks above the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>3:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Aperitivo, then Villa Rufolo's gardens</t>
+  </si>
+  <si>
+    <t>RAVELLO FESTIVAL — check the Aug 30 programme — Confirmed concerts run to Sep 5 — check what's actually on tonight before you commit to a table instead</t>
+  </si>
+  <si>
+    <t>Walk to Villa Rufolo</t>
+  </si>
+  <si>
+    <t>Programme -&gt;</t>
+  </si>
+  <si>
+    <t>9:30pm</t>
+  </si>
+  <si>
+    <t>Late dinner — Il Flauto di Pan — In the Villa Cimbrone gardens. Rossellinis is the other option.</t>
+  </si>
+  <si>
+    <t>Walk; drive down after</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>AMALFI → FLORENCE — driver to Salerno, then Frecciarossa</t>
+  </si>
+  <si>
+    <t>12:00pm</t>
+  </si>
+  <si>
+    <t>Check out — Anantara Convento — Checkout is exactly noon here</t>
+  </si>
+  <si>
+    <t>12:15pm</t>
+  </si>
+  <si>
+    <t>Private driver to Salerno — Along the coast road via Vietri, then a short stretch of highway — about an hour</t>
+  </si>
+  <si>
+    <t>Private driver, ~1 hr</t>
   </si>
   <si>
     <t>1:15pm</t>
   </si>
   <si>
-    <t>Lunch at the Mercato Centrale — Five minutes north — the upstairs food hall, no booking, no ceremony</t>
+    <t>Arrive Salerno station; lunch on the concourse</t>
+  </si>
+  <si>
+    <t>2:22pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Florence — Salerno → Firenze S.M.N., direct via Naples and Rome — about 3.5 hours. Ten-plus direct departures a day; book ahead for a better fare.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~3.5 hrs</t>
+  </si>
+  <si>
+    <t>5:50pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze S.M.N.</t>
+  </si>
+  <si>
+    <t>Check in — The Hoxton Florence — Via delle Mantellate, on the quieter west side near the river</t>
+  </si>
+  <si>
+    <t>Walk or taxi, ~12 min</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>Dinner near the hotel — Something easy after a long travel day — Borgo Ognissanti has plenty of options</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
   </si>
   <si>
     <t>Walk, ~5 min</t>
   </si>
   <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>1:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>FLORENCE — hills in the morning, Santa Croce after</t>
+  </si>
+  <si>
+    <t>Bus to Fiesole — ATAF #7 from Piazza San Marco, about twenty minutes up into the hills</t>
+  </si>
+  <si>
+    <t>Bus, ~20 min</t>
+  </si>
+  <si>
+    <t>The Roman theatre and Etruscan walls — Still-standing tiers of a 1st-century BC theatre, with the whole Arno valley behind it</t>
+  </si>
+  <si>
+    <t>Coffee on the terrace — The view back over Florence, with Brunelleschi's dome on the skyline</t>
+  </si>
+  <si>
+    <t>Bus back down to Florence</t>
+  </si>
+  <si>
+    <t>Lunch — San Lorenzo Market — The upstairs food hall, casual, no booking</t>
+  </si>
+  <si>
+    <t>San Lorenzo — the Medici Chapels — Michelangelo's New Sacristy, a short walk from the market stalls</t>
+  </si>
+  <si>
+    <t>Santa Croce — Michelangelo, Galileo and Machiavelli are all buried here; the Pazzi Chapel is Brunelleschi at his plainest and best</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change</t>
+  </si>
+  <si>
+    <t>Walk or taxi</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, a ten-minute walk from the Hoxton and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a Chianti Montespertoli estate</t>
+  </si>
+  <si>
+    <t>Driver to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli, then lunch and a Vernaccia tasting — A two-time world gelato champion on Piazza della Cisterna, then San Gimignano's own DOCG white with lunch</t>
+  </si>
+  <si>
+    <t>Driver to a Montespertoli estate — About forty minutes across the Val d'Elsa</t>
+  </si>
+  <si>
     <t>2:45pm</t>
   </si>
   <si>
-    <t>First orientation walk — The Duomo and Baptistery from the outside, then Piazza della Repubblica and down to the Arno. The ticketed interiors are all tomorrow — today is just getting your bearings.</t>
-  </si>
-  <si>
-    <t>Unpack and reset — The train bought you an afternoon the drive would have eaten</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at the hotel bar — A Belle Époque room to ease into Florence — no need to go anywhere</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita — booked for arrival evening, comfortably clear now the train lands you at midday.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>1:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, ~10 min on foot and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and Volterra</t>
-  </si>
-  <si>
-    <t>Driver to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>10:00am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion, right on Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>Lunch + a Vernaccia tasting — San Gimignano's own DOCG white, crisp and mineral, made for a hot afternoon</t>
-  </si>
-  <si>
-    <t>Driver to Volterra — About forty-five minutes</t>
-  </si>
-  <si>
-    <t>3:30pm</t>
-  </si>
-  <si>
-    <t>Piazza dei Priori and the Roman theatre — Tuscany's most complete medieval civic square, plus a 1st-century BC theatre still being excavated</t>
-  </si>
-  <si>
-    <t>Arrive Volterra</t>
-  </si>
-  <si>
-    <t>Alabaster workshops — A carving tradition here since Etruscan times — several studios welcome walk-ins</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Drive back to Castelfalfi — About fifty minutes</t>
-  </si>
-  <si>
-    <t>Dinner at the resort — Or a quieter table down in Montaione village</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY — Montespertoli wine day</t>
-  </si>
-  <si>
-    <t>The estate's 27-hole course, or the spa — Tuscany's largest golf course, or a morning at the newly renovated spa</t>
-  </si>
-  <si>
-    <t>12:00pm</t>
-  </si>
-  <si>
-    <t>Driver to Montespertoli — About forty minutes</t>
-  </si>
-  <si>
-    <t>A Chianti Montespertoli estate — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper</t>
-  </si>
-  <si>
-    <t>1:30pm</t>
-  </si>
-  <si>
-    <t>Lunch among the vines</t>
-  </si>
-  <si>
-    <t>At the estate</t>
-  </si>
-  <si>
-    <t>The village and a second cellar — Small enough to see on foot between tastings</t>
+    <t>A Chianti Montespertoli cellar — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper. Small enough to see the village on foot between tastings.</t>
   </si>
   <si>
     <t>Back to Castelfalfi — About forty minutes</t>
   </si>
   <si>
-    <t>The pool or the spa terrace at sunset</t>
-  </si>
-  <si>
-    <t>Dinner — Giglio Blu or La Via del Sale — Something casual, or a second night at the estate's fine-dining room</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>TUSCANY → NAPLES — return the car in Florence, then the train</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Check out; drive to Florence — Back the way you came — about ninety minutes, less traffic than the Friday-afternoon drive in</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti, near Firenze S.M.N. — reservation #21586310US4 ends here</t>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>TUSCANY → FLORENCE → ROME — drop the car, then the train</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Thursday's route</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — reservation #21586310US4 ends here</t>
   </si>
   <si>
     <t>Rental desk</t>
   </si>
   <si>
-    <t>Coffee, then the platform — A buffer before the train — Frecciarossa 9413 doesn't wait</t>
-  </si>
-  <si>
-    <t>12:48pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9413 to Naples — Firenze S.M.N. → Napoli Centrale, direct — 3h15. Super Economy fare, from €71.80.</t>
-  </si>
-  <si>
-    <t>Train</t>
-  </si>
-  <si>
-    <t>4:03pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale</t>
-  </si>
-  <si>
-    <t>4:30pm</t>
-  </si>
-  <si>
-    <t>Check in — De Bonart, Curio Collection — An art palazzo on Via Partenope in Chiaia, facing the bay</t>
+    <t>Coffee, then the platform</t>
+  </si>
+  <si>
+    <t>12:03pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Rome — Firenze S.M.N. → Roma Termini, direct — about 1.5 hours</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1.5 hrs</t>
+  </si>
+  <si>
+    <t>Arrive Roma Termini; taxi to the hotel</t>
+  </si>
+  <si>
+    <t>Check in — Nobu Hotel Roma — Via Vittorio Veneto, at the top of the street by Villa Borghese — five minutes from Wednesday's photo spot</t>
+  </si>
+  <si>
+    <t>Last Roman afternoon — Via Veneto and the Spanish Steps — La Dolce Vita's old strip, then down to Piazza di Spagna</t>
+  </si>
+  <si>
+    <t>Aperitivo at the hotel</t>
+  </si>
+  <si>
+    <t>Farewell dinner — Nobu Roma — The hotel's namesake restaurant, for the last night</t>
+  </si>
+  <si>
+    <t>Nobu Roma -&gt;</t>
+  </si>
+  <si>
+    <t>Sun, Sep 6</t>
+  </si>
+  <si>
+    <t>DEPART — FCO → IAH</t>
+  </si>
+  <si>
+    <t>6:40am</t>
+  </si>
+  <si>
+    <t>Taxi to FCO — About forty minutes on an empty Sunday road. No rental to return this time — that ended in Florence on Sep 5.</t>
+  </si>
+  <si>
+    <t>7:20am</t>
+  </si>
+  <si>
+    <t>Check in and bag drop — Three hours ahead for an intercontinental departure</t>
+  </si>
+  <si>
+    <t>At FCO</t>
+  </si>
+  <si>
+    <t>10:20am</t>
+  </si>
+  <si>
+    <t>FCO → IAH — Arrivederci, Italia.</t>
+  </si>
+  <si>
+    <t>Depart by air</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>Brand / Program</t>
+  </si>
+  <si>
+    <t>Check-in</t>
+  </si>
+  <si>
+    <t>Check-out</t>
+  </si>
+  <si>
+    <t>Nights</t>
+  </si>
+  <si>
+    <t>Est. nightly (USD)</t>
+  </si>
+  <si>
+    <t>Est. total (USD)</t>
+  </si>
+  <si>
+    <t>Book (Trip.com)</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>Hotel Trame</t>
+  </si>
+  <si>
+    <t>Independent boutique</t>
   </si>
   <si>
     <t>Trip.com -&gt;</t>
   </si>
   <si>
-    <t>Rooftop aperitivo — Vesuvius on one side, the bay on the other</t>
-  </si>
-  <si>
-    <t>Dinner — pizza at Sorbillo — Via dei Tribunali. You are in the city that invented it; do this before anything fancier.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>NAPLES — Capri day trip</t>
-  </si>
-  <si>
-    <t>Walk down to Molo Beverello — The fast-ferry pier is fifteen minutes along the seafront from the hotel</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
-    <t>9:20am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Naples → Capri — NLG, SNAV and Caremar all run it in about fifty minutes. Sailings are frequent in September but sell out at the counter — book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~50 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>The Faraglioni, the grottoes, the swim coves — Pick up a round-the-island boat at Marina Grande — Blue Grotto if the sea is calm enough to enter</t>
-  </si>
-  <si>
-    <t>Local boat from Marina Grande</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Marina Grande, then the funicular</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
-  </si>
-  <si>
-    <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
-  </si>
-  <si>
-    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu, back in the old city — the celebration dinner for the boat day</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>NAPLES → AMALFI — private driver</t>
-  </si>
-  <si>
-    <t>Pizza for breakfast — Di Matteo — Also on Via dei Tribunali, a few doors from last night's Sorbillo. Yes, at 8:30am. It's Naples.</t>
-  </si>
-  <si>
-    <t>Spaccanapoli — The dead-straight Greek road that still splits the old city in half</t>
-  </si>
-  <si>
-    <t>Check out; last look at the bay</t>
-  </si>
-  <si>
-    <t>Private driver to Amalfi — Coast road via Vietri — narrow, slow, spectacular. Sit back, someone else is driving.</t>
-  </si>
-  <si>
-    <t>Private driver, ~1.5–2 hrs</t>
-  </si>
-  <si>
-    <t>Check in — Anantara Convento di Amalfi — A 13th-century monastery on the cliff edge, with the original cloister still standing</t>
-  </si>
-  <si>
-    <t>The beach club, by cliff lift — A slow afternoon at sea level after the drive</t>
-  </si>
-  <si>
-    <t>Hotel cliff lift</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo in the cloister</t>
-  </si>
-  <si>
-    <t>Dinner — Dei Cappuccini — The hotel's Michelin room, or La Locanda for pizza if the day has beaten you</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>AMALFI — Nerano lunch and Ravello</t>
-  </si>
-  <si>
-    <t>A slow morning on the cloister terrace — The one unhurried morning on the coast — use it</t>
-  </si>
-  <si>
-    <t>Lunch — Lo Scoglio — Nerano. The original spaghetti alla Nerano, and worth the boat ride on its own.</t>
-  </si>
-  <si>
-    <t>Hotel car or boat, ~40 min</t>
-  </si>
-  <si>
-    <t>Up to Ravello — Forty-five minutes of switchbacks above the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>3:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>Aperitivo, then Villa Rufolo's gardens</t>
-  </si>
-  <si>
-    <t>RAVELLO FESTIVAL — check the Sep 4 programme — Confirmed concerts run to Sep 5, so both your Amalfi nights are inside the festival window.</t>
-  </si>
-  <si>
-    <t>Walk to Villa Rufolo</t>
-  </si>
-  <si>
-    <t>Programme -&gt;</t>
-  </si>
-  <si>
-    <t>9:30pm</t>
-  </si>
-  <si>
-    <t>Late dinner — Il Flauto di Pan — In the Villa Cimbrone gardens. Rossellinis is the other option.</t>
-  </si>
-  <si>
-    <t>Walk; drive down after</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>AMALFI → NAPLES → ROME — driver, then train</t>
-  </si>
-  <si>
-    <t>Check out; last look at the coast — Breakfast on the cloister terrace before you give the room back</t>
-  </si>
-  <si>
-    <t>Private driver to Naples — Back along the coast road to Napoli Centrale</t>
-  </si>
-  <si>
-    <t>Private driver, ~1.5 hrs</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale; drop bags, coffee</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Rome — Napoli Centrale → Roma Termini, direct — about 1h10. Frequent departures; no need to book far ahead.</t>
-  </si>
-  <si>
-    <t>Arrive Roma Termini; taxi to the hotel</t>
-  </si>
-  <si>
-    <t>Check in — The St. Regis Rome — The hotel is inside Rome's ZTL — use valet or a garage nearby; don't try to park at the curb.</t>
-  </si>
-  <si>
-    <t>Last Roman afternoon — Piazza di Spagna and the windows along Via Condotti</t>
-  </si>
-  <si>
-    <t>Aperitivo at Lumen — The St. Regis bar — the grand-hotel version of a last night</t>
-  </si>
-  <si>
-    <t>Farewell dinner — Aroma — A rooftop table level with the top tier of the Colosseum. Imago is the alternative, over the Spanish Steps.</t>
-  </si>
-  <si>
-    <t>Sun, Sep 6</t>
-  </si>
-  <si>
-    <t>DEPART — FCO → IAH</t>
-  </si>
-  <si>
-    <t>6:40am</t>
-  </si>
-  <si>
-    <t>Taxi to FCO — About forty minutes on an empty Sunday road. No rental to return this time — that ended in Florence on Sep 1.</t>
-  </si>
-  <si>
-    <t>7:20am</t>
-  </si>
-  <si>
-    <t>Check in and bag drop — Three hours ahead for an intercontinental departure</t>
-  </si>
-  <si>
-    <t>At FCO</t>
-  </si>
-  <si>
-    <t>10:20am</t>
-  </si>
-  <si>
-    <t>FCO → IAH — Arrivederci, Italia.</t>
-  </si>
-  <si>
-    <t>Depart by air</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>Brand / Program</t>
-  </si>
-  <si>
-    <t>Check-in</t>
-  </si>
-  <si>
-    <t>Check-out</t>
-  </si>
-  <si>
-    <t>Nights</t>
-  </si>
-  <si>
-    <t>Est. nightly (USD)</t>
-  </si>
-  <si>
-    <t>Est. total (USD)</t>
-  </si>
-  <si>
-    <t>Book (Trip.com)</t>
-  </si>
-  <si>
-    <t>Rome</t>
-  </si>
-  <si>
-    <t>Hotel Trame</t>
-  </si>
-  <si>
-    <t>Independent boutique</t>
+    <t>Naples</t>
+  </si>
+  <si>
+    <t>Grand Hotel Vesuvio</t>
+  </si>
+  <si>
+    <t>Leading Hotels of the World</t>
+  </si>
+  <si>
+    <t>Amalfi Coast</t>
+  </si>
+  <si>
+    <t>Anantara Convento di Amalfi</t>
+  </si>
+  <si>
+    <t>Minor / GHA Discovery</t>
   </si>
   <si>
     <t>Florence</t>
   </si>
   <si>
-    <t>Helvetia&amp;Bristol Firenze</t>
-  </si>
-  <si>
-    <t>Starhotels Collezione</t>
+    <t>The Hoxton Florence</t>
+  </si>
+  <si>
+    <t>Independent</t>
   </si>
   <si>
     <t>Tuscany</t>
@@ -964,31 +985,13 @@
     <t>TUI Blue Selection</t>
   </si>
   <si>
-    <t>Naples</t>
-  </si>
-  <si>
-    <t>De Bonart Naples</t>
-  </si>
-  <si>
-    <t>Curio Collection / Hilton Honors</t>
-  </si>
-  <si>
-    <t>Amalfi Coast</t>
-  </si>
-  <si>
-    <t>Anantara Convento di Amalfi</t>
-  </si>
-  <si>
-    <t>Minor / GHA Discovery</t>
-  </si>
-  <si>
     <t>Rome (finale)</t>
   </si>
   <si>
-    <t>The St. Regis Rome</t>
-  </si>
-  <si>
-    <t>Marriott Bonvoy</t>
+    <t>Nobu Hotel Roma</t>
+  </si>
+  <si>
+    <t>Nobu Hospitality</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -1006,16 +1009,16 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>6 hotels, 13 nights. Trame ($1,571.58), Helvetia&amp;Bristol ($1,486), Castelfalfi ($3,764.98) and De Bonart ($1,071) are confirmed bookings; Convento is a quote, 2 nights rather than 3. The St. Regis is still an estimate.</t>
-  </si>
-  <si>
-    <t>Holding the old total pending a re-quote: the rental drops from 14 days to 3 (Florence Aug 29 → Florence Sep 1, both ends the same city now), but a one-way-turned-round-trip re-quote could move that either way. New costs: the FCO private transfer (~€70–90), two Frecciarossa fares, and private drivers for both Naples↔Amalfi legs. Rome and FCO parking are gone entirely.</t>
+    <t>6 hotels, 13 nights — all six are now confirmed bookings. Trame ($1,588), Grand Hotel Vesuvio ($1,180), Anantara Convento ($4,115.74, includes breakfast for two and a $100 experience credit), The Hoxton ($1,492), Castelfalfi ($2,848), Nobu Hotel Roma ($874).</t>
+  </si>
+  <si>
+    <t>Estimate. FCO private driver, Rome→Naples train, Naples↔Capri ferry, Naples→Amalfi→Positano ferry, Amalfi→Salerno private driver, Salerno→Florence train, a 2-day Florence–Tuscany rental car, and Florence→Rome train.</t>
   </si>
   <si>
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Colosseum, Capri, wineries, Florence galleries, operas. Held pending a re-quote: swapping the private Lucibello charter for the Capri ferry takes a four-figure line down to about €50 of tickets for the two of you, and dropping Pompeii removes a guide fee, so this should come down materially.</t>
+    <t>Vatican, Colosseum, Capri boat tour, wineries, Florence galleries, operas — no Pompeii or Volterra guide fees this time.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1060,19 +1063,67 @@
     <t>High-speed rail</t>
   </si>
   <si>
-    <t>Roma Termini → Firenze S.M.N.  (Frecciarossa or Italo, hourly — no car in Rome, nothing to park)</t>
-  </si>
-  <si>
-    <t>~1h30</t>
+    <t>Roma Termini → Napoli Centrale  (Frecciarossa, roughly every half hour)</t>
+  </si>
+  <si>
+    <t>~1h10</t>
+  </si>
+  <si>
+    <t>Aug 28</t>
+  </si>
+  <si>
+    <t>Fast ferry</t>
+  </si>
+  <si>
+    <t>Molo Beverello, Naples → Capri → back  (NLG / SNAV / Caremar — book online the night before, and check the last sailing back)</t>
+  </si>
+  <si>
+    <t>~50 min each way</t>
   </si>
   <si>
     <t>Aug 29</t>
   </si>
   <si>
+    <t>Ferry</t>
+  </si>
+  <si>
+    <t>Molo Beverello, Naples → Positano → Amalfi  (Seasonal, July–August only — Positano Jet and similar operators)</t>
+  </si>
+  <si>
+    <t>~2.5 hrs</t>
+  </si>
+  <si>
+    <t>Aug 30</t>
+  </si>
+  <si>
+    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks, and no rental car this stretch — a local driver handles it)</t>
+  </si>
+  <si>
+    <t>~5 hrs</t>
+  </si>
+  <si>
+    <t>Aug 31</t>
+  </si>
+  <si>
+    <t>Anantara Convento, Amalfi → Salerno station</t>
+  </si>
+  <si>
+    <t>~1 hr</t>
+  </si>
+  <si>
+    <t>Salerno → Firenze S.M.N. (Frecciarossa)  (Direct via Naples and Rome, 10+ departures a day)</t>
+  </si>
+  <si>
+    <t>~3.5 hrs</t>
+  </si>
+  <si>
+    <t>Sep 3</t>
+  </si>
+  <si>
     <t>Collect the car</t>
   </si>
   <si>
-    <t>Borgo Ognissanti, Florence — outside the ZTL  (Reservation #21586310US4 — needs rebooking from FCO Aug 24 to Florence Aug 29)</t>
+    <t>Borgo Ognissanti, Florence — outside the ZTL  (Reservation #21586310US4 — Florence pickup, Florence drop-off, not FCO)</t>
   </si>
   <si>
     <t>~30 min</t>
@@ -1084,97 +1135,40 @@
     <t>~2 hrs</t>
   </si>
   <si>
-    <t>Aug 30</t>
+    <t>Sep 4</t>
   </si>
   <si>
     <t>Full day</t>
   </si>
   <si>
-    <t>Castelfalfi → San Gimignano → Volterra → back</t>
+    <t>Castelfalfi → San Gimignano → Montespertoli → back</t>
   </si>
   <si>
     <t>~8 hrs</t>
   </si>
   <si>
-    <t>Aug 31</t>
-  </si>
-  <si>
-    <t>Half day</t>
-  </si>
-  <si>
-    <t>Castelfalfi → Montespertoli wine estates → back</t>
-  </si>
-  <si>
-    <t>~6 hrs</t>
-  </si>
-  <si>
-    <t>Sep 1</t>
-  </si>
-  <si>
-    <t>Self-drive, then train</t>
-  </si>
-  <si>
-    <t>Il Castelfalfi → Firenze S.M.N. (drop the car) → Napoli Centrale  (Frecciarossa 9413, 12:48 → 16:03. Return the rental in Florence before the train — it does not go on to Naples.)</t>
-  </si>
-  <si>
-    <t>~1.5 hrs drive + 3h15 train</t>
-  </si>
-  <si>
-    <t>Sep 2</t>
-  </si>
-  <si>
-    <t>Fast ferry</t>
-  </si>
-  <si>
-    <t>Molo Beverello, Naples → Capri → back  (NLG / SNAV / Caremar — book online the night before, and check the last sailing back)</t>
-  </si>
-  <si>
-    <t>~50 min each way</t>
-  </si>
-  <si>
-    <t>Sep 3</t>
-  </si>
-  <si>
-    <t>De Bonart Naples → Anantara Convento, Amalfi  (No rental car for this leg, and Pompeii is dropped with it — book a car service for the coast road)</t>
-  </si>
-  <si>
-    <t>~1.5–2 hrs</t>
-  </si>
-  <si>
-    <t>Sep 4</t>
-  </si>
-  <si>
-    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks, and no rental car by this point — a local driver is the only option, not just the easy one)</t>
-  </si>
-  <si>
-    <t>~5 hrs</t>
-  </si>
-  <si>
     <t>Sep 5</t>
   </si>
   <si>
-    <t>Anantara Convento, Amalfi → Napoli Centrale</t>
-  </si>
-  <si>
-    <t>~1.5 hrs</t>
-  </si>
-  <si>
-    <t>Napoli Centrale → Roma Termini (Frecciarossa)  (Frequent departures — no need to pre-book far ahead)</t>
-  </si>
-  <si>
-    <t>~1h10</t>
+    <t>Self-drive, then rail</t>
+  </si>
+  <si>
+    <t>Il Castelfalfi → Borgo Ognissanti (drop the car) → Roma Termini  (Rental ends where it started, in Florence — then the Frecciarossa to Rome)</t>
+  </si>
+  <si>
+    <t>~1.5 hrs drive + 1.5 hrs train</t>
   </si>
   <si>
     <t>Sep 6</t>
   </si>
   <si>
-    <t>The St. Regis Rome → FCO  (No rental to return — that was dropped off in Florence on Sep 1)</t>
+    <t>Nobu Hotel Roma → FCO  (No rental to return — that was dropped off in Florence on Sep 5)</t>
   </si>
   <si>
     <t>~40 min</t>
   </si>
   <si>
-    <t>You are car-free for the first five days: a private driver in from FCO, taxis and your feet in Rome, the Frecciarossa to Florence. The rental is only collected on Aug 29, on Borgo Ognissanti just outside Florence's ZTL, and returned in Florence again on Sep 1 before the Naples train — three driving days, not fourteen. Everything south of that (Naples, Capri, Amalfi, and the ride back to Rome) is ferry, private driver or train, never a car you're driving yourself. The IDP ships by Aug 3; pack it with the physical licence, not just a photo of it. Never drive into either historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking. Budget roughly €40 in tolls for the Florence–Tuscany stretch and a full tank each way.</t>
+    <t>Almost the whole trip is car-free: a private driver in from FCO, the Frecciarossa to Naples, ferries to Capri and on to Amalfi, a private driver over to Ravello and later to Salerno, and the Frecciarossa up to Florence. The rental is only collected on Sep 3, on Borgo Ognissanti just outside Florence's ZTL, and returned to the same spot on Sep 5 before the train to Rome — two driving days, not fourteen. The IDP ships by Aug 3; pack it with the physical licence even though it's only needed that once. Never drive into the historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking. The Naples–Positano–Amalfi ferry only runs July–August, so there's no fallback date if it's ever cancelled for weather — have the hotel's driver number ready as backup.</t>
   </si>
   <si>
     <t>#</t>
@@ -1189,100 +1183,118 @@
     <t>Urgency</t>
   </si>
   <si>
-    <t>Reserve dinners at Il Castelfalfi — La Via del Sale, Aug 29 &amp; 31</t>
+    <t>Book the FCO → Hotel Trame private driver</t>
+  </si>
+  <si>
+    <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
+  </si>
+  <si>
+    <t>DO NOW</t>
+  </si>
+  <si>
+    <t>Open -&gt;</t>
+  </si>
+  <si>
+    <t>Frecciarossa tickets — Roma Termini → Napoli Centrale, Aug 27</t>
+  </si>
+  <si>
+    <t>Runs roughly every half hour, about 1h10 — book ahead for the fare, not because it sells out.</t>
+  </si>
+  <si>
+    <t>Naples → Amalfi ferry via Positano, Aug 29</t>
+  </si>
+  <si>
+    <t>Positano Jet's seasonal route, July–August only. Book the Amalfi-bound leg specifically, and check the current 2026 timetable close to the date — schedules shift with the season.</t>
+  </si>
+  <si>
+    <t>Rebook the rental car — Florence pickup and drop-off, Sep 3 → Sep 5</t>
+  </si>
+  <si>
+    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Sep 3 → Florence Sep 5: two days rather than fourteen, both ends the same city. A different pickup/drop-off city usually carries a fee, so the €1,087.81 quote will not hold — re-quote before cancelling.</t>
+  </si>
+  <si>
+    <t>Caruso Roof Garden dinner, Aug 27</t>
+  </si>
+  <si>
+    <t>Grand Hotel Vesuvio's Michelin-starred rooftop room only takes reservations up to 14 days out — put a reminder in your calendar rather than trying to book now.</t>
+  </si>
+  <si>
+    <t>BEFORE YOU GO</t>
+  </si>
+  <si>
+    <t>Capri ferry — Naples → Capri return, Aug 28</t>
+  </si>
+  <si>
+    <t>Fast ferries from Molo Beverello take about fifty minutes; NLG, SNAV and Caremar all run the route. Book both legs online the night before rather than queueing at the counter, and note the last sailing back. The round-the-island boat can be picked up at Marina Grande on the day.</t>
+  </si>
+  <si>
+    <t>THIS WEEK</t>
+  </si>
+  <si>
+    <t>Salerno → Florence Frecciarossa, Aug 31</t>
+  </si>
+  <si>
+    <t>Direct via Naples and Rome, about 3.5 hours, 10+ departures a day — book ahead for a better fare, not out of scarcity.</t>
+  </si>
+  <si>
+    <t>Florence → Rome Frecciarossa, Sep 5</t>
+  </si>
+  <si>
+    <t>About 1.5 hours, frequent departures — no need to lock this in until closer to the date.</t>
+  </si>
+  <si>
+    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26)</t>
+  </si>
+  <si>
+    <t>Both need booking — the Vatican slots go first.</t>
+  </si>
+  <si>
+    <t>Timed entries — Accademia, Duomo dome, Uffizi, all on Sep 1</t>
+  </si>
+  <si>
+    <t>Three in one morning, in that order. Book the dome climb first; it has the fewest slots.</t>
+  </si>
+  <si>
+    <t>Florence opera — La Traviata at St. Mark's, Sep 2</t>
+  </si>
+  <si>
+    <t>Now on the second, lighter Florence day rather than the arrival evening — book before the seats go.</t>
+  </si>
+  <si>
+    <t>Rome opera — All Saints' Anglican, Aug 25</t>
+  </si>
+  <si>
+    <t>Confirm the programme is posted before booking.</t>
+  </si>
+  <si>
+    <t>Montespertoli estate visit for Fri Sep 4</t>
+  </si>
+  <si>
+    <t>A Chianti Montespertoli producer, now paired with San Gimignano in one day — most require an appointment rather than taking walk-ins.</t>
+  </si>
+  <si>
+    <t>Reserve dinners at Il Castelfalfi — La Via del Sale, Sep 3 &amp; 4</t>
   </si>
   <si>
     <t>The estate's fine-dining room. Worth booking ahead even though the room itself is already confirmed.</t>
   </si>
   <si>
-    <t>THIS WEEK</t>
-  </si>
-  <si>
-    <t>Open -&gt;</t>
-  </si>
-  <si>
-    <t>Rebook the rental car — Florence pickup and drop-off, not FCO</t>
-  </si>
-  <si>
-    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → Florence Sep 1: three days rather than fourteen, both ends in the same city. A different pickup/drop-off city usually carries a fee, so the €1,087.81 quote will not hold — re-quote before cancelling.</t>
-  </si>
-  <si>
-    <t>DO NOW</t>
-  </si>
-  <si>
-    <t>Book the FCO → Hotel Trame private driver</t>
-  </si>
-  <si>
-    <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
-  </si>
-  <si>
-    <t>Frecciarossa tickets — Roma Termini → Firenze S.M.N., Aug 27</t>
-  </si>
-  <si>
-    <t>Trenitalia and Italo both run the route hourly in about 1h30. Advance fares open around four months out and are a fraction of the walk-up price, so book as soon as the date is loaded. Aim for a departure around 10:35am.</t>
-  </si>
-  <si>
-    <t>Florence opera — La Traviata at St. Mark's, Aug 27</t>
-  </si>
-  <si>
-    <t>The train lands you at midday, so the evening is no longer tight — but book it before the seats go.</t>
-  </si>
-  <si>
-    <t>Rome opera — All Saints' Anglican, Aug 25</t>
-  </si>
-  <si>
-    <t>Confirm the programme is posted before booking.</t>
-  </si>
-  <si>
-    <t>Montespertoli estate visit for Mon Aug 31</t>
-  </si>
-  <si>
-    <t>A Chianti Montespertoli producer, plus lunch — most require an appointment rather than taking walk-ins.</t>
-  </si>
-  <si>
-    <t>Timed entries — Accademia, Duomo dome, Uffizi, all on Aug 28</t>
-  </si>
-  <si>
-    <t>Three in one morning, in that order. Book the dome climb first; it has the fewest slots.</t>
-  </si>
-  <si>
-    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26)</t>
-  </si>
-  <si>
-    <t>Both need booking — the Vatican slots go first. Pompeii is dropped from the itinerary, so there's no third guide to book here.</t>
-  </si>
-  <si>
-    <t>Arrange private drivers — Naples → Amalfi (Sep 3) and Amalfi → Naples (Sep 5)</t>
-  </si>
-  <si>
-    <t>No rental car for either leg. Book a local car service for the coast road in both directions — the hotel can usually arrange this directly.</t>
-  </si>
-  <si>
-    <t>Capri ferry — Naples → Capri return, Sep 2</t>
-  </si>
-  <si>
-    <t>Fast ferries from Molo Beverello take about fifty minutes; NLG, SNAV and Caremar all run the route. Book both legs online the night before rather than queueing at the counter, and note the last sailing back. The round-the-island boat can be picked up at Marina Grande on the day.</t>
-  </si>
-  <si>
-    <t>BEFORE YOU GO</t>
-  </si>
-  <si>
-    <t>Ravello Festival — check the Sep 4 programme</t>
-  </si>
-  <si>
-    <t>Festival runs to Sep 5, so both Amalfi nights now fall inside the window. The Aug 29 Mahler date still lands on your Florence→Castelfalfi transfer, so it was never reachable.</t>
-  </si>
-  <si>
-    <t>Naples → Rome train, Sep 5</t>
-  </si>
-  <si>
-    <t>Frecciarossa runs the route roughly every half hour, about 1h10 — no need to lock this in until closer to the date.</t>
+    <t>Ravello Festival — check the Aug 30 programme</t>
+  </si>
+  <si>
+    <t>Festival runs to Sep 5, so your one Ravello night is well inside the window.</t>
+  </si>
+  <si>
+    <t>Nobu Roma farewell dinner, Sep 5</t>
+  </si>
+  <si>
+    <t>The hotel's own restaurant, on your last night — worth reserving ahead given the brand.</t>
   </si>
   <si>
     <t>Headline dinners on their dates</t>
   </si>
   <si>
-    <t>Sostanza Aug 27 · Borgo San Jacopo Aug 28 · La Via del Sale Aug 29 &amp; 31 · San Gimignano lunch Aug 30. Plus Armando, Roscioli, Lo Scoglio — reserve ahead where they take bookings.</t>
+    <t>Caruso Roof Garden Aug 27 · Palazzo Petrucci Aug 28 · Dei Cappuccini Aug 29 · Borgo San Jacopo Sep 1 · Sostanza Sep 2 · La Via del Sale Sep 3 &amp; 4. Plus Armando, Roscioli, Da Enzo, Lo Scoglio — reserve ahead where they take bookings.</t>
   </si>
   <si>
     <t>RULED OUT</t>
@@ -1297,7 +1309,13 @@
     <t>Arena di Verona — Aida (Zeffirelli), Sep 4 &amp; 10</t>
   </si>
   <si>
-    <t>Needs a Verona overnight, and Sep 4 is your Ravello night on the Amalfi Coast.</t>
+    <t>No open night in the schedule for a Verona detour — every night from Aug 24 to Sep 5 has a confirmed hotel booking elsewhere.</t>
+  </si>
+  <si>
+    <t>Volterra</t>
+  </si>
+  <si>
+    <t>Fit fine as a full day when Tuscany was three nights; with the coast now taking a night from it, San Gimignano and Montespertoli fill the single Tuscan day instead.</t>
   </si>
   <si>
     <t>Location</t>
@@ -1345,13 +1363,28 @@
     <t>小红书 -&gt;</t>
   </si>
   <si>
-    <t>Days 4–5</t>
+    <t>Days 6–8</t>
+  </si>
+  <si>
+    <t>Flytographer Amalfi / Giuseppe Di Martino</t>
+  </si>
+  <si>
+    <t>Positano's pastel stairs, seen from the ferry; the Ravello gardens; Amalfi's Duomo steps</t>
+  </si>
+  <si>
+    <t>小红书: 阿马尔菲/positano旅拍</t>
+  </si>
+  <si>
+    <t>~$325–425</t>
+  </si>
+  <si>
+    <t>Days 8–11</t>
   </si>
   <si>
     <t>Flytographer Florence / Localgrapher</t>
   </si>
   <si>
-    <t>Piazzale Michelangelo at sunset; Ponte Vecchio at dawn; the Uffizi loggia</t>
+    <t>Piazzale Michelangelo at sunset; Ponte Vecchio at dawn; the Fiesole hillside; the Uffizi loggia</t>
   </si>
   <si>
     <t>小红书: 佛罗伦萨旅拍</t>
@@ -1360,13 +1393,13 @@
     <t>Tuscany / San Gimignano</t>
   </si>
   <si>
-    <t>Days 6–8</t>
+    <t>Days 11–13</t>
   </si>
   <si>
     <t>Flytographer Tuscany / Localgrapher</t>
   </si>
   <si>
-    <t>San Gimignano's towers at golden hour; the Castelfalfi vineyards and golf course; Volterra's alabaster studios</t>
+    <t>San Gimignano's towers at golden hour; the Castelfalfi vineyards and golf course; Montespertoli's vine rows</t>
   </si>
   <si>
     <t>小红书: 托斯卡纳旅拍</t>
@@ -1375,25 +1408,10 @@
     <t>~$425 / 60 min</t>
   </si>
   <si>
-    <t>Days 11–13</t>
-  </si>
-  <si>
-    <t>Flytographer Amalfi / Giuseppe Di Martino</t>
-  </si>
-  <si>
-    <t>Positano's pastel stairs and Spiaggia Grande; Amalfi Drive viewpoints; the Ravello gardens</t>
-  </si>
-  <si>
-    <t>小红书: 阿马尔菲/positano旅拍</t>
-  </si>
-  <si>
-    <t>~$325–425</t>
-  </si>
-  <si>
     <t>Capri</t>
   </si>
   <si>
-    <t>Day 10, optional</t>
+    <t>Day 5, optional</t>
   </si>
   <si>
     <t>Flytographer Capri</t>
@@ -1474,17 +1492,17 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF8A6D1F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF9E4529"/>
       <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FF7A6E62"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF8A6D1F"/>
       <sz val="9"/>
     </font>
     <font>
@@ -2085,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2637,7 +2655,7 @@
         <v>123</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="F32" t="s">
         <v>48</v>
@@ -2651,16 +2669,16 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2671,13 +2689,13 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="E34" s="13" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s">
         <v>48</v>
@@ -2691,13 +2709,13 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
         <v>48</v>
@@ -2711,10 +2729,10 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>63</v>
@@ -2731,67 +2749,67 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="12" t="s">
+      <c r="F37" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
+        <v>5</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E40" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="F40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="D41" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E41" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
-        <v>5</v>
-      </c>
-      <c r="B41" s="10" t="s">
+      <c r="F41" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2802,16 +2820,16 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>77</v>
+      <c r="F42" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2822,7 +2840,7 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>144</v>
@@ -2831,7 +2849,7 @@
         <v>145</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2848,10 +2866,10 @@
         <v>147</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F44" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,16 +2880,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="E45" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>77</v>
+        <v>139</v>
+      </c>
+      <c r="F45" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,56 +2900,30 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F48" t="s">
-        <v>48</v>
+    <row r="48" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="10">
+        <v>6</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2942,13 +2934,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
@@ -2962,30 +2954,56 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="E50" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10">
-        <v>6</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>115</v>
+      <c r="F52" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2996,13 +3014,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3016,13 +3034,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3036,16 +3054,16 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>104</v>
+        <v>57</v>
+      </c>
+      <c r="F55" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,13 +3074,13 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F56" t="s">
         <v>48</v>
@@ -3076,56 +3094,27 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F57" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="F58" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>48</v>
-      </c>
-      <c r="B59" t="s">
-        <v>48</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>178</v>
+        <v>63</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
+        <v>7</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,13 +3125,13 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="F60" t="s">
         <v>48</v>
@@ -3156,16 +3145,16 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" t="s">
-        <v>48</v>
+        <v>175</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,27 +3165,56 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E62" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="10">
-        <v>7</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>184</v>
+      <c r="E64" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3207,16 +3225,16 @@
         <v>48</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="F65" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3233,50 +3251,24 @@
         <v>187</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>48</v>
-      </c>
-      <c r="B67" t="s">
-        <v>48</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D67" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E67" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F67" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>48</v>
-      </c>
-      <c r="B68" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" s="12" t="s">
+      <c r="F66" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
+        <v>8</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="C68" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E68" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F68" t="s">
-        <v>48</v>
+      <c r="F68" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3287,13 +3279,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3307,13 +3299,13 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -3327,13 +3319,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>195</v>
+        <v>57</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3347,16 +3339,16 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F72" t="s">
-        <v>48</v>
+        <v>200</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3367,13 +3359,13 @@
         <v>48</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="F73" t="s">
         <v>48</v>
@@ -3387,47 +3379,47 @@
         <v>48</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="10">
-        <v>8</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" t="s">
-        <v>48</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F77" t="s">
-        <v>48</v>
+        <v>204</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F75" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="10">
+        <v>9</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,16 +3430,16 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="F78" t="s">
-        <v>48</v>
+        <v>211</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,16 +3450,16 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F79" t="s">
-        <v>48</v>
+        <v>213</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3478,13 +3470,13 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F80" t="s">
         <v>48</v>
@@ -3498,16 +3490,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F81" t="s">
-        <v>48</v>
+        <v>217</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3518,16 +3510,16 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="F82" t="s">
-        <v>48</v>
+        <v>220</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3538,16 +3530,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F83" t="s">
-        <v>48</v>
+        <v>215</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3558,70 +3550,67 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F85" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B86" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F84" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="10">
-        <v>9</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="F86" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>48</v>
-      </c>
-      <c r="B87" t="s">
-        <v>48</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="F87" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>48</v>
-      </c>
-      <c r="B88" t="s">
-        <v>48</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F88" t="s">
-        <v>48</v>
+      <c r="D86" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
+        <v>10</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3632,13 +3621,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>88</v>
+        <v>232</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3652,16 +3641,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>121</v>
+        <v>57</v>
+      </c>
+      <c r="F90" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3672,13 +3661,13 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F91" t="s">
         <v>48</v>
@@ -3692,16 +3681,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
+      </c>
+      <c r="F92" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3712,13 +3701,13 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F93" t="s">
         <v>48</v>
@@ -3732,27 +3721,56 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
-        <v>10</v>
-      </c>
-      <c r="B96" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>231</v>
+        <v>88</v>
+      </c>
+      <c r="F94" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F95" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B96" t="s">
+        <v>48</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F96" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3763,16 +3781,16 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F97" t="s">
-        <v>48</v>
+        <v>86</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3783,56 +3801,30 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>48</v>
-      </c>
-      <c r="B99" t="s">
-        <v>48</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="F99" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>48</v>
-      </c>
-      <c r="B100" t="s">
-        <v>48</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F100" s="7" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
+        <v>11</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3843,16 +3835,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>104</v>
+        <v>211</v>
+      </c>
+      <c r="F101" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,13 +3855,13 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F102" t="s">
         <v>48</v>
@@ -3883,30 +3875,56 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
-        <v>11</v>
-      </c>
-      <c r="B105" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>115</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>48</v>
+      </c>
+      <c r="B104" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F104" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>48</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F105" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3917,13 +3935,13 @@
         <v>48</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>137</v>
+        <v>254</v>
       </c>
       <c r="F106" t="s">
         <v>48</v>
@@ -3937,16 +3955,16 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F107" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3957,13 +3975,13 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F108" t="s">
         <v>48</v>
@@ -3977,13 +3995,13 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>251</v>
+        <v>63</v>
       </c>
       <c r="F109" t="s">
         <v>48</v>
@@ -3997,56 +4015,27 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>48</v>
-      </c>
-      <c r="B111" t="s">
-        <v>48</v>
-      </c>
-      <c r="C111" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F111" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>48</v>
-      </c>
-      <c r="B112" t="s">
-        <v>48</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E112" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F112" t="s">
-        <v>48</v>
+      <c r="F110" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="10">
+        <v>12</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4057,27 +4046,56 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="10">
-        <v>12</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>259</v>
+        <v>248</v>
+      </c>
+      <c r="F113" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>48</v>
+      </c>
+      <c r="B114" t="s">
+        <v>48</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F114" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F115" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4088,13 +4106,13 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F116" t="s">
         <v>48</v>
@@ -4108,16 +4126,16 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>71</v>
+        <v>248</v>
+      </c>
+      <c r="F117" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4128,13 +4146,13 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -4148,16 +4166,16 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>77</v>
+        <v>254</v>
+      </c>
+      <c r="F119" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4168,70 +4186,70 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>48</v>
-      </c>
-      <c r="B121" t="s">
-        <v>48</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>48</v>
-      </c>
-      <c r="B122" t="s">
-        <v>48</v>
-      </c>
-      <c r="C122" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F120" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="10">
+        <v>13</v>
+      </c>
+      <c r="B122" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="C122" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="E122" s="13" t="s">
+      <c r="F122" s="14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123" t="s">
+        <v>48</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="10">
-        <v>13</v>
-      </c>
-      <c r="B124" s="10" t="s">
+      <c r="E123" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F123" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s">
+        <v>48</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="E124" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="F124" s="14" t="s">
-        <v>115</v>
+      <c r="F124" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,13 +4260,13 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>277</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F125" t="s">
         <v>48</v>
@@ -4262,16 +4280,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>116</v>
+        <v>278</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F126" t="s">
-        <v>48</v>
+        <v>280</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4282,13 +4300,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F127" t="s">
         <v>48</v>
@@ -4302,16 +4320,16 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>222</v>
+        <v>57</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,13 +4340,13 @@
         <v>48</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="F129" t="s">
         <v>48</v>
@@ -4342,16 +4360,16 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>227</v>
+        <v>63</v>
+      </c>
+      <c r="F130" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4362,67 +4380,67 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F131" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>48</v>
-      </c>
-      <c r="B132" t="s">
-        <v>48</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E132" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F132" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>48</v>
-      </c>
-      <c r="B133" t="s">
-        <v>48</v>
-      </c>
-      <c r="C133" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D133" s="4" t="s">
+      <c r="F131" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E133" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="10">
+    </row>
+    <row r="133" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="10">
         <v>14</v>
       </c>
-      <c r="B135" s="10" t="s">
+      <c r="B133" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C135" s="11" t="s">
+      <c r="C133" s="11" t="s">
         <v>288</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>48</v>
+      </c>
+      <c r="B134" t="s">
+        <v>48</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F134" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>48</v>
+      </c>
+      <c r="B135" t="s">
+        <v>48</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F135" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,55 +4451,15 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="F136" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>48</v>
-      </c>
-      <c r="B137" t="s">
-        <v>48</v>
-      </c>
-      <c r="C137" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="F137" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>48</v>
-      </c>
-      <c r="B138" t="s">
-        <v>48</v>
-      </c>
-      <c r="C138" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F138" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4500,33 +4478,33 @@
     <hyperlink ref="F27" r:id="rId11"/>
     <hyperlink ref="F31" r:id="rId12"/>
     <hyperlink ref="F33" r:id="rId13"/>
-    <hyperlink ref="F38" r:id="rId14"/>
-    <hyperlink ref="F39" r:id="rId15"/>
-    <hyperlink ref="F42" r:id="rId16"/>
-    <hyperlink ref="F43" r:id="rId17"/>
-    <hyperlink ref="F45" r:id="rId18"/>
-    <hyperlink ref="F46" r:id="rId19"/>
-    <hyperlink ref="F47" r:id="rId20"/>
-    <hyperlink ref="F50" r:id="rId21"/>
-    <hyperlink ref="F55" r:id="rId22"/>
-    <hyperlink ref="F59" r:id="rId23"/>
-    <hyperlink ref="F90" r:id="rId24"/>
-    <hyperlink ref="F92" r:id="rId25"/>
-    <hyperlink ref="F94" r:id="rId26"/>
-    <hyperlink ref="F98" r:id="rId27"/>
-    <hyperlink ref="F100" r:id="rId28"/>
-    <hyperlink ref="F101" r:id="rId29"/>
-    <hyperlink ref="F103" r:id="rId30"/>
-    <hyperlink ref="F110" r:id="rId31"/>
-    <hyperlink ref="F113" r:id="rId32"/>
-    <hyperlink ref="F117" r:id="rId33"/>
-    <hyperlink ref="F119" r:id="rId34"/>
-    <hyperlink ref="F120" r:id="rId35"/>
-    <hyperlink ref="F121" r:id="rId36"/>
-    <hyperlink ref="F122" r:id="rId37"/>
-    <hyperlink ref="F128" r:id="rId38"/>
-    <hyperlink ref="F130" r:id="rId39"/>
-    <hyperlink ref="F133" r:id="rId40"/>
+    <hyperlink ref="F37" r:id="rId14"/>
+    <hyperlink ref="F41" r:id="rId15"/>
+    <hyperlink ref="F43" r:id="rId16"/>
+    <hyperlink ref="F44" r:id="rId17"/>
+    <hyperlink ref="F46" r:id="rId18"/>
+    <hyperlink ref="F51" r:id="rId19"/>
+    <hyperlink ref="F57" r:id="rId20"/>
+    <hyperlink ref="F61" r:id="rId21"/>
+    <hyperlink ref="F63" r:id="rId22"/>
+    <hyperlink ref="F64" r:id="rId23"/>
+    <hyperlink ref="F65" r:id="rId24"/>
+    <hyperlink ref="F66" r:id="rId25"/>
+    <hyperlink ref="F72" r:id="rId26"/>
+    <hyperlink ref="F74" r:id="rId27"/>
+    <hyperlink ref="F78" r:id="rId28"/>
+    <hyperlink ref="F79" r:id="rId29"/>
+    <hyperlink ref="F81" r:id="rId30"/>
+    <hyperlink ref="F82" r:id="rId31"/>
+    <hyperlink ref="F83" r:id="rId32"/>
+    <hyperlink ref="F86" r:id="rId33"/>
+    <hyperlink ref="F97" r:id="rId34"/>
+    <hyperlink ref="F98" r:id="rId35"/>
+    <hyperlink ref="F103" r:id="rId36"/>
+    <hyperlink ref="F107" r:id="rId37"/>
+    <hyperlink ref="F126" r:id="rId38"/>
+    <hyperlink ref="F128" r:id="rId39"/>
+    <hyperlink ref="F131" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4596,143 +4574,143 @@
         <v>3</v>
       </c>
       <c r="G2" s="15">
-        <v>523.86</v>
+        <v>529.33</v>
       </c>
       <c r="H2" s="15">
-        <v>1571.58</v>
+        <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" s="15">
-        <v>743</v>
+        <v>590</v>
       </c>
       <c r="H3" s="15">
-        <v>1486</v>
+        <v>1180</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="15">
-        <v>1254.99</v>
+        <v>2057.87</v>
       </c>
       <c r="H4" s="15">
-        <v>3764.98</v>
+        <v>4115.74</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D5" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="15">
-        <v>535.5</v>
+        <v>497.33</v>
       </c>
       <c r="H5" s="15">
-        <v>1071</v>
+        <v>1492</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="15">
-        <v>1500</v>
+        <v>1424</v>
       </c>
       <c r="H6" s="15">
-        <v>3000</v>
+        <v>2848</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E7" t="s">
         <v>287</v>
@@ -4741,13 +4719,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="15">
-        <v>1000</v>
+        <v>874</v>
       </c>
       <c r="H7" s="15">
-        <v>1000</v>
+        <v>874</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4764,7 +4742,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F8" s="16">
         <v>13</v>
@@ -4773,7 +4751,7 @@
         <v>48</v>
       </c>
       <c r="H8" s="17">
-        <v>11893.56</v>
+        <v>12097.74</v>
       </c>
     </row>
   </sheetData>
@@ -4802,24 +4780,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B2" s="15">
-        <v>11893.56</v>
+        <v>12097.74</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,54 +4805,54 @@
         <v>12</v>
       </c>
       <c r="B3" s="15">
-        <v>1775</v>
+        <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B4" s="15">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B7" s="17">
-        <v>18368.559999999998</v>
+        <v>18547.739999999998</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4885,7 +4863,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4899,194 +4877,194 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="D3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="B3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="D3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>355</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B6" t="s">
-        <v>356</v>
+        <v>177</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B7" t="s">
-        <v>360</v>
+        <v>177</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" t="s">
         <v>365</v>
       </c>
-      <c r="D8" t="s">
-        <v>366</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" t="s">
         <v>367</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" t="s">
         <v>369</v>
       </c>
-      <c r="D9" t="s">
-        <v>370</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="D10" t="s">
         <v>371</v>
       </c>
-      <c r="B10" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D10" t="s">
-        <v>373</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>372</v>
+      </c>
+      <c r="B11" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="B11" t="s">
-        <v>264</v>
-      </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" t="s">
         <v>375</v>
       </c>
-      <c r="D11" t="s">
-        <v>376</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" t="s">
         <v>377</v>
-      </c>
-      <c r="B12" t="s">
-        <v>264</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>378</v>
@@ -5095,52 +5073,35 @@
         <v>379</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>382</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="D14" t="s">
-        <v>384</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5157,7 +5118,6 @@
     <hyperlink ref="E11" r:id="rId10"/>
     <hyperlink ref="E12" r:id="rId11"/>
     <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5166,7 +5126,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5177,16 +5137,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>387</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>389</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5197,16 +5157,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5214,16 +5174,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>396</v>
+        <v>393</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>390</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5231,16 +5191,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>396</v>
+        <v>395</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>390</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5248,16 +5208,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>396</v>
+        <v>397</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>390</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5265,16 +5225,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>392</v>
+        <v>399</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>400</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5282,16 +5242,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>392</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5299,16 +5259,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>392</v>
+      <c r="D8" s="21" t="s">
+        <v>403</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5316,16 +5276,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>392</v>
+      <c r="D9" s="21" t="s">
+        <v>403</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5333,16 +5293,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>392</v>
+      <c r="D10" s="21" t="s">
+        <v>403</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5350,16 +5310,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>392</v>
+      <c r="D11" s="21" t="s">
+        <v>403</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5367,16 +5327,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>414</v>
-      </c>
       <c r="D12" s="21" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5384,16 +5344,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5401,16 +5361,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5418,46 +5378,108 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="D16" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="23" t="s">
+      <c r="C17" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D17" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="23" t="s">
+      <c r="C18" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D18" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -5476,6 +5498,9 @@
     <hyperlink ref="E13" r:id="rId12"/>
     <hyperlink ref="E14" r:id="rId13"/>
     <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5498,28 +5523,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5527,129 +5552,129 @@
         <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F3" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" t="s">
+        <v>456</v>
+      </c>
+      <c r="F4" t="s">
+        <v>445</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H4" s="7" t="s">
         <v>447</v>
-      </c>
-      <c r="C4" t="s">
-        <v>448</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="E4" t="s">
-        <v>450</v>
-      </c>
-      <c r="F4" t="s">
-        <v>451</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>457</v>
       </c>
       <c r="B5" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C5" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F5" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B6" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F6" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5663,7 +5688,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="471">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -805,7 +805,7 @@
     <t>Fri, Sep 4</t>
   </si>
   <si>
-    <t>TUSCANY — San Gimignano and a Chianti Montespertoli estate</t>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
   </si>
   <si>
     <t>Driver to San Gimignano — About twenty-five minutes</t>
@@ -814,22 +814,28 @@
     <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
   </si>
   <si>
+    <t>10:15am</t>
+  </si>
+  <si>
     <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
   </si>
   <si>
-    <t>Gelato at Dondoli, then lunch and a Vernaccia tasting — A two-time world gelato champion on Piazza della Cisterna, then San Gimignano's own DOCG white with lunch</t>
-  </si>
-  <si>
-    <t>Driver to a Montespertoli estate — About forty minutes across the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>A Chianti Montespertoli cellar — The smallest Chianti DOCG sub-zone, carved out of the old Colli Fiorentini in 1997 — quieter than Chianti Classico proper. Small enough to see the village on foot between tastings.</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About forty minutes</t>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
   </si>
   <si>
     <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
@@ -1018,7 +1024,7 @@
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Colosseum, Capri boat tour, wineries, Florence galleries, operas — no Pompeii or Volterra guide fees this time.</t>
+    <t>Vatican, Colosseum, Capri boat tour, Florence galleries, operas, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two) — no Pompeii or Volterra guide fees this time.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1141,10 +1147,10 @@
     <t>Full day</t>
   </si>
   <si>
-    <t>Castelfalfi → San Gimignano → Montespertoli → back</t>
-  </si>
-  <si>
-    <t>~8 hrs</t>
+    <t>Castelfalfi → San Gimignano → horseback tour → back</t>
+  </si>
+  <si>
+    <t>~7 hrs</t>
   </si>
   <si>
     <t>Sep 5</t>
@@ -1267,10 +1273,10 @@
     <t>Confirm the programme is posted before booking.</t>
   </si>
   <si>
-    <t>Montespertoli estate visit for Fri Sep 4</t>
-  </si>
-  <si>
-    <t>A Chianti Montespertoli producer, now paired with San Gimignano in one day — most require an appointment rather than taking walk-ins.</t>
+    <t>Horseback riding, lunch &amp; winery tour — San Gimignano, Fri Sep 4</t>
+  </si>
+  <si>
+    <t>San Gimignano Experience, 11am–3pm, ~€120pp: about an hour on horseback through vineyards and olive groves, then lunch, a cellar tour and wine tastings. Replaces the old Montespertoli visit. Meets at the Bivio Volterra bus stop — book ahead, it's a small-group tour.</t>
   </si>
   <si>
     <t>Reserve dinners at Il Castelfalfi — La Via del Sale, Sep 3 &amp; 4</t>
@@ -1315,7 +1321,7 @@
     <t>Volterra</t>
   </si>
   <si>
-    <t>Fit fine as a full day when Tuscany was three nights; with the coast now taking a night from it, San Gimignano and Montespertoli fill the single Tuscan day instead.</t>
+    <t>Fit fine as a full day when Tuscany was three nights; with the coast now taking a night from it, San Gimignano and the horseback vineyard tour fill the single Tuscan day instead.</t>
   </si>
   <si>
     <t>Location</t>
@@ -1399,7 +1405,7 @@
     <t>Flytographer Tuscany / Localgrapher</t>
   </si>
   <si>
-    <t>San Gimignano's towers at golden hour; the Castelfalfi vineyards and golf course; Montespertoli's vine rows</t>
+    <t>San Gimignano's towers at golden hour; the Castelfalfi vineyards and golf course; on horseback in the vines outside town</t>
   </si>
   <si>
     <t>小红书: 托斯卡纳旅拍</t>
@@ -4086,10 +4092,10 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E115" s="13" t="s">
         <v>88</v>
@@ -4106,10 +4112,10 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E116" s="13" t="s">
         <v>88</v>
@@ -4126,16 +4132,16 @@
         <v>48</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F117" t="s">
-        <v>48</v>
+        <v>270</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4146,13 +4152,13 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>57</v>
+        <v>248</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -4166,13 +4172,13 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>254</v>
+        <v>63</v>
       </c>
       <c r="F119" t="s">
         <v>48</v>
@@ -4189,7 +4195,7 @@
         <v>89</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E120" s="13" t="s">
         <v>63</v>
@@ -4203,10 +4209,10 @@
         <v>13</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F122" s="14" t="s">
         <v>115</v>
@@ -4223,7 +4229,7 @@
         <v>116</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E123" s="13" t="s">
         <v>248</v>
@@ -4243,10 +4249,10 @@
         <v>141</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F124" t="s">
         <v>48</v>
@@ -4263,7 +4269,7 @@
         <v>158</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>88</v>
@@ -4280,13 +4286,13 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>121</v>
@@ -4303,7 +4309,7 @@
         <v>163</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E127" s="13" t="s">
         <v>76</v>
@@ -4323,7 +4329,7 @@
         <v>55</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E128" s="13" t="s">
         <v>57</v>
@@ -4343,7 +4349,7 @@
         <v>58</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E129" s="13" t="s">
         <v>136</v>
@@ -4363,7 +4369,7 @@
         <v>181</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>63</v>
@@ -4383,13 +4389,13 @@
         <v>89</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E131" s="13" t="s">
         <v>63</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4397,10 +4403,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,10 +4417,10 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>83</v>
@@ -4431,13 +4437,13 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F135" t="s">
         <v>48</v>
@@ -4451,13 +4457,13 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F136" t="s">
         <v>48</v>
@@ -4502,9 +4508,10 @@
     <hyperlink ref="F98" r:id="rId35"/>
     <hyperlink ref="F103" r:id="rId36"/>
     <hyperlink ref="F107" r:id="rId37"/>
-    <hyperlink ref="F126" r:id="rId38"/>
-    <hyperlink ref="F128" r:id="rId39"/>
-    <hyperlink ref="F131" r:id="rId40"/>
+    <hyperlink ref="F117" r:id="rId38"/>
+    <hyperlink ref="F126" r:id="rId39"/>
+    <hyperlink ref="F128" r:id="rId40"/>
+    <hyperlink ref="F131" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4527,42 +4534,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4580,18 +4587,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
@@ -4609,18 +4616,18 @@
         <v>1180</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
         <v>150</v>
@@ -4638,18 +4645,18 @@
         <v>4115.74</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
         <v>189</v>
@@ -4667,24 +4674,24 @@
         <v>1492</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
         <v>244</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -4696,24 +4703,24 @@
         <v>2848</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -4725,7 +4732,7 @@
         <v>874</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4742,7 +4749,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F8" s="16">
         <v>13</v>
@@ -4780,24 +4787,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B2" s="15">
         <v>12097.74</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4808,51 +4815,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B4" s="15">
-        <v>1800</v>
+        <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B7" s="17">
-        <v>18547.739999999998</v>
+        <v>18797.739999999998</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -4877,220 +4884,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B2" t="s">
         <v>177</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="D3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B6" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B7" t="s">
         <v>177</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="D8" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="D8" t="s">
-        <v>365</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B10" t="s">
         <v>248</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B11" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5101,7 +5108,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5137,16 +5144,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5157,16 +5164,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5174,16 +5181,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5191,16 +5198,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5208,16 +5215,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5225,16 +5232,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5242,16 +5249,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5259,16 +5266,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>403</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5276,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5293,16 +5300,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5310,16 +5317,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5327,16 +5334,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5344,16 +5351,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5361,16 +5368,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>403</v>
+        <v>419</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5378,16 +5385,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5395,16 +5402,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5412,16 +5419,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,16 +5436,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -5446,7 +5453,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5454,10 +5461,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5465,10 +5472,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5476,10 +5483,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -5523,158 +5530,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" s="7" t="s">
         <v>449</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="E3" t="s">
-        <v>451</v>
-      </c>
-      <c r="F3" t="s">
-        <v>452</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B5" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E6" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5688,7 +5695,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="481">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
   <si>
-    <t>Updated Fri, Jul 31</t>
+    <t>Updated Sat, Aug 1</t>
   </si>
   <si>
     <t>Travelers</t>
@@ -52,19 +52,19 @@
     <t>Route</t>
   </si>
   <si>
-    <t>Rome (3) → Naples (2) → Amalfi (2) → Florence (3) → Tuscany (2) → Rome finale (1)</t>
+    <t>Rome (3) → Florence (2) → Castelfalfi (2) → Sorrento (5) → Rome finale (1)</t>
   </si>
   <si>
     <t>Transport</t>
   </si>
   <si>
-    <t>Private driver in from FCO · Frecciarossa to Naples · ferry to Capri and on to Amalfi via Positano · driver to Salerno, Frecciarossa to Florence · self-drive Florence–Tuscany only (Sep 3–5) · Frecciarossa back to Rome</t>
+    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive Florence–Castelfalfi only (Aug 29–31) · rail to Naples, driver over to Sorrento · ferries to Capri, Positano and Amalfi · Frecciarossa back to Rome</t>
   </si>
   <si>
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → Grand Hotel Vesuvio (Naples, Leading Hotels of the World) → Anantara Convento (Amalfi, Minor / GHA) → The Hoxton Florence (independent) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Nobu Hotel Roma (Rome, Nobu Hospitality)</t>
+    <t>Hotel Trame (Rome, independent) → W Florence (Marriott Luxury) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Grand Hotel Excelsior Vittoria (Sorrento, Leading Hotels of the World) → InterContinental Rome Ambasciatori Palace (IHG)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -127,18 +127,18 @@
     <t>https://www.getyourguide.com/</t>
   </si>
   <si>
+    <t>Coast ferries — Capri.com timetables</t>
+  </si>
+  <si>
+    <t>https://www.capri.com/en/ferry-schedule</t>
+  </si>
+  <si>
     <t>Opera tickets — OperaTicketsItaly</t>
   </si>
   <si>
     <t>https://operaticketsitaly.com/</t>
   </si>
   <si>
-    <t>Local driver (Ravello day) — RomaTaxi</t>
-  </si>
-  <si>
-    <t>https://romataxi.cn/</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -361,529 +361,556 @@
     <t>Thu, Aug 27</t>
   </si>
   <si>
-    <t>ROME → NAPLES — direct by Frecciarossa</t>
+    <t>ROME → FLORENCE — direct by Frecciarossa</t>
   </si>
   <si>
     <t>TRAVEL DAY</t>
   </si>
   <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>9:20am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Florence — Roma Termini → Firenze S.M.N., direct — about 1h30. Departures roughly every half hour; book ahead for the fare, not for the seat.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1h30</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>10:50am</t>
+  </si>
+  <si>
+    <t>Arrive Firenze S.M.N.</t>
+  </si>
+  <si>
+    <t>11:05am</t>
+  </si>
+  <si>
+    <t>Drop bags — W Florence — Piazza dell'Unità Italiana, a two-minute walk from the station door. Rooms are ready from 3:00pm; they'll hold the luggage.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>11:45am</t>
+  </si>
+  <si>
+    <t>Lunch — Trattoria Mario, by San Lorenzo — Shared tables, cash, closed by 3:30pm. Mercato Centrale upstairs is the no-queue fallback.</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Accademia — David at the afternoon slot — Forty-five minutes is genuinely enough. Go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>4:30pm</t>
+  </si>
+  <si>
+    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to the river</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>2:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change</t>
+  </si>
+  <si>
+    <t>Walk or taxi</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
     <t>9:00am</t>
   </si>
   <si>
-    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Naples — Roma Termini → Napoli Centrale, direct — about 1h10. Trains run roughly every half hour; no need to book far ahead.</t>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, about eight minutes on foot from the W and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Coffee, then the platform</t>
+  </si>
+  <si>
+    <t>10:52am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Naples — Firenze S.M.N. → Napoli Centrale, direct via Rome — about 3 hours. Book this one ahead; it's the leg where a good fare is worth having.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~3 hrs</t>
+  </si>
+  <si>
+    <t>1:50pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse</t>
+  </si>
+  <si>
+    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h15</t>
+  </si>
+  <si>
+    <t>3:40pm</t>
+  </si>
+  <si>
+    <t>Check in — Grand Hotel Excelsior Vittoria — Piazza Tasso, on the cliff over Marina Piccola. Five acres of citrus garden behind it and a private lift straight down to the water.</t>
+  </si>
+  <si>
+    <t>The citrus gardens, then the lift to the sea — Unpack properly — this is home for five nights</t>
+  </si>
+  <si>
+    <t>Aperitivo on the terrace over the bay — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>Dinner — Terrazza Bosquet — The hotel's Michelin-starred room, on the terrace. Worth booking for the first night rather than the last.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>Swim, or the pool on the cliff — The private lift drops you at Marina Piccola if you want salt water instead</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola by the hotel lift — The ferry pier is a two-minute walk from where the lift lets you out</t>
+  </si>
+  <si>
+    <t>Hotel lift</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Sunset from the Villa Comunale terrace — A public balcony on the cliff edge, two minutes from the hotel, straight out over the Bay of Naples</t>
+  </si>
+  <si>
+    <t>Dinner — Da Emilia, Marina Grande — Sixty years old, plastic chairs on the harbour, and the best simple fish in Sorrento</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
+  </si>
+  <si>
+    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
+  </si>
+  <si>
+    <t>5:45pm</t>
+  </si>
+  <si>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h30</t>
+  </si>
+  <si>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
+  </si>
+  <si>
+    <t>Check out — Excelsior Vittoria</t>
+  </si>
+  <si>
+    <t>Private driver to Napoli Centrale — About 1h15 back around the bay</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale</t>
+  </si>
+  <si>
+    <t>11:20am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Rome — Napoli Centrale → Roma Termini, direct — about 1h10, departures roughly every half hour</t>
   </si>
   <si>
     <t>High-speed rail, ~1h10</t>
   </si>
   <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Drop bags — Grand Hotel Vesuvio — Via Partenope, facing Castel dell'Ovo and the bay. Rooms are ready from 3:00pm; they will hold luggage until then.</t>
-  </si>
-  <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>Spaccanapoli and the old city — The dead-straight Greek road that still splits Naples in half — pizza fritta and sfogliatelle along the way</t>
-  </si>
-  <si>
-    <t>Check in and reset</t>
-  </si>
-  <si>
-    <t>Aperitivo — Sky Lounge — The hotel's rooftop bar, one floor below dinner</t>
-  </si>
-  <si>
-    <t>Dinner — Caruso Roof Garden — Ninth floor, Michelin-starred, named for Enrico Caruso, who called this hotel his Neapolitan home. Reservations open only 14 days out — call as soon as the window opens. The Bucatini alla Caruso is the dish to order.</t>
-  </si>
-  <si>
-    <t>Caruso -&gt;</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>NAPLES — Capri day trip</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Walk down to Molo Beverello — The fast-ferry pier is fifteen minutes along the seafront from the hotel</t>
+    <t>Arrive Roma Termini; taxi to the hotel</t>
+  </si>
+  <si>
+    <t>1:15pm</t>
+  </si>
+  <si>
+    <t>Check in — InterContinental Rome Ambasciatori Palace — Via Vittorio Veneto, the La Dolce Vita address, at the Villa Borghese end of the street — five minutes from the gardens you photographed on the first Wednesday</t>
+  </si>
+  <si>
+    <t>Down Via Veneto to the Spanish Steps — Past Palazzo Margherita and the Capuchin crypt, then down to Piazza di Spagna</t>
   </si>
   <si>
     <t>Walk, ~15 min</t>
   </si>
   <si>
-    <t>9:20am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Naples → Capri — NLG, SNAV and Caremar all run it in about fifty minutes. Sailings are frequent in summer but sell out at the counter — book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~50 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>The Faraglioni, the grottoes, the swim coves — Pick up a round-the-island boat at Marina Grande — Blue Grotto if the sea is calm enough to enter</t>
-  </si>
-  <si>
-    <t>Local boat from Marina Grande</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Marina Grande, then the funicular</t>
-  </si>
-  <si>
-    <t>3:30pm</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp</t>
-  </si>
-  <si>
-    <t>Ferry back to Naples — Check the final sailing when you arrive — the last fast boats go early evening, and missing one means a night on the island</t>
-  </si>
-  <si>
-    <t>Dinner — Palazzo Petrucci — Michelin-starred Neapolitan tasting menu, back in the old city — the celebration dinner for the boat day</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>NAPLES → AMALFI — ferry via Positano</t>
-  </si>
-  <si>
-    <t>Check out — Grand Hotel Vesuvio</t>
-  </si>
-  <si>
-    <t>Walk to Molo Beverello — Fifteen minutes along the seafront</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>Ferry to Positano and Amalfi — Positano Jet and a couple of other operators run this seasonal route — book the Amalfi-bound leg specifically, not just the Positano hop.</t>
-  </si>
-  <si>
-    <t>Ferry, ~2.5 hrs total</t>
-  </si>
-  <si>
-    <t>Positano Jet -&gt;</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Positano from the water — The pastel stairs climbing straight up from the sea — the best view of the town is from the boat, not the beach</t>
-  </si>
-  <si>
-    <t>By ferry</t>
-  </si>
-  <si>
-    <t>11:45am</t>
-  </si>
-  <si>
-    <t>Arrive Amalfi marina; lunch nearby — A table just off Piazza Duomo before checking in</t>
-  </si>
-  <si>
-    <t>1:30pm</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the old town — The striped façade of Sant'Andrea and the Cloister of Paradise, then the lemon-lined lanes behind the piazza</t>
-  </si>
-  <si>
-    <t>Check in — Anantara Convento di Amalfi — Deluxe Sea View Room. A 13th-century monastery on the cliff edge, with the original cloister still standing.</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo in the cloister</t>
-  </si>
-  <si>
-    <t>Dinner — Dei Cappuccini — The hotel's Michelin room, or La Locanda for pizza if the day has beaten you</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>AMALFI — Nerano lunch and Ravello</t>
-  </si>
-  <si>
-    <t>The beach club, by cliff lift — A slow morning at sea level before the day starts properly</t>
-  </si>
-  <si>
-    <t>Hotel cliff lift</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Lunch — Lo Scoglio — Nerano. The original spaghetti alla Nerano, and worth the boat ride on its own.</t>
-  </si>
-  <si>
-    <t>Hotel car or boat, ~40 min</t>
-  </si>
-  <si>
-    <t>Up to Ravello — Forty-five minutes of switchbacks above the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>3:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Aperitivo, then Villa Rufolo's gardens</t>
-  </si>
-  <si>
-    <t>RAVELLO FESTIVAL — check the Aug 30 programme — Confirmed concerts run to Sep 5 — check what's actually on tonight before you commit to a table instead</t>
-  </si>
-  <si>
-    <t>Walk to Villa Rufolo</t>
-  </si>
-  <si>
-    <t>Programme -&gt;</t>
-  </si>
-  <si>
-    <t>9:30pm</t>
-  </si>
-  <si>
-    <t>Late dinner — Il Flauto di Pan — In the Villa Cimbrone gardens. Rossellinis is the other option.</t>
-  </si>
-  <si>
-    <t>Walk; drive down after</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>AMALFI → FLORENCE — driver to Salerno, then Frecciarossa</t>
-  </si>
-  <si>
-    <t>12:00pm</t>
-  </si>
-  <si>
-    <t>Check out — Anantara Convento — Checkout is exactly noon here</t>
-  </si>
-  <si>
-    <t>12:15pm</t>
-  </si>
-  <si>
-    <t>Private driver to Salerno — Along the coast road via Vietri, then a short stretch of highway — about an hour</t>
-  </si>
-  <si>
-    <t>Private driver, ~1 hr</t>
-  </si>
-  <si>
-    <t>1:15pm</t>
-  </si>
-  <si>
-    <t>Arrive Salerno station; lunch on the concourse</t>
-  </si>
-  <si>
-    <t>2:22pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Florence — Salerno → Firenze S.M.N., direct via Naples and Rome — about 3.5 hours. Ten-plus direct departures a day; book ahead for a better fare.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~3.5 hrs</t>
-  </si>
-  <si>
-    <t>5:50pm</t>
-  </si>
-  <si>
-    <t>Arrive Firenze S.M.N.</t>
-  </si>
-  <si>
-    <t>Check in — The Hoxton Florence — Via delle Mantellate, on the quieter west side near the river</t>
-  </si>
-  <si>
-    <t>Walk or taxi, ~12 min</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>Dinner near the hotel — Something easy after a long travel day — Borgo Ognissanti has plenty of options</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Accademia — David at first entry — Forty-five minutes is genuinely enough. Go straight down the hall.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and much better before the day heats up</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>Coffee on Piazza della Signoria — The Loggia dei Lanzi is an open-air sculpture hall and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>1:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria if you want the splurge. Trattoria Mario is the third option if you'd rather eat near San Lorenzo.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers, restorers still working street level</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>FLORENCE — hills in the morning, Santa Croce after</t>
-  </si>
-  <si>
-    <t>Bus to Fiesole — ATAF #7 from Piazza San Marco, about twenty minutes up into the hills</t>
-  </si>
-  <si>
-    <t>Bus, ~20 min</t>
-  </si>
-  <si>
-    <t>The Roman theatre and Etruscan walls — Still-standing tiers of a 1st-century BC theatre, with the whole Arno valley behind it</t>
-  </si>
-  <si>
-    <t>Coffee on the terrace — The view back over Florence, with Brunelleschi's dome on the skyline</t>
-  </si>
-  <si>
-    <t>Bus back down to Florence</t>
-  </si>
-  <si>
-    <t>Lunch — San Lorenzo Market — The upstairs food hall, casual, no booking</t>
-  </si>
-  <si>
-    <t>San Lorenzo — the Medici Chapels — Michelangelo's New Sacristy, a short walk from the market stalls</t>
-  </si>
-  <si>
-    <t>Santa Croce — Michelangelo, Galileo and Machiavelli are all buried here; the Pazzi Chapel is Brunelleschi at his plainest and best</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change</t>
-  </si>
-  <si>
-    <t>Walk or taxi</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, a ten-minute walk from the Hoxton and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Driver to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>TUSCANY → FLORENCE → ROME — drop the car, then the train</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Thursday's route</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — reservation #21586310US4 ends here</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Coffee, then the platform</t>
-  </si>
-  <si>
-    <t>12:03pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Rome — Firenze S.M.N. → Roma Termini, direct — about 1.5 hours</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1.5 hrs</t>
-  </si>
-  <si>
-    <t>Arrive Roma Termini; taxi to the hotel</t>
-  </si>
-  <si>
-    <t>Check in — Nobu Hotel Roma — Via Vittorio Veneto, at the top of the street by Villa Borghese — five minutes from Wednesday's photo spot</t>
-  </si>
-  <si>
-    <t>Last Roman afternoon — Via Veneto and the Spanish Steps — La Dolce Vita's old strip, then down to Piazza di Spagna</t>
-  </si>
-  <si>
-    <t>Aperitivo at the hotel</t>
-  </si>
-  <si>
-    <t>Farewell dinner — Nobu Roma — The hotel's namesake restaurant, for the last night</t>
-  </si>
-  <si>
-    <t>Nobu Roma -&gt;</t>
+    <t>Trevi Fountain, one last time — Ten minutes on from the steps, and worth the crowd on a final evening</t>
+  </si>
+  <si>
+    <t>Aperitivo on Via Veneto — The hotel's own bar, or Harry's Bar a few doors down</t>
+  </si>
+  <si>
+    <t>Farewell dinner — Aroma, at Palazzo Manfredi — Michelin-starred, on a rooftop that looks straight into the Colosseum. Book this one early; there are only a dozen tables with the view.</t>
   </si>
   <si>
     <t>Sun, Sep 6</t>
@@ -895,7 +922,7 @@
     <t>6:40am</t>
   </si>
   <si>
-    <t>Taxi to FCO — About forty minutes on an empty Sunday road. No rental to return this time — that ended in Florence on Sep 5.</t>
+    <t>Taxi to FCO — About forty minutes on an empty Sunday road. No rental to return — that ended in Florence on Aug 31.</t>
   </si>
   <si>
     <t>7:20am</t>
@@ -955,49 +982,40 @@
     <t>Trip.com -&gt;</t>
   </si>
   <si>
-    <t>Naples</t>
-  </si>
-  <si>
-    <t>Grand Hotel Vesuvio</t>
+    <t>Florence</t>
+  </si>
+  <si>
+    <t>W Florence</t>
+  </si>
+  <si>
+    <t>Marriott Luxury</t>
+  </si>
+  <si>
+    <t>Tuscany</t>
+  </si>
+  <si>
+    <t>Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>TUI Blue Selection</t>
+  </si>
+  <si>
+    <t>Sorrento</t>
+  </si>
+  <si>
+    <t>Grand Hotel Excelsior Vittoria</t>
   </si>
   <si>
     <t>Leading Hotels of the World</t>
   </si>
   <si>
-    <t>Amalfi Coast</t>
-  </si>
-  <si>
-    <t>Anantara Convento di Amalfi</t>
-  </si>
-  <si>
-    <t>Minor / GHA Discovery</t>
-  </si>
-  <si>
-    <t>Florence</t>
-  </si>
-  <si>
-    <t>The Hoxton Florence</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>Tuscany</t>
-  </si>
-  <si>
-    <t>Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>TUI Blue Selection</t>
-  </si>
-  <si>
     <t>Rome (finale)</t>
   </si>
   <si>
-    <t>Nobu Hotel Roma</t>
-  </si>
-  <si>
-    <t>Nobu Hospitality</t>
+    <t>InterContinental Rome Ambasciatori Palace</t>
+  </si>
+  <si>
+    <t>IHG</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -1015,16 +1033,16 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>6 hotels, 13 nights — all six are now confirmed bookings. Trame ($1,588), Grand Hotel Vesuvio ($1,180), Anantara Convento ($4,115.74, includes breakfast for two and a $100 experience credit), The Hoxton ($1,492), Castelfalfi ($2,848), Nobu Hotel Roma ($874).</t>
-  </si>
-  <si>
-    <t>Estimate. FCO private driver, Rome→Naples train, Naples↔Capri ferry, Naples→Amalfi→Positano ferry, Amalfi→Salerno private driver, Salerno→Florence train, a 2-day Florence–Tuscany rental car, and Florence→Rome train.</t>
+    <t>5 hotels, 13 nights. Confirmed or quoted: Trame ($1,588), W Florence ($1,236), Castelfalfi ($1,841), InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $6,906 if you hold the old $12,098 lodging total.</t>
+  </si>
+  <si>
+    <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
   </si>
   <si>
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Colosseum, Capri boat tour, Florence galleries, operas, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two) — no Pompeii or Volterra guide fees this time.</t>
+    <t>Vatican, Colosseum, Florence galleries and the dome climb, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two).</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1036,7 +1054,7 @@
     <t>Buffer &amp; gratuities</t>
   </si>
   <si>
-    <t>Taxis, tips, Naples street food, incidentals.</t>
+    <t>Taxis, tips, ferry-day incidentals.</t>
   </si>
   <si>
     <t>Cash, before points. Two travellers.</t>
@@ -1069,112 +1087,115 @@
     <t>High-speed rail</t>
   </si>
   <si>
-    <t>Roma Termini → Napoli Centrale  (Frecciarossa, roughly every half hour)</t>
-  </si>
-  <si>
-    <t>~1h10</t>
-  </si>
-  <si>
-    <t>Aug 28</t>
+    <t>Roma Termini → Firenze S.M.N.  (Frecciarossa, roughly every half hour; the W is a two-minute walk from the platform)</t>
+  </si>
+  <si>
+    <t>~1h30</t>
+  </si>
+  <si>
+    <t>Aug 29</t>
+  </si>
+  <si>
+    <t>Collect the car</t>
+  </si>
+  <si>
+    <t>Borgo Ognissanti, Florence — outside the ZTL  (Florence pickup, Florence drop-off, two days only — not FCO)</t>
+  </si>
+  <si>
+    <t>~30 min</t>
+  </si>
+  <si>
+    <t>Florence → Certaldo (lunch stop) → Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>~2 hrs</t>
+  </si>
+  <si>
+    <t>Aug 30</t>
+  </si>
+  <si>
+    <t>Castelfalfi → San Gimignano → horseback tour → back</t>
+  </si>
+  <si>
+    <t>~7 hrs</t>
+  </si>
+  <si>
+    <t>Aug 31</t>
+  </si>
+  <si>
+    <t>Self-drive, then rail</t>
+  </si>
+  <si>
+    <t>Il Castelfalfi → Borgo Ognissanti (drop the car) → Napoli Centrale  (The rental ends where it started. Book the Florence–Naples Frecciarossa ahead — it's the longest leg of the trip.)</t>
+  </si>
+  <si>
+    <t>~1.5 hrs drive + 3 hrs train</t>
+  </si>
+  <si>
+    <t>Napoli Centrale → Grand Hotel Excelsior Vittoria, Sorrento  (Pre-book. The Circumvesuviana is cheaper but has nowhere to put luggage in August.)</t>
+  </si>
+  <si>
+    <t>~1h15</t>
+  </si>
+  <si>
+    <t>Sep 2</t>
   </si>
   <si>
     <t>Fast ferry</t>
   </si>
   <si>
-    <t>Molo Beverello, Naples → Capri → back  (NLG / SNAV / Caremar — book online the night before, and check the last sailing back)</t>
-  </si>
-  <si>
-    <t>~50 min each way</t>
-  </si>
-  <si>
-    <t>Aug 29</t>
+    <t>Sorrento Marina Piccola → Capri → back  (Up to forty crossings a day in high season — still book online the night before, and note the last sailing back)</t>
+  </si>
+  <si>
+    <t>~25 min each way</t>
+  </si>
+  <si>
+    <t>Sep 3</t>
   </si>
   <si>
     <t>Ferry</t>
   </si>
   <si>
-    <t>Molo Beverello, Naples → Positano → Amalfi  (Seasonal, July–August only — Positano Jet and similar operators)</t>
-  </si>
-  <si>
-    <t>~2.5 hrs</t>
-  </si>
-  <si>
-    <t>Aug 30</t>
-  </si>
-  <si>
-    <t>Anantara Convento → Ravello (evening concert) → back  (Tight switchbacks, and no rental car this stretch — a local driver handles it)</t>
-  </si>
-  <si>
-    <t>~5 hrs</t>
-  </si>
-  <si>
-    <t>Aug 31</t>
-  </si>
-  <si>
-    <t>Anantara Convento, Amalfi → Salerno station</t>
-  </si>
-  <si>
-    <t>~1 hr</t>
-  </si>
-  <si>
-    <t>Salerno → Firenze S.M.N. (Frecciarossa)  (Direct via Naples and Rome, 10+ departures a day)</t>
-  </si>
-  <si>
-    <t>~3.5 hrs</t>
-  </si>
-  <si>
-    <t>Sep 3</t>
-  </si>
-  <si>
-    <t>Collect the car</t>
-  </si>
-  <si>
-    <t>Borgo Ognissanti, Florence — outside the ZTL  (Reservation #21586310US4 — Florence pickup, Florence drop-off, not FCO)</t>
-  </si>
-  <si>
-    <t>~30 min</t>
-  </si>
-  <si>
-    <t>Florence → Certaldo (lunch stop) → Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>~2 hrs</t>
+    <t>Sorrento → Positano → back  (Seasonal, mid-April to mid-October. Positano's pier closes in rough seas.)</t>
+  </si>
+  <si>
+    <t>~35 min each way</t>
   </si>
   <si>
     <t>Sep 4</t>
   </si>
   <si>
-    <t>Full day</t>
-  </si>
-  <si>
-    <t>Castelfalfi → San Gimignano → horseback tour → back</t>
-  </si>
-  <si>
-    <t>~7 hrs</t>
+    <t>Ferry, then private driver</t>
+  </si>
+  <si>
+    <t>Sorrento → Amalfi by sea; Amalfi → Ravello → Sorrento by road  (Ravello is car-free at the top — the driver waits at the gate. Allow 1h30 for the drive back over the pass.)</t>
+  </si>
+  <si>
+    <t>~1h15 ferry + ~2 hrs driving</t>
   </si>
   <si>
     <t>Sep 5</t>
   </si>
   <si>
-    <t>Self-drive, then rail</t>
-  </si>
-  <si>
-    <t>Il Castelfalfi → Borgo Ognissanti (drop the car) → Roma Termini  (Rental ends where it started, in Florence — then the Frecciarossa to Rome)</t>
-  </si>
-  <si>
-    <t>~1.5 hrs drive + 1.5 hrs train</t>
+    <t>Private driver, then rail</t>
+  </si>
+  <si>
+    <t>Sorrento → Napoli Centrale → Roma Termini</t>
+  </si>
+  <si>
+    <t>~1h15 driver + 1h10 train</t>
   </si>
   <si>
     <t>Sep 6</t>
   </si>
   <si>
-    <t>Nobu Hotel Roma → FCO  (No rental to return — that was dropped off in Florence on Sep 5)</t>
+    <t>InterContinental Ambasciatori → FCO  (No rental to return — that was dropped off in Florence on Aug 31)</t>
   </si>
   <si>
     <t>~40 min</t>
   </si>
   <si>
-    <t>Almost the whole trip is car-free: a private driver in from FCO, the Frecciarossa to Naples, ferries to Capri and on to Amalfi, a private driver over to Ravello and later to Salerno, and the Frecciarossa up to Florence. The rental is only collected on Sep 3, on Borgo Ognissanti just outside Florence's ZTL, and returned to the same spot on Sep 5 before the train to Rome — two driving days, not fourteen. The IDP ships by Aug 3; pack it with the physical licence even though it's only needed that once. Never drive into the historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking. The Naples–Positano–Amalfi ferry only runs July–August, so there's no fallback date if it's ever cancelled for weather — have the hotel's driver number ready as backup.</t>
+    <t>Almost the whole trip is car-free: a private driver in from FCO, the Frecciarossa up to Florence, a two-day rental for Tuscany, then rail to Naples and a driver over the peninsula to Sorrento, where everything after is a ferry. The car is collected on Aug 29 on Borgo Ognissanti — just outside Florence's ZTL, eight minutes on foot from the W — and returned to the same desk on Aug 31 before the train south. Two driving days, not fourteen. The IDP ships by Aug 3; pack it with the physical licence even though it's only needed that once. Never drive into a historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking, and the Excelsior Vittoria's garage is the only place in central Sorrento you'd want to park anyway. The Sorrento–Positano–Amalfi ferries run mid-April to mid-October, so the whole window is covered, but any of them can be cancelled for weather — keep the hotel's driver number as a backup for the Amalfi day.</t>
   </si>
   <si>
     <t>#</t>
@@ -1189,118 +1210,112 @@
     <t>Urgency</t>
   </si>
   <si>
+    <t>Book the Sorrento hotel — five nights, Aug 31 → Sep 5</t>
+  </si>
+  <si>
+    <t>The one open booking left, and the biggest single line in the budget. Holding the old lodging total leaves $6,906 for these five nights, or about $1,381 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands ~$1,150 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
+  </si>
+  <si>
+    <t>DO NOW</t>
+  </si>
+  <si>
+    <t>Open -&gt;</t>
+  </si>
+  <si>
     <t>Book the FCO → Hotel Trame private driver</t>
   </si>
   <si>
     <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
   </si>
   <si>
-    <t>DO NOW</t>
-  </si>
-  <si>
-    <t>Open -&gt;</t>
-  </si>
-  <si>
-    <t>Frecciarossa tickets — Roma Termini → Napoli Centrale, Aug 27</t>
-  </si>
-  <si>
-    <t>Runs roughly every half hour, about 1h10 — book ahead for the fare, not because it sells out.</t>
-  </si>
-  <si>
-    <t>Naples → Amalfi ferry via Positano, Aug 29</t>
-  </si>
-  <si>
-    <t>Positano Jet's seasonal route, July–August only. Book the Amalfi-bound leg specifically, and check the current 2026 timetable close to the date — schedules shift with the season.</t>
-  </si>
-  <si>
-    <t>Rebook the rental car — Florence pickup and drop-off, Sep 3 → Sep 5</t>
-  </si>
-  <si>
-    <t>Reservation #21586310US4 is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Sep 3 → Florence Sep 5: two days rather than fourteen, both ends the same city. A different pickup/drop-off city usually carries a fee, so the €1,087.81 quote will not hold — re-quote before cancelling.</t>
-  </si>
-  <si>
-    <t>Caruso Roof Garden dinner, Aug 27</t>
-  </si>
-  <si>
-    <t>Grand Hotel Vesuvio's Michelin-starred rooftop room only takes reservations up to 14 days out — put a reminder in your calendar rather than trying to book now.</t>
+    <t>Rebook the rental car — Florence pickup and drop-off, Aug 29 → Aug 31</t>
+  </si>
+  <si>
+    <t>The old reservation is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → Florence Aug 31: two days rather than fourteen, both ends the same city. Re-quote before cancelling — the old €1,087.81 figure was for a fourteen-day FCO round trip and will not carry over.</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch &amp; winery tour — San Gimignano, Sun Aug 30</t>
+  </si>
+  <si>
+    <t>San Gimignano Experience, 11am–3pm, ~€120pp: about an hour on horseback through vineyards and olive groves, then lunch, a cellar tour and wine tastings. Note the date moved from Sep 4 to Aug 30 in the replan. Meets at the Bivio Volterra bus stop — book ahead, it's a small-group tour.</t>
+  </si>
+  <si>
+    <t>Frecciarossa — Firenze S.M.N. → Napoli Centrale, Aug 31</t>
+  </si>
+  <si>
+    <t>About 3 hours, direct via Rome. The longest single leg of the trip and the one where booking ahead actually saves money.</t>
+  </si>
+  <si>
+    <t>Private driver — Napoli Centrale → Sorrento, Aug 31, and back on Sep 5</t>
+  </si>
+  <si>
+    <t>About 1h15 each way. Book both directions with the same operator. The Circumvesuviana costs €5 but has no luggage space and no air conditioning worth the name in August.</t>
+  </si>
+  <si>
+    <t>Timed entries — Accademia (Aug 27), Duomo dome + Uffizi (Aug 28)</t>
+  </si>
+  <si>
+    <t>Only two Florence days now, so these three are the tight ones. Book the dome climb first — it has the fewest slots of anything in the city — then the Uffizi guided slot behind it.</t>
   </si>
   <si>
     <t>BEFORE YOU GO</t>
   </si>
   <si>
-    <t>Capri ferry — Naples → Capri return, Aug 28</t>
-  </si>
-  <si>
-    <t>Fast ferries from Molo Beverello take about fifty minutes; NLG, SNAV and Caremar all run the route. Book both legs online the night before rather than queueing at the counter, and note the last sailing back. The round-the-island boat can be picked up at Marina Grande on the day.</t>
+    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26)</t>
+  </si>
+  <si>
+    <t>Both need booking — the Vatican slots go first.</t>
+  </si>
+  <si>
+    <t>Florence opera — La Traviata at St. Mark's, Aug 28</t>
+  </si>
+  <si>
+    <t>Moved from Sep 2 in the replan. Now on the single full Florence day, after the Boboli afternoon.</t>
+  </si>
+  <si>
+    <t>Rome opera — All Saints' Anglican, Aug 25</t>
+  </si>
+  <si>
+    <t>Confirm the programme is posted before booking.</t>
+  </si>
+  <si>
+    <t>Frecciarossa — Napoli Centrale → Roma Termini, Sep 5</t>
+  </si>
+  <si>
+    <t>About 1h10, departures every half hour — no scarcity, book for the fare.</t>
   </si>
   <si>
     <t>THIS WEEK</t>
   </si>
   <si>
-    <t>Salerno → Florence Frecciarossa, Aug 31</t>
-  </si>
-  <si>
-    <t>Direct via Naples and Rome, about 3.5 hours, 10+ departures a day — book ahead for a better fare, not out of scarcity.</t>
-  </si>
-  <si>
-    <t>Florence → Rome Frecciarossa, Sep 5</t>
-  </si>
-  <si>
-    <t>About 1.5 hours, frequent departures — no need to lock this in until closer to the date.</t>
-  </si>
-  <si>
-    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26)</t>
-  </si>
-  <si>
-    <t>Both need booking — the Vatican slots go first.</t>
-  </si>
-  <si>
-    <t>Timed entries — Accademia, Duomo dome, Uffizi, all on Sep 1</t>
-  </si>
-  <si>
-    <t>Three in one morning, in that order. Book the dome climb first; it has the fewest slots.</t>
-  </si>
-  <si>
-    <t>Florence opera — La Traviata at St. Mark's, Sep 2</t>
-  </si>
-  <si>
-    <t>Now on the second, lighter Florence day rather than the arrival evening — book before the seats go.</t>
-  </si>
-  <si>
-    <t>Rome opera — All Saints' Anglican, Aug 25</t>
-  </si>
-  <si>
-    <t>Confirm the programme is posted before booking.</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch &amp; winery tour — San Gimignano, Fri Sep 4</t>
-  </si>
-  <si>
-    <t>San Gimignano Experience, 11am–3pm, ~€120pp: about an hour on horseback through vineyards and olive groves, then lunch, a cellar tour and wine tastings. Replaces the old Montespertoli visit. Meets at the Bivio Volterra bus stop — book ahead, it's a small-group tour.</t>
-  </si>
-  <si>
-    <t>Reserve dinners at Il Castelfalfi — La Via del Sale, Sep 3 &amp; 4</t>
-  </si>
-  <si>
-    <t>The estate's fine-dining room. Worth booking ahead even though the room itself is already confirmed.</t>
-  </si>
-  <si>
-    <t>Ravello Festival — check the Aug 30 programme</t>
-  </si>
-  <si>
-    <t>Festival runs to Sep 5, so your one Ravello night is well inside the window.</t>
-  </si>
-  <si>
-    <t>Nobu Roma farewell dinner, Sep 5</t>
-  </si>
-  <si>
-    <t>The hotel's own restaurant, on your last night — worth reserving ahead given the brand.</t>
+    <t>Capri ferry — Sorrento → Capri return, Sep 2</t>
+  </si>
+  <si>
+    <t>About 25 minutes each way from Marina Piccola, directly below the hotel lift. Book both legs online the night before and note the last sailing back. The round-the-island boat can be picked up at Capri's Marina Grande on the day.</t>
+  </si>
+  <si>
+    <t>Coast ferries — Positano (Sep 3) and Amalfi (Sep 4)</t>
+  </si>
+  <si>
+    <t>Both from Sorrento's Marina Piccola, seasonal but well inside the window. Two or three morning departures down the coast and two or three back in the afternoon — check the current timetable close to the date, the schedules shift with the season.</t>
+  </si>
+  <si>
+    <t>Amalfi → Ravello → Sorrento driver, Sep 4</t>
+  </si>
+  <si>
+    <t>Picks you up in Amalfi after lunch, waits at Ravello's gate (the town is car-free), and drives you back over the pass. Roughly 2 hours of driving in total.</t>
+  </si>
+  <si>
+    <t>Ravello Festival — check the Sep 4 programme</t>
+  </si>
+  <si>
+    <t>The festival runs to Sep 5, so your Ravello day is inside the window. A concert on the Villa Rufolo stage is the one thing worth reshaping the evening for — but it means a 1h30 drive back to Sorrento afterwards.</t>
   </si>
   <si>
     <t>Headline dinners on their dates</t>
   </si>
   <si>
-    <t>Caruso Roof Garden Aug 27 · Palazzo Petrucci Aug 28 · Dei Cappuccini Aug 29 · Borgo San Jacopo Sep 1 · Sostanza Sep 2 · La Via del Sale Sep 3 &amp; 4. Plus Armando, Roscioli, Da Enzo, Lo Scoglio — reserve ahead where they take bookings.</t>
+    <t>Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Terrazza Bosquet Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Terrazza Bosquet are the two to book first.</t>
   </si>
   <si>
     <t>RULED OUT</t>
@@ -1315,13 +1330,25 @@
     <t>Arena di Verona — Aida (Zeffirelli), Sep 4 &amp; 10</t>
   </si>
   <si>
-    <t>No open night in the schedule for a Verona detour — every night from Aug 24 to Sep 5 has a confirmed hotel booking elsewhere.</t>
-  </si>
-  <si>
-    <t>Volterra</t>
-  </si>
-  <si>
-    <t>Fit fine as a full day when Tuscany was three nights; with the coast now taking a night from it, San Gimignano and the horseback vineyard tour fill the single Tuscan day instead.</t>
+    <t>No open night in the schedule for a Verona detour — every night from Aug 24 to Sep 5 has a hotel booked elsewhere.</t>
+  </si>
+  <si>
+    <t>A night in Naples</t>
+  </si>
+  <si>
+    <t>Dropped in the replan. Naples is now a change of trains on the way down and on the way back — the five nights it would have cost go to the single coast base instead.</t>
+  </si>
+  <si>
+    <t>Volterra, and a second Tuscan wine estate</t>
+  </si>
+  <si>
+    <t>Tuscany is two nights. San Gimignano and the horseback vineyard tour fill the one full day there.</t>
+  </si>
+  <si>
+    <t>Positano or Amalfi as the base</t>
+  </si>
+  <si>
+    <t>Both are beautiful and both are stairs. With one of you working four days out of five, Sorrento wins on flat ground, a real town, fibre, and ferries to everywhere else on the coast.</t>
   </si>
   <si>
     <t>Location</t>
@@ -1348,7 +1375,7 @@
     <t>小红书</t>
   </si>
   <si>
-    <t>Days 1–3</t>
+    <t>Days 1–3 and 13</t>
   </si>
   <si>
     <t>Flytographer Rome / Localgrapher</t>
@@ -1369,13 +1396,46 @@
     <t>小红书 -&gt;</t>
   </si>
   <si>
-    <t>Days 6–8</t>
+    <t>Days 4–5</t>
+  </si>
+  <si>
+    <t>Flytographer Florence / Localgrapher</t>
+  </si>
+  <si>
+    <t>Piazzale Michelangelo at sunset; Ponte Vecchio at dawn; the Boboli terraces; the Uffizi loggia</t>
+  </si>
+  <si>
+    <t>小红书: 佛罗伦萨旅拍</t>
+  </si>
+  <si>
+    <t>Tuscany / San Gimignano</t>
+  </si>
+  <si>
+    <t>Days 6–7</t>
+  </si>
+  <si>
+    <t>Flytographer Tuscany / Localgrapher</t>
+  </si>
+  <si>
+    <t>San Gimignano's towers at golden hour; the Castelfalfi vineyards and golf course; on horseback in the vines outside town</t>
+  </si>
+  <si>
+    <t>小红书: 托斯卡纳旅拍</t>
+  </si>
+  <si>
+    <t>~$425 / 60 min</t>
+  </si>
+  <si>
+    <t>Sorrento &amp; Positano</t>
+  </si>
+  <si>
+    <t>Days 8–12</t>
   </si>
   <si>
     <t>Flytographer Amalfi / Giuseppe Di Martino</t>
   </si>
   <si>
-    <t>Positano's pastel stairs, seen from the ferry; the Ravello gardens; Amalfi's Duomo steps</t>
+    <t>The Excelsior Vittoria's citrus gardens and cliff terrace; Marina Grande's fishing boats; Positano's pastel stairs from the water; the Villa Comunale balcony at sunset</t>
   </si>
   <si>
     <t>小红书: 阿马尔菲/positano旅拍</t>
@@ -1384,40 +1444,10 @@
     <t>~$325–425</t>
   </si>
   <si>
-    <t>Days 8–11</t>
-  </si>
-  <si>
-    <t>Flytographer Florence / Localgrapher</t>
-  </si>
-  <si>
-    <t>Piazzale Michelangelo at sunset; Ponte Vecchio at dawn; the Fiesole hillside; the Uffizi loggia</t>
-  </si>
-  <si>
-    <t>小红书: 佛罗伦萨旅拍</t>
-  </si>
-  <si>
-    <t>Tuscany / San Gimignano</t>
-  </si>
-  <si>
-    <t>Days 11–13</t>
-  </si>
-  <si>
-    <t>Flytographer Tuscany / Localgrapher</t>
-  </si>
-  <si>
-    <t>San Gimignano's towers at golden hour; the Castelfalfi vineyards and golf course; on horseback in the vines outside town</t>
-  </si>
-  <si>
-    <t>小红书: 托斯卡纳旅拍</t>
-  </si>
-  <si>
-    <t>~$425 / 60 min</t>
-  </si>
-  <si>
     <t>Capri</t>
   </si>
   <si>
-    <t>Day 5, optional</t>
+    <t>Day 10, optional</t>
   </si>
   <si>
     <t>Flytographer Capri</t>
@@ -2109,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2681,10 +2711,10 @@
         <v>125</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2695,16 +2725,16 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" t="s">
-        <v>48</v>
+        <v>130</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2715,16 +2745,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" t="s">
-        <v>48</v>
+        <v>132</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2735,16 +2765,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F36" t="s">
-        <v>48</v>
+        <v>134</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2755,27 +2785,56 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E37" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
-        <v>5</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>133</v>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2786,56 +2845,27 @@
         <v>48</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="F42" t="s">
-        <v>48</v>
+        <v>144</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
+        <v>5</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,16 +2876,16 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,16 +2896,16 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>104</v>
+        <v>88</v>
+      </c>
+      <c r="F44" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2886,16 +2916,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F45" t="s">
-        <v>48</v>
+        <v>134</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2906,30 +2936,56 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="10">
-        <v>6</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>115</v>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2940,13 +2996,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
@@ -2960,16 +3016,16 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F50" t="s">
-        <v>48</v>
+        <v>86</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2980,56 +3036,30 @@
         <v>48</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="F52" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F53" t="s">
-        <v>48</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="10">
+        <v>6</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3040,13 +3070,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3060,13 +3090,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -3080,16 +3110,16 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F56" t="s">
-        <v>48</v>
+        <v>175</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3100,27 +3130,56 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="10">
-        <v>7</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>170</v>
+        <v>88</v>
+      </c>
+      <c r="F57" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F58" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3131,16 +3190,16 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F60" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3151,16 +3210,16 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>71</v>
+        <v>60</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3171,13 +3230,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="F62" t="s">
         <v>48</v>
@@ -3191,56 +3250,27 @@
         <v>48</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>48</v>
-      </c>
-      <c r="B64" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>185</v>
+        <v>63</v>
+      </c>
+      <c r="F63" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>7</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3251,30 +3281,56 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="10">
-        <v>8</v>
-      </c>
-      <c r="B68" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F66" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="D67" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F68" s="14" t="s">
-        <v>115</v>
+      <c r="E67" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F67" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3285,13 +3341,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3305,16 +3361,16 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F70" t="s">
-        <v>48</v>
+        <v>196</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3325,13 +3381,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3345,16 +3401,16 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>121</v>
+        <v>63</v>
+      </c>
+      <c r="F72" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3365,67 +3421,70 @@
         <v>48</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
+        <v>8</v>
+      </c>
+      <c r="B75" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="C75" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E73" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F73" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>48</v>
-      </c>
-      <c r="B74" t="s">
-        <v>48</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="F75" s="14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="D76" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>48</v>
-      </c>
-      <c r="B75" t="s">
-        <v>48</v>
-      </c>
-      <c r="C75" s="12" t="s">
+      <c r="E76" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F76" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="E77" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="E75" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F75" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="10">
-        <v>9</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>208</v>
+      <c r="F77" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3436,16 +3495,16 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>77</v>
+        <v>137</v>
+      </c>
+      <c r="F78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3456,16 +3515,16 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3476,13 +3535,13 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F80" t="s">
         <v>48</v>
@@ -3496,16 +3555,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>77</v>
+        <v>214</v>
+      </c>
+      <c r="F81" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,16 +3575,16 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3536,16 +3595,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>77</v>
+        <v>63</v>
+      </c>
+      <c r="F83" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3556,13 +3615,13 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F84" t="s">
         <v>48</v>
@@ -3576,47 +3635,47 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>224</v>
+        <v>68</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F85" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>48</v>
-      </c>
-      <c r="B86" t="s">
-        <v>48</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F86" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
-        <v>10</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>230</v>
+    <row r="87" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="10">
+        <v>9</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>48</v>
+      </c>
+      <c r="B88" t="s">
+        <v>48</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F88" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3627,13 +3686,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3647,16 +3706,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F90" t="s">
-        <v>48</v>
+        <v>137</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3667,16 +3726,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>122</v>
+        <v>226</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F91" t="s">
-        <v>48</v>
+        <v>144</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3687,13 +3746,13 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>232</v>
+        <v>63</v>
       </c>
       <c r="F92" t="s">
         <v>48</v>
@@ -3707,13 +3766,13 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F93" t="s">
         <v>48</v>
@@ -3727,56 +3786,27 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F94" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>48</v>
-      </c>
-      <c r="B95" t="s">
-        <v>48</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F95" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" t="s">
-        <v>48</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F96" t="s">
-        <v>48</v>
+        <v>134</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
+        <v>10</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3787,16 +3817,16 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>77</v>
+        <v>234</v>
+      </c>
+      <c r="F97" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3807,30 +3837,56 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>48</v>
+      </c>
+      <c r="B99" t="s">
+        <v>48</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F99" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>48</v>
+      </c>
+      <c r="B100" t="s">
+        <v>48</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E100" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="E98" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="F98" s="7" t="s">
+      <c r="F100" s="7" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="10">
-        <v>11</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3841,16 +3897,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="F101" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3861,13 +3917,13 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>48</v>
@@ -3881,16 +3937,16 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>104</v>
+        <v>63</v>
+      </c>
+      <c r="F103" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3901,56 +3957,27 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F104" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>48</v>
-      </c>
-      <c r="B105" t="s">
-        <v>48</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F105" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>48</v>
-      </c>
-      <c r="B106" t="s">
-        <v>48</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F106" t="s">
-        <v>48</v>
+        <v>130</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
+        <v>11</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3961,16 +3988,16 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>256</v>
+        <v>63</v>
+      </c>
+      <c r="F107" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3981,16 +4008,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F108" t="s">
-        <v>48</v>
+        <v>252</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4001,13 +4028,13 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F109" t="s">
         <v>48</v>
@@ -4021,27 +4048,56 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F110" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="10">
-        <v>12</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>262</v>
+        <v>88</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>48</v>
+      </c>
+      <c r="B111" t="s">
+        <v>48</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F111" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" t="s">
+        <v>48</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F112" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4052,13 +4108,13 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4072,13 +4128,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4092,56 +4148,27 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>265</v>
+        <v>110</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F115" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>48</v>
-      </c>
-      <c r="B116" t="s">
-        <v>48</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F116" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>48</v>
-      </c>
-      <c r="B117" t="s">
-        <v>48</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>256</v>
+        <v>144</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="10">
+        <v>12</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4152,13 +4179,13 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -4172,16 +4199,16 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F119" t="s">
-        <v>48</v>
+        <v>266</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4192,30 +4219,56 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="122" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="10">
-        <v>13</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="F122" s="14" t="s">
-        <v>115</v>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>48</v>
+      </c>
+      <c r="B121" t="s">
+        <v>48</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F121" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" t="s">
+        <v>48</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4226,13 +4279,13 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="F123" t="s">
         <v>48</v>
@@ -4246,16 +4299,16 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>141</v>
+        <v>274</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="F124" t="s">
-        <v>48</v>
+        <v>276</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,16 +4319,16 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F125" t="s">
-        <v>48</v>
+      <c r="F125" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4286,16 +4339,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E126" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="D126" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>121</v>
+      <c r="F126" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4306,56 +4359,30 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="D127" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="10">
+        <v>13</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C129" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="E127" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F127" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>48</v>
-      </c>
-      <c r="B128" t="s">
-        <v>48</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>48</v>
-      </c>
-      <c r="B129" t="s">
-        <v>48</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F129" t="s">
-        <v>48</v>
+      <c r="F129" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4366,10 +4393,10 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>63</v>
@@ -4386,27 +4413,56 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D131" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="F131" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>48</v>
+      </c>
+      <c r="B132" t="s">
+        <v>48</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F132" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>48</v>
+      </c>
+      <c r="B133" t="s">
+        <v>48</v>
+      </c>
+      <c r="C133" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="E131" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F131" s="7" t="s">
+      <c r="D133" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="133" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="10">
-        <v>14</v>
-      </c>
-      <c r="B133" s="10" t="s">
+      <c r="E133" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="C133" s="11" t="s">
-        <v>290</v>
+      <c r="F133" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4417,13 +4473,13 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>291</v>
+        <v>52</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F134" t="s">
         <v>48</v>
@@ -4437,16 +4493,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="F135" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4457,15 +4513,146 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="F136" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F137" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>48</v>
+      </c>
+      <c r="B138" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="E138" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F138" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>48</v>
+      </c>
+      <c r="B139" t="s">
+        <v>48</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="E136" s="13" t="s">
+      <c r="E139" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="10">
+        <v>14</v>
+      </c>
+      <c r="B141" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="F136" t="s">
+      <c r="C141" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>48</v>
+      </c>
+      <c r="B142" t="s">
+        <v>48</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F142" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" t="s">
+        <v>48</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="F143" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>48</v>
+      </c>
+      <c r="B144" t="s">
+        <v>48</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="F144" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4484,34 +4671,40 @@
     <hyperlink ref="F27" r:id="rId11"/>
     <hyperlink ref="F31" r:id="rId12"/>
     <hyperlink ref="F33" r:id="rId13"/>
-    <hyperlink ref="F37" r:id="rId14"/>
-    <hyperlink ref="F41" r:id="rId15"/>
-    <hyperlink ref="F43" r:id="rId16"/>
-    <hyperlink ref="F44" r:id="rId17"/>
-    <hyperlink ref="F46" r:id="rId18"/>
-    <hyperlink ref="F51" r:id="rId19"/>
-    <hyperlink ref="F57" r:id="rId20"/>
-    <hyperlink ref="F61" r:id="rId21"/>
-    <hyperlink ref="F63" r:id="rId22"/>
-    <hyperlink ref="F64" r:id="rId23"/>
-    <hyperlink ref="F65" r:id="rId24"/>
-    <hyperlink ref="F66" r:id="rId25"/>
-    <hyperlink ref="F72" r:id="rId26"/>
-    <hyperlink ref="F74" r:id="rId27"/>
-    <hyperlink ref="F78" r:id="rId28"/>
-    <hyperlink ref="F79" r:id="rId29"/>
-    <hyperlink ref="F81" r:id="rId30"/>
-    <hyperlink ref="F82" r:id="rId31"/>
-    <hyperlink ref="F83" r:id="rId32"/>
-    <hyperlink ref="F86" r:id="rId33"/>
-    <hyperlink ref="F97" r:id="rId34"/>
-    <hyperlink ref="F98" r:id="rId35"/>
-    <hyperlink ref="F103" r:id="rId36"/>
-    <hyperlink ref="F107" r:id="rId37"/>
-    <hyperlink ref="F117" r:id="rId38"/>
-    <hyperlink ref="F126" r:id="rId39"/>
-    <hyperlink ref="F128" r:id="rId40"/>
-    <hyperlink ref="F131" r:id="rId41"/>
+    <hyperlink ref="F34" r:id="rId14"/>
+    <hyperlink ref="F35" r:id="rId15"/>
+    <hyperlink ref="F36" r:id="rId16"/>
+    <hyperlink ref="F40" r:id="rId17"/>
+    <hyperlink ref="F43" r:id="rId18"/>
+    <hyperlink ref="F45" r:id="rId19"/>
+    <hyperlink ref="F46" r:id="rId20"/>
+    <hyperlink ref="F47" r:id="rId21"/>
+    <hyperlink ref="F50" r:id="rId22"/>
+    <hyperlink ref="F51" r:id="rId23"/>
+    <hyperlink ref="F56" r:id="rId24"/>
+    <hyperlink ref="F60" r:id="rId25"/>
+    <hyperlink ref="F70" r:id="rId26"/>
+    <hyperlink ref="F79" r:id="rId27"/>
+    <hyperlink ref="F82" r:id="rId28"/>
+    <hyperlink ref="F85" r:id="rId29"/>
+    <hyperlink ref="F90" r:id="rId30"/>
+    <hyperlink ref="F91" r:id="rId31"/>
+    <hyperlink ref="F94" r:id="rId32"/>
+    <hyperlink ref="F98" r:id="rId33"/>
+    <hyperlink ref="F100" r:id="rId34"/>
+    <hyperlink ref="F101" r:id="rId35"/>
+    <hyperlink ref="F104" r:id="rId36"/>
+    <hyperlink ref="F108" r:id="rId37"/>
+    <hyperlink ref="F110" r:id="rId38"/>
+    <hyperlink ref="F115" r:id="rId39"/>
+    <hyperlink ref="F119" r:id="rId40"/>
+    <hyperlink ref="F122" r:id="rId41"/>
+    <hyperlink ref="F124" r:id="rId42"/>
+    <hyperlink ref="F125" r:id="rId43"/>
+    <hyperlink ref="F127" r:id="rId44"/>
+    <hyperlink ref="F133" r:id="rId45"/>
+    <hyperlink ref="F135" r:id="rId46"/>
+    <hyperlink ref="F139" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4520,7 +4713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -4534,42 +4727,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C2" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4587,178 +4780,149 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" s="15">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="H3" s="15">
-        <v>1180</v>
+        <v>1236</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" s="15">
-        <v>2057.87</v>
+        <v>920.5</v>
       </c>
       <c r="H4" s="15">
-        <v>4115.74</v>
+        <v>1841</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B5" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="15">
+        <v>1150</v>
+      </c>
+      <c r="H5" s="15">
+        <v>5750</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="D5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" s="15">
-        <v>497.33</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1492</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D6" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="15">
-        <v>1424</v>
+        <v>527</v>
       </c>
       <c r="H6" s="15">
-        <v>2848</v>
+        <v>527</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>324</v>
-      </c>
-      <c r="B7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E7" t="s">
-        <v>289</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>874</v>
-      </c>
-      <c r="H7" s="15">
-        <v>874</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="F8" s="16">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="16">
         <v>13</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="17">
-        <v>12097.74</v>
+      <c r="G7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="17">
+        <v>10942</v>
       </c>
     </row>
   </sheetData>
@@ -4768,7 +4932,6 @@
     <hyperlink ref="I4" r:id="rId3"/>
     <hyperlink ref="I5" r:id="rId4"/>
     <hyperlink ref="I6" r:id="rId5"/>
-    <hyperlink ref="I7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4787,24 +4950,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B2" s="15">
-        <v>12097.74</v>
+        <v>10942</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4812,54 +4975,54 @@
         <v>12</v>
       </c>
       <c r="B3" s="15">
-        <v>1850</v>
+        <v>1650</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B7" s="17">
-        <v>18797.739999999998</v>
+        <v>17442</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4884,220 +5047,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>273</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="D4" t="s">
-        <v>355</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B5" t="s">
-        <v>357</v>
+        <v>172</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>368</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D7" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D8" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B9" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D9" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>378</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D10" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B11" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D11" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B12" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D12" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D13" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5108,7 +5271,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -5133,7 +5296,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5144,16 +5307,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5164,16 +5327,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5181,16 +5344,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5198,16 +5361,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5215,16 +5378,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>392</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5232,16 +5395,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5249,16 +5412,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>405</v>
+        <v>410</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>399</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5266,16 +5429,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>405</v>
+        <v>412</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>413</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5283,16 +5446,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>405</v>
+        <v>415</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>413</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5300,16 +5463,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>405</v>
+        <v>417</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>413</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5317,16 +5480,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>405</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5334,16 +5497,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5351,16 +5514,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5368,16 +5531,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>392</v>
+        <v>426</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>422</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5385,16 +5548,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5402,16 +5565,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5419,41 +5582,35 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>428</v>
+      <c r="B20" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5461,10 +5618,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5472,10 +5629,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5483,10 +5640,21 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -5507,7 +5675,6 @@
     <hyperlink ref="E15" r:id="rId14"/>
     <hyperlink ref="E16" r:id="rId15"/>
     <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5530,158 +5697,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C2" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E2" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C3" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E3" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="F3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>463</v>
       </c>
       <c r="B4" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C4" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F4" t="s">
+        <v>468</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" s="7" t="s">
         <v>458</v>
-      </c>
-      <c r="F4" t="s">
-        <v>447</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B5" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="C5" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="E5" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="F5" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B6" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="C6" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="E6" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="F6" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5695,7 +5862,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="483">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -673,9 +673,15 @@
     <t>The citrus gardens, then the lift to the sea — Unpack properly — this is home for five nights</t>
   </si>
   <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
     <t>Aperitivo on the terrace over the bay — Vesuvius on the far shore, and it goes pink at sunset</t>
   </si>
   <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
     <t>Dinner — Terrazza Bosquet — The hotel's Michelin-starred room, on the terrace. Worth booking for the first night rather than the last.</t>
   </si>
   <si>
@@ -709,7 +715,7 @@
     <t>Swim, or the pool on the cliff — The private lift drops you at Marina Piccola if you want salt water instead</t>
   </si>
   <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it.</t>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
   </si>
   <si>
     <t>Wed, Sep 2</t>
@@ -796,13 +802,13 @@
     <t>Desk hours</t>
   </si>
   <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Sunset from the Villa Comunale terrace — A public balcony on the cliff edge, two minutes from the hotel, straight out over the Bay of Naples</t>
-  </si>
-  <si>
-    <t>Dinner — Da Emilia, Marina Grande — Sixty years old, plastic chairs on the harbour, and the best simple fish in Sorrento</t>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
   </si>
   <si>
     <t>Fri, Sep 4</t>
@@ -850,13 +856,13 @@
     <t>On foot; Ravello is car-free</t>
   </si>
   <si>
+    <t>3:50pm</t>
+  </si>
+  <si>
     <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
   </si>
   <si>
-    <t>5:45pm</t>
-  </si>
-  <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way</t>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
   </si>
   <si>
     <t>Private driver, ~1h30</t>
@@ -3615,10 +3621,10 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>64</v>
+        <v>218</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>63</v>
@@ -3635,10 +3641,10 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>68</v>
+        <v>220</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>63</v>
@@ -3652,10 +3658,10 @@
         <v>9</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3669,7 +3675,7 @@
         <v>116</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E88" s="13" t="s">
         <v>63</v>
@@ -3689,10 +3695,10 @@
         <v>189</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3709,7 +3715,7 @@
         <v>194</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E90" s="13" t="s">
         <v>137</v>
@@ -3726,10 +3732,10 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>144</v>
@@ -3749,7 +3755,7 @@
         <v>81</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E92" s="13" t="s">
         <v>63</v>
@@ -3766,10 +3772,10 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>63</v>
@@ -3786,10 +3792,10 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E94" s="13" t="s">
         <v>134</v>
@@ -3803,10 +3809,10 @@
         <v>10</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3820,10 +3826,10 @@
         <v>203</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F97" t="s">
         <v>48</v>
@@ -3837,16 +3843,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,13 +3863,13 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F99" t="s">
         <v>48</v>
@@ -3877,13 +3883,13 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>71</v>
@@ -3900,7 +3906,7 @@
         <v>81</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>60</v>
@@ -3920,10 +3926,10 @@
         <v>159</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F102" t="s">
         <v>48</v>
@@ -3940,7 +3946,7 @@
         <v>138</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E103" s="13" t="s">
         <v>63</v>
@@ -3957,10 +3963,10 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>68</v>
+        <v>220</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>130</v>
@@ -3974,10 +3980,10 @@
         <v>11</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3991,7 +3997,7 @@
         <v>116</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E107" s="13" t="s">
         <v>63</v>
@@ -4011,13 +4017,13 @@
         <v>151</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,7 +4037,7 @@
         <v>194</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E109" s="13" t="s">
         <v>57</v>
@@ -4048,10 +4054,10 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>88</v>
@@ -4071,10 +4077,10 @@
         <v>55</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
@@ -4091,10 +4097,10 @@
         <v>58</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4111,7 +4117,7 @@
         <v>102</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E113" s="13" t="s">
         <v>63</v>
@@ -4128,10 +4134,10 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>126</v>
@@ -4148,16 +4154,16 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4165,10 +4171,10 @@
         <v>12</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,10 +4188,10 @@
         <v>147</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -4202,13 +4208,13 @@
         <v>96</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4222,10 +4228,10 @@
         <v>151</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
@@ -4239,10 +4245,10 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>88</v>
@@ -4262,7 +4268,7 @@
         <v>153</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>88</v>
@@ -4282,10 +4288,10 @@
         <v>156</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F123" t="s">
         <v>48</v>
@@ -4299,13 +4305,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>77</v>
@@ -4319,10 +4325,10 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>159</v>
+        <v>279</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>88</v>
@@ -4339,13 +4345,13 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F126" t="s">
         <v>48</v>
@@ -4359,10 +4365,10 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>89</v>
+        <v>220</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E127" s="13" t="s">
         <v>137</v>
@@ -4376,10 +4382,10 @@
         <v>13</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F129" s="14" t="s">
         <v>115</v>
@@ -4396,7 +4402,7 @@
         <v>169</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>63</v>
@@ -4416,7 +4422,7 @@
         <v>118</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E131" s="13" t="s">
         <v>214</v>
@@ -4436,7 +4442,7 @@
         <v>192</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E132" s="13" t="s">
         <v>57</v>
@@ -4453,13 +4459,13 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>121</v>
@@ -4476,7 +4482,7 @@
         <v>52</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>98</v>
@@ -4493,10 +4499,10 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E135" s="13" t="s">
         <v>57</v>
@@ -4516,10 +4522,10 @@
         <v>58</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F136" t="s">
         <v>48</v>
@@ -4536,7 +4542,7 @@
         <v>84</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E137" s="13" t="s">
         <v>132</v>
@@ -4556,7 +4562,7 @@
         <v>183</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>63</v>
@@ -4576,7 +4582,7 @@
         <v>68</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E139" s="13" t="s">
         <v>76</v>
@@ -4590,10 +4596,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4604,10 +4610,10 @@
         <v>48</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E142" s="13" t="s">
         <v>83</v>
@@ -4624,13 +4630,13 @@
         <v>48</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F143" t="s">
         <v>48</v>
@@ -4644,13 +4650,13 @@
         <v>48</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F144" t="s">
         <v>48</v>
@@ -4727,42 +4733,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4780,18 +4786,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
@@ -4809,18 +4815,18 @@
         <v>1236</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
         <v>167</v>
@@ -4838,24 +4844,24 @@
         <v>1841</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D5" t="s">
         <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4867,24 +4873,24 @@
         <v>5750</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4896,7 +4902,7 @@
         <v>527</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4913,7 +4919,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -4950,24 +4956,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B2" s="15">
         <v>10942</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,51 +4984,51 @@
         <v>1650</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B7" s="17">
         <v>17442</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -5047,220 +5053,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="D3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="D3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B5" t="s">
         <v>172</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B6" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B12" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5271,7 +5277,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -5307,16 +5313,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5327,16 +5333,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5344,16 +5350,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>402</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5361,16 +5367,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5378,16 +5384,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5395,16 +5401,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5412,16 +5418,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,16 +5435,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5446,16 +5452,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>413</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,16 +5469,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5480,16 +5486,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5497,16 +5503,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5514,16 +5520,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>424</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>422</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5531,16 +5537,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5548,16 +5554,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,16 +5571,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5582,16 +5588,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5599,7 +5605,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5607,10 +5613,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5618,10 +5624,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5629,10 +5635,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5640,10 +5646,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5651,10 +5657,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -5697,158 +5703,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" s="7" t="s">
         <v>460</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="E3" t="s">
-        <v>462</v>
-      </c>
-      <c r="F3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5862,7 +5868,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -559,7 +559,7 @@
     <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
   </si>
   <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre</t>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
   </si>
   <si>
     <t>Book -&gt;</t>
@@ -1039,7 +1039,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>5 hotels, 13 nights. Confirmed or quoted: Trame ($1,588), W Florence ($1,236), Castelfalfi ($1,841), InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $6,906 if you hold the old $12,098 lodging total.</t>
+    <t>5 hotels, 13 nights. Confirmed: Trame ($1,588), Castelfalfi ($2,132, Deluxe Room with breakfast). Quoted: W Florence ($1,236), InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $6,615 if you hold the old $12,098 lodging total.</t>
   </si>
   <si>
     <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
@@ -1219,7 +1219,7 @@
     <t>Book the Sorrento hotel — five nights, Aug 31 → Sep 5</t>
   </si>
   <si>
-    <t>The one open booking left, and the biggest single line in the budget. Holding the old lodging total leaves $6,906 for these five nights, or about $1,381 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands ~$1,150 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
+    <t>The one open booking left, and the biggest single line in the budget. The other four now cost $5,483, so holding the old $12,098 lodging total leaves $6,615 for these five nights — about $1,323 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $865 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
   </si>
   <si>
     <t>DO NOW</t>
@@ -4838,10 +4838,10 @@
         <v>2</v>
       </c>
       <c r="G4" s="15">
-        <v>920.5</v>
+        <v>1066</v>
       </c>
       <c r="H4" s="15">
-        <v>1841</v>
+        <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>322</v>
@@ -4928,7 +4928,7 @@
         <v>48</v>
       </c>
       <c r="H7" s="17">
-        <v>10942</v>
+        <v>11233</v>
       </c>
     </row>
   </sheetData>
@@ -4970,7 +4970,7 @@
         <v>339</v>
       </c>
       <c r="B2" s="15">
-        <v>10942</v>
+        <v>11233</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>340</v>
@@ -5025,7 +5025,7 @@
         <v>335</v>
       </c>
       <c r="B7" s="17">
-        <v>17442</v>
+        <v>17733</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>348</v>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -394,7 +394,7 @@
     <t>11:05am</t>
   </si>
   <si>
-    <t>Drop bags — W Florence — Piazza dell'Unità Italiana, a two-minute walk from the station door. Rooms are ready from 3:00pm; they'll hold the luggage.</t>
+    <t>Drop bags — W Florence — Piazza dell'Unità Italiana 4/B, a two-minute walk from the station door. Rooms are ready from 3:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
   </si>
   <si>
     <t>Walk, ~3 min</t>
@@ -1039,7 +1039,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>5 hotels, 13 nights. Confirmed: Trame ($1,588), Castelfalfi ($2,132, Deluxe Room with breakfast). Quoted: W Florence ($1,236), InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $6,615 if you hold the old $12,098 lodging total.</t>
+    <t>5 hotels, 13 nights. Confirmed: Trame ($1,588), W Florence ($1,533, room only, paid in euros at the property), Castelfalfi ($2,132, Deluxe Room with breakfast). Quoted: InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $6,318 if you hold the old $12,098 lodging total.</t>
   </si>
   <si>
     <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
@@ -1219,7 +1219,7 @@
     <t>Book the Sorrento hotel — five nights, Aug 31 → Sep 5</t>
   </si>
   <si>
-    <t>The one open booking left, and the biggest single line in the budget. The other four now cost $5,483, so holding the old $12,098 lodging total leaves $6,615 for these five nights — about $1,323 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $865 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
+    <t>The one open booking left, and the biggest single line in the budget. The other four now cost $5,780, so holding the old $12,098 lodging total leaves $6,318 for these five nights — about $1,264 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $568 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
   </si>
   <si>
     <t>DO NOW</t>
@@ -4809,10 +4809,10 @@
         <v>2</v>
       </c>
       <c r="G3" s="15">
-        <v>618</v>
+        <v>766.5</v>
       </c>
       <c r="H3" s="15">
-        <v>1236</v>
+        <v>1533</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>322</v>
@@ -4928,7 +4928,7 @@
         <v>48</v>
       </c>
       <c r="H7" s="17">
-        <v>11233</v>
+        <v>11530</v>
       </c>
     </row>
   </sheetData>
@@ -4970,7 +4970,7 @@
         <v>339</v>
       </c>
       <c r="B2" s="15">
-        <v>11233</v>
+        <v>11530</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>340</v>
@@ -5025,7 +5025,7 @@
         <v>335</v>
       </c>
       <c r="B7" s="17">
-        <v>17733</v>
+        <v>18030</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>348</v>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="484">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → W Florence (Marriott Luxury) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Grand Hotel Excelsior Vittoria (Sorrento, Leading Hotels of the World) → InterContinental Rome Ambasciatori Palace (IHG)</t>
+    <t>Hotel Trame (Rome, independent) → The Hoxton, Florence (Ennismore) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Grand Hotel Excelsior Vittoria (Sorrento, Leading Hotels of the World) → InterContinental Rome Ambasciatori Palace (IHG)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -394,420 +394,423 @@
     <t>11:05am</t>
   </si>
   <si>
-    <t>Drop bags — W Florence — Piazza dell'Unità Italiana 4/B, a two-minute walk from the station door. Rooms are ready from 3:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+  </si>
+  <si>
+    <t>Taxi, ~8 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>11:45am</t>
+  </si>
+  <si>
+    <t>Lunch — Trattoria Mario, by San Lorenzo — Shared tables, cash, closed by 3:30pm. Mercato Centrale upstairs is the no-queue fallback.</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Accademia — David at the afternoon slot — Forty-five minutes is genuinely enough. Go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>4:30pm</t>
+  </si>
+  <si>
+    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
+  </si>
+  <si>
+    <t>Walk, ~14 min</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to the river</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>2:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Coffee, then the platform</t>
+  </si>
+  <si>
+    <t>10:52am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Naples — Firenze S.M.N. → Napoli Centrale, direct via Rome — about 3 hours. Book this one ahead; it's the leg where a good fare is worth having.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~3 hrs</t>
+  </si>
+  <si>
+    <t>1:50pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse</t>
+  </si>
+  <si>
+    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h15</t>
+  </si>
+  <si>
+    <t>3:40pm</t>
+  </si>
+  <si>
+    <t>Check in — Grand Hotel Excelsior Vittoria — Piazza Tasso, on the cliff over Marina Piccola. Five acres of citrus garden behind it and a private lift straight down to the water.</t>
+  </si>
+  <si>
+    <t>The citrus gardens, then the lift to the sea — Unpack properly — this is home for five nights</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo on the terrace over the bay — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Terrazza Bosquet — The hotel's Michelin-starred room, on the terrace. Worth booking for the first night rather than the last.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>Swim, or the pool on the cliff — The private lift drops you at Marina Piccola if you want salt water instead</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola by the hotel lift — The ferry pier is a two-minute walk from where the lift lets you out</t>
+  </si>
+  <si>
+    <t>Hotel lift</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
   </si>
   <si>
     <t>Walk, ~3 min</t>
   </si>
   <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>11:45am</t>
-  </si>
-  <si>
-    <t>Lunch — Trattoria Mario, by San Lorenzo — Shared tables, cash, closed by 3:30pm. Mercato Centrale upstairs is the no-queue fallback.</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Accademia — David at the afternoon slot — Forty-five minutes is genuinely enough. Go straight down the hall of the Prisoners.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>4:30pm</t>
-  </si>
-  <si>
-    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Check in properly and change</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to the river</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>2:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change</t>
-  </si>
-  <si>
-    <t>Walk or taxi</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, about eight minutes on foot from the W and just outside the ZTL — so you never drive into the centro storico. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Coffee, then the platform</t>
-  </si>
-  <si>
-    <t>10:52am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Naples — Firenze S.M.N. → Napoli Centrale, direct via Rome — about 3 hours. Book this one ahead; it's the leg where a good fare is worth having.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~3 hrs</t>
-  </si>
-  <si>
-    <t>1:50pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse</t>
-  </si>
-  <si>
-    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h15</t>
-  </si>
-  <si>
-    <t>3:40pm</t>
-  </si>
-  <si>
-    <t>Check in — Grand Hotel Excelsior Vittoria — Piazza Tasso, on the cliff over Marina Piccola. Five acres of citrus garden behind it and a private lift straight down to the water.</t>
-  </si>
-  <si>
-    <t>The citrus gardens, then the lift to the sea — Unpack properly — this is home for five nights</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo on the terrace over the bay — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Terrazza Bosquet — The hotel's Michelin-starred room, on the terrace. Worth booking for the first night rather than the last.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>Swim, or the pool on the cliff — The private lift drops you at Marina Piccola if you want salt water instead</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola by the hotel lift — The ferry pier is a two-minute walk from where the lift lets you out</t>
-  </si>
-  <si>
-    <t>Hotel lift</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
     <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
   </si>
   <si>
@@ -991,10 +994,10 @@
     <t>Florence</t>
   </si>
   <si>
-    <t>W Florence</t>
-  </si>
-  <si>
-    <t>Marriott Luxury</t>
+    <t>The Hoxton, Florence</t>
+  </si>
+  <si>
+    <t>Ennismore</t>
   </si>
   <si>
     <t>Tuscany</t>
@@ -1039,7 +1042,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>5 hotels, 13 nights. Confirmed: Trame ($1,588), W Florence ($1,533, room only, paid in euros at the property), Castelfalfi ($2,132, Deluxe Room with breakfast). Quoted: InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $6,318 if you hold the old $12,098 lodging total.</t>
+    <t>5 hotels, 13 nights. Confirmed: Trame ($1,588), The Hoxton Florence ($693, room only — the W was swapped out for it and saved $840), Castelfalfi ($2,132, Deluxe Room with breakfast). Quoted: InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $7,158 if you hold the old $12,098 lodging total.</t>
   </si>
   <si>
     <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
@@ -1105,7 +1108,7 @@
     <t>Collect the car</t>
   </si>
   <si>
-    <t>Borgo Ognissanti, Florence — outside the ZTL  (Florence pickup, Florence drop-off, two days only — not FCO)</t>
+    <t>Borgo Ognissanti, Florence — outside the ZTL  (Florence pickup, Florence drop-off, two days only — not FCO. Twenty minutes on foot from the Hoxton; taxi with the luggage.)</t>
   </si>
   <si>
     <t>~30 min</t>
@@ -1219,7 +1222,7 @@
     <t>Book the Sorrento hotel — five nights, Aug 31 → Sep 5</t>
   </si>
   <si>
-    <t>The one open booking left, and the biggest single line in the budget. The other four now cost $5,780, so holding the old $12,098 lodging total leaves $6,318 for these five nights — about $1,264 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $568 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
+    <t>The one open booking left, and the biggest single line in the budget. The other four now cost $4,940, so holding the old $12,098 lodging total leaves $7,158 for these five nights — about $1,432 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $1,408 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
   </si>
   <si>
     <t>DO NOW</t>
@@ -2817,7 +2820,7 @@
         <v>139</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
         <v>48</v>
@@ -2888,7 +2891,7 @@
         <v>148</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>77</v>
@@ -2902,10 +2905,10 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>88</v>
@@ -2922,10 +2925,10 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>134</v>
@@ -2942,13 +2945,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>71</v>
@@ -2962,13 +2965,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>77</v>
@@ -2982,10 +2985,10 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>88</v>
@@ -3005,10 +3008,10 @@
         <v>105</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
@@ -3082,7 +3085,7 @@
         <v>170</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3096,7 +3099,7 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>171</v>
@@ -3327,7 +3330,7 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>191</v>
@@ -3501,7 +3504,7 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>207</v>
@@ -3561,7 +3564,7 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>213</v>
@@ -3923,7 +3926,7 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>247</v>
@@ -4014,7 +4017,7 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>253</v>
@@ -4140,7 +4143,7 @@
         <v>262</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>126</v>
+        <v>263</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4157,7 +4160,7 @@
         <v>64</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E115" s="13" t="s">
         <v>130</v>
@@ -4171,10 +4174,10 @@
         <v>12</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4188,7 +4191,7 @@
         <v>147</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>236</v>
@@ -4208,10 +4211,10 @@
         <v>96</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>240</v>
@@ -4225,13 +4228,13 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
@@ -4245,10 +4248,10 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>88</v>
@@ -4265,10 +4268,10 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>88</v>
@@ -4285,13 +4288,13 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F123" t="s">
         <v>48</v>
@@ -4305,13 +4308,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>77</v>
@@ -4325,10 +4328,10 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>88</v>
@@ -4348,10 +4351,10 @@
         <v>84</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F126" t="s">
         <v>48</v>
@@ -4368,7 +4371,7 @@
         <v>220</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E127" s="13" t="s">
         <v>137</v>
@@ -4382,10 +4385,10 @@
         <v>13</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F129" s="14" t="s">
         <v>115</v>
@@ -4402,7 +4405,7 @@
         <v>169</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>63</v>
@@ -4422,7 +4425,7 @@
         <v>118</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E131" s="13" t="s">
         <v>214</v>
@@ -4442,7 +4445,7 @@
         <v>192</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E132" s="13" t="s">
         <v>57</v>
@@ -4459,13 +4462,13 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>121</v>
@@ -4482,7 +4485,7 @@
         <v>52</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>98</v>
@@ -4499,10 +4502,10 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E135" s="13" t="s">
         <v>57</v>
@@ -4522,10 +4525,10 @@
         <v>58</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F136" t="s">
         <v>48</v>
@@ -4542,7 +4545,7 @@
         <v>84</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E137" s="13" t="s">
         <v>132</v>
@@ -4562,7 +4565,7 @@
         <v>183</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>63</v>
@@ -4582,7 +4585,7 @@
         <v>68</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E139" s="13" t="s">
         <v>76</v>
@@ -4596,10 +4599,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4610,10 +4613,10 @@
         <v>48</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E142" s="13" t="s">
         <v>83</v>
@@ -4630,13 +4633,13 @@
         <v>48</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F143" t="s">
         <v>48</v>
@@ -4650,13 +4653,13 @@
         <v>48</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F144" t="s">
         <v>48</v>
@@ -4733,42 +4736,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4786,18 +4789,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
@@ -4809,24 +4812,24 @@
         <v>2</v>
       </c>
       <c r="G3" s="15">
-        <v>766.5</v>
+        <v>346.42</v>
       </c>
       <c r="H3" s="15">
-        <v>1533</v>
+        <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
         <v>167</v>
@@ -4844,24 +4847,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D5" t="s">
         <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4873,24 +4876,24 @@
         <v>5750</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4902,7 +4905,7 @@
         <v>527</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4919,7 +4922,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -4928,7 +4931,7 @@
         <v>48</v>
       </c>
       <c r="H7" s="17">
-        <v>11530</v>
+        <v>10689.83</v>
       </c>
     </row>
   </sheetData>
@@ -4956,24 +4959,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B2" s="15">
-        <v>11530</v>
+        <v>10689.83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4984,51 +4987,51 @@
         <v>1650</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B7" s="17">
-        <v>18030</v>
+        <v>17189.83</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -5053,220 +5056,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="D3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="B3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="D3" t="s">
-        <v>359</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B5" t="s">
         <v>172</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B6" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5277,7 +5280,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -5313,16 +5316,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5333,16 +5336,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5350,16 +5353,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>403</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5367,16 +5370,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5384,16 +5387,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5401,16 +5404,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5418,16 +5421,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5435,16 +5438,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5452,16 +5455,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>415</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5469,16 +5472,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5486,16 +5489,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5503,16 +5506,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5520,16 +5523,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>424</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5537,16 +5540,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5554,16 +5557,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5571,16 +5574,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5588,16 +5591,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5605,7 +5608,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5613,10 +5616,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5624,10 +5627,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5635,10 +5638,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5646,10 +5649,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5657,10 +5660,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -5703,158 +5706,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="E3" t="s">
+        <v>465</v>
+      </c>
+      <c r="F3" t="s">
+        <v>459</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>461</v>
-      </c>
-      <c r="C3" t="s">
-        <v>462</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="E3" t="s">
-        <v>464</v>
-      </c>
-      <c r="F3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5868,7 +5871,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="486">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → The Hoxton, Florence (Ennismore) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Grand Hotel Excelsior Vittoria (Sorrento, Leading Hotels of the World) → InterContinental Rome Ambasciatori Palace (IHG)</t>
+    <t>Hotel Trame (Rome, independent) → The Hoxton, Florence (Ennismore) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Grand Hotel Excelsior Vittoria (Sorrento, Leading Hotels of the World) → Nomos Hotel (Rome, DNA Hotels)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -904,19 +904,25 @@
     <t>1:15pm</t>
   </si>
   <si>
-    <t>Check in — InterContinental Rome Ambasciatori Palace — Via Vittorio Veneto, the La Dolce Vita address, at the Villa Borghese end of the street — five minutes from the gardens you photographed on the first Wednesday</t>
-  </si>
-  <si>
-    <t>Down Via Veneto to the Spanish Steps — Past Palazzo Margherita and the Capuchin crypt, then down to Piazza di Spagna</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
-    <t>Trevi Fountain, one last time — Ten minutes on from the steps, and worth the crowd on a final evening</t>
-  </si>
-  <si>
-    <t>Aperitivo on Via Veneto — The hotel's own bar, or Harry's Bar a few doors down</t>
+    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began at Hotel Trame. Superior Double; nothing is prepaid, you settle €530 with the hotel.</t>
+  </si>
+  <si>
+    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door and the one corner of the centre you haven't walked yet — Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
+  </si>
+  <si>
+    <t>Tiber Island and the Ponte Fabricio — The bridge has carried people across since 62 BC and is still the original stone</t>
+  </si>
+  <si>
+    <t>Trevi Fountain, one last time — Twenty minutes up through the centre, and worth the crowd on a final evening</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min</t>
+  </si>
+  <si>
+    <t>Aperitivo on Campo de' Fiori — The market stalls are long packed away by now and the square turns over to drinking</t>
+  </si>
+  <si>
+    <t>Walk, ~4 min</t>
   </si>
   <si>
     <t>Farewell dinner — Aroma, at Palazzo Manfredi — Michelin-starred, on a rooftop that looks straight into the Colosseum. Book this one early; there are only a dozen tables with the view.</t>
@@ -931,7 +937,7 @@
     <t>6:40am</t>
   </si>
   <si>
-    <t>Taxi to FCO — About forty minutes on an empty Sunday road. No rental to return — that ended in Florence on Aug 31.</t>
+    <t>Taxi to FCO — About thirty-five minutes on an empty Sunday road. No rental to return — that ended in Florence on Aug 31.</t>
   </si>
   <si>
     <t>7:20am</t>
@@ -1021,10 +1027,10 @@
     <t>Rome (finale)</t>
   </si>
   <si>
-    <t>InterContinental Rome Ambasciatori Palace</t>
-  </si>
-  <si>
-    <t>IHG</t>
+    <t>Nomos Hotel</t>
+  </si>
+  <si>
+    <t>DNA Hotels</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -1042,7 +1048,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>5 hotels, 13 nights. Confirmed: Trame ($1,588), The Hoxton Florence ($693, room only — the W was swapped out for it and saved $840), Castelfalfi ($2,132, Deluxe Room with breakfast). Quoted: InterContinental Ambasciatori ($527). The Sorrento base is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $7,158 if you hold the old $12,098 lodging total.</t>
+    <t>5 hotels, 13 nights. Four are now confirmed and settled: Trame ($1,588), The Hoxton Florence ($693, room only), Castelfalfi ($2,132, Deluxe Room with breakfast), Nomos Rome ($658). Sorrento is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $7,027 if you hold the old $12,098 lodging total.</t>
   </si>
   <si>
     <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
@@ -1198,10 +1204,10 @@
     <t>Sep 6</t>
   </si>
   <si>
-    <t>InterContinental Ambasciatori → FCO  (No rental to return — that was dropped off in Florence on Aug 31)</t>
-  </si>
-  <si>
-    <t>~40 min</t>
+    <t>Nomos Hotel, Regola → FCO  (No rental to return — that was dropped off in Florence on Aug 31)</t>
+  </si>
+  <si>
+    <t>~35 min</t>
   </si>
   <si>
     <t>Almost the whole trip is car-free: a private driver in from FCO, the Frecciarossa up to Florence, a two-day rental for Tuscany, then rail to Naples and a driver over the peninsula to Sorrento, where everything after is a ferry. The car is collected on Aug 29 on Borgo Ognissanti — just outside Florence's ZTL, eight minutes on foot from the W — and returned to the same desk on Aug 31 before the train south. Two driving days, not fourteen. The IDP ships by Aug 3; pack it with the physical licence even though it's only needed that once. Never drive into a historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking, and the Excelsior Vittoria's garage is the only place in central Sorrento you'd want to park anyway. The Sorrento–Positano–Amalfi ferries run mid-April to mid-October, so the whole window is covered, but any of them can be cancelled for weather — keep the hotel's driver number as a backup for the Amalfi day.</t>
@@ -1222,7 +1228,7 @@
     <t>Book the Sorrento hotel — five nights, Aug 31 → Sep 5</t>
   </si>
   <si>
-    <t>The one open booking left, and the biggest single line in the budget. The other four now cost $4,940, so holding the old $12,098 lodging total leaves $7,158 for these five nights — about $1,432 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $1,408 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
+    <t>The last open booking, and the biggest single line in the budget. The other four are now all confirmed at $5,071 together, so the ceiling is firm rather than an estimate: holding the old $12,098 lodging total leaves $7,027 for these five nights, about $1,405 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $1,277 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
   </si>
   <si>
     <t>DO NOW</t>
@@ -2148,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4528,7 +4534,7 @@
         <v>296</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>297</v>
+        <v>134</v>
       </c>
       <c r="F136" t="s">
         <v>48</v>
@@ -4542,13 +4548,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4562,13 +4568,13 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="D138" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E138" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="F138" t="s">
         <v>48</v>
@@ -4582,47 +4588,47 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>300</v>
       </c>
       <c r="E139" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F139" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>48</v>
+      </c>
+      <c r="B140" t="s">
+        <v>48</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E140" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F139" s="7" t="s">
+      <c r="F140" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="10">
+    <row r="142" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="10">
         <v>14</v>
       </c>
-      <c r="B141" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>48</v>
-      </c>
-      <c r="B142" t="s">
-        <v>48</v>
-      </c>
-      <c r="C142" s="12" t="s">
+      <c r="B142" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="C142" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="E142" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F142" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,7 +4645,7 @@
         <v>306</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="F143" t="s">
         <v>48</v>
@@ -4653,15 +4659,35 @@
         <v>48</v>
       </c>
       <c r="C144" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="E144" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="E144" s="13" t="s">
+      <c r="F144" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>48</v>
+      </c>
+      <c r="B145" t="s">
+        <v>48</v>
+      </c>
+      <c r="C145" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="F144" t="s">
+      <c r="D145" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F145" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4713,7 +4739,7 @@
     <hyperlink ref="F127" r:id="rId44"/>
     <hyperlink ref="F133" r:id="rId45"/>
     <hyperlink ref="F135" r:id="rId46"/>
-    <hyperlink ref="F139" r:id="rId47"/>
+    <hyperlink ref="F140" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4736,42 +4762,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4789,18 +4815,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
@@ -4818,18 +4844,18 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D4" t="s">
         <v>167</v>
@@ -4847,18 +4873,18 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D5" t="s">
         <v>201</v>
@@ -4876,36 +4902,36 @@
         <v>5750</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D6" t="s">
         <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="15">
-        <v>527</v>
+        <v>658</v>
       </c>
       <c r="H6" s="15">
-        <v>527</v>
+        <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4922,7 +4948,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -4931,7 +4957,7 @@
         <v>48</v>
       </c>
       <c r="H7" s="17">
-        <v>10689.83</v>
+        <v>10820.83</v>
       </c>
     </row>
   </sheetData>
@@ -4959,24 +4985,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B2" s="15">
-        <v>10689.83</v>
+        <v>10820.83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4987,51 +5013,51 @@
         <v>1650</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B7" s="17">
-        <v>17189.83</v>
+        <v>17320.83</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5056,220 +5082,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B2" t="s">
         <v>276</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="D3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>358</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="D3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
         <v>172</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B6" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B8" t="s">
         <v>276</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5280,7 +5306,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5316,16 +5342,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5336,16 +5362,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5353,16 +5379,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5370,16 +5396,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5387,16 +5413,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5404,16 +5430,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5421,16 +5447,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5438,16 +5464,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5455,16 +5481,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>416</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5472,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5489,16 +5515,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5506,16 +5532,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5523,16 +5549,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>427</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>425</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5540,16 +5566,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5557,16 +5583,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5574,16 +5600,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5591,16 +5617,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5608,7 +5634,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5642,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,10 +5653,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5638,10 +5664,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5649,10 +5675,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5660,10 +5686,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -5706,158 +5732,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F3" t="s">
+        <v>461</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" s="7" t="s">
         <v>463</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="E3" t="s">
-        <v>465</v>
-      </c>
-      <c r="F3" t="s">
-        <v>459</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5871,7 +5897,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -64,7 +64,7 @@
     <t>Chain story</t>
   </si>
   <si>
-    <t>Hotel Trame (Rome, independent) → The Hoxton, Florence (Ennismore) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Grand Hotel Excelsior Vittoria (Sorrento, Leading Hotels of the World) → Nomos Hotel (Rome, DNA Hotels)</t>
+    <t>Hotel Trame (Rome, independent) → The Hoxton, Florence (Ennismore) → Il Castelfalfi (Tuscany, TUI Blue Selection) → Ara Maris Hotel &amp; Spa (Sorrento) → Nomos Hotel (Rome, DNA Hotels)</t>
   </si>
   <si>
     <t>HOW TO READ THIS WORKBOOK</t>
@@ -667,22 +667,22 @@
     <t>3:40pm</t>
   </si>
   <si>
-    <t>Check in — Grand Hotel Excelsior Vittoria — Piazza Tasso, on the cliff over Marina Piccola. Five acres of citrus garden behind it and a private lift straight down to the water.</t>
-  </si>
-  <si>
-    <t>The citrus gardens, then the lift to the sea — Unpack properly — this is home for five nights</t>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+  </si>
+  <si>
+    <t>The gardens and the elliptical pool — Two thousand square metres of Mediterranean garden behind the building. Unpack properly — this is home for five nights.</t>
   </si>
   <si>
     <t>6:45pm</t>
   </si>
   <si>
-    <t>Aperitivo on the terrace over the bay — Vesuvius on the far shore, and it goes pink at sunset</t>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
   </si>
   <si>
     <t>7:45pm</t>
   </si>
   <si>
-    <t>Dinner — Terrazza Bosquet — The hotel's Michelin-starred room, on the terrace. Worth booking for the first night rather than the last.</t>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
   </si>
   <si>
     <t>Tue, Sep 1</t>
@@ -712,7 +712,7 @@
     <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
   </si>
   <si>
-    <t>Swim, or the pool on the cliff — The private lift drops you at Marina Piccola if you want salt water instead</t>
+    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
   </si>
   <si>
     <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
@@ -724,10 +724,10 @@
     <t>SORRENTO — Capri day trip</t>
   </si>
   <si>
-    <t>Down to Marina Piccola by the hotel lift — The ferry pier is a two-minute walk from where the lift lets you out</t>
-  </si>
-  <si>
-    <t>Hotel lift</t>
+    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
   </si>
   <si>
     <t>8:40am</t>
@@ -820,7 +820,7 @@
     <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
   </si>
   <si>
-    <t>Down to Marina Piccola</t>
+    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
   </si>
   <si>
     <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
@@ -880,7 +880,7 @@
     <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
   </si>
   <si>
-    <t>Check out — Excelsior Vittoria</t>
+    <t>Check out — Ara Maris — Checkout is 11:00am, so there is no rush</t>
   </si>
   <si>
     <t>Private driver to Napoli Centrale — About 1h15 back around the bay</t>
@@ -1018,10 +1018,10 @@
     <t>Sorrento</t>
   </si>
   <si>
-    <t>Grand Hotel Excelsior Vittoria</t>
-  </si>
-  <si>
-    <t>Leading Hotels of the World</t>
+    <t>Ara Maris Hotel &amp; Spa</t>
+  </si>
+  <si>
+    <t>Independent, 5-star</t>
   </si>
   <si>
     <t>Rome (finale)</t>
@@ -1048,7 +1048,7 @@
     <t>Lodging</t>
   </si>
   <si>
-    <t>5 hotels, 13 nights. Four are now confirmed and settled: Trame ($1,588), The Hoxton Florence ($693, room only), Castelfalfi ($2,132, Deluxe Room with breakfast), Nomos Rome ($658). Sorrento is the one line still open — penciled in at $5,750 for five nights, against a ceiling of $7,027 if you hold the old $12,098 lodging total.</t>
+    <t>5 hotels, 13 nights — all five now booked. Trame ($1,588), The Hoxton Florence ($693, room only), Castelfalfi ($2,132), Ara Maris Sorrento ($6,363 across two bookings with a room change on Sep 4), Nomos Rome ($658). That is $664 under the $12,098 the earlier plan carried.</t>
   </si>
   <si>
     <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
@@ -1147,7 +1147,7 @@
     <t>~1.5 hrs drive + 3 hrs train</t>
   </si>
   <si>
-    <t>Napoli Centrale → Grand Hotel Excelsior Vittoria, Sorrento  (Pre-book. The Circumvesuviana is cheaper but has nowhere to put luggage in August.)</t>
+    <t>Napoli Centrale → Ara Maris Hotel &amp; Spa, Sorrento  (Pre-book. The Circumvesuviana is cheaper but has nowhere to put luggage in August.)</t>
   </si>
   <si>
     <t>~1h15</t>
@@ -1210,7 +1210,7 @@
     <t>~35 min</t>
   </si>
   <si>
-    <t>Almost the whole trip is car-free: a private driver in from FCO, the Frecciarossa up to Florence, a two-day rental for Tuscany, then rail to Naples and a driver over the peninsula to Sorrento, where everything after is a ferry. The car is collected on Aug 29 on Borgo Ognissanti — just outside Florence's ZTL, eight minutes on foot from the W — and returned to the same desk on Aug 31 before the train south. Two driving days, not fourteen. The IDP ships by Aug 3; pack it with the physical licence even though it's only needed that once. Never drive into a historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking, and the Excelsior Vittoria's garage is the only place in central Sorrento you'd want to park anyway. The Sorrento–Positano–Amalfi ferries run mid-April to mid-October, so the whole window is covered, but any of them can be cancelled for weather — keep the hotel's driver number as a backup for the Amalfi day.</t>
+    <t>Almost the whole trip is car-free: a private driver in from FCO, the Frecciarossa up to Florence, a two-day rental for Tuscany, then rail to Naples and a driver over the peninsula to Sorrento, where everything after is a ferry. The car is collected on Aug 29 on Borgo Ognissanti — just outside Florence's ZTL, eight minutes on foot from the W — and returned to the same desk on Aug 31 before the train south. Two driving days, not fourteen. The IDP ships by Aug 3; pack it with the physical licence even though it's only needed that once. Never drive into a historic centre — Florence's ZTL alone is ~€200 a crossing. Castelfalfi has its own parking, and you have no car on the coast at all — which is the right answer for Sorrento in September. The Sorrento–Positano–Amalfi ferries run mid-April to mid-October, so the whole window is covered, but any of them can be cancelled for weather — keep the hotel's driver number as a backup for the Amalfi day.</t>
   </si>
   <si>
     <t>#</t>
@@ -1225,10 +1225,10 @@
     <t>Urgency</t>
   </si>
   <si>
-    <t>Book the Sorrento hotel — five nights, Aug 31 → Sep 5</t>
-  </si>
-  <si>
-    <t>The last open booking, and the biggest single line in the budget. The other four are now all confirmed at $5,071 together, so the ceiling is firm rather than an estimate: holding the old $12,098 lodging total leaves $7,027 for these five nights, about $1,405 a night. The Excelsior Vittoria is penciled in at ~$1,150/night, which lands $1,277 under the ceiling. Whatever you pick, confirm the wifi is fibre and the room has a desk — one of you is working four of these five days.</t>
+    <t>PAY FOR SORRENTO BY AUG 6 — the automatic payment failed</t>
+  </si>
+  <si>
+    <t>Vio could not set up the card for the four-night Deluxe Sea View, so it has to be paid by hand: $5,087.62 by Aug 6 at 15:00. If it is not paid the booking cancels itself, and that is the room for four of your five coast nights. The one-night Superior on Sep 4 ($1,073.77) is on the normal automatic schedule for Aug 10 and needs nothing from you. Local fees of $161.38 and $40.35 are settled at the property, in euros.</t>
   </si>
   <si>
     <t>DO NOW</t>
@@ -1306,7 +1306,7 @@
     <t>Capri ferry — Sorrento → Capri return, Sep 2</t>
   </si>
   <si>
-    <t>About 25 minutes each way from Marina Piccola, directly below the hotel lift. Book both legs online the night before and note the last sailing back. The round-the-island boat can be picked up at Capri's Marina Grande on the day.</t>
+    <t>About 25 minutes each way from Marina Piccola, which is a twenty-minute walk downhill from the hotel or a short taxi. Book both legs online the night before and note the last sailing back. The round-the-island boat can be picked up at Capri's Marina Grande on the day.</t>
   </si>
   <si>
     <t>Coast ferries — Positano (Sep 3) and Amalfi (Sep 4)</t>
@@ -1330,7 +1330,7 @@
     <t>Headline dinners on their dates</t>
   </si>
   <si>
-    <t>Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Terrazza Bosquet Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Terrazza Bosquet are the two to book first.</t>
+    <t>Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Cora Bistrot are the two to book first.</t>
   </si>
   <si>
     <t>RULED OUT</t>
@@ -1450,7 +1450,7 @@
     <t>Flytographer Amalfi / Giuseppe Di Martino</t>
   </si>
   <si>
-    <t>The Excelsior Vittoria's citrus gardens and cliff terrace; Marina Grande's fishing boats; Positano's pastel stairs from the water; the Villa Comunale balcony at sunset</t>
+    <t>The Ara Maris rooftop at sunset; Marina Grande's fishing boats; Positano's pastel stairs from the water; the Villa Comunale balcony</t>
   </si>
   <si>
     <t>小红书: 阿马尔菲/positano旅拍</t>
@@ -3659,7 +3659,7 @@
         <v>63</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4200,7 +4200,7 @@
         <v>267</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -4896,10 +4896,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="15">
-        <v>1150</v>
+        <v>1272.624</v>
       </c>
       <c r="H5" s="15">
-        <v>5750</v>
+        <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>325</v>
@@ -4957,7 +4957,7 @@
         <v>48</v>
       </c>
       <c r="H7" s="17">
-        <v>10820.83</v>
+        <v>11433.95</v>
       </c>
     </row>
   </sheetData>
@@ -4999,7 +4999,7 @@
         <v>342</v>
       </c>
       <c r="B2" s="15">
-        <v>10820.83</v>
+        <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>343</v>
@@ -5054,7 +5054,7 @@
         <v>338</v>
       </c>
       <c r="B7" s="17">
-        <v>17320.83</v>
+        <v>17933.95</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>351</v>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="488">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -367,549 +367,549 @@
     <t>TRAVEL DAY</t>
   </si>
   <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
+  </si>
+  <si>
+    <t>11:45am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Florence — Roma Termini → Firenze S.M.N., direct — about 1h30. Departures roughly every half hour, so pick the one nearest this once you book; the rest of the day hangs off it.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1h30</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>1:15pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze S.M.N.</t>
+  </si>
+  <si>
+    <t>1:30pm</t>
+  </si>
+  <si>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+  </si>
+  <si>
+    <t>Taxi, ~8 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>Late lunch — Trattoria Mario, by San Lorenzo — Shared tables, cash, and the kitchen stops at 3:30pm — so this is the one part of the later start that is tight. Many Florence trattorie also shut for part of August; Mercato Centrale upstairs is open daily and takes no booking.</t>
+  </si>
+  <si>
+    <t>Walk, ~11 min</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Accademia — David at the afternoon slot — Forty-five minutes is genuinely enough. Go straight down the hall of the Prisoners. Book this slot, not the old one — the day moved.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>4:45pm</t>
+  </si>
+  <si>
+    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
+  </si>
+  <si>
+    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm, so this is timed to it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
+  </si>
+  <si>
+    <t>Walk, ~14 min</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to the river</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>2:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Coffee, then the platform</t>
+  </si>
+  <si>
+    <t>10:52am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Naples — Firenze S.M.N. → Napoli Centrale, direct via Rome — about 3 hours. Book this one ahead; it's the leg where a good fare is worth having.</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~3 hrs</t>
+  </si>
+  <si>
+    <t>1:50pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse</t>
+  </si>
+  <si>
+    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h15</t>
+  </si>
+  <si>
+    <t>3:40pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+  </si>
+  <si>
+    <t>The gardens and the elliptical pool — Two thousand square metres of Mediterranean garden behind the building. Unpack properly — this is home for five nights.</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
     <t>8:30am</t>
   </si>
   <si>
-    <t>Check out; taxi to Roma Termini — About fifteen minutes from Campo de' Fiori</t>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
+  </si>
+  <si>
+    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>3:50pm</t>
+  </si>
+  <si>
+    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
+  </si>
+  <si>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h30</t>
+  </si>
+  <si>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
+  </si>
+  <si>
+    <t>Check out — Ara Maris — Checkout is 11:00am, so there is no rush</t>
   </si>
   <si>
     <t>9:20am</t>
   </si>
   <si>
-    <t>Frecciarossa to Florence — Roma Termini → Firenze S.M.N., direct — about 1h30. Departures roughly every half hour; book ahead for the fare, not for the seat.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1h30</t>
-  </si>
-  <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>10:50am</t>
-  </si>
-  <si>
-    <t>Arrive Firenze S.M.N.</t>
-  </si>
-  <si>
-    <t>11:05am</t>
-  </si>
-  <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
-  </si>
-  <si>
-    <t>Taxi, ~8 min</t>
-  </si>
-  <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>11:45am</t>
-  </si>
-  <si>
-    <t>Lunch — Trattoria Mario, by San Lorenzo — Shared tables, cash, closed by 3:30pm. Mercato Centrale upstairs is the no-queue fallback.</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Accademia — David at the afternoon slot — Forty-five minutes is genuinely enough. Go straight down the hall of the Prisoners.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
+    <t>Private driver to Napoli Centrale — About 1h15 back around the bay</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale</t>
+  </si>
+  <si>
+    <t>11:20am</t>
+  </si>
+  <si>
+    <t>Frecciarossa to Rome — Napoli Centrale → Roma Termini, direct — about 1h10, departures roughly every half hour</t>
+  </si>
+  <si>
+    <t>High-speed rail, ~1h10</t>
+  </si>
+  <si>
+    <t>Arrive Roma Termini; taxi to the hotel</t>
+  </si>
+  <si>
+    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began at Hotel Trame. Superior Double; nothing is prepaid, you settle €530 with the hotel.</t>
+  </si>
+  <si>
+    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door and the one corner of the centre you haven't walked yet — Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
   </si>
   <si>
     <t>4:30pm</t>
   </si>
   <si>
-    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
-  </si>
-  <si>
-    <t>Walk, ~14 min</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to the river</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>2:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Coffee, then the platform</t>
-  </si>
-  <si>
-    <t>10:52am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Naples — Firenze S.M.N. → Napoli Centrale, direct via Rome — about 3 hours. Book this one ahead; it's the leg where a good fare is worth having.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~3 hrs</t>
-  </si>
-  <si>
-    <t>1:50pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse</t>
-  </si>
-  <si>
-    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h15</t>
-  </si>
-  <si>
-    <t>3:40pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
-  </si>
-  <si>
-    <t>The gardens and the elliptical pool — Two thousand square metres of Mediterranean garden behind the building. Unpack properly — this is home for five nights.</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
-  </si>
-  <si>
-    <t>Walk ~20 min, or taxi</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
-  </si>
-  <si>
-    <t>Ferry, ~1h15</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
-  </si>
-  <si>
-    <t>Walk from the marina</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
-  </si>
-  <si>
-    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>3:50pm</t>
-  </si>
-  <si>
-    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
-  </si>
-  <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h30</t>
-  </si>
-  <si>
-    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
-  </si>
-  <si>
-    <t>Check out — Ara Maris — Checkout is 11:00am, so there is no rush</t>
-  </si>
-  <si>
-    <t>Private driver to Napoli Centrale — About 1h15 back around the bay</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale</t>
-  </si>
-  <si>
-    <t>11:20am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Rome — Napoli Centrale → Roma Termini, direct — about 1h10, departures roughly every half hour</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1h10</t>
-  </si>
-  <si>
-    <t>Arrive Roma Termini; taxi to the hotel</t>
-  </si>
-  <si>
-    <t>1:15pm</t>
-  </si>
-  <si>
-    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began at Hotel Trame. Superior Double; nothing is prepaid, you settle €530 with the hotel.</t>
-  </si>
-  <si>
-    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door and the one corner of the centre you haven't walked yet — Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
-  </si>
-  <si>
     <t>Tiber Island and the Ponte Fabricio — The bridge has carried people across since 62 BC and is still the original stone</t>
   </si>
   <si>
@@ -1237,100 +1237,106 @@
     <t>Open -&gt;</t>
   </si>
   <si>
-    <t>Book the FCO → Hotel Trame private driver</t>
+    <t>Rental car — cancel the old FCO booking, rebook Florence Aug 29 → 31</t>
+  </si>
+  <si>
+    <t>Two problems in one. The old reservation is still FCO Aug 24 → FCO Sep 6, so left alone it bills you for a fortnight's hire you will not take. And the car you do need — Borgo Ognissanti, Florence, Aug 29 to Aug 31 — is not booked at all. Re-quote before cancelling; the old €1,087.81 was a fourteen-day FCO round trip and will not carry over.</t>
+  </si>
+  <si>
+    <t>Frecciarossa — all three legs, in one sitting</t>
+  </si>
+  <si>
+    <t>None of the rail is booked yet, including the very first leg. Roma Termini → Firenze S.M.N. on Aug 27, ~1h30, is the one to do first. Then Firenze S.M.N. → Napoli Centrale on Aug 31, ~3 hrs, the longest leg of the trip. Then Napoli Centrale → Roma Termini on Sep 5, ~1h10. None of them sell out, but the cheap Super Economy fares do — three weeks out they are already thinning, and the difference across three legs for two people is real money.</t>
+  </si>
+  <si>
+    <t>Duomo dome climb — Aug 28, 8:15am</t>
+  </si>
+  <si>
+    <t>The tightest ticket in the itinerary: 463 steps on a timed slot, and it has the fewest places of anything in Florence. Late August with one Florence morning to spend means booking this before any other ticket.</t>
+  </si>
+  <si>
+    <t>Vatican early entry — Aug 25, 7:45am</t>
+  </si>
+  <si>
+    <t>The whole point of the Vatican day is being in the Sistine Chapel before general admission, and those slots go first.</t>
+  </si>
+  <si>
+    <t>Accademia (Aug 27) and the Uffizi (Aug 28)</t>
+  </si>
+  <si>
+    <t>Two Florence days means no second chance at either. The Accademia is the 3:15pm slot on arrival day — the day now starts at checkout, so book the afternoon, not the lunchtime. The Uffizi is guided at 10:15am the morning after the dome.</t>
+  </si>
+  <si>
+    <t>Colosseum with arena floor — Aug 26</t>
+  </si>
+  <si>
+    <t>The arena-floor add-on is a separate, smaller allocation than general admission.</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch &amp; winery — San Gimignano, Aug 30</t>
+  </si>
+  <si>
+    <t>San Gimignano Experience, 11am–3pm, ~€120pp: an hour in the saddle through vineyards and olive groves, then lunch, a cellar tour and tastings. A small-group tour, so it fills. Meets at the Bivio Volterra bus stop.</t>
+  </si>
+  <si>
+    <t>Private driver — FCO → Hotel Trame, Aug 24</t>
   </si>
   <si>
     <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
   </si>
   <si>
-    <t>Rebook the rental car — Florence pickup and drop-off, Aug 29 → Aug 31</t>
-  </si>
-  <si>
-    <t>The old reservation is still FCO Aug 24 → FCO Sep 6. It needs to become Borgo Ognissanti, Florence, Aug 29 → Florence Aug 31: two days rather than fourteen, both ends the same city. Re-quote before cancelling — the old €1,087.81 figure was for a fourteen-day FCO round trip and will not carry over.</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch &amp; winery tour — San Gimignano, Sun Aug 30</t>
-  </si>
-  <si>
-    <t>San Gimignano Experience, 11am–3pm, ~€120pp: about an hour on horseback through vineyards and olive groves, then lunch, a cellar tour and wine tastings. Note the date moved from Sep 4 to Aug 30 in the replan. Meets at the Bivio Volterra bus stop — book ahead, it's a small-group tour.</t>
-  </si>
-  <si>
-    <t>Frecciarossa — Firenze S.M.N. → Napoli Centrale, Aug 31</t>
-  </si>
-  <si>
-    <t>About 3 hours, direct via Rome. The longest single leg of the trip and the one where booking ahead actually saves money.</t>
-  </si>
-  <si>
-    <t>Private driver — Napoli Centrale → Sorrento, Aug 31, and back on Sep 5</t>
+    <t>THIS WEEK</t>
+  </si>
+  <si>
+    <t>Private drivers — Naples ↔ Sorrento, Aug 31 and Sep 5</t>
   </si>
   <si>
     <t>About 1h15 each way. Book both directions with the same operator. The Circumvesuviana costs €5 but has no luggage space and no air conditioning worth the name in August.</t>
   </si>
   <si>
-    <t>Timed entries — Accademia (Aug 27), Duomo dome + Uffizi (Aug 28)</t>
-  </si>
-  <si>
-    <t>Only two Florence days now, so these three are the tight ones. Book the dome climb first — it has the fewest slots of anything in the city — then the Uffizi guided slot behind it.</t>
+    <t>Florence opera — La Traviata at St. Mark's, Aug 28</t>
+  </si>
+  <si>
+    <t>A chamber staging in a small church, so the room is small too. Follows the Boboli afternoon on the single full Florence day.</t>
+  </si>
+  <si>
+    <t>Rome opera — All Saints' Anglican, Aug 25</t>
+  </si>
+  <si>
+    <t>Confirm the programme is posted before booking.</t>
+  </si>
+  <si>
+    <t>Driver — Amalfi → Ravello → Sorrento, Sep 4</t>
+  </si>
+  <si>
+    <t>Picks you up in Amalfi after lunch, waits at Ravello's gate (the town is car-free), and drives you back over the pass. Roughly 2 hours of driving. Leave Ravello by 5pm to hold the 7pm rule.</t>
+  </si>
+  <si>
+    <t>Headline dinners on their dates</t>
+  </si>
+  <si>
+    <t>Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice.</t>
   </si>
   <si>
     <t>BEFORE YOU GO</t>
   </si>
   <si>
-    <t>Vatican early entry (Aug 25), Colosseum arena floor (Aug 26)</t>
-  </si>
-  <si>
-    <t>Both need booking — the Vatican slots go first.</t>
-  </si>
-  <si>
-    <t>Florence opera — La Traviata at St. Mark's, Aug 28</t>
-  </si>
-  <si>
-    <t>Moved from Sep 2 in the replan. Now on the single full Florence day, after the Boboli afternoon.</t>
-  </si>
-  <si>
-    <t>Rome opera — All Saints' Anglican, Aug 25</t>
-  </si>
-  <si>
-    <t>Confirm the programme is posted before booking.</t>
-  </si>
-  <si>
-    <t>Frecciarossa — Napoli Centrale → Roma Termini, Sep 5</t>
-  </si>
-  <si>
-    <t>About 1h10, departures every half hour — no scarcity, book for the fare.</t>
-  </si>
-  <si>
-    <t>THIS WEEK</t>
+    <t>Ravello Festival — check the Sep 4 programme</t>
+  </si>
+  <si>
+    <t>The festival runs to Sep 5, so your Ravello day is inside the window. A concert on the Villa Rufolo stage is the one thing worth reshaping the evening for — but it means a 1h30 drive back to Sorrento afterwards.</t>
   </si>
   <si>
     <t>Capri ferry — Sorrento → Capri return, Sep 2</t>
   </si>
   <si>
-    <t>About 25 minutes each way from Marina Piccola, which is a twenty-minute walk downhill from the hotel or a short taxi. Book both legs online the night before and note the last sailing back. The round-the-island boat can be picked up at Capri's Marina Grande on the day.</t>
+    <t>About 25 minutes each way from Marina Piccola, a twenty-minute walk downhill from the hotel or a short taxi. Book both legs online the night before and note the last sailing back. The round-the-island boat can be picked up at Capri's Marina Grande on the day.</t>
   </si>
   <si>
     <t>Coast ferries — Positano (Sep 3) and Amalfi (Sep 4)</t>
   </si>
   <si>
     <t>Both from Sorrento's Marina Piccola, seasonal but well inside the window. Two or three morning departures down the coast and two or three back in the afternoon — check the current timetable close to the date, the schedules shift with the season.</t>
-  </si>
-  <si>
-    <t>Amalfi → Ravello → Sorrento driver, Sep 4</t>
-  </si>
-  <si>
-    <t>Picks you up in Amalfi after lunch, waits at Ravello's gate (the town is car-free), and drives you back over the pass. Roughly 2 hours of driving in total.</t>
-  </si>
-  <si>
-    <t>Ravello Festival — check the Sep 4 programme</t>
-  </si>
-  <si>
-    <t>The festival runs to Sep 5, so your Ravello day is inside the window. A concert on the Villa Rufolo stage is the one thing worth reshaping the evening for — but it means a 1h30 drive back to Sorrento afterwards.</t>
-  </si>
-  <si>
-    <t>Headline dinners on their dates</t>
-  </si>
-  <si>
-    <t>Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Cora Bistrot are the two to book first.</t>
   </si>
   <si>
     <t>RULED OUT</t>
@@ -1548,12 +1554,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF7A6E62"/>
+      <color rgb="FF8A6D1F"/>
       <sz val="9"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF8A6D1F"/>
+      <color rgb="FF7A6E62"/>
       <sz val="9"/>
     </font>
     <font>
@@ -2740,13 +2746,13 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>130</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>67</v>
@@ -2760,7 +2766,7 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>131</v>
@@ -2780,13 +2786,13 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>77</v>
@@ -2800,13 +2806,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2820,10 +2826,10 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>126</v>
@@ -2840,13 +2846,13 @@
         <v>48</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="F39" t="s">
         <v>48</v>
@@ -2863,10 +2869,10 @@
         <v>110</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>71</v>
@@ -2877,10 +2883,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2891,13 +2897,13 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="13" t="s">
         <v>148</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>77</v>
@@ -2911,10 +2917,10 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>88</v>
@@ -2931,13 +2937,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="E45" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>77</v>
@@ -2951,13 +2957,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>71</v>
@@ -2971,13 +2977,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="13" t="s">
         <v>158</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>159</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>77</v>
@@ -2991,10 +2997,10 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>88</v>
@@ -3014,7 +3020,7 @@
         <v>105</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>86</v>
@@ -3031,10 +3037,10 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>86</v>
@@ -3051,13 +3057,13 @@
         <v>48</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="13" t="s">
         <v>166</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>132</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>71</v>
@@ -3105,7 +3111,7 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>171</v>
@@ -3336,7 +3342,7 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>191</v>
@@ -3376,13 +3382,13 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="E70" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>181</v>
@@ -3396,10 +3402,10 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E71" s="13" t="s">
         <v>172</v>
@@ -3419,7 +3425,7 @@
         <v>102</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>63</v>
@@ -3439,7 +3445,7 @@
         <v>89</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E73" s="13" t="s">
         <v>63</v>
@@ -3453,10 +3459,10 @@
         <v>8</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F75" s="14" t="s">
         <v>115</v>
@@ -3470,10 +3476,10 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>172</v>
@@ -3493,10 +3499,10 @@
         <v>189</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3510,13 +3516,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3530,13 +3536,13 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E79" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>210</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>121</v>
@@ -3550,10 +3556,10 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>57</v>
@@ -3570,13 +3576,13 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F81" t="s">
         <v>48</v>
@@ -3590,10 +3596,10 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>57</v>
@@ -3613,7 +3619,7 @@
         <v>105</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>63</v>
@@ -3630,10 +3636,10 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>63</v>
@@ -3650,10 +3656,10 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>63</v>
@@ -3667,10 +3673,10 @@
         <v>9</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,10 +3687,10 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E88" s="13" t="s">
         <v>63</v>
@@ -3704,10 +3710,10 @@
         <v>189</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3721,13 +3727,13 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>104</v>
@@ -3741,13 +3747,13 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>71</v>
@@ -3764,7 +3770,7 @@
         <v>81</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E92" s="13" t="s">
         <v>63</v>
@@ -3784,7 +3790,7 @@
         <v>61</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>63</v>
@@ -3804,10 +3810,10 @@
         <v>64</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>71</v>
@@ -3818,10 +3824,10 @@
         <v>10</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3832,13 +3838,13 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F97" t="s">
         <v>48</v>
@@ -3852,16 +3858,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F98" s="7" t="s">
         <v>237</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3872,13 +3878,13 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F99" t="s">
         <v>48</v>
@@ -3892,13 +3898,13 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>71</v>
@@ -3915,7 +3921,7 @@
         <v>81</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>60</v>
@@ -3932,13 +3938,13 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F102" t="s">
         <v>48</v>
@@ -3952,10 +3958,10 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>138</v>
+        <v>245</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E103" s="13" t="s">
         <v>63</v>
@@ -3972,13 +3978,13 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>71</v>
@@ -3989,10 +3995,10 @@
         <v>11</v>
       </c>
       <c r="B106" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C106" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4003,10 +4009,10 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E107" s="13" t="s">
         <v>63</v>
@@ -4023,16 +4029,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D108" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E108" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="E108" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="F108" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4043,10 +4049,10 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E109" s="13" t="s">
         <v>57</v>
@@ -4063,10 +4069,10 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>88</v>
@@ -4086,10 +4092,10 @@
         <v>55</v>
       </c>
       <c r="D111" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E111" s="13" t="s">
         <v>257</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>258</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
@@ -4106,10 +4112,10 @@
         <v>58</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4126,7 +4132,7 @@
         <v>102</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E113" s="13" t="s">
         <v>63</v>
@@ -4143,13 +4149,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="E114" s="13" t="s">
         <v>262</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>263</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4166,10 +4172,10 @@
         <v>64</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>71</v>
@@ -4180,10 +4186,10 @@
         <v>12</v>
       </c>
       <c r="B117" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C117" s="11" t="s">
         <v>265</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4194,10 +4200,10 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>126</v>
@@ -4217,13 +4223,13 @@
         <v>96</v>
       </c>
       <c r="D119" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E119" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="E119" s="13" t="s">
-        <v>269</v>
-      </c>
       <c r="F119" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4234,13 +4240,13 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D120" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E120" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>271</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
@@ -4254,10 +4260,10 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>88</v>
@@ -4274,10 +4280,10 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>88</v>
@@ -4294,13 +4300,13 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D123" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E123" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>276</v>
       </c>
       <c r="F123" t="s">
         <v>48</v>
@@ -4314,13 +4320,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="E124" s="13" t="s">
         <v>278</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>279</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>77</v>
@@ -4334,10 +4340,10 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>281</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>88</v>
@@ -4357,10 +4363,10 @@
         <v>84</v>
       </c>
       <c r="D126" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E126" s="13" t="s">
         <v>282</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>283</v>
       </c>
       <c r="F126" t="s">
         <v>48</v>
@@ -4374,13 +4380,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>71</v>
@@ -4391,10 +4397,10 @@
         <v>13</v>
       </c>
       <c r="B129" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C129" s="11" t="s">
         <v>285</v>
-      </c>
-      <c r="C129" s="11" t="s">
-        <v>286</v>
       </c>
       <c r="F129" s="14" t="s">
         <v>115</v>
@@ -4411,7 +4417,7 @@
         <v>169</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>63</v>
@@ -4428,13 +4434,13 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>118</v>
+        <v>287</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>288</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4508,10 +4514,10 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="E135" s="13" t="s">
         <v>57</v>
@@ -4531,10 +4537,10 @@
         <v>58</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F136" t="s">
         <v>48</v>
@@ -4548,13 +4554,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>135</v>
+        <v>296</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>297</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4861,7 +4867,7 @@
         <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4887,10 +4893,10 @@
         <v>334</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4916,7 +4922,7 @@
         <v>337</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E6" t="s">
         <v>303</v>
@@ -5099,7 +5105,7 @@
         <v>355</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>356</v>
@@ -5201,7 +5207,7 @@
         <v>372</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>376</v>
@@ -5331,7 +5337,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5469,8 +5475,8 @@
       <c r="C8" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>418</v>
+      <c r="D8" s="19" t="s">
+        <v>404</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>405</v>
@@ -5481,13 +5487,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>418</v>
+      <c r="D9" s="19" t="s">
+        <v>404</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>405</v>
@@ -5498,13 +5504,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="20" t="s">
         <v>422</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>418</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>405</v>
@@ -5521,7 +5527,7 @@
         <v>424</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>405</v>
@@ -5537,8 +5543,8 @@
       <c r="C12" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>427</v>
+      <c r="D12" s="20" t="s">
+        <v>422</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>405</v>
@@ -5549,13 +5555,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>427</v>
+      <c r="D13" s="20" t="s">
+        <v>422</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>405</v>
@@ -5566,13 +5572,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>427</v>
+      <c r="D14" s="20" t="s">
+        <v>422</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>405</v>
@@ -5583,13 +5589,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="21" t="s">
         <v>433</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>427</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>405</v>
@@ -5605,8 +5611,8 @@
       <c r="C16" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>418</v>
+      <c r="D16" s="21" t="s">
+        <v>433</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>405</v>
@@ -5622,29 +5628,35 @@
       <c r="C17" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>418</v>
+      <c r="D17" s="21" t="s">
+        <v>433</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="22" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="22" t="s">
         <v>440</v>
       </c>
     </row>
@@ -5690,6 +5702,17 @@
       </c>
       <c r="C24" s="2" t="s">
         <v>448</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -5710,6 +5733,7 @@
     <hyperlink ref="E15" r:id="rId14"/>
     <hyperlink ref="E16" r:id="rId15"/>
     <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5732,28 +5756,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5761,25 +5785,25 @@
         <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5787,103 +5811,103 @@
         <v>326</v>
       </c>
       <c r="B3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="E3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F3" t="s">
+        <v>463</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" s="7" t="s">
         <v>465</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="E3" t="s">
-        <v>467</v>
-      </c>
-      <c r="F3" t="s">
-        <v>461</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B5" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E5" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F5" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5897,7 +5921,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="487">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -373,543 +373,546 @@
     <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
   </si>
   <si>
-    <t>11:45am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Florence — Roma Termini → Firenze S.M.N., direct — about 1h30. Departures roughly every half hour, so pick the one nearest this once you book; the rest of the day hangs off it.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1h30</t>
+    <t>12:10pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9420 to Florence — Booked. Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 2h01</t>
   </si>
   <si>
     <t>Trenitalia -&gt;</t>
   </si>
   <si>
-    <t>1:15pm</t>
+    <t>2:11pm</t>
   </si>
   <si>
     <t>Arrive Firenze S.M.N.</t>
   </si>
   <si>
+    <t>2:25pm</t>
+  </si>
+  <si>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+  </si>
+  <si>
+    <t>Taxi, ~8 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>2:50pm</t>
+  </si>
+  <si>
+    <t>Late lunch — Mercato Centrale — The booked train lands at 2:11pm, which puts Trattoria Mario inside twenty minutes of its 3:30pm kitchen close — not worth the run. The market's upstairs food hall is open all day and takes no booking. Mario is the gamble if you are quick off the platform.</t>
+  </si>
+  <si>
+    <t>Walk, ~11 min</t>
+  </si>
+  <si>
+    <t>Accademia — David at the afternoon slot — Book the 4:00pm entry — the train now lands at 2:11pm. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm, so this is timed to it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
+  </si>
+  <si>
+    <t>Walk, ~14 min</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to the river</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>2:15pm</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
+  </si>
+  <si>
+    <t>1:14pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 3h09</t>
+  </si>
+  <si>
+    <t>4:23pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse — book him for 4:30pm, not the old 2:15pm</t>
+  </si>
+  <si>
+    <t>4:35pm</t>
+  </si>
+  <si>
+    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h15</t>
+  </si>
+  <si>
+    <t>5:55pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+  </si>
+  <si>
+    <t>Unpack — this is home for five nights — Two thousand square metres of Mediterranean garden and the elliptical pool can wait for tomorrow; the train lands late enough that tonight is just arriving</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
+  </si>
+  <si>
+    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>3:50pm</t>
+  </si>
+  <si>
+    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
+  </si>
+  <si>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h30</t>
+  </si>
+  <si>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
+  </si>
+  <si>
+    <t>Check out — Ara Maris — Checkout is 11:00am and the booked train is the 1:30pm, so use the morning — the rooftop, or the walk into town</t>
+  </si>
+  <si>
+    <t>Private driver to Napoli Centrale — About 1h15 back around the bay. Booked for the old 9:20am it would have left you nearly three hours on the concourse.</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Just under an hour before the train — enough for a coffee, not enough to leave the station</t>
+  </si>
+  <si>
     <t>1:30pm</t>
   </si>
   <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
-  </si>
-  <si>
-    <t>Taxi, ~8 min</t>
-  </si>
-  <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>Late lunch — Trattoria Mario, by San Lorenzo — Shared tables, cash, and the kitchen stops at 3:30pm — so this is the one part of the later start that is tight. Many Florence trattorie also shut for part of August; Mercato Centrale upstairs is open daily and takes no booking.</t>
-  </si>
-  <si>
-    <t>Walk, ~11 min</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Accademia — David at the afternoon slot — Forty-five minutes is genuinely enough. Go straight down the hall of the Prisoners. Book this slot, not the old one — the day moved.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>4:45pm</t>
-  </si>
-  <si>
-    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
-  </si>
-  <si>
-    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm, so this is timed to it. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
-  </si>
-  <si>
-    <t>Walk, ~14 min</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to the river</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>2:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Coffee, then the platform</t>
-  </si>
-  <si>
-    <t>10:52am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Naples — Firenze S.M.N. → Napoli Centrale, direct via Rome — about 3 hours. Book this one ahead; it's the leg where a good fare is worth having.</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~3 hrs</t>
-  </si>
-  <si>
-    <t>1:50pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse</t>
-  </si>
-  <si>
-    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h15</t>
-  </si>
-  <si>
-    <t>3:40pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
-  </si>
-  <si>
-    <t>The gardens and the elliptical pool — Two thousand square metres of Mediterranean garden behind the building. Unpack properly — this is home for five nights.</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
-  </si>
-  <si>
-    <t>Walk ~20 min, or taxi</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
-  </si>
-  <si>
-    <t>Ferry, ~1h15</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
-  </si>
-  <si>
-    <t>Walk from the marina</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
-  </si>
-  <si>
-    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>3:50pm</t>
-  </si>
-  <si>
-    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
-  </si>
-  <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h30</t>
-  </si>
-  <si>
-    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
-  </si>
-  <si>
-    <t>Check out — Ara Maris — Checkout is 11:00am, so there is no rush</t>
-  </si>
-  <si>
-    <t>9:20am</t>
-  </si>
-  <si>
-    <t>Private driver to Napoli Centrale — About 1h15 back around the bay</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale</t>
-  </si>
-  <si>
-    <t>11:20am</t>
-  </si>
-  <si>
-    <t>Frecciarossa to Rome — Napoli Centrale → Roma Termini, direct — about 1h10, departures roughly every half hour</t>
-  </si>
-  <si>
-    <t>High-speed rail, ~1h10</t>
+    <t>Frecciarossa 9544 to Rome — Booked. Napoli Centrale 13:30 → Roma Termini 14:55, Executive, coach 1.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 1h25</t>
+  </si>
+  <si>
+    <t>2:55pm</t>
   </si>
   <si>
     <t>Arrive Roma Termini; taxi to the hotel</t>
   </si>
   <si>
+    <t>3:20pm</t>
+  </si>
+  <si>
     <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began at Hotel Trame. Superior Double; nothing is prepaid, you settle €530 with the hotel.</t>
   </si>
   <si>
     <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door and the one corner of the centre you haven't walked yet — Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
   </si>
   <si>
-    <t>4:30pm</t>
-  </si>
-  <si>
     <t>Tiber Island and the Ponte Fabricio — The bridge has carried people across since 62 BC and is still the original stone</t>
   </si>
   <si>
@@ -1051,7 +1054,7 @@
     <t>5 hotels, 13 nights — all five now booked. Trame ($1,588), The Hoxton Florence ($693, room only), Castelfalfi ($2,132), Ara Maris Sorrento ($6,363 across two bookings with a room change on Sep 4), Nomos Rome ($658). That is $664 under the $12,098 the earlier plan carried.</t>
   </si>
   <si>
-    <t>Estimate. FCO private driver, Rome→Florence train, a 2-day Florence–Tuscany rental car, Florence→Naples train, Naples↔Sorrento private drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and Naples→Rome train.</t>
+    <t>Rail is now booked and firm: €1,000 for the two of you across all three Frecciarossa legs in Executive (€290 Rome–Florence, €450 Florence–Naples, €260 Naples–Rome), about $1,080. The rest is still estimate — FCO private driver, a 2-day Florence–Tuscany rental car, Naples↔Sorrento drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and taxis.</t>
   </si>
   <si>
     <t>Excursions &amp; guides</t>
@@ -1102,10 +1105,10 @@
     <t>High-speed rail</t>
   </si>
   <si>
-    <t>Roma Termini → Firenze S.M.N.  (Frecciarossa, roughly every half hour; the W is a two-minute walk from the platform)</t>
-  </si>
-  <si>
-    <t>~1h30</t>
+    <t>Roma Termini 12:10 → Firenze S.M.N. 14:11  (Booked — Frecciarossa 9420, Executive, coach 1. Hoxton is a taxi from the platform, not a walk.)</t>
+  </si>
+  <si>
+    <t>2h01</t>
   </si>
   <si>
     <t>Aug 29</t>
@@ -1141,10 +1144,10 @@
     <t>Self-drive, then rail</t>
   </si>
   <si>
-    <t>Il Castelfalfi → Borgo Ognissanti (drop the car) → Napoli Centrale  (The rental ends where it started. Book the Florence–Naples Frecciarossa ahead — it's the longest leg of the trip.)</t>
-  </si>
-  <si>
-    <t>~1.5 hrs drive + 3 hrs train</t>
+    <t>Il Castelfalfi → Borgo Ognissanti (drop the car) → Napoli Centrale 16:23  (Booked — Frecciarossa 9587, 13:14 from Firenze S.M.N., Executive, coach 1. The rental ends where it started.)</t>
+  </si>
+  <si>
+    <t>~1.5 hrs drive + 3h09 train</t>
   </si>
   <si>
     <t>Napoli Centrale → Ara Maris Hotel &amp; Spa, Sorrento  (Pre-book. The Circumvesuviana is cheaper but has nowhere to put luggage in August.)</t>
@@ -1195,10 +1198,10 @@
     <t>Private driver, then rail</t>
   </si>
   <si>
-    <t>Sorrento → Napoli Centrale → Roma Termini</t>
-  </si>
-  <si>
-    <t>~1h15 driver + 1h10 train</t>
+    <t>Sorrento → Napoli Centrale → Roma Termini 14:55  (Booked — Frecciarossa 9544, 13:30 from Napoli Centrale, Executive, coach 1. Leave Sorrento at 11:15am, not earlier.)</t>
+  </si>
+  <si>
+    <t>~1h15 driver + 1h25 train</t>
   </si>
   <si>
     <t>Sep 6</t>
@@ -1243,12 +1246,6 @@
     <t>Two problems in one. The old reservation is still FCO Aug 24 → FCO Sep 6, so left alone it bills you for a fortnight's hire you will not take. And the car you do need — Borgo Ognissanti, Florence, Aug 29 to Aug 31 — is not booked at all. Re-quote before cancelling; the old €1,087.81 was a fourteen-day FCO round trip and will not carry over.</t>
   </si>
   <si>
-    <t>Frecciarossa — all three legs, in one sitting</t>
-  </si>
-  <si>
-    <t>None of the rail is booked yet, including the very first leg. Roma Termini → Firenze S.M.N. on Aug 27, ~1h30, is the one to do first. Then Firenze S.M.N. → Napoli Centrale on Aug 31, ~3 hrs, the longest leg of the trip. Then Napoli Centrale → Roma Termini on Sep 5, ~1h10. None of them sell out, but the cheap Super Economy fares do — three weeks out they are already thinning, and the difference across three legs for two people is real money.</t>
-  </si>
-  <si>
     <t>Duomo dome climb — Aug 28, 8:15am</t>
   </si>
   <si>
@@ -1291,7 +1288,7 @@
     <t>Private drivers — Naples ↔ Sorrento, Aug 31 and Sep 5</t>
   </si>
   <si>
-    <t>About 1h15 each way. Book both directions with the same operator. The Circumvesuviana costs €5 but has no luggage space and no air conditioning worth the name in August.</t>
+    <t>Now that the trains are booked these have fixed times: 4:30pm at Napoli Centrale on Aug 31 (the train lands 16:23), and 11:15am from the hotel on Sep 5 (the train goes at 13:30). About 1h15 each way — book both with the same operator. The Circumvesuviana costs €5 but has no luggage space and no air conditioning worth the name in August.</t>
   </si>
   <si>
     <t>Florence opera — La Traviata at St. Mark's, Aug 28</t>
@@ -2746,16 +2743,16 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>67</v>
+        <v>130</v>
+      </c>
+      <c r="F34" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,7 +2763,7 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>131</v>
@@ -2806,13 +2803,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2826,10 +2823,10 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>126</v>
@@ -2846,13 +2843,13 @@
         <v>48</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" t="s">
         <v>48</v>
@@ -2869,10 +2866,10 @@
         <v>110</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>71</v>
@@ -2883,10 +2880,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2897,13 +2894,13 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>77</v>
@@ -2917,10 +2914,10 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>88</v>
@@ -2937,10 +2934,10 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>132</v>
@@ -2957,13 +2954,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>71</v>
@@ -2977,13 +2974,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>77</v>
@@ -2997,10 +2994,10 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>88</v>
@@ -3020,7 +3017,7 @@
         <v>105</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>86</v>
@@ -3037,10 +3034,10 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>86</v>
@@ -3057,13 +3054,13 @@
         <v>48</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>71</v>
@@ -3074,10 +3071,10 @@
         <v>6</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>115</v>
@@ -3091,10 +3088,10 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>86</v>
@@ -3111,13 +3108,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -3131,13 +3128,13 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>104</v>
@@ -3151,10 +3148,10 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>88</v>
@@ -3174,7 +3171,7 @@
         <v>78</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>88</v>
@@ -3194,10 +3191,10 @@
         <v>81</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F59" t="s">
         <v>48</v>
@@ -3214,13 +3211,13 @@
         <v>58</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3234,7 +3231,7 @@
         <v>84</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>60</v>
@@ -3251,7 +3248,7 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>184</v>
@@ -3302,13 +3299,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3342,7 +3339,7 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>191</v>
@@ -3391,7 +3388,7 @@
         <v>195</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3402,13 +3399,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3425,7 +3422,7 @@
         <v>102</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>63</v>
@@ -3445,7 +3442,7 @@
         <v>89</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E73" s="13" t="s">
         <v>63</v>
@@ -3459,10 +3456,10 @@
         <v>8</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F75" s="14" t="s">
         <v>115</v>
@@ -3476,13 +3473,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3496,13 +3493,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3516,13 +3513,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3536,13 +3533,13 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>121</v>
@@ -3556,10 +3553,10 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>57</v>
@@ -3576,13 +3573,13 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F81" t="s">
         <v>48</v>
@@ -3596,10 +3593,10 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>57</v>
@@ -3616,10 +3613,10 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>63</v>
@@ -3636,10 +3633,10 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>63</v>
@@ -3656,10 +3653,10 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>63</v>
@@ -3673,10 +3670,10 @@
         <v>9</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3687,10 +3684,10 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E88" s="13" t="s">
         <v>63</v>
@@ -3710,10 +3707,10 @@
         <v>189</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3730,10 +3727,10 @@
         <v>116</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>104</v>
@@ -3747,13 +3744,13 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>71</v>
@@ -3770,7 +3767,7 @@
         <v>81</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E92" s="13" t="s">
         <v>63</v>
@@ -3790,7 +3787,7 @@
         <v>61</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>63</v>
@@ -3810,7 +3807,7 @@
         <v>64</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E94" s="13" t="s">
         <v>132</v>
@@ -3824,10 +3821,10 @@
         <v>10</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,13 +3835,13 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F97" t="s">
         <v>48</v>
@@ -3858,16 +3855,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,13 +3875,13 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F99" t="s">
         <v>48</v>
@@ -3898,13 +3895,13 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>71</v>
@@ -3921,7 +3918,7 @@
         <v>81</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>60</v>
@@ -3938,13 +3935,13 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F102" t="s">
         <v>48</v>
@@ -3958,10 +3955,10 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>245</v>
+        <v>133</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E103" s="13" t="s">
         <v>63</v>
@@ -3978,13 +3975,13 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>71</v>
@@ -3995,10 +3992,10 @@
         <v>11</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4009,10 +4006,10 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E107" s="13" t="s">
         <v>63</v>
@@ -4029,16 +4026,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4052,7 +4049,7 @@
         <v>116</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E109" s="13" t="s">
         <v>57</v>
@@ -4069,10 +4066,10 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>88</v>
@@ -4092,10 +4089,10 @@
         <v>55</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
@@ -4112,10 +4109,10 @@
         <v>58</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4132,7 +4129,7 @@
         <v>102</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E113" s="13" t="s">
         <v>63</v>
@@ -4149,13 +4146,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>260</v>
+        <v>135</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4172,10 +4169,10 @@
         <v>64</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>71</v>
@@ -4186,10 +4183,10 @@
         <v>12</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4200,10 +4197,10 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>126</v>
@@ -4223,13 +4220,13 @@
         <v>96</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4240,13 +4237,13 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
@@ -4260,10 +4257,10 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>271</v>
+        <v>206</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>88</v>
@@ -4280,10 +4277,10 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>88</v>
@@ -4300,13 +4297,13 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F123" t="s">
         <v>48</v>
@@ -4320,13 +4317,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>77</v>
@@ -4340,10 +4337,10 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>88</v>
@@ -4363,10 +4360,10 @@
         <v>84</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F126" t="s">
         <v>48</v>
@@ -4380,13 +4377,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>71</v>
@@ -4397,10 +4394,10 @@
         <v>13</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F129" s="14" t="s">
         <v>115</v>
@@ -4414,10 +4411,10 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>63</v>
@@ -4434,13 +4431,13 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>287</v>
+        <v>177</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>288</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4454,7 +4451,7 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>192</v>
+        <v>52</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>289</v>
@@ -4494,10 +4491,10 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>52</v>
+        <v>293</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>98</v>
@@ -4514,10 +4511,10 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>122</v>
+        <v>295</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E135" s="13" t="s">
         <v>57</v>
@@ -4534,10 +4531,10 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E136" s="13" t="s">
         <v>132</v>
@@ -4554,13 +4551,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>296</v>
+        <v>133</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4574,13 +4571,13 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F138" t="s">
         <v>48</v>
@@ -4594,13 +4591,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4617,7 +4614,7 @@
         <v>68</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E140" s="13" t="s">
         <v>76</v>
@@ -4631,10 +4628,10 @@
         <v>14</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4645,10 +4642,10 @@
         <v>48</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E143" s="13" t="s">
         <v>83</v>
@@ -4665,13 +4662,13 @@
         <v>48</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F144" t="s">
         <v>48</v>
@@ -4685,13 +4682,13 @@
         <v>48</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F145" t="s">
         <v>48</v>
@@ -4712,40 +4709,39 @@
     <hyperlink ref="F27" r:id="rId11"/>
     <hyperlink ref="F31" r:id="rId12"/>
     <hyperlink ref="F33" r:id="rId13"/>
-    <hyperlink ref="F34" r:id="rId14"/>
-    <hyperlink ref="F35" r:id="rId15"/>
-    <hyperlink ref="F36" r:id="rId16"/>
-    <hyperlink ref="F40" r:id="rId17"/>
-    <hyperlink ref="F43" r:id="rId18"/>
-    <hyperlink ref="F45" r:id="rId19"/>
-    <hyperlink ref="F46" r:id="rId20"/>
-    <hyperlink ref="F47" r:id="rId21"/>
-    <hyperlink ref="F50" r:id="rId22"/>
-    <hyperlink ref="F51" r:id="rId23"/>
-    <hyperlink ref="F56" r:id="rId24"/>
-    <hyperlink ref="F60" r:id="rId25"/>
-    <hyperlink ref="F70" r:id="rId26"/>
-    <hyperlink ref="F79" r:id="rId27"/>
-    <hyperlink ref="F82" r:id="rId28"/>
-    <hyperlink ref="F85" r:id="rId29"/>
-    <hyperlink ref="F90" r:id="rId30"/>
-    <hyperlink ref="F91" r:id="rId31"/>
-    <hyperlink ref="F94" r:id="rId32"/>
-    <hyperlink ref="F98" r:id="rId33"/>
-    <hyperlink ref="F100" r:id="rId34"/>
-    <hyperlink ref="F101" r:id="rId35"/>
-    <hyperlink ref="F104" r:id="rId36"/>
-    <hyperlink ref="F108" r:id="rId37"/>
-    <hyperlink ref="F110" r:id="rId38"/>
-    <hyperlink ref="F115" r:id="rId39"/>
-    <hyperlink ref="F119" r:id="rId40"/>
-    <hyperlink ref="F122" r:id="rId41"/>
-    <hyperlink ref="F124" r:id="rId42"/>
-    <hyperlink ref="F125" r:id="rId43"/>
-    <hyperlink ref="F127" r:id="rId44"/>
-    <hyperlink ref="F133" r:id="rId45"/>
-    <hyperlink ref="F135" r:id="rId46"/>
-    <hyperlink ref="F140" r:id="rId47"/>
+    <hyperlink ref="F35" r:id="rId14"/>
+    <hyperlink ref="F36" r:id="rId15"/>
+    <hyperlink ref="F40" r:id="rId16"/>
+    <hyperlink ref="F43" r:id="rId17"/>
+    <hyperlink ref="F45" r:id="rId18"/>
+    <hyperlink ref="F46" r:id="rId19"/>
+    <hyperlink ref="F47" r:id="rId20"/>
+    <hyperlink ref="F50" r:id="rId21"/>
+    <hyperlink ref="F51" r:id="rId22"/>
+    <hyperlink ref="F56" r:id="rId23"/>
+    <hyperlink ref="F60" r:id="rId24"/>
+    <hyperlink ref="F70" r:id="rId25"/>
+    <hyperlink ref="F79" r:id="rId26"/>
+    <hyperlink ref="F82" r:id="rId27"/>
+    <hyperlink ref="F85" r:id="rId28"/>
+    <hyperlink ref="F90" r:id="rId29"/>
+    <hyperlink ref="F91" r:id="rId30"/>
+    <hyperlink ref="F94" r:id="rId31"/>
+    <hyperlink ref="F98" r:id="rId32"/>
+    <hyperlink ref="F100" r:id="rId33"/>
+    <hyperlink ref="F101" r:id="rId34"/>
+    <hyperlink ref="F104" r:id="rId35"/>
+    <hyperlink ref="F108" r:id="rId36"/>
+    <hyperlink ref="F110" r:id="rId37"/>
+    <hyperlink ref="F115" r:id="rId38"/>
+    <hyperlink ref="F119" r:id="rId39"/>
+    <hyperlink ref="F122" r:id="rId40"/>
+    <hyperlink ref="F124" r:id="rId41"/>
+    <hyperlink ref="F125" r:id="rId42"/>
+    <hyperlink ref="F127" r:id="rId43"/>
+    <hyperlink ref="F133" r:id="rId44"/>
+    <hyperlink ref="F135" r:id="rId45"/>
+    <hyperlink ref="F140" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4768,42 +4764,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4821,24 +4817,24 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4850,24 +4846,24 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4879,24 +4875,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4908,24 +4904,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4937,7 +4933,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4954,7 +4950,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -4991,24 +4987,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5016,54 +5012,54 @@
         <v>12</v>
       </c>
       <c r="B3" s="15">
-        <v>1650</v>
+        <v>2080</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B7" s="17">
-        <v>17933.95</v>
+        <v>18363.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5088,220 +5084,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="B3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="D3" t="s">
-        <v>362</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5312,7 +5308,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -5337,7 +5333,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5348,16 +5344,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5368,16 +5364,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5385,16 +5381,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5402,16 +5398,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5419,16 +5415,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5436,16 +5432,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5453,16 +5449,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5470,16 +5466,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5487,16 +5483,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>404</v>
+        <v>420</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>421</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5504,16 +5500,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>422</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5521,16 +5517,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5538,16 +5534,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5555,16 +5551,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5572,16 +5568,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>422</v>
+        <v>431</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>432</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5589,16 +5585,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>433</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5606,16 +5602,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5623,41 +5619,35 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="C18" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>439</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>433</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="23" t="s">
         <v>440</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5665,10 +5655,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5676,10 +5666,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5687,10 +5677,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5698,21 +5688,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="23" t="s">
         <v>449</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -5733,7 +5712,6 @@
     <hyperlink ref="E15" r:id="rId14"/>
     <hyperlink ref="E16" r:id="rId15"/>
     <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5756,158 +5734,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>457</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2" t="s">
         <v>459</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" t="s">
         <v>461</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>462</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C3" t="s">
         <v>466</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" t="s">
         <v>468</v>
       </c>
-      <c r="E3" t="s">
-        <v>469</v>
-      </c>
       <c r="F3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B4" t="s">
         <v>470</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>471</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" t="s">
         <v>473</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>474</v>
       </c>
-      <c r="F4" t="s">
-        <v>475</v>
-      </c>
       <c r="G4" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B5" t="s">
         <v>476</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>477</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" t="s">
         <v>479</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>480</v>
       </c>
-      <c r="F5" t="s">
-        <v>481</v>
-      </c>
       <c r="G5" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B6" t="s">
         <v>482</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>483</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" t="s">
         <v>485</v>
       </c>
-      <c r="E6" t="s">
-        <v>486</v>
-      </c>
       <c r="F6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5921,7 +5899,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="500">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -655,30 +655,39 @@
     <t>4:23pm</t>
   </si>
   <si>
-    <t>Arrive Napoli Centrale — Pre-booked driver meets you on the concourse — book him for 4:30pm, not the old 2:15pm</t>
-  </si>
-  <si>
-    <t>4:35pm</t>
-  </si>
-  <si>
-    <t>Driver around the bay to Sorrento — About 1h15 past Vesuvius and along the peninsula — the coast road tightens the whole way</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h15</t>
-  </si>
-  <si>
-    <t>5:55pm</t>
+    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
+  </si>
+  <si>
+    <t>5:26pm</t>
+  </si>
+  <si>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h09</t>
+  </si>
+  <si>
+    <t>EAV -&gt;</t>
+  </si>
+  <si>
+    <t>6:35pm</t>
+  </si>
+  <si>
+    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
+  </si>
+  <si>
+    <t>6:50pm</t>
   </si>
   <si>
     <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
   </si>
   <si>
-    <t>Unpack — this is home for five nights — Two thousand square metres of Mediterranean garden and the elliptical pool can wait for tomorrow; the train lands late enough that tonight is just arriving</t>
-  </si>
-  <si>
     <t>7:15pm</t>
   </si>
   <si>
+    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
+  </si>
+  <si>
     <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
   </si>
   <si>
@@ -880,13 +889,34 @@
     <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
   </si>
   <si>
-    <t>Check out — Ara Maris — Checkout is 11:00am and the booked train is the 1:30pm, so use the morning — the rooftop, or the walk into town</t>
-  </si>
-  <si>
-    <t>Private driver to Napoli Centrale — About 1h15 back around the bay. Booked for the old 9:20am it would have left you nearly three hours on the concourse.</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Just under an hour before the train — enough for a coffee, not enough to leave the station</t>
+    <t>Last breakfast on the roof</t>
+  </si>
+  <si>
+    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice — it buys the Naples stop below</t>
+  </si>
+  <si>
+    <t>10:20am</t>
+  </si>
+  <si>
+    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train already standing where the next one leaves.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h14</t>
+  </si>
+  <si>
+    <t>11:34am</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Nearly two hours before the Frecciarossa, and the point of the early start</t>
+  </si>
+  <si>
+    <t>11:55am</t>
+  </si>
+  <si>
+    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city: Di Matteo and Sorbillo are both about twenty minutes' walk up Via dei Tribunali. Naples came out of this itinerary altogether, and this is the one window it gets back. If you would rather not carry the risk, there is good pizza within sight of the station.</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min</t>
   </si>
   <si>
     <t>1:30pm</t>
@@ -919,9 +949,6 @@
     <t>Trevi Fountain, one last time — Twenty minutes up through the centre, and worth the crowd on a final evening</t>
   </si>
   <si>
-    <t>Walk, ~20 min</t>
-  </si>
-  <si>
     <t>Aperitivo on Campo de' Fiori — The market stalls are long packed away by now and the square turns over to drinking</t>
   </si>
   <si>
@@ -952,9 +979,6 @@
     <t>At FCO</t>
   </si>
   <si>
-    <t>10:20am</t>
-  </si>
-  <si>
     <t>FCO → IAH — Arrivederci, Italia.</t>
   </si>
   <si>
@@ -1054,7 +1078,7 @@
     <t>5 hotels, 13 nights — all five now booked. Trame ($1,588), The Hoxton Florence ($693, room only), Castelfalfi ($2,132), Ara Maris Sorrento ($6,363 across two bookings with a room change on Sep 4), Nomos Rome ($658). That is $664 under the $12,098 the earlier plan carried.</t>
   </si>
   <si>
-    <t>Rail is now booked and firm: €1,000 for the two of you across all three Frecciarossa legs in Executive (€290 Rome–Florence, €450 Florence–Naples, €260 Naples–Rome), about $1,080. The rest is still estimate — FCO private driver, a 2-day Florence–Tuscany rental car, Naples↔Sorrento drivers both ways, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and taxis.</t>
+    <t>Rail is booked and firm: €1,000 for the two of you across all three Frecciarossa legs in Executive (€290 Rome–Florence, €450 Florence–Naples, €260 Naples–Rome), about $1,080. Naples↔Sorrento is the Campania Express both ways, €72 the pair, against roughly €280 for private drivers. The rest is still estimate — FCO driver, a 2-day Florence–Tuscany rental car, ferries to Capri, Positano and Amalfi, the Amalfi→Ravello→Sorrento driver, and taxis.</t>
   </si>
   <si>
     <t>Excursions &amp; guides</t>
@@ -1150,10 +1174,13 @@
     <t>~1.5 hrs drive + 3h09 train</t>
   </si>
   <si>
-    <t>Napoli Centrale → Ara Maris Hotel &amp; Spa, Sorrento  (Pre-book. The Circumvesuviana is cheaper but has nowhere to put luggage in August.)</t>
-  </si>
-  <si>
-    <t>~1h15</t>
+    <t>Campania Express</t>
+  </si>
+  <si>
+    <t>Napoli P. Garibaldi 17:26 → Sorrento 18:35  (EAV's tourist service — reserved seats, air conditioning, luggage space, €18pp. Leaves from the same building the Frecciarossa arrives in.)</t>
+  </si>
+  <si>
+    <t>1h09</t>
   </si>
   <si>
     <t>Sep 2</t>
@@ -1195,13 +1222,13 @@
     <t>Sep 5</t>
   </si>
   <si>
-    <t>Private driver, then rail</t>
-  </si>
-  <si>
-    <t>Sorrento → Napoli Centrale → Roma Termini 14:55  (Booked — Frecciarossa 9544, 13:30 from Napoli Centrale, Executive, coach 1. Leave Sorrento at 11:15am, not earlier.)</t>
-  </si>
-  <si>
-    <t>~1h15 driver + 1h25 train</t>
+    <t>Campania Express, then rail</t>
+  </si>
+  <si>
+    <t>Sorrento 10:20 → Napoli P. Garibaldi 11:34 → Roma Termini 14:55  (Booked — Frecciarossa 9544, 13:30 from Napoli Centrale, Executive, coach 1. The Campania Express in front of it leaves about two hours to spare, which is lunch in Naples.)</t>
+  </si>
+  <si>
+    <t>1h14 + 1h25</t>
   </si>
   <si>
     <t>Sep 6</t>
@@ -1285,10 +1312,10 @@
     <t>THIS WEEK</t>
   </si>
   <si>
-    <t>Private drivers — Naples ↔ Sorrento, Aug 31 and Sep 5</t>
-  </si>
-  <si>
-    <t>Now that the trains are booked these have fixed times: 4:30pm at Napoli Centrale on Aug 31 (the train lands 16:23), and 11:15am from the hotel on Sep 5 (the train goes at 13:30). About 1h15 each way — book both with the same operator. The Circumvesuviana costs €5 but has no luggage space and no air conditioning worth the name in August.</t>
+    <t>Campania Express — Naples ↔ Sorrento, Aug 31 and Sep 5</t>
+  </si>
+  <si>
+    <t>€18pp each way, and it does need booking: the Campania Express is a reserved-seat service, unlike the ordinary Circumvesuviana. Out on the 17:26 from Napoli P. Garibaldi on Aug 31, back on the 10:20 from Sorrento on Sep 5. Chosen over a private driver (~€140 a leg) and over the ferry — the ruled-out list says why.</t>
   </si>
   <si>
     <t>Florence opera — La Traviata at St. Mark's, Aug 28</t>
@@ -1349,6 +1376,18 @@
   </si>
   <si>
     <t>No open night in the schedule for a Verona detour — every night from Aug 24 to Sep 5 has a hotel booked elsewhere.</t>
+  </si>
+  <si>
+    <t>Naples → Sorrento by private driver (~€140 each way)</t>
+  </si>
+  <si>
+    <t>Door to door and about an hour quicker on Aug 31, but the Campania Express leaves from the same building the Frecciarossa arrives in and costs €36 for the two of you instead of €280 for the pair of transfers. Nothing on either day is tight enough to be worth the difference.</t>
+  </si>
+  <si>
+    <t>Naples ↔ Sorrento by ferry</t>
+  </si>
+  <si>
+    <t>The prettier way, and only 45 minutes on the water. But both legs need a taxi across Naples to Molo Beverello, which is the one part of this trip that depends on Naples traffic. Inbound it means catching the 17:15 within fifty minutes of the train landing; outbound the 12:00 puts you at Centrale around 13:10 for a 13:30 Frecciarossa. And Marina Piccola is uphill from the hotel where the station is flat. There are already three ferry days on the coast.</t>
   </si>
   <si>
     <t>A night in Naples</t>
@@ -2157,7 +2196,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3581,8 +3620,8 @@
       <c r="E81" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="F81" t="s">
-        <v>48</v>
+      <c r="F81" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3593,16 +3632,16 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>127</v>
+      <c r="F82" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3613,16 +3652,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F83" t="s">
-        <v>48</v>
+        <v>132</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3633,10 +3672,10 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>63</v>
@@ -3653,47 +3692,47 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F85" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B86" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F86" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+    <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
         <v>9</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>48</v>
-      </c>
-      <c r="B88" t="s">
-        <v>48</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="B88" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="E88" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F88" t="s">
-        <v>48</v>
+      <c r="C88" s="11" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3704,13 +3743,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>227</v>
+        <v>63</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3724,16 +3763,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>104</v>
+        <v>230</v>
+      </c>
+      <c r="F90" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,16 +3783,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>229</v>
+        <v>116</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,16 +3803,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F92" t="s">
-        <v>48</v>
+        <v>144</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3784,10 +3823,10 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>63</v>
@@ -3804,47 +3843,47 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E94" s="13" t="s">
+      <c r="D95" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E95" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="F95" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+    <row r="97" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
         <v>10</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>48</v>
-      </c>
-      <c r="B97" t="s">
-        <v>48</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="D97" s="4" t="s">
+      <c r="B97" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="E97" s="13" t="s">
+      <c r="C97" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="F97" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,8 +3902,8 @@
       <c r="E98" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>242</v>
+      <c r="F98" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3875,7 +3914,7 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>243</v>
@@ -3883,8 +3922,8 @@
       <c r="E99" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="F99" t="s">
-        <v>48</v>
+      <c r="F99" s="7" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3895,16 +3934,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>71</v>
+        <v>247</v>
+      </c>
+      <c r="F100" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3915,16 +3954,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>60</v>
+        <v>249</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F102" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3955,13 +3994,13 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>63</v>
+        <v>244</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -3975,47 +4014,47 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F104" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>48</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="F104" s="7" t="s">
+      <c r="D105" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F105" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="106" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="10">
+    <row r="107" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
         <v>11</v>
       </c>
-      <c r="B106" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>48</v>
-      </c>
-      <c r="B107" t="s">
-        <v>48</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F107" t="s">
-        <v>48</v>
+      <c r="B107" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4026,16 +4065,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>242</v>
+        <v>63</v>
+      </c>
+      <c r="F108" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4046,16 +4085,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F109" t="s">
-        <v>48</v>
+        <v>259</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4066,16 +4105,16 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>229</v>
+        <v>116</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>71</v>
+        <v>57</v>
+      </c>
+      <c r="F110" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4086,16 +4125,16 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>55</v>
+        <v>232</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="F111" t="s">
-        <v>48</v>
+        <v>88</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4106,13 +4145,13 @@
         <v>48</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4126,13 +4165,13 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>63</v>
+        <v>259</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4146,13 +4185,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>264</v>
+        <v>63</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4166,47 +4205,47 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="F115" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>48</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C116" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D115" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="F115" s="7" t="s">
+      <c r="D116" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="10">
+    <row r="118" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="10">
         <v>12</v>
       </c>
-      <c r="B117" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>48</v>
-      </c>
-      <c r="B118" t="s">
-        <v>48</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="F118" t="s">
-        <v>48</v>
+      <c r="B118" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4217,16 +4256,16 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>242</v>
+        <v>126</v>
+      </c>
+      <c r="F119" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4237,16 +4276,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="F120" t="s">
-        <v>48</v>
+        <v>273</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4257,13 +4296,13 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>88</v>
+        <v>275</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -4277,16 +4316,16 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>71</v>
+      <c r="F122" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,16 +4336,16 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="F123" t="s">
-        <v>48</v>
+        <v>88</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,7 +4356,7 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>278</v>
@@ -4325,8 +4364,8 @@
       <c r="E124" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>77</v>
+      <c r="F124" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4343,7 +4382,7 @@
         <v>281</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>77</v>
@@ -4357,16 +4396,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="F126" t="s">
-        <v>48</v>
+        <v>88</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4377,50 +4416,50 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F127" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>48</v>
+      </c>
+      <c r="B128" t="s">
+        <v>48</v>
+      </c>
+      <c r="C128" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D127" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E127" s="13" t="s">
+      <c r="D128" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E128" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="F127" s="7" t="s">
+      <c r="F128" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="129" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="10">
+    <row r="130" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="10">
         <v>13</v>
       </c>
-      <c r="B129" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="C129" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="F129" s="14" t="s">
+      <c r="B130" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F130" s="14" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>48</v>
-      </c>
-      <c r="B130" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E130" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F130" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,13 +4470,13 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4451,13 +4490,13 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F132" t="s">
         <v>48</v>
@@ -4471,16 +4510,16 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4491,13 +4530,13 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="F134" t="s">
         <v>48</v>
@@ -4511,16 +4550,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>57</v>
+        <v>299</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4531,16 +4570,16 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F136" t="s">
-        <v>48</v>
+        <v>302</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4551,13 +4590,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4571,16 +4610,16 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="F138" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4591,13 +4630,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>302</v>
+        <v>132</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4611,27 +4650,56 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="10">
-        <v>14</v>
-      </c>
-      <c r="B142" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>305</v>
+        <v>159</v>
+      </c>
+      <c r="F140" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>48</v>
+      </c>
+      <c r="B141" t="s">
+        <v>48</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F141" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>48</v>
+      </c>
+      <c r="B142" t="s">
+        <v>48</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F142" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4642,55 +4710,86 @@
         <v>48</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>306</v>
+        <v>68</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E143" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="10">
+        <v>14</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>48</v>
+      </c>
+      <c r="B146" t="s">
+        <v>48</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E146" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F143" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>48</v>
-      </c>
-      <c r="B144" t="s">
-        <v>48</v>
-      </c>
-      <c r="C144" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="F144" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>48</v>
-      </c>
-      <c r="B145" t="s">
-        <v>48</v>
-      </c>
-      <c r="C145" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E145" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F145" t="s">
+      <c r="F146" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>48</v>
+      </c>
+      <c r="B147" t="s">
+        <v>48</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="F147" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>48</v>
+      </c>
+      <c r="B148" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F148" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4722,26 +4821,29 @@
     <hyperlink ref="F60" r:id="rId24"/>
     <hyperlink ref="F70" r:id="rId25"/>
     <hyperlink ref="F79" r:id="rId26"/>
-    <hyperlink ref="F82" r:id="rId27"/>
-    <hyperlink ref="F85" r:id="rId28"/>
-    <hyperlink ref="F90" r:id="rId29"/>
+    <hyperlink ref="F81" r:id="rId27"/>
+    <hyperlink ref="F83" r:id="rId28"/>
+    <hyperlink ref="F86" r:id="rId29"/>
     <hyperlink ref="F91" r:id="rId30"/>
-    <hyperlink ref="F94" r:id="rId31"/>
-    <hyperlink ref="F98" r:id="rId32"/>
-    <hyperlink ref="F100" r:id="rId33"/>
+    <hyperlink ref="F92" r:id="rId31"/>
+    <hyperlink ref="F95" r:id="rId32"/>
+    <hyperlink ref="F99" r:id="rId33"/>
     <hyperlink ref="F101" r:id="rId34"/>
-    <hyperlink ref="F104" r:id="rId35"/>
-    <hyperlink ref="F108" r:id="rId36"/>
-    <hyperlink ref="F110" r:id="rId37"/>
-    <hyperlink ref="F115" r:id="rId38"/>
-    <hyperlink ref="F119" r:id="rId39"/>
-    <hyperlink ref="F122" r:id="rId40"/>
-    <hyperlink ref="F124" r:id="rId41"/>
+    <hyperlink ref="F102" r:id="rId35"/>
+    <hyperlink ref="F105" r:id="rId36"/>
+    <hyperlink ref="F109" r:id="rId37"/>
+    <hyperlink ref="F111" r:id="rId38"/>
+    <hyperlink ref="F116" r:id="rId39"/>
+    <hyperlink ref="F120" r:id="rId40"/>
+    <hyperlink ref="F123" r:id="rId41"/>
     <hyperlink ref="F125" r:id="rId42"/>
-    <hyperlink ref="F127" r:id="rId43"/>
-    <hyperlink ref="F133" r:id="rId44"/>
-    <hyperlink ref="F135" r:id="rId45"/>
-    <hyperlink ref="F140" r:id="rId46"/>
+    <hyperlink ref="F126" r:id="rId43"/>
+    <hyperlink ref="F128" r:id="rId44"/>
+    <hyperlink ref="F133" r:id="rId45"/>
+    <hyperlink ref="F135" r:id="rId46"/>
+    <hyperlink ref="F136" r:id="rId47"/>
+    <hyperlink ref="F138" r:id="rId48"/>
+    <hyperlink ref="F143" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4764,42 +4866,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4817,18 +4919,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
         <v>113</v>
@@ -4846,18 +4948,18 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B4" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D4" t="s">
         <v>168</v>
@@ -4875,24 +4977,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B5" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C5" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D5" t="s">
         <v>200</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4904,24 +5006,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B6" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4933,7 +5035,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -4950,7 +5052,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -4987,24 +5089,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5012,54 +5114,54 @@
         <v>12</v>
       </c>
       <c r="B3" s="15">
-        <v>2080</v>
+        <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B7" s="17">
-        <v>18363.95</v>
+        <v>18133.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -5084,220 +5186,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D4" t="s">
+        <v>375</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B5" t="s">
         <v>173</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B6" t="s">
         <v>173</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="D6" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B7" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D7" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="D8" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B9" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="D9" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B10" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D10" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B11" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="D11" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B12" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D13" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,7 +5410,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -5333,7 +5435,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5344,16 +5446,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5364,16 +5466,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5381,16 +5483,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5398,16 +5500,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5415,16 +5517,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5432,16 +5534,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>405</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5449,16 +5551,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>415</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5466,16 +5568,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5483,16 +5585,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5500,16 +5602,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5517,16 +5619,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5534,16 +5636,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5551,16 +5653,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5568,16 +5670,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5585,16 +5687,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5602,16 +5704,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5619,16 +5721,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5636,7 +5738,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5644,10 +5746,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5655,10 +5757,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5666,10 +5768,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5677,10 +5779,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5688,10 +5790,32 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -5734,158 +5858,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B2" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="C2" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="E2" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="F2" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="E3" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="F3" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B4" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="C4" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="E4" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="F4" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="B5" t="s">
+        <v>489</v>
+      </c>
+      <c r="C5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E5" t="s">
+        <v>492</v>
+      </c>
+      <c r="F5" t="s">
+        <v>493</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" s="7" t="s">
         <v>477</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="E5" t="s">
-        <v>479</v>
-      </c>
-      <c r="F5" t="s">
-        <v>480</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="B6" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="C6" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="E6" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="F6" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5899,7 +6023,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="502">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -226,10 +226,10 @@
     <t>8:45pm</t>
   </si>
   <si>
-    <t>Dinner — Armando al Pantheon — Tiny, family-run, and booked out weeks ahead. Reserve now.</t>
-  </si>
-  <si>
-    <t>Walk, 8 min</t>
+    <t>Dinner — La Campana — Armando is full, so: the oldest restaurant in Rome, feeding people on this lane since 1518 and still run by the family that has had it for a century. The same plain Roman cooking Armando does, in a bigger room that can actually seat you — and five minutes from the aperitivo rather than eight from the hotel. If it is also full, Der Pallaro on Largo del Pallaro is four minutes from Trame, takes no bookings and serves a fixed menu, which on a jet-lag night is a feature.</t>
+  </si>
+  <si>
+    <t>Walk, 5 min from Etabli</t>
   </si>
   <si>
     <t>Reserve -&gt;</t>
@@ -1339,7 +1339,7 @@
     <t>Headline dinners on their dates</t>
   </si>
   <si>
-    <t>Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice.</t>
+    <t>La Campana Aug 24 · Pierluigi Aug 25 · Da Enzo Aug 26 · Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice.</t>
   </si>
   <si>
     <t>BEFORE YOU GO</t>
@@ -1376,6 +1376,12 @@
   </si>
   <si>
     <t>No open night in the schedule for a Verona detour — every night from Aug 24 to Sep 5 has a hotel booked elsewhere.</t>
+  </si>
+  <si>
+    <t>Armando al Pantheon, first night</t>
+  </si>
+  <si>
+    <t>Fully booked for Aug 24 — it seats about forty and goes weeks ahead. La Campana takes the slot: same era of Roman cooking, a room that can seat two at short notice, and closer to the Etabli aperitivo.</t>
   </si>
   <si>
     <t>Naples → Sorrento by private driver (~€140 each way)</t>
@@ -5435,7 +5441,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5816,6 +5822,17 @@
       </c>
       <c r="C26" s="2" t="s">
         <v>462</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -5858,28 +5875,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5887,25 +5904,25 @@
         <v>331</v>
       </c>
       <c r="B2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5913,103 +5930,103 @@
         <v>335</v>
       </c>
       <c r="B3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" t="s">
-        <v>481</v>
-      </c>
-      <c r="F3" t="s">
-        <v>475</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B5" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6023,7 +6040,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="505">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -226,10 +226,7 @@
     <t>8:45pm</t>
   </si>
   <si>
-    <t>Dinner — La Campana — Armando is full, so: the oldest restaurant in Rome, feeding people on this lane since 1518 and still run by the family that has had it for a century. The same plain Roman cooking Armando does, in a bigger room that can actually seat you — and five minutes from the aperitivo rather than eight from the hotel. If it is also full, Der Pallaro on Largo del Pallaro is four minutes from Trame, takes no bookings and serves a fixed menu, which on a jet-lag night is a feature.</t>
-  </si>
-  <si>
-    <t>Walk, 5 min from Etabli</t>
+    <t>Dinner — Emma Pizzeria con Cucina — The Roscioli family's pizzeria: their salumeria supplies the kitchen, so the burrata and the cured meats are the same ones you get at Roscioli itself, on Roman-thin bases. A sharp modern room and a terrace on a quiet street four minutes from Trame — the shortest walk of anything considered, which is worth something after twenty hours awake. Book it; it fills.</t>
   </si>
   <si>
     <t>Reserve -&gt;</t>
@@ -1339,7 +1336,7 @@
     <t>Headline dinners on their dates</t>
   </si>
   <si>
-    <t>La Campana Aug 24 · Pierluigi Aug 25 · Da Enzo Aug 26 · Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice.</t>
+    <t>Emma Aug 24 · Pierluigi Aug 25 · Da Enzo Aug 26 · Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice.</t>
   </si>
   <si>
     <t>BEFORE YOU GO</t>
@@ -1376,6 +1373,18 @@
   </si>
   <si>
     <t>No open night in the schedule for a Verona detour — every night from Aug 24 to Sep 5 has a hotel booked elsewhere.</t>
+  </si>
+  <si>
+    <t>Pianostrada, first night</t>
+  </si>
+  <si>
+    <t>The right register for arrival night — cool rather than formal, six minutes from Trame, open kitchen and a courtyard garden — but it is closed on Mondays and Aug 24 is a Monday. Still available if you would rather move it onto the Wednesday in place of Da Enzo; that would cost you the Trastevere dinner.</t>
+  </si>
+  <si>
+    <t>La Campana, first night</t>
+  </si>
+  <si>
+    <t>Slotted in when Armando fell through, then reconsidered — a 1518 trattoria is characterful but it is not a step up. Worth keeping in mind as the classic-Roman option if Emma is full.</t>
   </si>
   <si>
     <t>Armando al Pantheon, first night</t>
@@ -2378,10 +2387,10 @@
         <v>69</v>
       </c>
       <c r="E9" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2389,10 +2398,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,16 +2412,16 @@
         <v>48</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="F12" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,16 +2432,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,13 +2452,13 @@
         <v>48</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="F14" t="s">
         <v>48</v>
@@ -2463,16 +2472,16 @@
         <v>48</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>86</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,10 +2495,10 @@
         <v>64</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="F16" t="s">
         <v>48</v>
@@ -2503,16 +2512,16 @@
         <v>48</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="E17" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,16 +2532,16 @@
         <v>48</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2540,10 +2549,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>94</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2554,16 +2563,16 @@
         <v>48</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2574,16 +2583,16 @@
         <v>48</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>100</v>
-      </c>
       <c r="F22" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2594,10 +2603,10 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>63</v>
@@ -2614,16 +2623,16 @@
         <v>48</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2634,13 +2643,13 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>107</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -2654,13 +2663,13 @@
         <v>48</v>
       </c>
       <c r="C26" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="E26" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>48</v>
@@ -2674,16 +2683,16 @@
         <v>48</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="F27" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2691,13 +2700,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="F29" s="14" t="s">
         <v>114</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2708,13 +2717,13 @@
         <v>48</v>
       </c>
       <c r="C30" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="E30" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>48</v>
@@ -2728,16 +2737,16 @@
         <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="F31" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2748,10 +2757,10 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>57</v>
@@ -2768,16 +2777,16 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="F33" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2788,13 +2797,13 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>130</v>
       </c>
       <c r="F34" t="s">
         <v>48</v>
@@ -2808,16 +2817,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>132</v>
-      </c>
       <c r="F35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2828,16 +2837,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="E36" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2848,13 +2857,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2868,13 +2877,13 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="E38" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F38" t="s">
         <v>48</v>
@@ -2888,13 +2897,13 @@
         <v>48</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="F39" t="s">
         <v>48</v>
@@ -2908,16 +2917,16 @@
         <v>48</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>144</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2925,10 +2934,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2939,16 +2948,16 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="F43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2959,13 +2968,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="E44" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2979,16 +2988,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="E45" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2999,16 +3008,16 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E46" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="F46" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3019,16 +3028,16 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="E47" s="13" t="s">
-        <v>159</v>
-      </c>
       <c r="F47" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3039,13 +3048,13 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="E48" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
@@ -3059,13 +3068,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
@@ -3079,16 +3088,16 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="E50" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3099,16 +3108,16 @@
         <v>48</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="E51" s="13" t="s">
-        <v>167</v>
-      </c>
       <c r="F51" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3116,13 +3125,13 @@
         <v>6</v>
       </c>
       <c r="B53" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C53" s="11" t="s">
-        <v>169</v>
-      </c>
       <c r="F53" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3133,13 +3142,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="E54" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3153,13 +3162,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D55" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" s="13" t="s">
         <v>172</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>173</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -3173,16 +3182,16 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="E56" s="13" t="s">
-        <v>176</v>
-      </c>
       <c r="F56" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3193,13 +3202,13 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="E57" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3213,13 +3222,13 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F58" t="s">
         <v>48</v>
@@ -3233,13 +3242,13 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F59" t="s">
         <v>48</v>
@@ -3256,13 +3265,13 @@
         <v>58</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3273,10 +3282,10 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>60</v>
@@ -3293,10 +3302,10 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>63</v>
@@ -3313,10 +3322,10 @@
         <v>48</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E63" s="13" t="s">
         <v>63</v>
@@ -3330,10 +3339,10 @@
         <v>7</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,13 +3353,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3364,10 +3373,10 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>57</v>
@@ -3384,13 +3393,13 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F68" t="s">
         <v>48</v>
@@ -3404,13 +3413,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>193</v>
-      </c>
       <c r="E69" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3424,16 +3433,16 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E70" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="E70" s="13" t="s">
-        <v>195</v>
-      </c>
       <c r="F70" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3444,13 +3453,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>197</v>
-      </c>
       <c r="E71" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3464,10 +3473,10 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>63</v>
@@ -3484,10 +3493,10 @@
         <v>48</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E73" s="13" t="s">
         <v>63</v>
@@ -3501,13 +3510,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C75" s="11" t="s">
-        <v>201</v>
-      </c>
       <c r="F75" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3518,13 +3527,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>203</v>
-      </c>
       <c r="E76" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3538,13 +3547,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E77" s="13" t="s">
         <v>204</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>205</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3558,13 +3567,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>207</v>
-      </c>
       <c r="E78" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3578,16 +3587,16 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="E79" s="13" t="s">
-        <v>210</v>
-      </c>
       <c r="F79" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,10 +3607,10 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>57</v>
@@ -3618,16 +3627,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E81" s="13" t="s">
+      <c r="F81" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,10 +3647,10 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>57</v>
@@ -3658,16 +3667,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="E83" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,10 +3687,10 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>63</v>
@@ -3698,10 +3707,10 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>63</v>
@@ -3721,13 +3730,13 @@
         <v>68</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E86" s="13" t="s">
         <v>63</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3735,10 +3744,10 @@
         <v>9</v>
       </c>
       <c r="B88" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C88" s="11" t="s">
         <v>225</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3749,10 +3758,10 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="E89" s="13" t="s">
         <v>63</v>
@@ -3769,13 +3778,13 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D90" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E90" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>230</v>
       </c>
       <c r="F90" t="s">
         <v>48</v>
@@ -3789,16 +3798,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,16 +3818,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>233</v>
-      </c>
       <c r="E92" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3829,10 +3838,10 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>63</v>
@@ -3852,7 +3861,7 @@
         <v>61</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E94" s="13" t="s">
         <v>63</v>
@@ -3872,13 +3881,13 @@
         <v>64</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3886,10 +3895,10 @@
         <v>10</v>
       </c>
       <c r="B97" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C97" s="11" t="s">
         <v>237</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,13 +3909,13 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="13" t="s">
         <v>240</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="F98" t="s">
         <v>48</v>
@@ -3920,16 +3929,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="E99" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="E99" s="13" t="s">
+      <c r="F99" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3940,13 +3949,13 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D100" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E100" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="F100" t="s">
         <v>48</v>
@@ -3960,16 +3969,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D101" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E101" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="E101" s="13" t="s">
-        <v>249</v>
-      </c>
       <c r="F101" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3980,16 +3989,16 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>60</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4000,13 +4009,13 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -4020,10 +4029,10 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>63</v>
@@ -4040,16 +4049,16 @@
         <v>48</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D105" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E105" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="E105" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="F105" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4057,10 +4066,10 @@
         <v>11</v>
       </c>
       <c r="B107" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C107" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4071,10 +4080,10 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>63</v>
@@ -4091,16 +4100,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D109" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E109" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="E109" s="13" t="s">
-        <v>259</v>
-      </c>
       <c r="F109" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4111,10 +4120,10 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>57</v>
@@ -4131,16 +4140,16 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,10 +4163,10 @@
         <v>55</v>
       </c>
       <c r="D112" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E112" s="13" t="s">
         <v>262</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>263</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4174,10 +4183,10 @@
         <v>58</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4191,10 +4200,10 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>63</v>
@@ -4211,13 +4220,13 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D115" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E115" s="13" t="s">
         <v>266</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>267</v>
       </c>
       <c r="F115" t="s">
         <v>48</v>
@@ -4234,13 +4243,13 @@
         <v>64</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4248,10 +4257,10 @@
         <v>12</v>
       </c>
       <c r="B118" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C118" s="11" t="s">
         <v>269</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4262,13 +4271,13 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F119" t="s">
         <v>48</v>
@@ -4282,16 +4291,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D120" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E120" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="E120" s="13" t="s">
-        <v>273</v>
-      </c>
       <c r="F120" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4302,13 +4311,13 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D121" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E121" s="13" t="s">
         <v>274</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>275</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -4322,13 +4331,13 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F122" t="s">
         <v>48</v>
@@ -4342,16 +4351,16 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4362,13 +4371,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D124" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E124" s="13" t="s">
         <v>278</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>279</v>
       </c>
       <c r="F124" t="s">
         <v>48</v>
@@ -4382,16 +4391,16 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="E125" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="E125" s="13" t="s">
-        <v>282</v>
-      </c>
       <c r="F125" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4402,16 +4411,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D126" s="4" t="s">
-        <v>284</v>
-      </c>
       <c r="E126" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4422,13 +4431,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D127" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E127" s="13" t="s">
         <v>285</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>286</v>
       </c>
       <c r="F127" t="s">
         <v>48</v>
@@ -4442,16 +4451,16 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4459,13 +4468,13 @@
         <v>13</v>
       </c>
       <c r="B130" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C130" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C130" s="11" t="s">
-        <v>289</v>
-      </c>
       <c r="F130" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4476,10 +4485,10 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E131" s="13" t="s">
         <v>63</v>
@@ -4496,10 +4505,10 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E132" s="13" t="s">
         <v>63</v>
@@ -4516,16 +4525,16 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="E133" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="E133" s="13" t="s">
-        <v>294</v>
-      </c>
       <c r="F133" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4536,10 +4545,10 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>57</v>
@@ -4556,13 +4565,13 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="E135" s="13" t="s">
         <v>298</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>299</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>67</v>
@@ -4576,16 +4585,16 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="E136" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="E136" s="13" t="s">
-        <v>302</v>
-      </c>
       <c r="F136" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4596,13 +4605,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D137" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="E137" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4616,16 +4625,16 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4636,13 +4645,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4656,13 +4665,13 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F140" t="s">
         <v>48</v>
@@ -4679,10 +4688,10 @@
         <v>61</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F141" t="s">
         <v>48</v>
@@ -4696,13 +4705,13 @@
         <v>48</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D142" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E142" s="13" t="s">
         <v>310</v>
-      </c>
-      <c r="E142" s="13" t="s">
-        <v>311</v>
       </c>
       <c r="F142" t="s">
         <v>48</v>
@@ -4719,13 +4728,13 @@
         <v>68</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4733,10 +4742,10 @@
         <v>14</v>
       </c>
       <c r="B145" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C145" s="11" t="s">
         <v>313</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4747,13 +4756,13 @@
         <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D146" s="4" t="s">
-        <v>316</v>
-      </c>
       <c r="E146" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F146" t="s">
         <v>48</v>
@@ -4767,13 +4776,13 @@
         <v>48</v>
       </c>
       <c r="C147" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="E147" s="13" t="s">
         <v>318</v>
-      </c>
-      <c r="E147" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="F147" t="s">
         <v>48</v>
@@ -4787,13 +4796,13 @@
         <v>48</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D148" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E148" s="13" t="s">
         <v>320</v>
-      </c>
-      <c r="E148" s="13" t="s">
-        <v>321</v>
       </c>
       <c r="F148" t="s">
         <v>48</v>
@@ -4872,48 +4881,48 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>329</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" t="s">
         <v>331</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>332</v>
-      </c>
-      <c r="C2" t="s">
-        <v>333</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -4925,24 +4934,24 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" t="s">
         <v>335</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>336</v>
       </c>
-      <c r="C3" t="s">
-        <v>337</v>
-      </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4954,24 +4963,24 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" t="s">
         <v>338</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>339</v>
       </c>
-      <c r="C4" t="s">
-        <v>340</v>
-      </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4983,24 +4992,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B5" t="s">
         <v>341</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>342</v>
       </c>
-      <c r="C5" t="s">
-        <v>343</v>
-      </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5012,24 +5021,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B6" t="s">
         <v>344</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>345</v>
       </c>
-      <c r="C6" t="s">
-        <v>346</v>
-      </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5041,7 +5050,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -5058,7 +5067,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -5095,24 +5104,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>349</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5123,51 +5132,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B7" s="17">
         <v>18133.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5192,220 +5201,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="B2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" t="s">
         <v>365</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B3" t="s">
         <v>368</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" t="s">
         <v>370</v>
       </c>
-      <c r="D3" t="s">
-        <v>371</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" t="s">
         <v>372</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="D4" t="s">
         <v>374</v>
       </c>
-      <c r="D4" t="s">
-        <v>375</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="D5" t="s">
         <v>376</v>
       </c>
-      <c r="D5" t="s">
-        <v>377</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="B6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="18" t="s">
+      <c r="D6" t="s">
         <v>379</v>
       </c>
-      <c r="D6" t="s">
-        <v>380</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7" t="s">
         <v>381</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" t="s">
         <v>383</v>
       </c>
-      <c r="D7" t="s">
-        <v>384</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" t="s">
         <v>386</v>
       </c>
-      <c r="D8" t="s">
-        <v>387</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B9" t="s">
         <v>388</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" t="s">
         <v>390</v>
       </c>
-      <c r="D9" t="s">
-        <v>391</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" t="s">
         <v>392</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="D10" t="s">
         <v>394</v>
       </c>
-      <c r="D10" t="s">
-        <v>395</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B11" t="s">
         <v>396</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" t="s">
         <v>398</v>
       </c>
-      <c r="D11" t="s">
-        <v>399</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B12" t="s">
         <v>400</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="D12" t="s">
         <v>402</v>
       </c>
-      <c r="D12" t="s">
-        <v>403</v>
-      </c>
       <c r="E12" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="18" t="s">
+      <c r="D13" t="s">
         <v>405</v>
       </c>
-      <c r="D13" t="s">
-        <v>406</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5416,7 +5425,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5441,7 +5450,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5452,16 +5461,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>410</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>411</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5472,16 +5481,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5489,16 +5498,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>417</v>
-      </c>
       <c r="D3" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5506,16 +5515,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>419</v>
-      </c>
       <c r="D4" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5523,16 +5532,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="D5" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5540,16 +5549,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>423</v>
-      </c>
       <c r="D6" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5557,16 +5566,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>425</v>
-      </c>
       <c r="D7" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5574,16 +5583,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>427</v>
-      </c>
       <c r="D8" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5591,16 +5600,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="20" t="s">
         <v>429</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>430</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5608,16 +5617,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>432</v>
-      </c>
       <c r="D10" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5625,16 +5634,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>434</v>
-      </c>
       <c r="D11" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5642,16 +5651,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>436</v>
-      </c>
       <c r="D12" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5659,16 +5668,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>438</v>
-      </c>
       <c r="D13" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5676,16 +5685,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="21" t="s">
         <v>440</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>441</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5693,16 +5702,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>443</v>
-      </c>
       <c r="D15" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5710,16 +5719,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>445</v>
-      </c>
       <c r="D16" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5727,16 +5736,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>447</v>
-      </c>
       <c r="D17" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5744,7 +5753,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5752,10 +5761,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5763,10 +5772,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5774,10 +5783,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5785,10 +5794,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5796,10 +5805,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5807,10 +5816,10 @@
         <v>48</v>
       </c>
       <c r="B25" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5818,10 +5827,10 @@
         <v>48</v>
       </c>
       <c r="B26" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5829,10 +5838,32 @@
         <v>48</v>
       </c>
       <c r="B27" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="23" t="s">
         <v>464</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -5875,158 +5906,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E3" t="s">
+        <v>486</v>
+      </c>
+      <c r="F3" t="s">
         <v>480</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>482</v>
-      </c>
-      <c r="E3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F3" t="s">
-        <v>477</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B4" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C4" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E4" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F4" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C5" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F6" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6040,7 +6071,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="508">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -196,741 +196,750 @@
     <t>3:00pm</t>
   </si>
   <si>
-    <t>First walk: Pantheon → Piazza Navona → Campo de' Fiori — The Pantheon is an eight-minute walk. Go before the nap, not after.</t>
+    <t>First walk: Pantheon → Piazza Navona → Campo de' Fiori — 1) Piazza Navona, 2) Pantheon, 3) Piazza di Montecitorio, 4) Trevi Fountain, 5) Spanish Steps</t>
   </si>
   <si>
     <t>On foot</t>
   </si>
   <si>
+    <t>7:30pm</t>
+  </si>
+  <si>
+    <t>Dinner — Emma Pizzeria con Cucina — The Roscioli family's pizzeria: their salumeria supplies the kitchen, so the burrata and the cured meats are the same ones you get at Roscioli itself, on Roman-thin bases. A sharp modern room and a terrace on a quiet street four minutes from Trame — the shortest walk of anything considered, which is worth something after twenty hours awake. Book the 7:30 sitting; it fills.</t>
+  </si>
+  <si>
+    <t>Walk, 4 min</t>
+  </si>
+  <si>
+    <t>Reserve -&gt;</t>
+  </si>
+  <si>
+    <t>Tue, Aug 25</t>
+  </si>
+  <si>
+    <t>ROME — Vatican</t>
+  </si>
+  <si>
+    <t>7:45am</t>
+  </si>
+  <si>
+    <t>Vatican early-entry private tour — Museums, Sistine Chapel, St Peter's — Into the Sistine Chapel before general admission, then the Museums at your own pace and through to St Peter's Basilica. Book the private guide well ahead — the direct passage from the chapel into the basilica is only open to guided groups. Roughly four hours end to end.</t>
+  </si>
+  <si>
+    <t>Taxi, ~15 min</t>
+  </si>
+  <si>
+    <t>Tickets -&gt;</t>
+  </si>
+  <si>
+    <t>1:00pm</t>
+  </si>
+  <si>
+    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
+  </si>
+  <si>
+    <t>Walk from the Vatican</t>
+  </si>
+  <si>
+    <t>2:30pm</t>
+  </si>
+  <si>
+    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>5:00pm</t>
+  </si>
+  <si>
+    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
+  </si>
+  <si>
+    <t>Taxi, ~10 min</t>
+  </si>
+  <si>
+    <t>Rooftop aperitivo near Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>8:30pm</t>
+  </si>
+  <si>
+    <t>OPERA — arias at All Saints' Anglican Church — Confirm the Aug 25 programme; Via del Babuino, off Piazza di Spagna</t>
+  </si>
+  <si>
+    <t>10:00pm</t>
+  </si>
+  <si>
+    <t>Late dinner — Pierluigi — Seafood on Piazza de' Ricci; a properly Roman hour to eat</t>
+  </si>
+  <si>
+    <t>Walk, 6 min</t>
+  </si>
+  <si>
+    <t>Wed, Aug 26</t>
+  </si>
+  <si>
+    <t>ROME — Caracalla &amp; the Galleria Borghese</t>
+  </si>
+  <si>
+    <t>8:45am</t>
+  </si>
+  <si>
+    <t>Baths of Caracalla — First, while it is still quiet — the brick vaults standing to full height, the scale of the bathing halls, patches of the mosaic floor still in place. Far emptier than anything else in ancient Rome at this hour.</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>The Colosseum from outside, and the Arch of Constantine — The exterior circuit: the arcades from the Via dei Fori Imperiali side, then the Arch of Constantine. No arena floor and no interior ticket, so nothing to book and no queue to stand in.</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min from Caracalla</t>
+  </si>
+  <si>
+    <t>Lunch — Roscioli — Carbonara and cacio e pepe, and the deli counter on the way out</t>
+  </si>
+  <si>
+    <t>Walk, 5 min via Campo de' Fiori</t>
+  </si>
+  <si>
+    <t>2:15pm</t>
+  </si>
+  <si>
+    <t>Siesta — An hour at most — the Galleria will not hold your slot, so leave in time for the taxi</t>
+  </si>
+  <si>
+    <t>At the hotel</t>
+  </si>
+  <si>
+    <t>3:30pm</t>
+  </si>
+  <si>
+    <t>Galleria Borghese — booked slot — Bernini's Apollo and Daphne and the Rape of Proserpina, and six Caravaggios, in a villa small enough to see properly. Entry is a hard two-hour window with a fixed start time and a capped room — you are let in and let out on the clock, so build the afternoon around it, not the other way round.</t>
+  </si>
+  <si>
+    <t>5:30pm</t>
+  </si>
+  <si>
+    <t>Villa Borghese Gardens and the Pincio, in the daylight — Straight out of the Galleria into the park — shaded avenues, the Fontana dei Cavalli Marini, and the Pincio terrace over Piazza del Popolo with St. Peter's dome on the skyline. This is the Rome photo session: low sun through the trees, which is what the half-hour was chosen for.</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min across the park</t>
+  </si>
+  <si>
+    <t>Info -&gt;</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
+  </si>
+  <si>
+    <t>Walk down, ~10 min</t>
+  </si>
+  <si>
+    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
+  </si>
+  <si>
+    <t>9:00pm</t>
+  </si>
+  <si>
+    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
+  </si>
+  <si>
+    <t>Walk, ~12 min</t>
+  </si>
+  <si>
+    <t>Thu, Aug 27</t>
+  </si>
+  <si>
+    <t>ROME → FLORENCE — direct by Frecciarossa</t>
+  </si>
+  <si>
+    <t>TRAVEL DAY</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
+  </si>
+  <si>
+    <t>12:10pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9420 to Florence — Booked. Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 2h01</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>2:11pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze S.M.N.</t>
+  </si>
+  <si>
+    <t>2:25pm</t>
+  </si>
+  <si>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+  </si>
+  <si>
+    <t>Taxi, ~8 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>2:50pm</t>
+  </si>
+  <si>
+    <t>Late lunch — Mercato Centrale — The booked train lands at 2:11pm, which puts Trattoria Mario inside twenty minutes of its 3:30pm kitchen close — not worth the run. The market's upstairs food hall is open all day and takes no booking. Mario is the gamble if you are quick off the platform.</t>
+  </si>
+  <si>
+    <t>Walk, ~11 min</t>
+  </si>
+  <si>
+    <t>4:00pm</t>
+  </si>
+  <si>
+    <t>Accademia — David at the afternoon slot — Book the 4:00pm entry — the train now lands at 2:11pm. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm, so this is timed to it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
+  </si>
+  <si>
+    <t>Walk, ~14 min</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to the river</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Santa Trinita, ~8 min</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>11:15am</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
+  </si>
+  <si>
+    <t>1:14pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 3h09</t>
+  </si>
+  <si>
+    <t>4:23pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
+  </si>
+  <si>
+    <t>5:26pm</t>
+  </si>
+  <si>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h09</t>
+  </si>
+  <si>
+    <t>EAV -&gt;</t>
+  </si>
+  <si>
+    <t>6:35pm</t>
+  </si>
+  <si>
+    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
+  </si>
+  <si>
+    <t>6:50pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
     <t>6:00pm</t>
   </si>
   <si>
-    <t>Nap, deliberately — Set an alarm. This is the single best defence against day-two jet lag.</t>
-  </si>
-  <si>
-    <t>At the hotel</t>
-  </si>
-  <si>
-    <t>7:30pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Etabli — Or the Campari bar on Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Walk, 4 min</t>
+    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
+  </si>
+  <si>
+    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>3:50pm</t>
+  </si>
+  <si>
+    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
+  </si>
+  <si>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h30</t>
+  </si>
+  <si>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
+  </si>
+  <si>
+    <t>Last breakfast on the roof</t>
+  </si>
+  <si>
+    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice — it buys the Naples stop below</t>
+  </si>
+  <si>
+    <t>10:20am</t>
+  </si>
+  <si>
+    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train already standing where the next one leaves.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h14</t>
+  </si>
+  <si>
+    <t>11:34am</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Nearly two hours before the Frecciarossa, and the point of the early start</t>
+  </si>
+  <si>
+    <t>11:55am</t>
+  </si>
+  <si>
+    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city: Di Matteo and Sorbillo are both about twenty minutes' walk up Via dei Tribunali. Naples came out of this itinerary altogether, and this is the one window it gets back. If you would rather not carry the risk, there is good pizza within sight of the station.</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min</t>
   </si>
   <si>
     <t>Find -&gt;</t>
   </si>
   <si>
-    <t>8:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Emma Pizzeria con Cucina — The Roscioli family's pizzeria: their salumeria supplies the kitchen, so the burrata and the cured meats are the same ones you get at Roscioli itself, on Roman-thin bases. A sharp modern room and a terrace on a quiet street four minutes from Trame — the shortest walk of anything considered, which is worth something after twenty hours awake. Book it; it fills.</t>
-  </si>
-  <si>
-    <t>Reserve -&gt;</t>
-  </si>
-  <si>
-    <t>Tue, Aug 25</t>
-  </si>
-  <si>
-    <t>ROME — Vatican</t>
-  </si>
-  <si>
-    <t>7:45am</t>
-  </si>
-  <si>
-    <t>Vatican early-entry private tour — Into the Sistine Chapel before general admission</t>
-  </si>
-  <si>
-    <t>Taxi, ~15 min</t>
-  </si>
-  <si>
-    <t>Tickets -&gt;</t>
-  </si>
-  <si>
-    <t>1:00pm</t>
-  </si>
-  <si>
-    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
-  </si>
-  <si>
-    <t>Walk from the Vatican</t>
-  </si>
-  <si>
-    <t>2:30pm</t>
-  </si>
-  <si>
-    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
-  </si>
-  <si>
-    <t>Taxi</t>
-  </si>
-  <si>
-    <t>5:00pm</t>
-  </si>
-  <si>
-    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
-  </si>
-  <si>
-    <t>Taxi, ~10 min</t>
-  </si>
-  <si>
-    <t>Rooftop aperitivo near Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Walk</t>
-  </si>
-  <si>
-    <t>8:30pm</t>
-  </si>
-  <si>
-    <t>OPERA — arias at All Saints' Anglican Church — Confirm the Aug 25 programme; Via del Babuino, off Piazza di Spagna</t>
-  </si>
-  <si>
-    <t>10:00pm</t>
-  </si>
-  <si>
-    <t>Late dinner — Pierluigi — Seafood on Piazza de' Ricci; a properly Roman hour to eat</t>
-  </si>
-  <si>
-    <t>Walk, 6 min</t>
-  </si>
-  <si>
-    <t>Wed, Aug 26</t>
-  </si>
-  <si>
-    <t>ROME — Colosseum &amp; the Forum</t>
-  </si>
-  <si>
-    <t>8:45am</t>
-  </si>
-  <si>
-    <t>Colosseum with arena floor, then Forum + Palatine — The arena-floor add-on is worth it — you stand where the sand was</t>
+    <t>1:30pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9544 to Rome — Booked. Napoli Centrale 13:30 → Roma Termini 14:55, Executive, coach 1.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 1h25</t>
+  </si>
+  <si>
+    <t>2:55pm</t>
+  </si>
+  <si>
+    <t>Arrive Roma Termini; taxi to the hotel</t>
   </si>
   <si>
     <t>Taxi, ~12 min</t>
   </si>
   <si>
-    <t>Lunch — Roscioli — Carbonara and cacio e pepe, and the deli counter on the way out</t>
-  </si>
-  <si>
-    <t>Walk, 5 min via Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Siesta — Shorter than the other days — the light at Borghese is worth trading a bit of rest for</t>
-  </si>
-  <si>
-    <t>4:00pm</t>
-  </si>
-  <si>
-    <t>Villa Borghese Gardens, in the daylight — Rome's largest park — shaded avenues, the Fontana dei Cavalli Marini, and the Pincio terrace over Piazza del Popolo with St. Peter's dome on the skyline. Soft light under the trees most of the afternoon — good ground for pictures. The Galleria itself needs a timed ticket booked weeks out; skip it unless you already have one.</t>
-  </si>
-  <si>
-    <t>Info -&gt;</t>
-  </si>
-  <si>
-    <t>5:30pm</t>
-  </si>
-  <si>
-    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
-  </si>
-  <si>
-    <t>Walk down, ~10 min</t>
-  </si>
-  <si>
-    <t>6:15pm</t>
-  </si>
-  <si>
-    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
-  </si>
-  <si>
-    <t>9:00pm</t>
-  </si>
-  <si>
-    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
-  </si>
-  <si>
-    <t>Walk, ~12 min</t>
-  </si>
-  <si>
-    <t>Thu, Aug 27</t>
-  </si>
-  <si>
-    <t>ROME → FLORENCE — direct by Frecciarossa</t>
-  </si>
-  <si>
-    <t>TRAVEL DAY</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
-  </si>
-  <si>
-    <t>12:10pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9420 to Florence — Booked. Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 2h01</t>
-  </si>
-  <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>2:11pm</t>
-  </si>
-  <si>
-    <t>Arrive Firenze S.M.N.</t>
-  </si>
-  <si>
-    <t>2:25pm</t>
-  </si>
-  <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
-  </si>
-  <si>
-    <t>Taxi, ~8 min</t>
-  </si>
-  <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>2:50pm</t>
-  </si>
-  <si>
-    <t>Late lunch — Mercato Centrale — The booked train lands at 2:11pm, which puts Trattoria Mario inside twenty minutes of its 3:30pm kitchen close — not worth the run. The market's upstairs food hall is open all day and takes no booking. Mario is the gamble if you are quick off the platform.</t>
-  </si>
-  <si>
-    <t>Walk, ~11 min</t>
-  </si>
-  <si>
-    <t>Accademia — David at the afternoon slot — Book the 4:00pm entry — the train now lands at 2:11pm. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm, so this is timed to it. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
-  </si>
-  <si>
-    <t>Walk, ~14 min</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to the river</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>2:15pm</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
-  </si>
-  <si>
-    <t>1:14pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 3h09</t>
-  </si>
-  <si>
-    <t>4:23pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
-  </si>
-  <si>
-    <t>5:26pm</t>
-  </si>
-  <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h09</t>
-  </si>
-  <si>
-    <t>EAV -&gt;</t>
-  </si>
-  <si>
-    <t>6:35pm</t>
-  </si>
-  <si>
-    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
-  </si>
-  <si>
-    <t>6:50pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
-  </si>
-  <si>
-    <t>Walk ~20 min, or taxi</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
-  </si>
-  <si>
-    <t>Ferry, ~1h15</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
-  </si>
-  <si>
-    <t>Walk from the marina</t>
-  </si>
-  <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
-  </si>
-  <si>
-    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>3:50pm</t>
-  </si>
-  <si>
-    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
-  </si>
-  <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h30</t>
-  </si>
-  <si>
-    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
-  </si>
-  <si>
-    <t>Last breakfast on the roof</t>
-  </si>
-  <si>
-    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice — it buys the Naples stop below</t>
-  </si>
-  <si>
-    <t>10:20am</t>
-  </si>
-  <si>
-    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train already standing where the next one leaves.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h14</t>
-  </si>
-  <si>
-    <t>11:34am</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Nearly two hours before the Frecciarossa, and the point of the early start</t>
-  </si>
-  <si>
-    <t>11:55am</t>
-  </si>
-  <si>
-    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city: Di Matteo and Sorbillo are both about twenty minutes' walk up Via dei Tribunali. Naples came out of this itinerary altogether, and this is the one window it gets back. If you would rather not carry the risk, there is good pizza within sight of the station.</t>
-  </si>
-  <si>
-    <t>Walk, ~20 min</t>
-  </si>
-  <si>
-    <t>1:30pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9544 to Rome — Booked. Napoli Centrale 13:30 → Roma Termini 14:55, Executive, coach 1.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 1h25</t>
-  </si>
-  <si>
-    <t>2:55pm</t>
-  </si>
-  <si>
-    <t>Arrive Roma Termini; taxi to the hotel</t>
-  </si>
-  <si>
     <t>3:20pm</t>
   </si>
   <si>
@@ -1081,7 +1090,7 @@
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Colosseum, Florence galleries and the dome climb, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two).</t>
+    <t>Vatican, Caracalla and the Galleria Borghese, Florence galleries and the dome climb, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two).</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1288,10 +1297,10 @@
     <t>Two Florence days means no second chance at either. The Accademia is the 3:15pm slot on arrival day — the day now starts at checkout, so book the afternoon, not the lunchtime. The Uffizi is guided at 10:15am the morning after the dome.</t>
   </si>
   <si>
-    <t>Colosseum with arena floor — Aug 26</t>
-  </si>
-  <si>
-    <t>The arena-floor add-on is a separate, smaller allocation than general admission.</t>
+    <t>Galleria Borghese — Aug 26, 3:30pm slot</t>
+  </si>
+  <si>
+    <t>Timed entry, two hours, a capped number of people in the building at once. Slots go weeks ahead and the 3:30pm one is what the rest of that afternoon is built around — if it is gone, take the nearest and tell me so I can move the gardens and the photo session with it.</t>
   </si>
   <si>
     <t>Horseback riding, lunch &amp; winery — San Gimignano, Aug 30</t>
@@ -2349,59 +2358,59 @@
       <c r="E7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="F7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>2</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="7" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="D10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E10" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>2</v>
-      </c>
-      <c r="B11" s="10" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="4" t="s">
         <v>72</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,16 +2421,16 @@
         <v>48</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="7" t="s">
         <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,13 +2461,13 @@
         <v>48</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="13" t="s">
         <v>81</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>82</v>
       </c>
       <c r="F14" t="s">
         <v>48</v>
@@ -2472,16 +2481,16 @@
         <v>48</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,67 +2501,67 @@
         <v>48</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="13" t="s">
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>3</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="4" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="12" t="s">
+      <c r="D19" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E19" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="D20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
-        <v>3</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="E20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>94</v>
+      <c r="F20" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,16 +2572,16 @@
         <v>48</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>97</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,16 +2592,16 @@
         <v>48</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>70</v>
+      <c r="F22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2603,16 +2612,16 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
+        <v>69</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2629,10 +2638,10 @@
         <v>102</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,13 +2652,13 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -2663,13 +2672,13 @@
         <v>48</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
         <v>48</v>
@@ -2692,7 +2701,7 @@
         <v>111</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2723,7 +2732,7 @@
         <v>116</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s">
         <v>48</v>
@@ -2817,16 +2826,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2837,16 +2846,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="F36" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2857,13 +2866,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2877,10 +2886,10 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>125</v>
@@ -2897,13 +2906,13 @@
         <v>48</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" t="s">
         <v>48</v>
@@ -2920,13 +2929,13 @@
         <v>109</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2934,10 +2943,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2948,16 +2957,16 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2968,13 +2977,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2988,16 +2997,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3008,16 +3017,16 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3028,7 +3037,7 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>157</v>
@@ -3037,7 +3046,7 @@
         <v>158</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3054,7 +3063,7 @@
         <v>160</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
@@ -3068,13 +3077,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
@@ -3094,10 +3103,10 @@
         <v>163</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3117,7 +3126,7 @@
         <v>166</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3148,7 +3157,7 @@
         <v>170</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3162,7 +3171,7 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>171</v>
@@ -3191,7 +3200,7 @@
         <v>175</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3208,7 +3217,7 @@
         <v>177</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3222,13 +3231,13 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>178</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F58" t="s">
         <v>48</v>
@@ -3242,7 +3251,7 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>179</v>
@@ -3282,7 +3291,7 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>182</v>
@@ -3302,13 +3311,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>183</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F62" t="s">
         <v>48</v>
@@ -3322,13 +3331,13 @@
         <v>48</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>184</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F63" t="s">
         <v>48</v>
@@ -3393,13 +3402,13 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F68" t="s">
         <v>48</v>
@@ -3413,13 +3422,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="E69" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3436,10 +3445,10 @@
         <v>115</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" s="13" t="s">
         <v>193</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>194</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>181</v>
@@ -3453,10 +3462,10 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="E71" s="13" t="s">
         <v>172</v>
@@ -3473,13 +3482,13 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
@@ -3493,13 +3502,13 @@
         <v>48</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F73" t="s">
         <v>48</v>
@@ -3510,10 +3519,10 @@
         <v>8</v>
       </c>
       <c r="B75" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="F75" s="14" t="s">
         <v>114</v>
@@ -3527,10 +3536,10 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>172</v>
@@ -3547,13 +3556,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="13" t="s">
         <v>203</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3567,13 +3576,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="E78" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3587,13 +3596,13 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>209</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>120</v>
@@ -3607,10 +3616,10 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>57</v>
@@ -3627,16 +3636,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="E81" s="13" t="s">
+      <c r="F81" s="7" t="s">
         <v>214</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3647,10 +3656,10 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>57</v>
@@ -3667,13 +3676,13 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="E83" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>126</v>
@@ -3687,13 +3696,13 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="E84" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F84" t="s">
         <v>48</v>
@@ -3707,13 +3716,13 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F85" t="s">
         <v>48</v>
@@ -3727,13 +3736,13 @@
         <v>48</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>223</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>126</v>
@@ -3764,7 +3773,7 @@
         <v>227</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3804,10 +3813,10 @@
         <v>230</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,10 +3833,10 @@
         <v>232</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,13 +3847,13 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>233</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F93" t="s">
         <v>48</v>
@@ -3858,13 +3867,13 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F94" t="s">
         <v>48</v>
@@ -3878,16 +3887,16 @@
         <v>48</v>
       </c>
       <c r="C95" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F95" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3895,10 +3904,10 @@
         <v>10</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3909,13 +3918,13 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F98" t="s">
         <v>48</v>
@@ -3929,16 +3938,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3949,13 +3958,13 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F100" t="s">
         <v>48</v>
@@ -3972,13 +3981,13 @@
         <v>231</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3989,16 +3998,16 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>60</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4012,10 +4021,10 @@
         <v>159</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -4029,13 +4038,13 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F104" t="s">
         <v>48</v>
@@ -4049,16 +4058,16 @@
         <v>48</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4066,10 +4075,10 @@
         <v>11</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4083,10 +4092,10 @@
         <v>226</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F108" t="s">
         <v>48</v>
@@ -4100,16 +4109,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4123,7 +4132,7 @@
         <v>115</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>57</v>
@@ -4143,13 +4152,13 @@
         <v>231</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4163,10 +4172,10 @@
         <v>55</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4183,10 +4192,10 @@
         <v>58</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4200,13 +4209,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4220,13 +4229,13 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F115" t="s">
         <v>48</v>
@@ -4240,16 +4249,16 @@
         <v>48</v>
       </c>
       <c r="C116" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4257,10 +4266,10 @@
         <v>12</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4271,10 +4280,10 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>125</v>
@@ -4291,16 +4300,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,13 +4320,13 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -4331,13 +4340,13 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F122" t="s">
         <v>48</v>
@@ -4351,16 +4360,16 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4371,13 +4380,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F124" t="s">
         <v>48</v>
@@ -4391,16 +4400,16 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,16 +4420,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,13 +4440,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F127" t="s">
         <v>48</v>
@@ -4451,16 +4460,16 @@
         <v>48</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4468,10 +4477,10 @@
         <v>13</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F130" s="14" t="s">
         <v>114</v>
@@ -4485,13 +4494,13 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4505,13 +4514,13 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F132" t="s">
         <v>48</v>
@@ -4525,16 +4534,16 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4545,10 +4554,10 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>57</v>
@@ -4565,16 +4574,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>67</v>
+        <v>300</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4585,13 +4594,13 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>120</v>
@@ -4605,13 +4614,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4625,10 +4634,10 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>57</v>
@@ -4648,10 +4657,10 @@
         <v>159</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4665,10 +4674,10 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E140" s="13" t="s">
         <v>158</v>
@@ -4685,13 +4694,13 @@
         <v>48</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F141" t="s">
         <v>48</v>
@@ -4705,13 +4714,13 @@
         <v>48</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F142" t="s">
         <v>48</v>
@@ -4725,16 +4734,16 @@
         <v>48</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4742,10 +4751,10 @@
         <v>14</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4756,13 +4765,13 @@
         <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F146" t="s">
         <v>48</v>
@@ -4776,13 +4785,13 @@
         <v>48</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F147" t="s">
         <v>48</v>
@@ -4796,13 +4805,13 @@
         <v>48</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F148" t="s">
         <v>48</v>
@@ -4810,15 +4819,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F8" r:id="rId1"/>
-    <hyperlink ref="F9" r:id="rId2"/>
-    <hyperlink ref="F12" r:id="rId3"/>
+    <hyperlink ref="F7" r:id="rId1"/>
+    <hyperlink ref="F10" r:id="rId2"/>
+    <hyperlink ref="F11" r:id="rId3"/>
     <hyperlink ref="F13" r:id="rId4"/>
     <hyperlink ref="F15" r:id="rId5"/>
-    <hyperlink ref="F17" r:id="rId6"/>
-    <hyperlink ref="F18" r:id="rId7"/>
+    <hyperlink ref="F16" r:id="rId6"/>
+    <hyperlink ref="F19" r:id="rId7"/>
     <hyperlink ref="F21" r:id="rId8"/>
-    <hyperlink ref="F22" r:id="rId9"/>
+    <hyperlink ref="F23" r:id="rId9"/>
     <hyperlink ref="F24" r:id="rId10"/>
     <hyperlink ref="F27" r:id="rId11"/>
     <hyperlink ref="F31" r:id="rId12"/>
@@ -4881,42 +4890,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4934,18 +4943,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D3" t="s">
         <v>112</v>
@@ -4963,24 +4972,24 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
         <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4992,24 +5001,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5021,24 +5030,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5050,7 +5059,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -5067,7 +5076,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -5104,24 +5113,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5132,51 +5141,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B7" s="17">
         <v>18133.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -5201,220 +5210,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="D3" t="s">
-        <v>370</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B5" t="s">
         <v>172</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B6" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B7" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D9" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B12" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D12" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5425,7 +5434,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -5461,16 +5470,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5481,16 +5490,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5498,16 +5507,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>413</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5515,16 +5524,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>417</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5532,16 +5541,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5549,16 +5558,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5566,16 +5575,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5583,16 +5592,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5600,16 +5609,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5617,16 +5626,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5634,16 +5643,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>429</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5651,16 +5660,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5668,16 +5677,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5685,16 +5694,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5702,16 +5711,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5719,16 +5728,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>440</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5736,16 +5745,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5753,7 +5762,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5761,10 +5770,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5772,10 +5781,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5783,10 +5792,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5794,10 +5803,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5805,10 +5814,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5816,10 +5825,10 @@
         <v>48</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5827,10 +5836,10 @@
         <v>48</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5838,10 +5847,10 @@
         <v>48</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -5849,10 +5858,10 @@
         <v>48</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5860,10 +5869,10 @@
         <v>48</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5906,158 +5915,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" t="s">
         <v>483</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>485</v>
-      </c>
-      <c r="E3" t="s">
-        <v>486</v>
-      </c>
-      <c r="F3" t="s">
-        <v>480</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B4" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C4" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E4" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F4" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E5" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F5" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E6" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6071,7 +6080,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="507">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
   <si>
-    <t>Updated Sat, Aug 1</t>
+    <t>Updated Wed, Aug 5</t>
   </si>
   <si>
     <t>Travelers</t>
@@ -400,498 +400,495 @@
     <t>Hotel site -&gt;</t>
   </si>
   <si>
-    <t>2:50pm</t>
-  </si>
-  <si>
-    <t>Late lunch — Mercato Centrale — The booked train lands at 2:11pm, which puts Trattoria Mario inside twenty minutes of its 3:30pm kitchen close — not worth the run. The market's upstairs food hall is open all day and takes no booking. Mario is the gamble if you are quick off the platform.</t>
-  </si>
-  <si>
-    <t>Walk, ~11 min</t>
+    <t>Accademia — David at the afternoon slot — Book the 3:00pm entry — the train lands at 2:11pm and lunch is already behind you, on board. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
   </si>
   <si>
     <t>4:00pm</t>
   </si>
   <si>
-    <t>Accademia — David at the afternoon slot — Book the 4:00pm entry — the train now lands at 2:11pm. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
+    <t>Duomo — Baptistery, cathedral and the Opera del Duomo museum, where the Ghiberti doors are the originals. Four o'clock rather than the old 5:15pm slot: the cathedral stops admitting in the late afternoon, and arriving at a quarter past five would have left you the museum and not much else. One pass covers the complex — the dome climb is no longer part of the trip, so you do not need the one that includes it.</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm and the hill is the place to watch it from — this is timed to it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — A quarter past eight is the minute the gates open, and that is the whole point: Boboli is terraced, unshaded and unwalkable by mid-afternoon, so it goes first. The Palatine Gallery is hung floor to ceiling in the old manner; climb to the top of the gardens for the view back over the city.</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs straight from the palace gates to the bridge — stop halfway down it.</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>12:15pm</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Vecchio, ~6 min</t>
+  </si>
+  <si>
+    <t>Late lunch — 'Ino — Two hours in the Uffizi from a quarter past twelve puts you out at half past two, which is when the Oltrarno kitchens stop serving — so lunch is thirty seconds from the gallery door instead. Panini made to order, Tuscan wine by the glass, open straight through the afternoon. Il Santo Bevitore across the river stays the sit-down alternative if the tour runs short.</t>
+  </si>
+  <si>
+    <t>Walk, ~2 min</t>
+  </si>
+  <si>
+    <t>Reverse Renaissance Walk — The centre backwards, starting where it started: the Casa di Dante, then Orsanmichele, then out into Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, and free. This was Thursday evening's block, moved here because it never had the daylight there.</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Fifteen minutes on foot up from the centre, so taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>Fiesole — Florence from the hill — Twenty-five minutes up out of the valley for the view back over the whole city: the roofs, the river and the dome seen from above rather than beneath. Go out along the viali — the ZTL starts the moment you cut through the centre — and leave the car at Piazza Mino.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~25 min</t>
+  </si>
+  <si>
+    <t>Southwest to Certaldo — Back down through the valley and out the other side — about an hour and ten from Fiesole, against forty-five minutes had you driven straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~1h10</t>
+  </si>
+  <si>
+    <t>12:00pm</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told. Alternative operator for the same kind of morning, if this one fills: CET Experience, cetexperience.it.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
+  </si>
+  <si>
+    <t>1:14pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 3h09</t>
+  </si>
+  <si>
+    <t>4:23pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
+  </si>
+  <si>
+    <t>5:26pm</t>
+  </si>
+  <si>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h09</t>
+  </si>
+  <si>
+    <t>EAV -&gt;</t>
+  </si>
+  <si>
+    <t>6:35pm</t>
+  </si>
+  <si>
+    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
+  </si>
+  <si>
+    <t>6:50pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>6:00pm</t>
+  </si>
+  <si>
+    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
   </si>
   <si>
     <t>5:15pm</t>
   </si>
   <si>
-    <t>The Duomo complex — Baptistery, cathedral, museum — Everything but the dome climb, which is booked for tomorrow's first slot. The Ghiberti doors in the Opera del Duomo museum are the originals.</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Piazza della Signoria and the Loggia dei Lanzi — An open-air sculpture hall, and it is free</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm, so this is timed to it. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Duomo — climb Brunelleschi's dome — 463 steps, timed slot, and far better before the day heats up. Book this one first — it has the fewest slots of anything in the city.</t>
-  </si>
-  <si>
-    <t>Walk, ~14 min</t>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
+  </si>
+  <si>
+    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>3:50pm</t>
+  </si>
+  <si>
+    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
+  </si>
+  <si>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h30</t>
+  </si>
+  <si>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
+  </si>
+  <si>
+    <t>Last breakfast on the roof</t>
   </si>
   <si>
     <t>9:45am</t>
   </si>
   <si>
-    <t>Coffee on the way down to the river</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Lunch in the Oltrarno — Il Santo Bevitore — Or Gucci Osteria on Piazza della Signoria if you want the splurge instead.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Santa Trinita, ~8 min</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — The gardens are the reason to go; climb to the top for the view back over the city</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Oltrarno artisan workshops — Via Maggio and Santo Spirito — gilders, leatherworkers and restorers still working at street level</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Twenty minutes on foot from the Oltrarno, so taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>Southwest out of the city — Florence → Certaldo is about 45 minutes</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>11:15am</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
-  </si>
-  <si>
-    <t>1:14pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 3h09</t>
-  </si>
-  <si>
-    <t>4:23pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
-  </si>
-  <si>
-    <t>5:26pm</t>
-  </si>
-  <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h09</t>
-  </si>
-  <si>
-    <t>EAV -&gt;</t>
-  </si>
-  <si>
-    <t>6:35pm</t>
-  </si>
-  <si>
-    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
-  </si>
-  <si>
-    <t>6:50pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>8:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>6:00pm</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
-  </si>
-  <si>
-    <t>Walk ~20 min, or taxi</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
-  </si>
-  <si>
-    <t>Ferry, ~1h15</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
-  </si>
-  <si>
-    <t>Walk from the marina</t>
-  </si>
-  <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
-  </si>
-  <si>
-    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>3:50pm</t>
-  </si>
-  <si>
-    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
-  </si>
-  <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h30</t>
-  </si>
-  <si>
-    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
-  </si>
-  <si>
-    <t>Last breakfast on the roof</t>
-  </si>
-  <si>
     <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice — it buys the Naples stop below</t>
   </si>
   <si>
@@ -1090,7 +1087,7 @@
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Caracalla and the Galleria Borghese, Florence galleries and the dome climb, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two).</t>
+    <t>Vatican, Caracalla and the Galleria Borghese, the Florence galleries (Accademia, the guided Uffizi, Pitti and Boboli) and the Duomo complex pass, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two). Unchanged in total despite the dome climb coming out: the ~$65 it saved is near enough what Pitti and Boboli now cost as a ticketed morning.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1279,10 +1276,10 @@
     <t>Two problems in one. The old reservation is still FCO Aug 24 → FCO Sep 6, so left alone it bills you for a fortnight's hire you will not take. And the car you do need — Borgo Ognissanti, Florence, Aug 29 to Aug 31 — is not booked at all. Re-quote before cancelling; the old €1,087.81 was a fourteen-day FCO round trip and will not carry over.</t>
   </si>
   <si>
-    <t>Duomo dome climb — Aug 28, 8:15am</t>
-  </si>
-  <si>
-    <t>The tightest ticket in the itinerary: 463 steps on a timed slot, and it has the fewest places of anything in Florence. Late August with one Florence morning to spend means booking this before any other ticket.</t>
+    <t>Duomo complex pass — Aug 27, 4:00pm</t>
+  </si>
+  <si>
+    <t>Baptistery, cathedral and the Opera del Duomo museum on arrival afternoon. The dome climb is off the trip, so this is the pass without it — cheaper, and far easier to get. Book the four o'clock entry rather than later: the cathedral stops admitting well before the museum does.</t>
   </si>
   <si>
     <t>Vatican early entry — Aug 25, 7:45am</t>
@@ -1291,10 +1288,10 @@
     <t>The whole point of the Vatican day is being in the Sistine Chapel before general admission, and those slots go first.</t>
   </si>
   <si>
-    <t>Accademia (Aug 27) and the Uffizi (Aug 28)</t>
-  </si>
-  <si>
-    <t>Two Florence days means no second chance at either. The Accademia is the 3:15pm slot on arrival day — the day now starts at checkout, so book the afternoon, not the lunchtime. The Uffizi is guided at 10:15am the morning after the dome.</t>
+    <t>Accademia (Aug 27), then Pitti and the Uffizi (Aug 28)</t>
+  </si>
+  <si>
+    <t>Two Florence days means no second chance at any of them. The Accademia is the 3:00pm slot on arrival day, once the train is in. The next day opens at Pitti — book the 8:15am opening, which is what gets Boboli done before the heat — and the Uffizi is guided at 12:15pm, after the walk down from the palace.</t>
   </si>
   <si>
     <t>Galleria Borghese — Aug 26, 3:30pm slot</t>
@@ -1327,7 +1324,7 @@
     <t>Florence opera — La Traviata at St. Mark's, Aug 28</t>
   </si>
   <si>
-    <t>A chamber staging in a small church, so the room is small too. Follows the Boboli afternoon on the single full Florence day.</t>
+    <t>A chamber staging in a small church, so the room is small too. Closes the single full Florence day, after the walk back through the centre.</t>
   </si>
   <si>
     <t>Rome opera — All Saints' Anglican, Aug 25</t>
@@ -2220,7 +2217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2806,16 +2803,16 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F34" t="s">
-        <v>48</v>
+      <c r="F34" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2826,13 +2823,13 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="E35" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>70</v>
@@ -2846,16 +2843,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>70</v>
+        <v>125</v>
+      </c>
+      <c r="F36" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,13 +2863,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2886,67 +2883,67 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
+        <v>5</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="4" t="s">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="F38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="D41" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E41" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="D42" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="E42" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10">
-        <v>5</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>146</v>
+      <c r="F42" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2957,13 +2954,13 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>70</v>
@@ -2977,13 +2974,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2997,16 +2994,16 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>70</v>
+        <v>150</v>
+      </c>
+      <c r="F45" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3017,16 +3014,16 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>64</v>
+        <v>152</v>
+      </c>
+      <c r="F46" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3037,13 +3034,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>70</v>
@@ -3057,56 +3054,30 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="10">
+        <v>6</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>70</v>
+      <c r="F50" s="14" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3117,30 +3088,56 @@
         <v>48</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="F52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E53" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
-        <v>6</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>114</v>
+      <c r="F53" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3151,16 +3148,16 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F54" t="s">
-        <v>48</v>
+      <c r="F54" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3171,13 +3168,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>171</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -3191,16 +3188,16 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>104</v>
+        <v>81</v>
+      </c>
+      <c r="F56" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3211,13 +3208,13 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3231,16 +3228,16 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F58" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3251,13 +3248,13 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="F59" t="s">
         <v>48</v>
@@ -3271,16 +3268,16 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>181</v>
+        <v>98</v>
+      </c>
+      <c r="F60" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3291,67 +3288,67 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
+        <v>7</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E61" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F61" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" t="s">
-        <v>48</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" s="4" t="s">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E62" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F62" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>48</v>
-      </c>
-      <c r="B63" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="E64" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F64" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F63" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
-        <v>7</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>186</v>
+      <c r="E65" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3362,13 +3359,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3382,13 +3379,13 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F67" t="s">
         <v>48</v>
@@ -3402,16 +3399,16 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F68" t="s">
-        <v>48</v>
+        <v>189</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,13 +3419,13 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>191</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -3442,16 +3439,16 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>181</v>
+        <v>98</v>
+      </c>
+      <c r="F70" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3462,70 +3459,70 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F71" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
+        <v>8</v>
+      </c>
+      <c r="B73" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="C73" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="E71" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F71" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>48</v>
-      </c>
-      <c r="B72" t="s">
-        <v>48</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="F73" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E72" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F72" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>48</v>
-      </c>
-      <c r="B73" t="s">
-        <v>48</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73" s="4" t="s">
+      <c r="D74" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E73" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F73" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="10">
-        <v>8</v>
-      </c>
-      <c r="B75" s="10" t="s">
+      <c r="E74" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="E75" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="F75" s="14" t="s">
-        <v>114</v>
+      <c r="F75" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3536,13 +3533,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="E76" s="13" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3556,7 +3553,7 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>202</v>
@@ -3564,8 +3561,8 @@
       <c r="E77" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="F77" t="s">
-        <v>48</v>
+      <c r="F77" s="7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3582,7 +3579,7 @@
         <v>205</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3605,7 +3602,7 @@
         <v>208</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>120</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,10 +3613,10 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>57</v>
@@ -3636,16 +3633,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>214</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3656,13 +3653,13 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="E82" s="13" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="F82" t="s">
         <v>48</v>
@@ -3676,16 +3673,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="E83" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>126</v>
+        <v>98</v>
+      </c>
+      <c r="F83" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,67 +3693,67 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F84" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>48</v>
-      </c>
-      <c r="B85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="F84" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="10">
+        <v>9</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C86" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E85" s="13" t="s">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" t="s">
+        <v>48</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E87" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F85" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>48</v>
-      </c>
-      <c r="B86" t="s">
-        <v>48</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
-        <v>9</v>
-      </c>
-      <c r="B88" s="10" t="s">
+      <c r="F87" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>48</v>
+      </c>
+      <c r="B88" t="s">
+        <v>48</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="E88" s="13" t="s">
         <v>225</v>
+      </c>
+      <c r="F88" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3767,16 +3764,16 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>227</v>
-      </c>
       <c r="E89" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F89" t="s">
-        <v>48</v>
+        <v>150</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3787,16 +3784,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="F90" t="s">
-        <v>48</v>
+        <v>136</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3807,16 +3804,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="F91" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3827,16 +3824,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>64</v>
+        <v>98</v>
+      </c>
+      <c r="F92" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3847,67 +3844,67 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D93" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
+        <v>10</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C95" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E93" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F93" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>48</v>
-      </c>
-      <c r="B94" t="s">
-        <v>48</v>
-      </c>
-      <c r="C94" s="12" t="s">
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B96" t="s">
+        <v>48</v>
+      </c>
+      <c r="C96" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D96" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E94" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F94" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>48</v>
-      </c>
-      <c r="B95" t="s">
-        <v>48</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="E96" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="E95" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="10">
-        <v>10</v>
-      </c>
-      <c r="B97" s="10" t="s">
+      <c r="F96" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>48</v>
+      </c>
+      <c r="B97" t="s">
+        <v>48</v>
+      </c>
+      <c r="C97" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="D97" s="4" t="s">
         <v>238</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,13 +3915,13 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F98" t="s">
         <v>48</v>
@@ -3938,7 +3935,7 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>243</v>
@@ -3947,7 +3944,7 @@
         <v>244</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,16 +3955,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F100" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3978,16 +3975,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>64</v>
+        <v>239</v>
+      </c>
+      <c r="F101" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,16 +3995,16 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="F102" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,67 +4015,67 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="D103" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E103" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="E103" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F103" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>48</v>
-      </c>
-      <c r="B104" t="s">
-        <v>48</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="F103" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
+        <v>11</v>
+      </c>
+      <c r="B105" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="E104" s="13" t="s">
+      <c r="C105" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>48</v>
+      </c>
+      <c r="B106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E106" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F104" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>48</v>
-      </c>
-      <c r="B105" t="s">
-        <v>48</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="10">
-        <v>11</v>
-      </c>
-      <c r="B107" s="10" t="s">
+      <c r="F106" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>48</v>
+      </c>
+      <c r="B107" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="E107" s="13" t="s">
         <v>256</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4089,13 +4086,13 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>257</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="F108" t="s">
         <v>48</v>
@@ -4109,16 +4106,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>258</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,13 +4126,13 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D110" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E110" s="13" t="s">
         <v>260</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="F110" t="s">
         <v>48</v>
@@ -4149,16 +4146,16 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>261</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>64</v>
+        <v>256</v>
+      </c>
+      <c r="F111" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4169,13 +4166,13 @@
         <v>48</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>262</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4189,13 +4186,13 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="D113" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E113" s="13" t="s">
         <v>264</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>259</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4209,67 +4206,67 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>265</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F114" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>48</v>
-      </c>
-      <c r="B115" t="s">
-        <v>48</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D115" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="10">
+        <v>12</v>
+      </c>
+      <c r="B116" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="C116" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="F115" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>48</v>
-      </c>
-      <c r="B116" t="s">
-        <v>48</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D116" s="4" t="s">
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>48</v>
+      </c>
+      <c r="B117" t="s">
+        <v>48</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E116" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="10">
-        <v>12</v>
-      </c>
-      <c r="B118" s="10" t="s">
+      <c r="E117" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F117" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>48</v>
+      </c>
+      <c r="B118" t="s">
+        <v>48</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="E118" s="13" t="s">
         <v>270</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4280,13 +4277,13 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>271</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>125</v>
+        <v>272</v>
       </c>
       <c r="F119" t="s">
         <v>48</v>
@@ -4300,16 +4297,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>245</v>
+        <v>81</v>
+      </c>
+      <c r="F120" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,16 +4317,16 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>152</v>
+        <v>274</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="F121" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,13 +4337,13 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>276</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="F122" t="s">
         <v>48</v>
@@ -4360,16 +4357,16 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>154</v>
+        <v>278</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4380,16 +4377,16 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F124" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4400,16 +4397,16 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>70</v>
+        <v>284</v>
+      </c>
+      <c r="F125" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,70 +4417,70 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>48</v>
-      </c>
-      <c r="B127" t="s">
-        <v>48</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E127" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="10">
+        <v>13</v>
+      </c>
+      <c r="B128" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="F127" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>48</v>
-      </c>
-      <c r="B128" t="s">
-        <v>48</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D128" s="4" t="s">
+      <c r="C128" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="E128" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="10">
-        <v>13</v>
-      </c>
-      <c r="B130" s="10" t="s">
+      <c r="F128" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" t="s">
+        <v>48</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="E129" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F129" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>48</v>
+      </c>
+      <c r="B130" t="s">
+        <v>48</v>
+      </c>
+      <c r="C130" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="F130" s="14" t="s">
-        <v>114</v>
+      <c r="D130" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F130" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4494,16 +4491,16 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F131" t="s">
-        <v>48</v>
+        <v>293</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4514,13 +4511,13 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>150</v>
+        <v>294</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="F132" t="s">
         <v>48</v>
@@ -4534,16 +4531,16 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>214</v>
+        <v>299</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4554,16 +4551,16 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F134" t="s">
-        <v>48</v>
+        <v>302</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4574,16 +4571,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>300</v>
+        <v>305</v>
+      </c>
+      <c r="F135" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4594,16 +4591,16 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>303</v>
+        <v>57</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4614,13 +4611,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>304</v>
+        <v>246</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>306</v>
+        <v>128</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4634,16 +4631,16 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>126</v>
+        <v>143</v>
+      </c>
+      <c r="F138" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4654,13 +4651,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>132</v>
+        <v>298</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4674,13 +4671,13 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>158</v>
+        <v>312</v>
       </c>
       <c r="F140" t="s">
         <v>48</v>
@@ -4694,67 +4691,67 @@
         <v>48</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="F141" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>48</v>
-      </c>
-      <c r="B142" t="s">
-        <v>48</v>
-      </c>
-      <c r="C142" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E142" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F142" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>48</v>
-      </c>
-      <c r="B143" t="s">
-        <v>48</v>
-      </c>
-      <c r="C143" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D143" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="10">
+        <v>14</v>
+      </c>
+      <c r="B143" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="E143" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="10">
-        <v>14</v>
-      </c>
-      <c r="B145" s="10" t="s">
+      <c r="C143" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C145" s="11" t="s">
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>48</v>
+      </c>
+      <c r="B144" t="s">
+        <v>48</v>
+      </c>
+      <c r="C144" s="12" t="s">
         <v>316</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F144" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>48</v>
+      </c>
+      <c r="B145" t="s">
+        <v>48</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="F145" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4765,55 +4762,15 @@
         <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="F146" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>48</v>
-      </c>
-      <c r="B147" t="s">
-        <v>48</v>
-      </c>
-      <c r="C147" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E147" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="F147" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>48</v>
-      </c>
-      <c r="B148" t="s">
-        <v>48</v>
-      </c>
-      <c r="C148" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E148" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="F148" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4832,42 +4789,40 @@
     <hyperlink ref="F27" r:id="rId11"/>
     <hyperlink ref="F31" r:id="rId12"/>
     <hyperlink ref="F33" r:id="rId13"/>
-    <hyperlink ref="F35" r:id="rId14"/>
-    <hyperlink ref="F36" r:id="rId15"/>
-    <hyperlink ref="F40" r:id="rId16"/>
-    <hyperlink ref="F43" r:id="rId17"/>
-    <hyperlink ref="F45" r:id="rId18"/>
-    <hyperlink ref="F46" r:id="rId19"/>
-    <hyperlink ref="F47" r:id="rId20"/>
-    <hyperlink ref="F50" r:id="rId21"/>
-    <hyperlink ref="F51" r:id="rId22"/>
-    <hyperlink ref="F56" r:id="rId23"/>
-    <hyperlink ref="F60" r:id="rId24"/>
-    <hyperlink ref="F70" r:id="rId25"/>
-    <hyperlink ref="F79" r:id="rId26"/>
-    <hyperlink ref="F81" r:id="rId27"/>
-    <hyperlink ref="F83" r:id="rId28"/>
-    <hyperlink ref="F86" r:id="rId29"/>
-    <hyperlink ref="F91" r:id="rId30"/>
-    <hyperlink ref="F92" r:id="rId31"/>
-    <hyperlink ref="F95" r:id="rId32"/>
-    <hyperlink ref="F99" r:id="rId33"/>
-    <hyperlink ref="F101" r:id="rId34"/>
-    <hyperlink ref="F102" r:id="rId35"/>
-    <hyperlink ref="F105" r:id="rId36"/>
-    <hyperlink ref="F109" r:id="rId37"/>
-    <hyperlink ref="F111" r:id="rId38"/>
-    <hyperlink ref="F116" r:id="rId39"/>
-    <hyperlink ref="F120" r:id="rId40"/>
-    <hyperlink ref="F123" r:id="rId41"/>
-    <hyperlink ref="F125" r:id="rId42"/>
-    <hyperlink ref="F126" r:id="rId43"/>
-    <hyperlink ref="F128" r:id="rId44"/>
-    <hyperlink ref="F133" r:id="rId45"/>
-    <hyperlink ref="F135" r:id="rId46"/>
-    <hyperlink ref="F136" r:id="rId47"/>
-    <hyperlink ref="F138" r:id="rId48"/>
-    <hyperlink ref="F143" r:id="rId49"/>
+    <hyperlink ref="F34" r:id="rId14"/>
+    <hyperlink ref="F35" r:id="rId15"/>
+    <hyperlink ref="F38" r:id="rId16"/>
+    <hyperlink ref="F41" r:id="rId17"/>
+    <hyperlink ref="F43" r:id="rId18"/>
+    <hyperlink ref="F47" r:id="rId19"/>
+    <hyperlink ref="F48" r:id="rId20"/>
+    <hyperlink ref="F54" r:id="rId21"/>
+    <hyperlink ref="F58" r:id="rId22"/>
+    <hyperlink ref="F68" r:id="rId23"/>
+    <hyperlink ref="F77" r:id="rId24"/>
+    <hyperlink ref="F79" r:id="rId25"/>
+    <hyperlink ref="F81" r:id="rId26"/>
+    <hyperlink ref="F84" r:id="rId27"/>
+    <hyperlink ref="F89" r:id="rId28"/>
+    <hyperlink ref="F90" r:id="rId29"/>
+    <hyperlink ref="F93" r:id="rId30"/>
+    <hyperlink ref="F97" r:id="rId31"/>
+    <hyperlink ref="F99" r:id="rId32"/>
+    <hyperlink ref="F100" r:id="rId33"/>
+    <hyperlink ref="F103" r:id="rId34"/>
+    <hyperlink ref="F107" r:id="rId35"/>
+    <hyperlink ref="F109" r:id="rId36"/>
+    <hyperlink ref="F114" r:id="rId37"/>
+    <hyperlink ref="F118" r:id="rId38"/>
+    <hyperlink ref="F121" r:id="rId39"/>
+    <hyperlink ref="F123" r:id="rId40"/>
+    <hyperlink ref="F124" r:id="rId41"/>
+    <hyperlink ref="F126" r:id="rId42"/>
+    <hyperlink ref="F131" r:id="rId43"/>
+    <hyperlink ref="F133" r:id="rId44"/>
+    <hyperlink ref="F134" r:id="rId45"/>
+    <hyperlink ref="F136" r:id="rId46"/>
+    <hyperlink ref="F141" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4890,42 +4845,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>331</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" t="s">
         <v>333</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>334</v>
-      </c>
-      <c r="C2" t="s">
-        <v>335</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4943,24 +4898,24 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" t="s">
         <v>337</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>338</v>
-      </c>
-      <c r="C3" t="s">
-        <v>339</v>
       </c>
       <c r="D3" t="s">
         <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4972,24 +4927,24 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" t="s">
         <v>340</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>341</v>
       </c>
-      <c r="C4" t="s">
-        <v>342</v>
-      </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -5001,24 +4956,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" t="s">
         <v>343</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>344</v>
       </c>
-      <c r="C5" t="s">
-        <v>345</v>
-      </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5030,24 +4985,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" t="s">
         <v>346</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>347</v>
       </c>
-      <c r="C6" t="s">
-        <v>348</v>
-      </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5059,7 +5014,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -5076,7 +5031,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -5113,24 +5068,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5141,51 +5096,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B4" s="15">
         <v>2050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B7" s="17">
         <v>18133.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -5210,220 +5165,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="B2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" t="s">
         <v>367</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="7" t="s">
         <v>368</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B3" t="s">
         <v>370</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" t="s">
         <v>372</v>
       </c>
-      <c r="D3" t="s">
-        <v>373</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B4" t="s">
         <v>374</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="D4" t="s">
         <v>376</v>
       </c>
-      <c r="D4" t="s">
-        <v>377</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C5" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" t="s">
         <v>378</v>
       </c>
-      <c r="D5" t="s">
-        <v>379</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="B6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="18" t="s">
+      <c r="D6" t="s">
         <v>381</v>
       </c>
-      <c r="D6" t="s">
-        <v>382</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B7" t="s">
         <v>383</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" t="s">
         <v>385</v>
       </c>
-      <c r="D7" t="s">
-        <v>386</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" t="s">
         <v>388</v>
       </c>
-      <c r="D8" t="s">
-        <v>389</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" t="s">
         <v>390</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" t="s">
         <v>392</v>
       </c>
-      <c r="D9" t="s">
-        <v>393</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B10" t="s">
         <v>394</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="D10" t="s">
         <v>396</v>
       </c>
-      <c r="D10" t="s">
-        <v>397</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>397</v>
+      </c>
+      <c r="B11" t="s">
         <v>398</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" t="s">
         <v>400</v>
       </c>
-      <c r="D11" t="s">
-        <v>401</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" t="s">
         <v>402</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="D12" t="s">
         <v>404</v>
       </c>
-      <c r="D12" t="s">
-        <v>405</v>
-      </c>
       <c r="E12" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B13" t="s">
         <v>76</v>
       </c>
       <c r="C13" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="D13" t="s">
         <v>407</v>
       </c>
-      <c r="D13" t="s">
-        <v>408</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5434,7 +5389,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -5470,16 +5425,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>412</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>413</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5490,16 +5445,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5507,16 +5462,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>419</v>
-      </c>
       <c r="D3" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5524,16 +5479,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="D4" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5541,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>423</v>
-      </c>
       <c r="D5" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5558,16 +5513,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>425</v>
-      </c>
       <c r="D6" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5575,16 +5530,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>427</v>
-      </c>
       <c r="D7" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5592,16 +5547,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="D8" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5609,16 +5564,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>432</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5626,16 +5581,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>434</v>
-      </c>
       <c r="D10" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5643,16 +5598,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>436</v>
-      </c>
       <c r="D11" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5660,16 +5615,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>438</v>
-      </c>
       <c r="D12" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5677,16 +5632,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>440</v>
-      </c>
       <c r="D13" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5694,16 +5649,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="21" t="s">
         <v>442</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>443</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5711,16 +5666,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>445</v>
-      </c>
       <c r="D15" s="21" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5728,16 +5683,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>447</v>
-      </c>
       <c r="D16" s="21" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5745,16 +5700,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>449</v>
-      </c>
       <c r="D17" s="21" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5762,7 +5717,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,10 +5725,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5781,10 +5736,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5792,10 +5747,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5758,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,10 +5769,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5825,10 +5780,10 @@
         <v>48</v>
       </c>
       <c r="B25" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,10 +5791,10 @@
         <v>48</v>
       </c>
       <c r="B26" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5847,10 +5802,10 @@
         <v>48</v>
       </c>
       <c r="B27" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,10 +5813,10 @@
         <v>48</v>
       </c>
       <c r="B28" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5869,10 +5824,10 @@
         <v>48</v>
       </c>
       <c r="B29" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5915,158 +5870,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>477</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C2" t="s">
         <v>479</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" t="s">
         <v>481</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>482</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" t="s">
         <v>486</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" t="s">
         <v>488</v>
       </c>
-      <c r="E3" t="s">
-        <v>489</v>
-      </c>
       <c r="F3" t="s">
+        <v>482</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B4" t="s">
         <v>490</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>491</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" t="s">
         <v>493</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>494</v>
       </c>
-      <c r="F4" t="s">
-        <v>495</v>
-      </c>
       <c r="G4" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>495</v>
+      </c>
+      <c r="B5" t="s">
         <v>496</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>497</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" t="s">
         <v>499</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>500</v>
       </c>
-      <c r="F5" t="s">
-        <v>501</v>
-      </c>
       <c r="G5" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B6" t="s">
         <v>502</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>503</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" t="s">
         <v>505</v>
       </c>
-      <c r="E6" t="s">
-        <v>506</v>
-      </c>
       <c r="F6" t="s">
+        <v>482</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6080,7 +6035,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="508">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Transport</t>
   </si>
   <si>
-    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive Florence–Castelfalfi only (Aug 29–31) · rail to Naples, driver over to Sorrento · ferries to Capri, Positano and Amalfi · Frecciarossa back to Rome</t>
+    <t>Private driver in from FCO · Frecciarossa to Florence · self-drive Florence–Castelfalfi only (Aug 29–31) · rail to Naples, Campania Express over to Sorrento · ferries to Capri, Positano and Amalfi · Frecciarossa back to Rome</t>
   </si>
   <si>
     <t>Chain story</t>
@@ -292,561 +292,570 @@
     <t>Baths of Caracalla — First, while it is still quiet — the brick vaults standing to full height, the scale of the bathing halls, patches of the mosaic floor still in place. Far emptier than anything else in ancient Rome at this hour.</t>
   </si>
   <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>The Colosseum from outside, and the Arch of Constantine — The exterior circuit: the arcades from the Via dei Fori Imperiali side, then the Arch of Constantine. No arena floor and no interior ticket, so nothing to book and no queue to stand in. Pulled fifteen minutes earlier than before to leave room for the gallery.</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min from Caracalla</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Quick lunch in Monti — A few minutes up from the Colosseum, and it does have to be quick — the Borghese meeting point is a fifteen-minute taxi away and will not hold. Eat by ten past twelve and you have a real buffer; leave it later and you are watching the clock. Roscioli had this slot and wants two unhurried hours, which the 1:00pm entry no longer leaves; better to lose it than to rush it, so find it another lunch.</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Booked: skip-the-line entry for two with a digital audioguide, English, two hours. Meet the host at the Fontana dei Mascheroni on Viale del Museo Borghese, directly in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone for the audioguide; large bags are not allowed inside, but the cloakroom is free. Bernini's Apollo and Daphne and the Rape of Proserpina, six Caravaggios, in a villa small enough to see properly — and you are let in and out on the clock.</t>
+  </si>
+  <si>
+    <t>Gallery -&gt;</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Villa Borghese Gardens — Straight out of the gallery into the park, and this is where the siesta went: shaded avenues, the Fontana dei Cavalli Marini, a bench under the pines through the worst of the heat.</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>5:30pm</t>
+  </si>
+  <si>
+    <t>The Pincio terrace, in the low sun — The terrace over Piazza del Popolo with St. Peter's dome on the skyline. This is the Rome photo session — low sun through the trees, which is what the half-hour was chosen for.</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min across the park</t>
+  </si>
+  <si>
+    <t>Info -&gt;</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
+  </si>
+  <si>
+    <t>Walk down, ~10 min</t>
+  </si>
+  <si>
+    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
+  </si>
+  <si>
+    <t>9:00pm</t>
+  </si>
+  <si>
+    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
+  </si>
+  <si>
+    <t>Walk, ~12 min</t>
+  </si>
+  <si>
+    <t>Thu, Aug 27</t>
+  </si>
+  <si>
+    <t>ROME → FLORENCE — direct by Frecciarossa</t>
+  </si>
+  <si>
+    <t>TRAVEL DAY</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
+  </si>
+  <si>
+    <t>12:10pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9420 to Florence — Booked. Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 2h01</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>2:11pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze S.M.N.</t>
+  </si>
+  <si>
+    <t>2:25pm</t>
+  </si>
+  <si>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+  </si>
+  <si>
+    <t>Taxi, ~8 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>Accademia — David at the afternoon slot — Book the 3:00pm entry — the train lands at 2:11pm and lunch is already behind you, on board. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>4:30pm</t>
+  </si>
+  <si>
+    <t>Climb Brunelleschi's dome — 4:30pm sharp — Booked: two Brunelleschi Passes, entry to the dome from the Porta della Mandorla. 463 steps and no lift. The time slot is not modifiable and names are checked against ID at the door, so be standing there by a quarter past. The same pass covers the Bell Tower, Baptistery, museum and the Santa Reparata crypt, and stays valid through 29 August — which is why the museum sits on tomorrow rather than being crammed in here.</t>
+  </si>
+  <si>
+    <t>Duomo -&gt;</t>
+  </si>
+  <si>
+    <t>6:00pm</t>
+  </si>
+  <si>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait — and you will want it after the stairs</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm and the hill is the place to watch it from — this is timed to it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — A quarter past eight is the minute the gates open, and that is the whole point: Boboli is terraced, unshaded and unwalkable by mid-afternoon, so it goes first. The Palatine Gallery is hung floor to ceiling in the old manner; climb to the top of the gardens for the view back over the city.</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs straight from the palace gates to the bridge — stop halfway down it.</t>
+  </si>
+  <si>
+    <t>12:15pm</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Vecchio, ~6 min</t>
+  </si>
+  <si>
+    <t>Late lunch — 'Ino — Two hours in the Uffizi from a quarter past twelve puts you out at half past two, which is when the Oltrarno kitchens stop serving — so lunch is thirty seconds from the gallery door instead. Panini made to order, Tuscan wine by the glass, open straight through the afternoon. Il Santo Bevitore across the river stays the sit-down alternative if the tour runs short.</t>
+  </si>
+  <si>
+    <t>Walk, ~2 min</t>
+  </si>
+  <si>
+    <t>4:00pm</t>
+  </si>
+  <si>
+    <t>Reverse Renaissance Walk — The centre backwards, starting where it started: the Casa di Dante, then Orsanmichele, then out into Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, and free. This was Thursday evening's block, moved here because it never had the daylight there.</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Opera del Duomo museum — Already paid for — Thursday's Brunelleschi Pass runs to the 29th, so this costs nothing more. Ghiberti's original Gates of Paradise are in here, and Michelangelo's late Pietà. Entrance is Piazza del Duomo 9, and it is the last thing the pass has left to give.</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Fifteen minutes on foot up from the centre, so taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>Fiesole — Florence from the hill — Twenty-five minutes up out of the valley for the view back over the whole city: the roofs, the river and the dome seen from above rather than beneath. Go out along the viali — the ZTL starts the moment you cut through the centre — and leave the car at Piazza Mino.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~25 min</t>
+  </si>
+  <si>
     <t>10:45am</t>
   </si>
   <si>
-    <t>The Colosseum from outside, and the Arch of Constantine — The exterior circuit: the arcades from the Via dei Fori Imperiali side, then the Arch of Constantine. No arena floor and no interior ticket, so nothing to book and no queue to stand in.</t>
-  </si>
-  <si>
-    <t>Walk, ~20 min from Caracalla</t>
-  </si>
-  <si>
-    <t>Lunch — Roscioli — Carbonara and cacio e pepe, and the deli counter on the way out</t>
-  </si>
-  <si>
-    <t>Walk, 5 min via Campo de' Fiori</t>
+    <t>Southwest to Certaldo — Back down through the valley and out the other side — about an hour and ten from Fiesole, against forty-five minutes had you driven straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~1h10</t>
+  </si>
+  <si>
+    <t>12:00pm</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>At the hotel</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told. Alternative operator for the same kind of morning, if this one fills: CET Experience, cetexperience.it.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
+  </si>
+  <si>
+    <t>1:14pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 3h09</t>
+  </si>
+  <si>
+    <t>4:23pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
+  </si>
+  <si>
+    <t>5:26pm</t>
+  </si>
+  <si>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h09</t>
+  </si>
+  <si>
+    <t>EAV -&gt;</t>
+  </si>
+  <si>
+    <t>6:35pm</t>
+  </si>
+  <si>
+    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
+  </si>
+  <si>
+    <t>6:50pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
   </si>
   <si>
     <t>2:15pm</t>
   </si>
   <si>
-    <t>Siesta — An hour at most — the Galleria will not hold your slot, so leave in time for the taxi</t>
-  </si>
-  <si>
-    <t>At the hotel</t>
-  </si>
-  <si>
-    <t>3:30pm</t>
-  </si>
-  <si>
-    <t>Galleria Borghese — booked slot — Bernini's Apollo and Daphne and the Rape of Proserpina, and six Caravaggios, in a villa small enough to see properly. Entry is a hard two-hour window with a fixed start time and a capped room — you are let in and let out on the clock, so build the afternoon around it, not the other way round.</t>
-  </si>
-  <si>
-    <t>5:30pm</t>
-  </si>
-  <si>
-    <t>Villa Borghese Gardens and the Pincio, in the daylight — Straight out of the Galleria into the park — shaded avenues, the Fontana dei Cavalli Marini, and the Pincio terrace over Piazza del Popolo with St. Peter's dome on the skyline. This is the Rome photo session: low sun through the trees, which is what the half-hour was chosen for.</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min across the park</t>
-  </si>
-  <si>
-    <t>Info -&gt;</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
-  </si>
-  <si>
-    <t>Walk down, ~10 min</t>
-  </si>
-  <si>
-    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
-  </si>
-  <si>
-    <t>9:00pm</t>
-  </si>
-  <si>
-    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
-  </si>
-  <si>
-    <t>Walk, ~12 min</t>
-  </si>
-  <si>
-    <t>Thu, Aug 27</t>
-  </si>
-  <si>
-    <t>ROME → FLORENCE — direct by Frecciarossa</t>
-  </si>
-  <si>
-    <t>TRAVEL DAY</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
-  </si>
-  <si>
-    <t>12:10pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9420 to Florence — Booked. Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 2h01</t>
-  </si>
-  <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>2:11pm</t>
-  </si>
-  <si>
-    <t>Arrive Firenze S.M.N.</t>
-  </si>
-  <si>
-    <t>2:25pm</t>
-  </si>
-  <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
-  </si>
-  <si>
-    <t>Taxi, ~8 min</t>
-  </si>
-  <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>Accademia — David at the afternoon slot — Book the 3:00pm entry — the train lands at 2:11pm and lunch is already behind you, on board. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>4:00pm</t>
-  </si>
-  <si>
-    <t>Duomo — Baptistery, cathedral and the Opera del Duomo museum, where the Ghiberti doors are the originals. Four o'clock rather than the old 5:15pm slot: the cathedral stops admitting in the late afternoon, and arriving at a quarter past five would have left you the museum and not much else. One pass covers the complex — the dome climb is no longer part of the trip, so you do not need the one that includes it.</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm and the hill is the place to watch it from — this is timed to it. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — A quarter past eight is the minute the gates open, and that is the whole point: Boboli is terraced, unshaded and unwalkable by mid-afternoon, so it goes first. The Palatine Gallery is hung floor to ceiling in the old manner; climb to the top of the gardens for the view back over the city.</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs straight from the palace gates to the bridge — stop halfway down it.</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>12:15pm</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Vecchio, ~6 min</t>
-  </si>
-  <si>
-    <t>Late lunch — 'Ino — Two hours in the Uffizi from a quarter past twelve puts you out at half past two, which is when the Oltrarno kitchens stop serving — so lunch is thirty seconds from the gallery door instead. Panini made to order, Tuscan wine by the glass, open straight through the afternoon. Il Santo Bevitore across the river stays the sit-down alternative if the tour runs short.</t>
-  </si>
-  <si>
-    <t>Walk, ~2 min</t>
-  </si>
-  <si>
-    <t>Reverse Renaissance Walk — The centre backwards, starting where it started: the Casa di Dante, then Orsanmichele, then out into Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, and free. This was Thursday evening's block, moved here because it never had the daylight there.</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Fifteen minutes on foot up from the centre, so taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>Fiesole — Florence from the hill — Twenty-five minutes up out of the valley for the view back over the whole city: the roofs, the river and the dome seen from above rather than beneath. Go out along the viali — the ZTL starts the moment you cut through the centre — and leave the car at Piazza Mino.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~25 min</t>
-  </si>
-  <si>
-    <t>Southwest to Certaldo — Back down through the valley and out the other side — about an hour and ten from Fiesole, against forty-five minutes had you driven straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~1h10</t>
-  </si>
-  <si>
-    <t>12:00pm</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told. Alternative operator for the same kind of morning, if this one fills: CET Experience, cetexperience.it.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
-  </si>
-  <si>
-    <t>1:14pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 3h09</t>
-  </si>
-  <si>
-    <t>4:23pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
-  </si>
-  <si>
-    <t>5:26pm</t>
-  </si>
-  <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h09</t>
-  </si>
-  <si>
-    <t>EAV -&gt;</t>
-  </si>
-  <si>
-    <t>6:35pm</t>
-  </si>
-  <si>
-    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
-  </si>
-  <si>
-    <t>6:50pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>8:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>6:00pm</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
-  </si>
-  <si>
-    <t>Walk ~20 min, or taxi</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
-  </si>
-  <si>
-    <t>Ferry, ~1h15</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
-  </si>
-  <si>
-    <t>Walk from the marina</t>
-  </si>
-  <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
-  </si>
-  <si>
     <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
   </si>
   <si>
@@ -1087,7 +1096,7 @@
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Caracalla and the Galleria Borghese, the Florence galleries (Accademia, the guided Uffizi, Pitti and Boboli) and the Duomo complex pass, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two). Unchanged in total despite the dome climb coming out: the ~$65 it saved is near enough what Pitti and Boboli now cost as a ticketed morning.</t>
+    <t>Vatican, Caracalla and the Galleria Borghese, the Florence galleries (Accademia, the guided Uffizi, Pitti and Boboli) and the Duomo, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two). Two lines are now real prices rather than estimates: the Brunelleschi Passes are bought and paid, €60 for the pair (~$65), and the Galleria Borghese is reserved at $113.22 for two with an audioguide, charged automatically on Aug 23. Up $65 on the last revision — that is the dome climb coming back onto the trip.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1276,12 +1285,6 @@
     <t>Two problems in one. The old reservation is still FCO Aug 24 → FCO Sep 6, so left alone it bills you for a fortnight's hire you will not take. And the car you do need — Borgo Ognissanti, Florence, Aug 29 to Aug 31 — is not booked at all. Re-quote before cancelling; the old €1,087.81 was a fourteen-day FCO round trip and will not carry over.</t>
   </si>
   <si>
-    <t>Duomo complex pass — Aug 27, 4:00pm</t>
-  </si>
-  <si>
-    <t>Baptistery, cathedral and the Opera del Duomo museum on arrival afternoon. The dome climb is off the trip, so this is the pass without it — cheaper, and far easier to get. Book the four o'clock entry rather than later: the cathedral stops admitting well before the museum does.</t>
-  </si>
-  <si>
     <t>Vatican early entry — Aug 25, 7:45am</t>
   </si>
   <si>
@@ -1291,13 +1294,7 @@
     <t>Accademia (Aug 27), then Pitti and the Uffizi (Aug 28)</t>
   </si>
   <si>
-    <t>Two Florence days means no second chance at any of them. The Accademia is the 3:00pm slot on arrival day, once the train is in. The next day opens at Pitti — book the 8:15am opening, which is what gets Boboli done before the heat — and the Uffizi is guided at 12:15pm, after the walk down from the palace.</t>
-  </si>
-  <si>
-    <t>Galleria Borghese — Aug 26, 3:30pm slot</t>
-  </si>
-  <si>
-    <t>Timed entry, two hours, a capped number of people in the building at once. Slots go weeks ahead and the 3:30pm one is what the rest of that afternoon is built around — if it is gone, take the nearest and tell me so I can move the gardens and the photo session with it.</t>
+    <t>Two Florence days means no second chance at any of them. The Accademia is the 3:00pm slot on arrival day, once the train is in — and it has to be out by 4:15pm, because the dome slot behind it cannot move. The next day opens at Pitti — book the 8:15am opening, which is what gets Boboli done before the heat — and the Uffizi is guided at 12:15pm, after the walk down from the palace.</t>
   </si>
   <si>
     <t>Horseback riding, lunch &amp; winery — San Gimignano, Aug 30</t>
@@ -1306,13 +1303,19 @@
     <t>San Gimignano Experience, 11am–3pm, ~€120pp: an hour in the saddle through vineyards and olive groves, then lunch, a cellar tour and tastings. A small-group tour, so it fills. Meets at the Bivio Volterra bus stop.</t>
   </si>
   <si>
+    <t>Galleria Borghese — reserved, card charged Aug 23</t>
+  </si>
+  <si>
+    <t>Booked through GetYourGuide for Aug 26, 1:00pm: skip-the-line entry for two with an English audioguide, $113.22. Nothing is paid yet — the card on file is charged automatically on Aug 23, so check that card actually works, given what Vio's did. Free cancellation until 1:00pm on Aug 25 if the day has to change.</t>
+  </si>
+  <si>
+    <t>THIS WEEK</t>
+  </si>
+  <si>
     <t>Private driver — FCO → Hotel Trame, Aug 24</t>
   </si>
   <si>
     <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
-  </si>
-  <si>
-    <t>THIS WEEK</t>
   </si>
   <si>
     <t>Campania Express — Naples ↔ Sorrento, Aug 31 and Sep 5</t>
@@ -2217,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2569,16 +2572,16 @@
         <v>48</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>64</v>
+        <v>96</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2589,16 +2592,16 @@
         <v>48</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" t="s">
-        <v>48</v>
+        <v>69</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2609,16 +2612,16 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2629,16 +2632,16 @@
         <v>48</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,13 +2652,13 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -2672,7 +2675,7 @@
         <v>61</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>69</v>
@@ -2689,13 +2692,13 @@
         <v>48</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>64</v>
@@ -2706,13 +2709,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,10 +2726,10 @@
         <v>48</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>69</v>
@@ -2743,16 +2746,16 @@
         <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2763,10 +2766,10 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>57</v>
@@ -2783,16 +2786,16 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2806,10 +2809,10 @@
         <v>58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>70</v>
@@ -2823,16 +2826,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,13 +2846,13 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
         <v>48</v>
@@ -2866,10 +2869,10 @@
         <v>61</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2883,13 +2886,13 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>64</v>
@@ -2900,10 +2903,10 @@
         <v>5</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2914,10 +2917,10 @@
         <v>48</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>79</v>
@@ -2934,13 +2937,13 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="F42" t="s">
         <v>48</v>
@@ -2954,13 +2957,13 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>70</v>
@@ -2977,10 +2980,10 @@
         <v>74</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2994,13 +2997,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="F45" t="s">
         <v>48</v>
@@ -3014,13 +3017,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
@@ -3034,16 +3037,16 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>70</v>
+        <v>156</v>
+      </c>
+      <c r="F47" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3054,50 +3057,50 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="F48" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10">
+    <row r="51" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="10">
         <v>6</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F51" t="s">
-        <v>48</v>
+      <c r="B51" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3108,13 +3111,13 @@
         <v>48</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
         <v>48</v>
@@ -3128,13 +3131,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3148,16 +3151,16 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>104</v>
+        <v>171</v>
+      </c>
+      <c r="F54" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3168,16 +3171,16 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F55" t="s">
-        <v>48</v>
+        <v>174</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3188,10 +3191,10 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>81</v>
@@ -3208,13 +3211,13 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3228,16 +3231,16 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="F58" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3248,16 +3251,16 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F59" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3268,13 +3271,13 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="F60" t="s">
         <v>48</v>
@@ -3288,47 +3291,47 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F61" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="10">
+      <c r="D62" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
         <v>7</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>48</v>
-      </c>
-      <c r="B64" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F64" t="s">
-        <v>48</v>
+      <c r="B64" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3339,13 +3342,13 @@
         <v>48</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="F65" t="s">
         <v>48</v>
@@ -3359,13 +3362,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3379,10 +3382,10 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>81</v>
@@ -3399,16 +3402,16 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>176</v>
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3419,16 +3422,16 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F69" t="s">
-        <v>48</v>
+        <v>195</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3439,13 +3442,13 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -3459,50 +3462,50 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F71" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F71" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
+      <c r="D72" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F72" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="10">
         <v>8</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F73" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>48</v>
-      </c>
-      <c r="B74" t="s">
-        <v>48</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>48</v>
+      <c r="B74" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3513,13 +3516,13 @@
         <v>48</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="F75" t="s">
         <v>48</v>
@@ -3533,13 +3536,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3553,16 +3556,16 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>120</v>
+        <v>96</v>
+      </c>
+      <c r="F77" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3573,16 +3576,16 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F78" t="s">
-        <v>48</v>
+        <v>208</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3593,16 +3596,16 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>209</v>
+        <v>57</v>
+      </c>
+      <c r="F79" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3613,16 +3616,16 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F80" t="s">
-        <v>48</v>
+        <v>213</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3633,16 +3636,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>126</v>
+        <v>57</v>
+      </c>
+      <c r="F81" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3653,16 +3656,16 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F82" t="s">
-        <v>48</v>
+        <v>130</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3673,13 +3676,13 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s">
         <v>48</v>
@@ -3693,47 +3696,47 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="10">
+        <v>185</v>
+      </c>
+      <c r="F84" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="10">
         <v>9</v>
       </c>
-      <c r="B86" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>48</v>
-      </c>
-      <c r="B87" t="s">
-        <v>48</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F87" t="s">
-        <v>48</v>
+      <c r="B87" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,13 +3747,13 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="F88" t="s">
         <v>48</v>
@@ -3764,16 +3767,16 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>104</v>
+        <v>230</v>
+      </c>
+      <c r="F89" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3784,16 +3787,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3804,16 +3807,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F91" t="s">
-        <v>48</v>
+        <v>139</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,13 +3827,13 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="F92" t="s">
         <v>48</v>
@@ -3844,47 +3847,47 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F93" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>48</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F93" s="7" t="s">
+      <c r="D94" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F94" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
         <v>10</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" t="s">
-        <v>48</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E96" s="13" t="s">
+      <c r="B96" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="F96" t="s">
-        <v>48</v>
+      <c r="C96" s="11" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3895,16 +3898,16 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="F97" s="7" t="s">
         <v>240</v>
+      </c>
+      <c r="F97" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3915,16 +3918,16 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="F98" t="s">
-        <v>48</v>
+        <v>243</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,16 +3938,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>64</v>
+        <v>246</v>
+      </c>
+      <c r="F99" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3955,16 +3958,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3975,16 +3978,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="F101" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3995,13 +3998,13 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="F102" t="s">
         <v>48</v>
@@ -4015,47 +4018,47 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="F103" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F103" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>48</v>
+      </c>
+      <c r="B104" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F104" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="105" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
+    <row r="106" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
         <v>11</v>
       </c>
-      <c r="B105" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>48</v>
-      </c>
-      <c r="B106" t="s">
-        <v>48</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F106" t="s">
-        <v>48</v>
+      <c r="B106" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4066,16 +4069,16 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E107" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>240</v>
+      <c r="F107" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4086,16 +4089,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>115</v>
+        <v>191</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F108" t="s">
-        <v>48</v>
+        <v>259</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4106,16 +4109,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+      <c r="F109" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4126,16 +4129,16 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="F110" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4146,13 +4149,13 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
@@ -4166,13 +4169,13 @@
         <v>48</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4186,13 +4189,13 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4206,47 +4209,47 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="F114" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="F114" s="7" t="s">
+      <c r="D115" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="10">
+    <row r="117" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="10">
         <v>12</v>
       </c>
-      <c r="B116" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>48</v>
-      </c>
-      <c r="B117" t="s">
-        <v>48</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="F117" t="s">
-        <v>48</v>
+      <c r="B117" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4257,16 +4260,16 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>240</v>
+        <v>127</v>
+      </c>
+      <c r="F118" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4277,16 +4280,16 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="F119" t="s">
-        <v>48</v>
+        <v>273</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,13 +4300,13 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
@@ -4317,16 +4320,16 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>274</v>
+        <v>94</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F121" s="7" t="s">
-        <v>64</v>
+      <c r="F121" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4337,16 +4340,16 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="F122" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4365,8 +4368,8 @@
       <c r="E123" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>70</v>
+      <c r="F123" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4383,7 +4386,7 @@
         <v>282</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>70</v>
@@ -4397,16 +4400,16 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="F125" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4417,50 +4420,50 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F126" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="F126" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" t="s">
+        <v>48</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F127" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="128" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="10">
+    <row r="129" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="10">
         <v>13</v>
       </c>
-      <c r="B128" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>48</v>
-      </c>
-      <c r="B129" t="s">
-        <v>48</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F129" t="s">
-        <v>48</v>
+      <c r="B129" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4471,13 +4474,13 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="F130" t="s">
         <v>48</v>
@@ -4491,16 +4494,16 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>209</v>
+        <v>185</v>
+      </c>
+      <c r="F131" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4517,10 +4520,10 @@
         <v>295</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F132" t="s">
-        <v>48</v>
+        <v>296</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4531,16 +4534,16 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>299</v>
+        <v>57</v>
+      </c>
+      <c r="F133" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4551,16 +4554,16 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="E134" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="E134" s="13" t="s">
+      <c r="F134" s="7" t="s">
         <v>302</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4579,8 +4582,8 @@
       <c r="E135" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="F135" t="s">
-        <v>48</v>
+      <c r="F135" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4597,10 +4600,10 @@
         <v>307</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>126</v>
+        <v>308</v>
+      </c>
+      <c r="F136" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,16 +4614,16 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E137" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F137" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="F137" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4631,13 +4634,13 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="F138" t="s">
         <v>48</v>
@@ -4651,13 +4654,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>229</v>
+        <v>152</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>298</v>
+        <v>102</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4671,13 +4674,13 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>214</v>
+        <v>134</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="F140" t="s">
         <v>48</v>
@@ -4691,47 +4694,47 @@
         <v>48</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E141" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F141" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>48</v>
+      </c>
+      <c r="B142" t="s">
+        <v>48</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E142" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F141" s="7" t="s">
+      <c r="F142" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="10">
+    <row r="144" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="10">
         <v>14</v>
       </c>
-      <c r="B143" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="C143" s="11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>48</v>
-      </c>
-      <c r="B144" t="s">
-        <v>48</v>
-      </c>
-      <c r="C144" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="D144" s="4" t="s">
+      <c r="B144" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="E144" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F144" t="s">
-        <v>48</v>
+      <c r="C144" s="11" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4742,13 +4745,13 @@
         <v>48</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>320</v>
+        <v>76</v>
       </c>
       <c r="F145" t="s">
         <v>48</v>
@@ -4762,15 +4765,35 @@
         <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F146" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>48</v>
+      </c>
+      <c r="B147" t="s">
+        <v>48</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="F147" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4783,46 +4806,45 @@
     <hyperlink ref="F15" r:id="rId5"/>
     <hyperlink ref="F16" r:id="rId6"/>
     <hyperlink ref="F19" r:id="rId7"/>
-    <hyperlink ref="F21" r:id="rId8"/>
-    <hyperlink ref="F23" r:id="rId9"/>
-    <hyperlink ref="F24" r:id="rId10"/>
-    <hyperlink ref="F27" r:id="rId11"/>
-    <hyperlink ref="F31" r:id="rId12"/>
-    <hyperlink ref="F33" r:id="rId13"/>
-    <hyperlink ref="F34" r:id="rId14"/>
-    <hyperlink ref="F35" r:id="rId15"/>
-    <hyperlink ref="F38" r:id="rId16"/>
-    <hyperlink ref="F41" r:id="rId17"/>
-    <hyperlink ref="F43" r:id="rId18"/>
-    <hyperlink ref="F47" r:id="rId19"/>
-    <hyperlink ref="F48" r:id="rId20"/>
-    <hyperlink ref="F54" r:id="rId21"/>
-    <hyperlink ref="F58" r:id="rId22"/>
-    <hyperlink ref="F68" r:id="rId23"/>
-    <hyperlink ref="F77" r:id="rId24"/>
-    <hyperlink ref="F79" r:id="rId25"/>
-    <hyperlink ref="F81" r:id="rId26"/>
-    <hyperlink ref="F84" r:id="rId27"/>
-    <hyperlink ref="F89" r:id="rId28"/>
-    <hyperlink ref="F90" r:id="rId29"/>
-    <hyperlink ref="F93" r:id="rId30"/>
-    <hyperlink ref="F97" r:id="rId31"/>
-    <hyperlink ref="F99" r:id="rId32"/>
-    <hyperlink ref="F100" r:id="rId33"/>
-    <hyperlink ref="F103" r:id="rId34"/>
-    <hyperlink ref="F107" r:id="rId35"/>
-    <hyperlink ref="F109" r:id="rId36"/>
-    <hyperlink ref="F114" r:id="rId37"/>
-    <hyperlink ref="F118" r:id="rId38"/>
-    <hyperlink ref="F121" r:id="rId39"/>
-    <hyperlink ref="F123" r:id="rId40"/>
-    <hyperlink ref="F124" r:id="rId41"/>
-    <hyperlink ref="F126" r:id="rId42"/>
-    <hyperlink ref="F131" r:id="rId43"/>
-    <hyperlink ref="F133" r:id="rId44"/>
-    <hyperlink ref="F134" r:id="rId45"/>
-    <hyperlink ref="F136" r:id="rId46"/>
-    <hyperlink ref="F141" r:id="rId47"/>
+    <hyperlink ref="F22" r:id="rId8"/>
+    <hyperlink ref="F24" r:id="rId9"/>
+    <hyperlink ref="F27" r:id="rId10"/>
+    <hyperlink ref="F31" r:id="rId11"/>
+    <hyperlink ref="F33" r:id="rId12"/>
+    <hyperlink ref="F34" r:id="rId13"/>
+    <hyperlink ref="F35" r:id="rId14"/>
+    <hyperlink ref="F38" r:id="rId15"/>
+    <hyperlink ref="F41" r:id="rId16"/>
+    <hyperlink ref="F43" r:id="rId17"/>
+    <hyperlink ref="F48" r:id="rId18"/>
+    <hyperlink ref="F49" r:id="rId19"/>
+    <hyperlink ref="F55" r:id="rId20"/>
+    <hyperlink ref="F59" r:id="rId21"/>
+    <hyperlink ref="F69" r:id="rId22"/>
+    <hyperlink ref="F78" r:id="rId23"/>
+    <hyperlink ref="F80" r:id="rId24"/>
+    <hyperlink ref="F82" r:id="rId25"/>
+    <hyperlink ref="F85" r:id="rId26"/>
+    <hyperlink ref="F90" r:id="rId27"/>
+    <hyperlink ref="F91" r:id="rId28"/>
+    <hyperlink ref="F94" r:id="rId29"/>
+    <hyperlink ref="F98" r:id="rId30"/>
+    <hyperlink ref="F100" r:id="rId31"/>
+    <hyperlink ref="F101" r:id="rId32"/>
+    <hyperlink ref="F104" r:id="rId33"/>
+    <hyperlink ref="F108" r:id="rId34"/>
+    <hyperlink ref="F110" r:id="rId35"/>
+    <hyperlink ref="F115" r:id="rId36"/>
+    <hyperlink ref="F119" r:id="rId37"/>
+    <hyperlink ref="F122" r:id="rId38"/>
+    <hyperlink ref="F124" r:id="rId39"/>
+    <hyperlink ref="F125" r:id="rId40"/>
+    <hyperlink ref="F127" r:id="rId41"/>
+    <hyperlink ref="F132" r:id="rId42"/>
+    <hyperlink ref="F134" r:id="rId43"/>
+    <hyperlink ref="F135" r:id="rId44"/>
+    <hyperlink ref="F137" r:id="rId45"/>
+    <hyperlink ref="F142" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4845,48 +4867,48 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -4898,24 +4920,24 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4927,24 +4949,24 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4956,24 +4978,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4985,24 +5007,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5014,7 +5036,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -5031,7 +5053,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -5068,24 +5090,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5096,51 +5118,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B4" s="15">
-        <v>2050</v>
+        <v>2115</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B7" s="17">
-        <v>18133.95</v>
+        <v>18198.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -5165,220 +5187,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="D3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D8" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B9" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B12" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D12" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B13" t="s">
         <v>76</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D13" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5389,7 +5411,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5414,7 +5436,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5425,16 +5447,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5445,16 +5467,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5462,16 +5484,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>415</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5479,16 +5501,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>419</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5496,16 +5518,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5513,16 +5535,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5530,16 +5552,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>415</v>
+        <v>429</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>430</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5547,16 +5569,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>415</v>
+        <v>432</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>430</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5564,16 +5586,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>431</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5581,16 +5603,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5598,16 +5620,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5615,16 +5637,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5632,16 +5654,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>431</v>
+        <v>442</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>443</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5649,16 +5671,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5666,16 +5688,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>442</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5683,41 +5705,35 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>449</v>
+      <c r="B19" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5725,10 +5741,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5736,10 +5752,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5747,10 +5763,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5758,10 +5774,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5769,10 +5785,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5780,10 +5796,10 @@
         <v>48</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5791,10 +5807,10 @@
         <v>48</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5802,10 +5818,10 @@
         <v>48</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -5813,21 +5829,10 @@
         <v>48</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5847,7 +5852,6 @@
     <hyperlink ref="E14" r:id="rId13"/>
     <hyperlink ref="E15" r:id="rId14"/>
     <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5870,158 +5874,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" t="s">
+        <v>483</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>485</v>
-      </c>
-      <c r="C3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="E3" t="s">
-        <v>488</v>
-      </c>
-      <c r="F3" t="s">
-        <v>482</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6035,7 +6039,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="506">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -217,48 +217,51 @@
     <t>Tue, Aug 25</t>
   </si>
   <si>
-    <t>ROME — Vatican</t>
-  </si>
-  <si>
-    <t>7:45am</t>
-  </si>
-  <si>
-    <t>Vatican early-entry private tour — Museums, Sistine Chapel, St Peter's — Into the Sistine Chapel before general admission, then the Museums at your own pace and through to St Peter's Basilica. Book the private guide well ahead — the direct passage from the chapel into the basilica is only open to guided groups. Roughly four hours end to end.</t>
+    <t>ROME — Vatican Gardens &amp; Museums</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Booked and paid, €90 for the two of you: the Vatican's own guided tour, English, with earphones. Both names are on the ticket and a ticket whose name does not match its holder is refused entry, so carry ID. Show the voucher to the Customer Care staff outside the Viale Vaticano entrance thirty minutes before departure; after security, up the stairs on the far left of the entrance hall to the 'Guided Tours' desk to collect the tickets and the service coupons, then on to the meeting point for earphones. Entrance is Passageway 2. Neither the date nor the time can be changed and it is not refundable. St Peter's is not part of this tour — the shortcut from the Sistine Chapel into the basilica is a guided-group privilege, so ask your guide on the day whether this one uses it.</t>
   </si>
   <si>
     <t>Taxi, ~15 min</t>
   </si>
   <si>
+    <t>Vatican Museums -&gt;</t>
+  </si>
+  <si>
+    <t>1:00pm</t>
+  </si>
+  <si>
+    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
+  </si>
+  <si>
+    <t>Walk from the Vatican</t>
+  </si>
+  <si>
+    <t>2:30pm</t>
+  </si>
+  <si>
+    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>5:00pm</t>
+  </si>
+  <si>
+    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
+  </si>
+  <si>
+    <t>Taxi, ~10 min</t>
+  </si>
+  <si>
     <t>Tickets -&gt;</t>
   </si>
   <si>
-    <t>1:00pm</t>
-  </si>
-  <si>
-    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
-  </si>
-  <si>
-    <t>Walk from the Vatican</t>
-  </si>
-  <si>
-    <t>2:30pm</t>
-  </si>
-  <si>
-    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
-  </si>
-  <si>
-    <t>Taxi</t>
-  </si>
-  <si>
-    <t>5:00pm</t>
-  </si>
-  <si>
-    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
-  </si>
-  <si>
-    <t>Taxi, ~10 min</t>
-  </si>
-  <si>
     <t>Rooftop aperitivo near Campo de' Fiori</t>
   </si>
   <si>
@@ -733,9 +736,6 @@
     <t>SORRENTO — Capri day trip</t>
   </si>
   <si>
-    <t>8:00am</t>
-  </si>
-  <si>
     <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
   </si>
   <si>
@@ -1096,7 +1096,7 @@
     <t>Excursions &amp; guides</t>
   </si>
   <si>
-    <t>Vatican, Caracalla and the Galleria Borghese, the Florence galleries (Accademia, the guided Uffizi, Pitti and Boboli) and the Duomo, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two). Two lines are now real prices rather than estimates: the Brunelleschi Passes are bought and paid, €60 for the pair (~$65), and the Galleria Borghese is reserved at $113.22 for two with an audioguide, charged automatically on Aug 23. Up $65 on the last revision — that is the dome climb coming back onto the trip.</t>
+    <t>Vatican, Caracalla and the Galleria Borghese, the Florence galleries (Accademia, the guided Uffizi, Pitti and Boboli) and the Duomo, two operas, the Capri round-the-island boat, Villa Cimbrone and Villa Rufolo, and the San Gimignano horseback/lunch/winery tour (~€120pp, ~$260 for two). Three lines are now real prices rather than estimates: the Brunelleschi Passes are bought and paid at €60 the pair (~$65), the Vatican came in at €90 for two (~$97), and the Galleria Borghese is reserved at $113.22 for two with an audioguide, charged automatically on Aug 23. Held at $2,115, but it now carries slack rather than running tight — the Vatican was costed here as the private early-entry guide the plan originally called for, and the booked group tour is a fraction of that. Worth re-baselining once the Florence galleries are booked and their real prices are in.</t>
   </si>
   <si>
     <t>Food &amp; wine</t>
@@ -1283,12 +1283,6 @@
   </si>
   <si>
     <t>Two problems in one. The old reservation is still FCO Aug 24 → FCO Sep 6, so left alone it bills you for a fortnight's hire you will not take. And the car you do need — Borgo Ognissanti, Florence, Aug 29 to Aug 31 — is not booked at all. Re-quote before cancelling; the old €1,087.81 was a fourteen-day FCO round trip and will not carry over.</t>
-  </si>
-  <si>
-    <t>Vatican early entry — Aug 25, 7:45am</t>
-  </si>
-  <si>
-    <t>The whole point of the Vatican day is being in the Sistine Chapel before general admission, and those slots go first.</t>
   </si>
   <si>
     <t>Accademia (Aug 27), then Pitti and the Uffizi (Aug 28)</t>
@@ -2450,7 +2444,7 @@
         <v>79</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2464,10 +2458,10 @@
         <v>61</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
         <v>48</v>
@@ -2481,16 +2475,16 @@
         <v>48</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>69</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2501,13 +2495,13 @@
         <v>48</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>64</v>
@@ -2518,10 +2512,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2532,16 +2526,16 @@
         <v>48</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>69</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2552,13 +2546,13 @@
         <v>48</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
         <v>48</v>
@@ -2572,13 +2566,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s">
         <v>48</v>
@@ -2592,16 +2586,16 @@
         <v>48</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>69</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2612,13 +2606,13 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s">
         <v>48</v>
@@ -2632,16 +2626,16 @@
         <v>48</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2652,13 +2646,13 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -2675,7 +2669,7 @@
         <v>61</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>69</v>
@@ -2692,13 +2686,13 @@
         <v>48</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>64</v>
@@ -2709,13 +2703,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2726,10 +2720,10 @@
         <v>48</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>69</v>
@@ -2746,16 +2740,16 @@
         <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,10 +2760,10 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>57</v>
@@ -2786,16 +2780,16 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2809,13 +2803,13 @@
         <v>58</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2826,16 +2820,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,13 +2840,13 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
         <v>48</v>
@@ -2869,10 +2863,10 @@
         <v>61</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2886,13 +2880,13 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>64</v>
@@ -2903,10 +2897,10 @@
         <v>5</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2917,16 +2911,16 @@
         <v>48</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>79</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2937,13 +2931,13 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F42" t="s">
         <v>48</v>
@@ -2957,16 +2951,16 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2980,10 +2974,10 @@
         <v>74</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2997,13 +2991,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
         <v>48</v>
@@ -3017,13 +3011,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
@@ -3037,13 +3031,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F47" t="s">
         <v>48</v>
@@ -3057,16 +3051,16 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>79</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3077,13 +3071,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>64</v>
@@ -3094,13 +3088,13 @@
         <v>6</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3111,10 +3105,10 @@
         <v>48</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>79</v>
@@ -3131,13 +3125,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3151,13 +3145,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3171,16 +3165,16 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3191,13 +3185,13 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F56" t="s">
         <v>48</v>
@@ -3214,10 +3208,10 @@
         <v>71</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3234,10 +3228,10 @@
         <v>74</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F58" t="s">
         <v>48</v>
@@ -3254,13 +3248,13 @@
         <v>58</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3274,7 +3268,7 @@
         <v>77</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>60</v>
@@ -3291,13 +3285,13 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F61" t="s">
         <v>48</v>
@@ -3311,13 +3305,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>185</v>
       </c>
       <c r="F62" t="s">
         <v>48</v>
@@ -3328,10 +3322,10 @@
         <v>7</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3342,13 +3336,13 @@
         <v>48</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F65" t="s">
         <v>48</v>
@@ -3362,10 +3356,10 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>57</v>
@@ -3382,13 +3376,13 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F67" t="s">
         <v>48</v>
@@ -3402,13 +3396,13 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F68" t="s">
         <v>48</v>
@@ -3422,16 +3416,16 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3442,13 +3436,13 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -3462,13 +3456,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3482,13 +3476,13 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
@@ -3499,13 +3493,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,13 +3510,13 @@
         <v>48</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F75" t="s">
         <v>48</v>
@@ -3536,13 +3530,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3556,13 +3550,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3576,16 +3570,16 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,10 +3590,10 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>57</v>
@@ -3616,16 +3610,16 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3636,10 +3630,10 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E81" s="13" t="s">
         <v>57</v>
@@ -3656,16 +3650,16 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,13 +3670,13 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F83" t="s">
         <v>48</v>
@@ -3696,13 +3690,13 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F84" t="s">
         <v>48</v>
@@ -3716,16 +3710,16 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3733,10 +3727,10 @@
         <v>9</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3747,13 +3741,13 @@
         <v>48</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F88" t="s">
         <v>48</v>
@@ -3767,13 +3761,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3787,16 +3781,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3807,13 +3801,13 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>64</v>
@@ -3830,10 +3824,10 @@
         <v>74</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F92" t="s">
         <v>48</v>
@@ -3847,13 +3841,13 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F93" t="s">
         <v>48</v>
@@ -3870,10 +3864,10 @@
         <v>61</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>64</v>
@@ -3884,10 +3878,10 @@
         <v>10</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,7 +3892,7 @@
         <v>48</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>238</v>
+        <v>67</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>239</v>
@@ -3938,7 +3932,7 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>245</v>
@@ -3958,7 +3952,7 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>247</v>
@@ -3987,7 +3981,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,13 +4012,13 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>252</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -4038,7 +4032,7 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>253</v>
@@ -4069,13 +4063,13 @@
         <v>48</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>257</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F107" t="s">
         <v>48</v>
@@ -4089,7 +4083,7 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>258</v>
@@ -4109,7 +4103,7 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>260</v>
@@ -4129,13 +4123,13 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>261</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>64</v>
@@ -4189,13 +4183,13 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>265</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4209,7 +4203,7 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>266</v>
@@ -4260,13 +4254,13 @@
         <v>48</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>271</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -4280,7 +4274,7 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>272</v>
@@ -4300,7 +4294,7 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>274</v>
@@ -4320,13 +4314,13 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>276</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -4340,13 +4334,13 @@
         <v>48</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>277</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>64</v>
@@ -4389,7 +4383,7 @@
         <v>283</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4406,10 +4400,10 @@
         <v>285</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4440,13 +4434,13 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>288</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>64</v>
@@ -4463,7 +4457,7 @@
         <v>290</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4474,13 +4468,13 @@
         <v>48</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>291</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F130" t="s">
         <v>48</v>
@@ -4500,7 +4494,7 @@
         <v>293</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4523,7 +4517,7 @@
         <v>296</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4583,7 +4577,7 @@
         <v>305</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,7 +4617,7 @@
         <v>57</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,7 +4634,7 @@
         <v>311</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F138" t="s">
         <v>48</v>
@@ -4654,13 +4648,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>312</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4674,7 +4668,7 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>313</v>
@@ -4694,7 +4688,7 @@
         <v>48</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>314</v>
@@ -4714,7 +4708,7 @@
         <v>48</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>316</v>
@@ -4908,7 +4902,7 @@
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -4934,10 +4928,10 @@
         <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4963,10 +4957,10 @@
         <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4992,7 +4986,7 @@
         <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s">
         <v>289</v>
@@ -5255,7 +5249,7 @@
         <v>376</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>380</v>
@@ -5272,7 +5266,7 @@
         <v>382</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>383</v>
@@ -5436,7 +5430,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5540,8 +5534,8 @@
       <c r="C6" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>418</v>
+      <c r="D6" s="20" t="s">
+        <v>428</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>419</v>
@@ -5552,13 +5546,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>428</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>430</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>419</v>
@@ -5575,7 +5569,7 @@
         <v>432</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>419</v>
@@ -5592,7 +5586,7 @@
         <v>434</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>419</v>
@@ -5609,7 +5603,7 @@
         <v>436</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>419</v>
@@ -5626,7 +5620,7 @@
         <v>438</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>419</v>
@@ -5642,8 +5636,8 @@
       <c r="C12" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D12" s="20" t="s">
-        <v>430</v>
+      <c r="D12" s="21" t="s">
+        <v>441</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>419</v>
@@ -5654,13 +5648,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>441</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>443</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>419</v>
@@ -5677,7 +5671,7 @@
         <v>445</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>419</v>
@@ -5694,34 +5688,28 @@
         <v>447</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>448</v>
       </c>
-      <c r="C16" s="4" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>449</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="C18" s="2" t="s">
         <v>450</v>
       </c>
     </row>
@@ -5822,17 +5810,6 @@
       </c>
       <c r="C27" s="2" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>469</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5851,7 +5828,6 @@
     <hyperlink ref="E13" r:id="rId12"/>
     <hyperlink ref="E14" r:id="rId13"/>
     <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5874,28 +5850,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>476</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5903,25 +5879,25 @@
         <v>335</v>
       </c>
       <c r="B2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>480</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" t="s">
         <v>481</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5929,103 +5905,103 @@
         <v>339</v>
       </c>
       <c r="B3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>487</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="E3" t="s">
-        <v>489</v>
-      </c>
       <c r="F3" t="s">
+        <v>481</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C4" t="s">
         <v>490</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>492</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" t="s">
         <v>493</v>
       </c>
-      <c r="E4" t="s">
-        <v>494</v>
-      </c>
-      <c r="F4" t="s">
-        <v>495</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>494</v>
+      </c>
+      <c r="B5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C5" t="s">
         <v>496</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>498</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" t="s">
         <v>499</v>
       </c>
-      <c r="E5" t="s">
-        <v>500</v>
-      </c>
-      <c r="F5" t="s">
-        <v>501</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" t="s">
         <v>502</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="E6" t="s">
-        <v>506</v>
-      </c>
       <c r="F6" t="s">
+        <v>481</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6039,7 +6015,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="509">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -178,7 +178,7 @@
     <t>12:35pm</t>
   </si>
   <si>
-    <t>Private driver to Hotel Trame — Pre-booked NCC, meeting you inside arrivals with a name board. Licensed cars may enter the ZTL to set down, so you are dropped at the hotel door — no garage, no walk with the bags.</t>
+    <t>Private driver to Hotel Trame — Pre-booked NCC, meeting you inside arrivals with a name board. Licensed cars may enter the ZTL, so you are dropped at the hotel door. On Uber: Italy has no UberX — the app offers only Uber Black, which costs more than a taxi. For a metered taxi use itTaxi or FreeNow, or a rank.</t>
   </si>
   <si>
     <t>Private transfer, ~45 min</t>
@@ -196,16 +196,28 @@
     <t>3:00pm</t>
   </si>
   <si>
-    <t>First walk: Pantheon → Piazza Navona → Campo de' Fiori — 1) Piazza Navona, 2) Pantheon, 3) Piazza di Montecitorio, 4) Trevi Fountain, 5) Spanish Steps</t>
+    <t>First walk: Piazza Navona → Pantheon → Trevi — Piazza Navona, then the Pantheon, Piazza di Montecitorio and the Trevi Fountain. About two hours at an easy pace, all of it flat.</t>
   </si>
   <si>
     <t>On foot</t>
   </si>
   <si>
+    <t>5:00pm</t>
+  </si>
+  <si>
+    <t>Shopping: Via del Corso up to the Spanish Steps — Timed on purpose: Aug 24 is a Monday, when Roman shops open late — most from 3:30 or 4pm until 7:30–8pm. Via del Corso is the chain high street, running from Piazza Venezia to Piazza del Popolo. Via dei Condotti at the top is the luxury row. Small independents may still be shut for the August break; the chains are not.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min from Trevi</t>
+  </si>
+  <si>
+    <t>Map -&gt;</t>
+  </si>
+  <si>
     <t>7:30pm</t>
   </si>
   <si>
-    <t>Dinner — Emma Pizzeria con Cucina — The Roscioli family's pizzeria: their salumeria supplies the kitchen, so the burrata and the cured meats are the same ones you get at Roscioli itself, on Roman-thin bases. A sharp modern room and a terrace on a quiet street four minutes from Trame — the shortest walk of anything considered, which is worth something after twenty hours awake. Book the 7:30 sitting; it fills.</t>
+    <t>Dinner — Emma Pizzeria con Cucina — The Roscioli family's pizzeria — the same burrata and cured meats as Roscioli itself, on thin Roman bases. Four minutes from the hotel, which matters after twenty hours awake. Book the 7:30 sitting; it fills.</t>
   </si>
   <si>
     <t>Walk, 4 min</t>
@@ -223,7 +235,7 @@
     <t>8:00am</t>
   </si>
   <si>
-    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Booked and paid, €90 for the two of you: the Vatican's own guided tour, English, with earphones. Both names are on the ticket and a ticket whose name does not match its holder is refused entry, so carry ID. Show the voucher to the Customer Care staff outside the Viale Vaticano entrance thirty minutes before departure; after security, up the stairs on the far left of the entrance hall to the 'Guided Tours' desk to collect the tickets and the service coupons, then on to the meeting point for earphones. Entrance is Passageway 2. Neither the date nor the time can be changed and it is not refundable. St Peter's is not part of this tour — the shortcut from the Sistine Chapel into the basilica is a guided-group privilege, so ask your guide on the day whether this one uses it.</t>
+    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Booked and paid, €90 for two. English, with earphones. Both names are on the ticket and ID is checked at the door, so carry it. Show the voucher to Customer Care outside the Viale Vaticano entrance 30 minutes before. After security, take the stairs at the far left of the entrance hall to the Guided Tours desk for tickets and coupons, then to the meeting point for earphones. Entrance is Passageway 2. Not changeable, not refundable. St Peter's is not included — ask your guide whether this tour uses the shortcut from the Sistine Chapel.</t>
   </si>
   <si>
     <t>Taxi, ~15 min</t>
@@ -250,10 +262,7 @@
     <t>Taxi</t>
   </si>
   <si>
-    <t>5:00pm</t>
-  </si>
-  <si>
-    <t>Castel Sant'Angelo, then the bridge at sunset — Ponte Sant'Angelo with Bernini's angels catching the last light</t>
+    <t>Castel Sant'Angelo, then the bridge at sunset — Bernini's angels on Ponte Sant'Angelo catch the last light</t>
   </si>
   <si>
     <t>Taxi, ~10 min</t>
@@ -292,13 +301,13 @@
     <t>8:45am</t>
   </si>
   <si>
-    <t>Baths of Caracalla — First, while it is still quiet — the brick vaults standing to full height, the scale of the bathing halls, patches of the mosaic floor still in place. Far emptier than anything else in ancient Rome at this hour.</t>
+    <t>Baths of Caracalla — Go first, while it is quiet. Brick vaults at full height, huge bathing halls, patches of the original mosaic floor. Far emptier than anything else in ancient Rome at this hour.</t>
   </si>
   <si>
     <t>10:30am</t>
   </si>
   <si>
-    <t>The Colosseum from outside, and the Arch of Constantine — The exterior circuit: the arcades from the Via dei Fori Imperiali side, then the Arch of Constantine. No arena floor and no interior ticket, so nothing to book and no queue to stand in. Pulled fifteen minutes earlier than before to leave room for the gallery.</t>
+    <t>The Colosseum from outside, and the Arch of Constantine — The outside circuit from the Via dei Fori Imperiali side, then the Arch of Constantine. No interior ticket, so nothing to book and no queue.</t>
   </si>
   <si>
     <t>Walk, ~20 min from Caracalla</t>
@@ -307,7 +316,7 @@
     <t>11:30am</t>
   </si>
   <si>
-    <t>Quick lunch in Monti — A few minutes up from the Colosseum, and it does have to be quick — the Borghese meeting point is a fifteen-minute taxi away and will not hold. Eat by ten past twelve and you have a real buffer; leave it later and you are watching the clock. Roscioli had this slot and wants two unhurried hours, which the 1:00pm entry no longer leaves; better to lose it than to rush it, so find it another lunch.</t>
+    <t>Quick lunch in Monti — It has to be quick: the Borghese meeting point is a fifteen-minute taxi away and will not hold. Eat by 12:10 and you have a buffer. Roscioli had this slot but wants two unhurried hours — give it another lunch rather than rush it.</t>
   </si>
   <si>
     <t>Walk, ~8 min</t>
@@ -316,7 +325,7 @@
     <t>12:45pm</t>
   </si>
   <si>
-    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Booked: skip-the-line entry for two with a digital audioguide, English, two hours. Meet the host at the Fontana dei Mascheroni on Viale del Museo Borghese, directly in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone for the audioguide; large bags are not allowed inside, but the cloakroom is free. Bernini's Apollo and Daphne and the Rape of Proserpina, six Caravaggios, in a villa small enough to see properly — and you are let in and out on the clock.</t>
+    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Booked: skip-the-line entry for two, digital audioguide in English, two hours. Meet the host at the Fontana dei Mascheroni on Viale del Museo Borghese, in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone. No large bags inside; the cloakroom is free. Bernini's Apollo and Daphne and the Rape of Proserpina, plus six Caravaggios. You are let in and out on the clock.</t>
   </si>
   <si>
     <t>Gallery -&gt;</t>
@@ -325,7 +334,7 @@
     <t>3:15pm</t>
   </si>
   <si>
-    <t>Villa Borghese Gardens — Straight out of the gallery into the park, and this is where the siesta went: shaded avenues, the Fontana dei Cavalli Marini, a bench under the pines through the worst of the heat.</t>
+    <t>Villa Borghese Gardens — Straight out of the gallery into the park. Shaded avenues, the Fontana dei Cavalli Marini, and a bench under the pines through the worst of the heat.</t>
   </si>
   <si>
     <t>Walk, ~5 min</t>
@@ -334,7 +343,7 @@
     <t>5:30pm</t>
   </si>
   <si>
-    <t>The Pincio terrace, in the low sun — The terrace over Piazza del Popolo with St. Peter's dome on the skyline. This is the Rome photo session — low sun through the trees, which is what the half-hour was chosen for.</t>
+    <t>The Pincio terrace, in the low sun — The terrace over Piazza del Popolo, St. Peter's dome on the skyline. This is the Rome photo session, timed for the low sun through the trees.</t>
   </si>
   <si>
     <t>Walk, ~15 min across the park</t>
@@ -376,7 +385,7 @@
     <t>11:00am</t>
   </si>
   <si>
-    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven. About fifteen minutes from Campo de' Fiori, so there is no need to be up early — have a last coffee on the piazza first.</t>
+    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven and Termini is fifteen minutes away. No need to be up early — have a last coffee on the piazza.</t>
   </si>
   <si>
     <t>12:10pm</t>
@@ -400,7 +409,7 @@
     <t>2:25pm</t>
   </si>
   <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco. It's about 1.3km from the platform — a twenty-minute walk, so take a taxi with the bags. Rooms are ready from 2:00pm; they'll hold the luggage until then. Checkout on the 29th is noon, and the rate is room-only — breakfast is on you both mornings.</t>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms from 2:00pm; they will hold luggage until then. Checkout the 29th at noon. Room-only rate, so breakfast is on you both mornings.</t>
   </si>
   <si>
     <t>Taxi, ~8 min</t>
@@ -409,7 +418,7 @@
     <t>Hotel site -&gt;</t>
   </si>
   <si>
-    <t>Accademia — David at the afternoon slot — Book the 3:00pm entry — the train lands at 2:11pm and lunch is already behind you, on board. Forty-five minutes is genuinely enough; go straight down the hall of the Prisoners.</t>
+    <t>Accademia — David at the afternoon slot — Book the 3:00pm entry; the train lands at 2:11pm. Forty-five minutes is enough — go straight down the hall of the Prisoners.</t>
   </si>
   <si>
     <t>Walk, ~6 min</t>
@@ -418,7 +427,7 @@
     <t>4:30pm</t>
   </si>
   <si>
-    <t>Climb Brunelleschi's dome — 4:30pm sharp — Booked: two Brunelleschi Passes, entry to the dome from the Porta della Mandorla. 463 steps and no lift. The time slot is not modifiable and names are checked against ID at the door, so be standing there by a quarter past. The same pass covers the Bell Tower, Baptistery, museum and the Santa Reparata crypt, and stays valid through 29 August — which is why the museum sits on tomorrow rather than being crammed in here.</t>
+    <t>Climb Brunelleschi's dome — 4:30pm sharp — Booked: two Brunelleschi Passes, dome entry at the Porta della Mandorla. 463 steps, no lift. The slot cannot be changed and names are checked against ID, so be there by 4:15. The pass also covers the Bell Tower, Baptistery, museum and Santa Reparata crypt and runs through 29 August — which is why the museum sits on tomorrow.</t>
   </si>
   <si>
     <t>Duomo -&gt;</t>
@@ -427,16 +436,16 @@
     <t>6:00pm</t>
   </si>
   <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait — and you will want it after the stairs</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is around 8:00pm and the hill is the place to watch it from — this is timed to it. Taxi up, walk down through the rose garden.</t>
+    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait — and you will want it after 463 steps</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is about 8:00pm and the hill is where to watch it. Taxi up, walk down through the rose garden.</t>
   </si>
   <si>
     <t>Taxi up, ~10 min</t>
   </si>
   <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a handful of window tables. Ask for one.</t>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a few window tables. Ask for one.</t>
   </si>
   <si>
     <t>Walk down, ~15 min</t>
@@ -451,22 +460,22 @@
     <t>8:15am</t>
   </si>
   <si>
-    <t>Pitti Palace and the Boboli Gardens — A quarter past eight is the minute the gates open, and that is the whole point: Boboli is terraced, unshaded and unwalkable by mid-afternoon, so it goes first. The Palatine Gallery is hung floor to ceiling in the old manner; climb to the top of the gardens for the view back over the city.</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs straight from the palace gates to the bridge — stop halfway down it.</t>
+    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced and unshaded, and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs from the palace gates to the bridge. Stop halfway.</t>
   </si>
   <si>
     <t>12:15pm</t>
   </si>
   <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. Roughly two hours with a guide, which is the right amount.</t>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. About two hours with a guide.</t>
   </si>
   <si>
     <t>Cross Ponte Vecchio, ~6 min</t>
   </si>
   <si>
-    <t>Late lunch — 'Ino — Two hours in the Uffizi from a quarter past twelve puts you out at half past two, which is when the Oltrarno kitchens stop serving — so lunch is thirty seconds from the gallery door instead. Panini made to order, Tuscan wine by the glass, open straight through the afternoon. Il Santo Bevitore across the river stays the sit-down alternative if the tour runs short.</t>
+    <t>Late lunch — 'Ino — Two hours from 12:15 puts you out at 2:30, which is when Oltrarno kitchens stop serving — so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
   </si>
   <si>
     <t>Walk, ~2 min</t>
@@ -475,19 +484,19 @@
     <t>4:00pm</t>
   </si>
   <si>
-    <t>Reverse Renaissance Walk — The centre backwards, starting where it started: the Casa di Dante, then Orsanmichele, then out into Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, and free. This was Thursday evening's block, moved here because it never had the daylight there.</t>
+    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, then Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free. Moved here from Thursday evening, which had no daylight for it.</t>
   </si>
   <si>
     <t>5:15pm</t>
   </si>
   <si>
-    <t>Opera del Duomo museum — Already paid for — Thursday's Brunelleschi Pass runs to the 29th, so this costs nothing more. Ghiberti's original Gates of Paradise are in here, and Michelangelo's late Pietà. Entrance is Piazza del Duomo 9, and it is the last thing the pass has left to give.</t>
+    <t>Opera del Duomo museum — Already paid — Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà. Entrance is Piazza del Duomo 9.</t>
   </si>
   <si>
     <t>6:30pm</t>
   </si>
   <si>
-    <t>Back to the hotel to change — Fifteen minutes on foot up from the centre, so taxi if the day has run long</t>
+    <t>Back to the hotel to change — Fifteen minutes uphill from the centre — taxi if the day has run long</t>
   </si>
   <si>
     <t>Walk, ~15 min</t>
@@ -496,7 +505,7 @@
     <t>8:00pm</t>
   </si>
   <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church — closer to the singers than any opera house puts you.</t>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church, closer to the singers than an opera house puts you.</t>
   </si>
   <si>
     <t>9:45pm</t>
@@ -517,13 +526,13 @@
     <t>9:00am</t>
   </si>
   <si>
-    <t>Check out; collect the rental car — The agencies cluster on Borgo Ognissanti, just outside the ZTL — so you never drive into the centro storico. It is a good twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, just outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton — taxi with the luggage. Have the IDP and licence ready.</t>
   </si>
   <si>
     <t>9:30am</t>
   </si>
   <si>
-    <t>Fiesole — Florence from the hill — Twenty-five minutes up out of the valley for the view back over the whole city: the roofs, the river and the dome seen from above rather than beneath. Go out along the viali — the ZTL starts the moment you cut through the centre — and leave the car at Piazza Mino.</t>
+    <t>Fiesole — Florence from the hill — Twenty-five minutes up for the view back over the city — roofs, river and dome from above. Go out along the viali to stay clear of the ZTL, and park at Piazza Mino.</t>
   </si>
   <si>
     <t>Self-drive, ~25 min</t>
@@ -532,7 +541,7 @@
     <t>10:45am</t>
   </si>
   <si>
-    <t>Southwest to Certaldo — Back down through the valley and out the other side — about an hour and ten from Fiesole, against forty-five minutes had you driven straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
+    <t>Southwest to Certaldo — An hour and ten from Fiesole, against forty-five minutes driving straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
   </si>
   <si>
     <t>Self-drive, ~1h10</t>
@@ -541,7 +550,7 @@
     <t>12:00pm</t>
   </si>
   <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace — a walled brick town, the funicular climbs from Piazza Boccaccio in under two minutes</t>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace, a walled brick town. The funicular climbs from Piazza Boccaccio in under two minutes</t>
   </si>
   <si>
     <t>Arrive Certaldo</t>
@@ -562,7 +571,7 @@
     <t>Self-drive</t>
   </si>
   <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, its own castle at the centre. Deluxe Room with breakfast; rooms are ready from 3:00pm and checkout is 11:00am on the 31st, which is why Monday starts at eight.</t>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st — which is why Monday starts at eight.</t>
   </si>
   <si>
     <t>Book -&gt;</t>
@@ -592,7 +601,7 @@
     <t>Drive to San Gimignano — About twenty-five minutes</t>
   </si>
   <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand — best seen from Piazza della Cisterna</t>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand. Best seen from Piazza della Cisterna</t>
   </si>
   <si>
     <t>10:15am</t>
@@ -601,10 +610,10 @@
     <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
   </si>
   <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna — quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and native woods, then a traditional Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; book ahead — 3-4 hours all told. Alternative operator for the same kind of morning, if this one fills: CET Experience, cetexperience.it.</t>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and woods, then a Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed. Three to four hours; book ahead. Backup operator: CET Experience, cetexperience.it.</t>
   </si>
   <si>
     <t>Meet at the Bivio Volterra bus stop</t>
@@ -628,7 +637,7 @@
     <t>9:15am</t>
   </si>
   <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so this is no longer the dawn start it was.</t>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so there is no need for a dawn start.</t>
   </si>
   <si>
     <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
@@ -637,7 +646,7 @@
     <t>Rental desk</t>
   </si>
   <si>
-    <t>Lunch by the station before the train — The later departure buys an unhurried hour here, which the old 10:52 did not — and the next real meal is dinner in Sorrento</t>
+    <t>Lunch by the station before the train — The later train buys an unhurried hour, and the next real meal is dinner in Sorrento</t>
   </si>
   <si>
     <t>1:14pm</t>
@@ -658,7 +667,7 @@
     <t>5:26pm</t>
   </si>
   <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. This is the tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning and somewhere to put a suitcase, €18pp. An hour to wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. The tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning, room for a suitcase, €18pp. An hour's wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
   </si>
   <si>
     <t>Campania Express, 1h09</t>
@@ -670,13 +679,13 @@
     <t>6:35pm</t>
   </si>
   <si>
-    <t>Arrive Sorrento station — The hotel is 480m away — six minutes on the flat, which is the real reason this beats the ferry: Marina Piccola is the same distance but uphill</t>
+    <t>Arrive Sorrento station — The hotel is 480m away, six minutes on the flat. That is why this beats the ferry — Marina Piccola is the same distance uphill</t>
   </si>
   <si>
     <t>6:50pm</t>
   </si>
   <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask at the desk to arrange the room move on the 4th while you're out at Amalfi — see that day.</t>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to arrange the room move on the 4th while you are out at Amalfi.</t>
   </si>
   <si>
     <t>7:15pm</t>
@@ -694,7 +703,7 @@
     <t>8:45pm</t>
   </si>
   <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room. Easiest possible first night after three legs of travel; book it before you arrive.</t>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room — the easiest first night after three legs. Book before you arrive.</t>
   </si>
   <si>
     <t>Tue, Sep 1</t>
@@ -706,28 +715,28 @@
     <t>8:30am</t>
   </si>
   <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees, which is the whole reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a ruined mill at the bottom of a gorge, swallowed by ferns, right in the middle of town</t>
+    <t>Breakfast in the garden — Under the lemon and orange trees — the reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a fern-covered ruined mill in a gorge in the middle of town</t>
   </si>
   <si>
     <t>Walk from the door</t>
   </si>
   <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of Sorrento, free to walk through, with limoncello made on site at the end of it</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck out over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Back up for the working afternoon. Fibre in the rooms, and the garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — There is no lift to the water here — the hotel works with a beach club down at the marina if you want salt water, so ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables set among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the hotel door.</t>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of town, free to walk through, with limoncello made on site</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Fibre in the rooms. The garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>The pool, or the Thala Spa — No lift down to the water here. The hotel works with a beach club at the marina — ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the door.</t>
   </si>
   <si>
     <t>Wed, Sep 2</t>
@@ -736,7 +745,7 @@
     <t>SORRENTO — Capri day trip</t>
   </si>
   <si>
-    <t>Down to Marina Piccola — About twenty minutes on foot from Via Correale, and the last stretch is steep — the public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+    <t>Down to Marina Piccola — Twenty minutes on foot, and the last stretch is steep. The public lift from the Villa Comunale gardens skips it, or take a taxi</t>
   </si>
   <si>
     <t>Walk ~20 min, or taxi</t>
@@ -745,7 +754,7 @@
     <t>8:40am</t>
   </si>
   <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes; up to forty crossings a day in high season, but they still sell out at the counter in August. Book online the night before.</t>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes. Up to forty crossings a day in season, but they sell out at the counter in August — book online the night before.</t>
   </si>
   <si>
     <t>Fast ferry, ~25 min</t>
@@ -754,7 +763,7 @@
     <t>Timetable -&gt;</t>
   </si>
   <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves — Blue Grotto if the sea is calm enough to enter. Two hours or so.</t>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves, plus the Blue Grotto if the sea is calm enough. About two hours.</t>
   </si>
   <si>
     <t>Local boat</t>
@@ -772,7 +781,7 @@
     <t>4:15pm</t>
   </si>
   <si>
-    <t>Ferry back to Sorrento — Check the final sailing when you land in the morning — missing the last boat means a night on the island</t>
+    <t>Ferry back to Sorrento — Check the last sailing when you land. Missing it means a night on the island</t>
   </si>
   <si>
     <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
@@ -793,19 +802,19 @@
     <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
   </si>
   <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula from Sorrento. Mid-April to mid-October only, and worth booking the day before in August.</t>
+    <t>Ferry to Positano — About 35 minutes down the peninsula. Mid-April to mid-October only; book the day before in August.</t>
   </si>
   <si>
     <t>Ferry, ~35 min</t>
   </si>
   <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in — have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, unpretentious despite the address. La Tagliata up in the hills is the other option if you'd rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — Positano's actual local industry</t>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in, so have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, and unpretentious despite the address. La Tagliata up in the hills is the alternative if you would rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — the town's real local industry</t>
   </si>
   <si>
     <t>Uphill on foot</t>
@@ -817,13 +826,13 @@
     <t>Desk hours</t>
   </si>
   <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, straight out over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
   </si>
   <si>
     <t>Walk, ~3 min</t>
   </si>
   <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia, and the seafood is better than the theme suggests</t>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia. The seafood is better than the theme suggests</t>
   </si>
   <si>
     <t>Fri, Sep 4</t>
@@ -832,25 +841,25 @@
     <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
   </si>
   <si>
-    <t>Down to Marina Piccola — Taxi this one — it is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Seasonal — mid-April to mid-October.</t>
+    <t>Down to Marina Piccola — Taxi this one. It is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Mid-April to mid-October only.</t>
   </si>
   <si>
     <t>Ferry, ~1h15</t>
   </si>
   <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea at the top of sixty-two steps, and a 13th-century cloister of interlaced Arab-Norman arches behind it</t>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea, up sixty-two steps, with a 13th-century cloister of Arab-Norman arches behind it</t>
   </si>
   <si>
     <t>Walk from the marina</t>
   </si>
   <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path — Amalfi made paper here for six hundred years, and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, a terrace above the street, and the best table in Amalfi town</t>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path. Amalfi made paper here for six hundred years and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, on a terrace above the street. The best table in Amalfi</t>
   </si>
   <si>
     <t>2:15pm</t>
@@ -865,7 +874,7 @@
     <t>2:45pm</t>
   </si>
   <si>
-    <t>Villa Cimbrone — The Terrace of Infinity — a marble balustrade lined with busts, and a thousand-foot drop to the sea behind them</t>
+    <t>Villa Cimbrone — The Terrace of Infinity: a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
   </si>
   <si>
     <t>On foot; Ravello is car-free</t>
@@ -877,13 +886,13 @@
     <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
   </si>
   <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving Ravello at five puts you back at the hotel around 6:30pm.</t>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving at five puts you back at the hotel by 6:30pm.</t>
   </si>
   <si>
     <t>Private driver, ~1h30</t>
   </si>
   <si>
-    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town, and the last proper dinner on the coast</t>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town. The last proper dinner on the coast</t>
   </si>
   <si>
     <t>Sat, Sep 5</t>
@@ -898,13 +907,13 @@
     <t>9:45am</t>
   </si>
   <si>
-    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice — it buys the Naples stop below</t>
+    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice. It buys the Naples stop below</t>
   </si>
   <si>
     <t>10:20am</t>
   </si>
   <si>
-    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train already standing where the next one leaves.</t>
+    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next one leaves.</t>
   </si>
   <si>
     <t>Campania Express, 1h14</t>
@@ -919,7 +928,7 @@
     <t>11:55am</t>
   </si>
   <si>
-    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city: Di Matteo and Sorbillo are both about twenty minutes' walk up Via dei Tribunali. Naples came out of this itinerary altogether, and this is the one window it gets back. If you would rather not carry the risk, there is good pizza within sight of the station.</t>
+    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city — Di Matteo and Sorbillo are both about twenty minutes up Via dei Tribunali. Naples came out of the itinerary altogether and this is the one window it gets back. If you would rather not risk it, there is good pizza in sight of the station.</t>
   </si>
   <si>
     <t>Walk, ~20 min</t>
@@ -949,25 +958,25 @@
     <t>3:20pm</t>
   </si>
   <si>
-    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began at Hotel Trame. Superior Double; nothing is prepaid, you settle €530 with the hotel.</t>
-  </si>
-  <si>
-    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door and the one corner of the centre you haven't walked yet — Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
-  </si>
-  <si>
-    <t>Tiber Island and the Ponte Fabricio — The bridge has carried people across since 62 BC and is still the original stone</t>
-  </si>
-  <si>
-    <t>Trevi Fountain, one last time — Twenty minutes up through the centre, and worth the crowd on a final evening</t>
-  </si>
-  <si>
-    <t>Aperitivo on Campo de' Fiori — The market stalls are long packed away by now and the square turns over to drinking</t>
+    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began. Superior Double. Nothing is prepaid — you settle €530 with the hotel.</t>
+  </si>
+  <si>
+    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door, and the one corner of the centre you have not walked. Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
+  </si>
+  <si>
+    <t>Tiber Island and the Ponte Fabricio — The bridge has carried people since 62 BC, still on the original stone</t>
+  </si>
+  <si>
+    <t>Trevi Fountain, one last time — Twenty minutes up through the centre. Worth the crowd on a last evening</t>
+  </si>
+  <si>
+    <t>Aperitivo on Campo de' Fiori — The market stalls are packed away by now and the square turns over to drinking</t>
   </si>
   <si>
     <t>Walk, ~4 min</t>
   </si>
   <si>
-    <t>Farewell dinner — Aroma, at Palazzo Manfredi — Michelin-starred, on a rooftop that looks straight into the Colosseum. Book this one early; there are only a dozen tables with the view.</t>
+    <t>Farewell dinner — Aroma, at Palazzo Manfredi — Michelin-starred, on a rooftop looking straight into the Colosseum. Book early — only a dozen tables have the view.</t>
   </si>
   <si>
     <t>Sun, Sep 6</t>
@@ -979,7 +988,7 @@
     <t>6:40am</t>
   </si>
   <si>
-    <t>Taxi to FCO — About thirty-five minutes on an empty Sunday road. No rental to return — that ended in Florence on Aug 31.</t>
+    <t>Taxi to FCO — About thirty-five minutes on an empty Sunday road. No rental to return; that ended in Florence on Aug 31.</t>
   </si>
   <si>
     <t>7:20am</t>
@@ -2214,7 +2223,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2356,34 +2365,34 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="C10" s="11" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2404,7 +2413,7 @@
         <v>73</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,16 +2424,16 @@
         <v>48</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
+        <v>77</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,16 +2444,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="7" t="s">
         <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,8 +2472,8 @@
       <c r="E14" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F14" t="s">
-        <v>48</v>
+      <c r="F14" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,16 +2484,16 @@
         <v>48</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2495,47 +2504,47 @@
         <v>48</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <v>3</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>80</v>
+      <c r="C19" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2546,16 +2555,16 @@
         <v>48</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" t="s">
-        <v>48</v>
+        <v>73</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2592,10 +2601,10 @@
         <v>99</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="7" t="s">
         <v>100</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2612,10 +2621,10 @@
         <v>102</v>
       </c>
       <c r="E23" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2634,8 +2643,8 @@
       <c r="E24" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>107</v>
+      <c r="F24" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2646,16 +2655,16 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="F25" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="F25" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2666,13 +2675,13 @@
         <v>48</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
         <v>48</v>
@@ -2686,50 +2695,50 @@
         <v>48</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+        <v>73</v>
+      </c>
+      <c r="F27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
         <v>4</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="C30" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" t="s">
-        <v>48</v>
+      <c r="F30" s="14" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2740,16 +2749,16 @@
         <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>123</v>
+        <v>73</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2760,16 +2769,16 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" t="s">
-        <v>48</v>
+      <c r="F32" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2780,16 +2789,16 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>129</v>
+        <v>57</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,7 +2809,7 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>130</v>
@@ -2809,7 +2818,7 @@
         <v>131</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2820,16 +2829,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>133</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,10 +2855,10 @@
         <v>136</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F36" t="s">
-        <v>48</v>
+        <v>100</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,13 +2869,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2880,47 +2889,47 @@
         <v>48</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+        <v>141</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
         <v>5</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="B41" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>80</v>
+      <c r="C41" s="11" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2931,16 +2940,16 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F42" t="s">
-        <v>48</v>
+        <v>82</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2951,16 +2960,16 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>80</v>
+        <v>106</v>
+      </c>
+      <c r="F43" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2971,16 +2980,16 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F44" t="s">
-        <v>48</v>
+        <v>151</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2991,13 +3000,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>152</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="F45" t="s">
         <v>48</v>
@@ -3011,13 +3020,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
@@ -3031,13 +3040,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>48</v>
@@ -3057,10 +3066,10 @@
         <v>159</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>80</v>
+        <v>160</v>
+      </c>
+      <c r="F48" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3071,50 +3080,50 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="10">
         <v>6</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="B52" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E52" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F52" t="s">
-        <v>48</v>
+      <c r="C52" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3125,13 +3134,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3173,8 +3182,8 @@
       <c r="E55" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>107</v>
+      <c r="F55" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3191,10 +3200,10 @@
         <v>177</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F56" t="s">
-        <v>48</v>
+        <v>178</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3205,13 +3214,13 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3225,13 +3234,13 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
         <v>48</v>
@@ -3245,16 +3254,16 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="F59" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3265,16 +3274,16 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F60" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3285,13 +3294,13 @@
         <v>48</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>184</v>
+        <v>61</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="F61" t="s">
         <v>48</v>
@@ -3305,47 +3314,47 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F62" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="10">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F63" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
         <v>7</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F65" t="s">
-        <v>48</v>
+      <c r="B65" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3356,13 +3365,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3376,13 +3385,13 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F67" t="s">
         <v>48</v>
@@ -3396,13 +3405,13 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F68" t="s">
         <v>48</v>
@@ -3416,16 +3425,16 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>182</v>
+        <v>85</v>
+      </c>
+      <c r="F69" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3436,16 +3445,16 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F70" t="s">
-        <v>48</v>
+        <v>199</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3456,13 +3465,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3476,50 +3485,50 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="10">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
         <v>8</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>48</v>
-      </c>
-      <c r="B75" t="s">
-        <v>48</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="B75" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="E75" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F75" t="s">
-        <v>48</v>
+      <c r="C75" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3530,13 +3539,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3550,13 +3559,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>97</v>
+        <v>208</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3570,16 +3579,16 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>123</v>
+        <v>100</v>
+      </c>
+      <c r="F78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,10 +3605,10 @@
         <v>211</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F79" t="s">
-        <v>48</v>
+        <v>212</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3610,16 +3619,16 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>215</v>
+        <v>57</v>
+      </c>
+      <c r="F80" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3630,16 +3639,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E81" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F81" t="s">
-        <v>48</v>
+      <c r="F81" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3650,16 +3659,16 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>129</v>
+        <v>57</v>
+      </c>
+      <c r="F82" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3670,16 +3679,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F83" t="s">
-        <v>48</v>
+        <v>134</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3690,13 +3699,13 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F84" t="s">
         <v>48</v>
@@ -3710,47 +3719,47 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+        <v>189</v>
+      </c>
+      <c r="F85" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B86" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
         <v>9</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>48</v>
-      </c>
-      <c r="B88" t="s">
-        <v>48</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="B88" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E88" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F88" t="s">
-        <v>48</v>
+      <c r="C88" s="11" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3761,13 +3770,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3781,16 +3790,16 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>107</v>
+        <v>234</v>
+      </c>
+      <c r="F90" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,16 +3810,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3821,16 +3830,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F92" t="s">
-        <v>48</v>
+        <v>143</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3841,13 +3850,13 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F93" t="s">
         <v>48</v>
@@ -3861,47 +3870,47 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+        <v>189</v>
+      </c>
+      <c r="F94" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
         <v>10</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>48</v>
-      </c>
-      <c r="B97" t="s">
-        <v>48</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E97" s="13" t="s">
+      <c r="B97" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F97" t="s">
-        <v>48</v>
+      <c r="C97" s="11" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3912,7 +3921,7 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>241</v>
+        <v>71</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>242</v>
@@ -3920,8 +3929,8 @@
       <c r="E98" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>244</v>
+      <c r="F98" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,7 +3941,7 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>245</v>
@@ -3940,8 +3949,8 @@
       <c r="E99" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="F99" t="s">
-        <v>48</v>
+      <c r="F99" s="7" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3952,16 +3961,16 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>64</v>
+        <v>249</v>
+      </c>
+      <c r="F100" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3972,16 +3981,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3992,16 +4001,16 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="F102" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4012,13 +4021,13 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -4032,47 +4041,47 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="10">
+        <v>189</v>
+      </c>
+      <c r="F104" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>48</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
         <v>11</v>
       </c>
-      <c r="B106" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>48</v>
-      </c>
-      <c r="B107" t="s">
-        <v>48</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F107" t="s">
-        <v>48</v>
+      <c r="B107" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4083,16 +4092,16 @@
         <v>48</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>244</v>
+        <v>189</v>
+      </c>
+      <c r="F108" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4103,16 +4112,16 @@
         <v>48</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F109" t="s">
-        <v>48</v>
+        <v>262</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4123,16 +4132,16 @@
         <v>48</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+      <c r="F110" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4143,16 +4152,16 @@
         <v>48</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="F111" t="s">
-        <v>48</v>
+        <v>85</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4163,13 +4172,13 @@
         <v>48</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4183,13 +4192,13 @@
         <v>48</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4203,13 +4212,13 @@
         <v>48</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -4223,47 +4232,47 @@
         <v>48</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="10">
+        <v>270</v>
+      </c>
+      <c r="F115" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>48</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="10">
         <v>12</v>
       </c>
-      <c r="B117" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>48</v>
-      </c>
-      <c r="B118" t="s">
-        <v>48</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F118" t="s">
-        <v>48</v>
+      <c r="B118" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4274,16 +4283,16 @@
         <v>48</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>244</v>
+        <v>131</v>
+      </c>
+      <c r="F119" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4294,16 +4303,16 @@
         <v>48</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="F120" t="s">
-        <v>48</v>
+        <v>276</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,13 +4323,13 @@
         <v>48</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -4337,13 +4346,13 @@
         <v>98</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>64</v>
+        <v>85</v>
+      </c>
+      <c r="F122" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4354,16 +4363,16 @@
         <v>48</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="F123" t="s">
-        <v>48</v>
+        <v>85</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4382,8 +4391,8 @@
       <c r="E124" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>80</v>
+      <c r="F124" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4400,10 +4409,10 @@
         <v>285</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4414,16 +4423,16 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="F126" t="s">
-        <v>48</v>
+        <v>85</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4434,50 +4443,50 @@
         <v>48</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="10">
+        <v>290</v>
+      </c>
+      <c r="F127" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>48</v>
+      </c>
+      <c r="B128" t="s">
+        <v>48</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="10">
         <v>13</v>
       </c>
-      <c r="B129" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="C129" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>48</v>
-      </c>
-      <c r="B130" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E130" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F130" t="s">
-        <v>48</v>
+      <c r="B130" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4488,13 +4497,13 @@
         <v>48</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>292</v>
+        <v>93</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F131" t="s">
         <v>48</v>
@@ -4508,16 +4517,16 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>215</v>
+        <v>189</v>
+      </c>
+      <c r="F132" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4534,10 +4543,10 @@
         <v>298</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F133" t="s">
-        <v>48</v>
+        <v>299</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4548,16 +4557,16 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>302</v>
+        <v>57</v>
+      </c>
+      <c r="F134" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4568,16 +4577,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="E135" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="E135" s="13" t="s">
+      <c r="F135" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4596,8 +4605,8 @@
       <c r="E136" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="F136" t="s">
-        <v>48</v>
+      <c r="F136" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4614,10 +4623,10 @@
         <v>310</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>129</v>
+        <v>311</v>
+      </c>
+      <c r="F137" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4628,16 +4637,16 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F138" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4648,13 +4657,13 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F139" t="s">
         <v>48</v>
@@ -4668,13 +4677,13 @@
         <v>48</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>301</v>
+        <v>106</v>
       </c>
       <c r="F140" t="s">
         <v>48</v>
@@ -4688,13 +4697,13 @@
         <v>48</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>220</v>
+        <v>138</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="F141" t="s">
         <v>48</v>
@@ -4708,47 +4717,47 @@
         <v>48</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="10">
+        <v>318</v>
+      </c>
+      <c r="F142" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" t="s">
+        <v>48</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="10">
         <v>14</v>
       </c>
-      <c r="B144" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>48</v>
-      </c>
-      <c r="B145" t="s">
-        <v>48</v>
-      </c>
-      <c r="C145" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="D145" s="4" t="s">
+      <c r="B145" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="E145" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F145" t="s">
-        <v>48</v>
+      <c r="C145" s="11" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,13 +4768,13 @@
         <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="F146" t="s">
         <v>48</v>
@@ -4779,66 +4788,87 @@
         <v>48</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F147" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>48</v>
+      </c>
+      <c r="B148" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="F148" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1"/>
-    <hyperlink ref="F10" r:id="rId2"/>
+    <hyperlink ref="F8" r:id="rId2"/>
     <hyperlink ref="F11" r:id="rId3"/>
-    <hyperlink ref="F13" r:id="rId4"/>
-    <hyperlink ref="F15" r:id="rId5"/>
+    <hyperlink ref="F12" r:id="rId4"/>
+    <hyperlink ref="F14" r:id="rId5"/>
     <hyperlink ref="F16" r:id="rId6"/>
-    <hyperlink ref="F19" r:id="rId7"/>
-    <hyperlink ref="F22" r:id="rId8"/>
-    <hyperlink ref="F24" r:id="rId9"/>
-    <hyperlink ref="F27" r:id="rId10"/>
-    <hyperlink ref="F31" r:id="rId11"/>
-    <hyperlink ref="F33" r:id="rId12"/>
+    <hyperlink ref="F17" r:id="rId7"/>
+    <hyperlink ref="F20" r:id="rId8"/>
+    <hyperlink ref="F23" r:id="rId9"/>
+    <hyperlink ref="F25" r:id="rId10"/>
+    <hyperlink ref="F28" r:id="rId11"/>
+    <hyperlink ref="F32" r:id="rId12"/>
     <hyperlink ref="F34" r:id="rId13"/>
     <hyperlink ref="F35" r:id="rId14"/>
-    <hyperlink ref="F38" r:id="rId15"/>
-    <hyperlink ref="F41" r:id="rId16"/>
-    <hyperlink ref="F43" r:id="rId17"/>
-    <hyperlink ref="F48" r:id="rId18"/>
+    <hyperlink ref="F36" r:id="rId15"/>
+    <hyperlink ref="F39" r:id="rId16"/>
+    <hyperlink ref="F42" r:id="rId17"/>
+    <hyperlink ref="F44" r:id="rId18"/>
     <hyperlink ref="F49" r:id="rId19"/>
-    <hyperlink ref="F55" r:id="rId20"/>
-    <hyperlink ref="F59" r:id="rId21"/>
-    <hyperlink ref="F69" r:id="rId22"/>
-    <hyperlink ref="F78" r:id="rId23"/>
-    <hyperlink ref="F80" r:id="rId24"/>
-    <hyperlink ref="F82" r:id="rId25"/>
-    <hyperlink ref="F85" r:id="rId26"/>
-    <hyperlink ref="F90" r:id="rId27"/>
+    <hyperlink ref="F50" r:id="rId20"/>
+    <hyperlink ref="F56" r:id="rId21"/>
+    <hyperlink ref="F60" r:id="rId22"/>
+    <hyperlink ref="F70" r:id="rId23"/>
+    <hyperlink ref="F79" r:id="rId24"/>
+    <hyperlink ref="F81" r:id="rId25"/>
+    <hyperlink ref="F83" r:id="rId26"/>
+    <hyperlink ref="F86" r:id="rId27"/>
     <hyperlink ref="F91" r:id="rId28"/>
-    <hyperlink ref="F94" r:id="rId29"/>
-    <hyperlink ref="F98" r:id="rId30"/>
-    <hyperlink ref="F100" r:id="rId31"/>
+    <hyperlink ref="F92" r:id="rId29"/>
+    <hyperlink ref="F95" r:id="rId30"/>
+    <hyperlink ref="F99" r:id="rId31"/>
     <hyperlink ref="F101" r:id="rId32"/>
-    <hyperlink ref="F104" r:id="rId33"/>
-    <hyperlink ref="F108" r:id="rId34"/>
-    <hyperlink ref="F110" r:id="rId35"/>
-    <hyperlink ref="F115" r:id="rId36"/>
-    <hyperlink ref="F119" r:id="rId37"/>
-    <hyperlink ref="F122" r:id="rId38"/>
-    <hyperlink ref="F124" r:id="rId39"/>
+    <hyperlink ref="F102" r:id="rId33"/>
+    <hyperlink ref="F105" r:id="rId34"/>
+    <hyperlink ref="F109" r:id="rId35"/>
+    <hyperlink ref="F111" r:id="rId36"/>
+    <hyperlink ref="F116" r:id="rId37"/>
+    <hyperlink ref="F120" r:id="rId38"/>
+    <hyperlink ref="F123" r:id="rId39"/>
     <hyperlink ref="F125" r:id="rId40"/>
-    <hyperlink ref="F127" r:id="rId41"/>
-    <hyperlink ref="F132" r:id="rId42"/>
-    <hyperlink ref="F134" r:id="rId43"/>
+    <hyperlink ref="F126" r:id="rId41"/>
+    <hyperlink ref="F128" r:id="rId42"/>
+    <hyperlink ref="F133" r:id="rId43"/>
     <hyperlink ref="F135" r:id="rId44"/>
-    <hyperlink ref="F137" r:id="rId45"/>
-    <hyperlink ref="F142" r:id="rId46"/>
+    <hyperlink ref="F136" r:id="rId45"/>
+    <hyperlink ref="F138" r:id="rId46"/>
+    <hyperlink ref="F143" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4861,48 +4891,48 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -4914,24 +4944,24 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4943,24 +4973,24 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -4972,24 +5002,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5001,24 +5031,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5030,7 +5060,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -5047,7 +5077,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -5084,24 +5114,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5112,51 +5142,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B4" s="15">
         <v>2115</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B7" s="17">
         <v>18198.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -5181,220 +5211,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>374</v>
-      </c>
-      <c r="D3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D5" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D8" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D9" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B10" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D10" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D12" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D13" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5405,7 +5435,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -5441,16 +5471,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5461,16 +5491,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5478,16 +5508,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>418</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5495,16 +5525,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5512,16 +5542,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5529,16 +5559,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5546,16 +5576,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5563,16 +5593,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>428</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5580,16 +5610,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5597,16 +5627,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5614,16 +5644,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5631,16 +5661,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5648,16 +5678,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5665,16 +5695,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>441</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5682,16 +5712,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5699,7 +5729,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5707,10 +5737,10 @@
         <v>48</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5718,10 +5748,10 @@
         <v>48</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5729,10 +5759,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5740,10 +5770,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5751,10 +5781,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5762,10 +5792,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5773,10 +5803,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5784,10 +5814,10 @@
         <v>48</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5795,10 +5825,10 @@
         <v>48</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5806,10 +5836,10 @@
         <v>48</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -5850,158 +5880,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="E3" t="s">
+        <v>490</v>
+      </c>
+      <c r="F3" t="s">
         <v>484</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>486</v>
-      </c>
-      <c r="E3" t="s">
-        <v>487</v>
-      </c>
-      <c r="F3" t="s">
-        <v>481</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B4" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C4" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C5" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E5" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F5" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C6" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F6" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6015,7 +6045,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -178,7 +178,7 @@
     <t>12:35pm</t>
   </si>
   <si>
-    <t>Private driver to Hotel Trame — Pre-booked NCC, meeting you inside arrivals with a name board. Licensed cars may enter the ZTL, so you are dropped at the hotel door. On Uber: Italy has no UberX — the app offers only Uber Black, which costs more than a taxi. For a metered taxi use itTaxi or FreeNow, or a rank.</t>
+    <t>Private driver to Hotel Trame — Pre-booked NCC, meeting you inside arrivals with a name board; licensed cars may enter the ZTL, so you are dropped at the door. Italy has no UberX — the app offers only Uber Black, dearer than a taxi. Use itTaxi or FreeNow for a metered cab.</t>
   </si>
   <si>
     <t>Private transfer, ~45 min</t>
@@ -205,7 +205,7 @@
     <t>5:00pm</t>
   </si>
   <si>
-    <t>Shopping: Via del Corso up to the Spanish Steps — Timed on purpose: Aug 24 is a Monday, when Roman shops open late — most from 3:30 or 4pm until 7:30–8pm. Via del Corso is the chain high street, running from Piazza Venezia to Piazza del Popolo. Via dei Condotti at the top is the luxury row. Small independents may still be shut for the August break; the chains are not.</t>
+    <t>Shopping: Via del Corso up to the Spanish Steps — Aug 24 is a Monday, when Roman shops open late — most from 3:30 or 4pm until 7:30–8pm. Via del Corso is the chain high street, Piazza Venezia up to Piazza del Popolo; Via dei Condotti at the top is the luxury row. Small independents may still be shut for August, the chains not.</t>
   </si>
   <si>
     <t>Walk, ~10 min from Trevi</t>
@@ -235,7 +235,7 @@
     <t>8:00am</t>
   </si>
   <si>
-    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Booked and paid, €90 for two. English, with earphones. Both names are on the ticket and ID is checked at the door, so carry it. Show the voucher to Customer Care outside the Viale Vaticano entrance 30 minutes before. After security, take the stairs at the far left of the entrance hall to the Guided Tours desk for tickets and coupons, then to the meeting point for earphones. Entrance is Passageway 2. Not changeable, not refundable. St Peter's is not included — ask your guide whether this tour uses the shortcut from the Sistine Chapel.</t>
+    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Booked and paid, €90 for two: guided tour in English with earphones, entrance at Passageway 2. Show the voucher to Customer Care outside the Viale Vaticano entrance 30 minutes before, then collect tickets up the stairs at the far left of the hall, at the Guided Tours desk. Carry ID — both names are checked, it cannot be changed or refunded, and St Peter's is not included.</t>
   </si>
   <si>
     <t>Taxi, ~15 min</t>
@@ -301,7 +301,7 @@
     <t>8:45am</t>
   </si>
   <si>
-    <t>Baths of Caracalla — Go first, while it is quiet. Brick vaults at full height, huge bathing halls, patches of the original mosaic floor. Far emptier than anything else in ancient Rome at this hour.</t>
+    <t>Baths of Caracalla — Go first, while it is quiet — far emptier than anything else in ancient Rome at this hour. Brick vaults at full height, huge bathing halls, patches of the original mosaic floor.</t>
   </si>
   <si>
     <t>10:30am</t>
@@ -316,7 +316,7 @@
     <t>11:30am</t>
   </si>
   <si>
-    <t>Quick lunch in Monti — It has to be quick: the Borghese meeting point is a fifteen-minute taxi away and will not hold. Eat by 12:10 and you have a buffer. Roscioli had this slot but wants two unhurried hours — give it another lunch rather than rush it.</t>
+    <t>Quick lunch in Monti — Quick by necessity: the Borghese meeting point is a fifteen-minute taxi away and will not hold, so eat by 12:10. Roscioli had this slot but wants two unhurried hours. Give it another lunch rather than rush it.</t>
   </si>
   <si>
     <t>Walk, ~8 min</t>
@@ -325,7 +325,7 @@
     <t>12:45pm</t>
   </si>
   <si>
-    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Booked: skip-the-line entry for two, digital audioguide in English, two hours. Meet the host at the Fontana dei Mascheroni on Viale del Museo Borghese, in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone. No large bags inside; the cloakroom is free. Bernini's Apollo and Daphne and the Rape of Proserpina, plus six Caravaggios. You are let in and out on the clock.</t>
+    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Booked: skip-the-line entry for two, English audioguide, two hours on the clock. Meet the host at the Fontana dei Mascheroni in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone; no large bags inside, but the cloakroom is free.</t>
   </si>
   <si>
     <t>Gallery -&gt;</t>
@@ -391,7 +391,7 @@
     <t>12:10pm</t>
   </si>
   <si>
-    <t>Frecciarossa 9420 to Florence — Booked. Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
+    <t>Frecciarossa 9420 to Florence — Booked: Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
   </si>
   <si>
     <t>High-speed rail, 2h01</t>
@@ -409,7 +409,7 @@
     <t>2:25pm</t>
   </si>
   <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms from 2:00pm; they will hold luggage until then. Checkout the 29th at noon. Room-only rate, so breakfast is on you both mornings.</t>
+    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms from 2:00pm, and they will hold luggage until then. Checkout the 29th at noon, room-only, so breakfast is on you.</t>
   </si>
   <si>
     <t>Taxi, ~8 min</t>
@@ -427,7 +427,7 @@
     <t>4:30pm</t>
   </si>
   <si>
-    <t>Climb Brunelleschi's dome — 4:30pm sharp — Booked: two Brunelleschi Passes, dome entry at the Porta della Mandorla. 463 steps, no lift. The slot cannot be changed and names are checked against ID, so be there by 4:15. The pass also covers the Bell Tower, Baptistery, museum and Santa Reparata crypt and runs through 29 August — which is why the museum sits on tomorrow.</t>
+    <t>Climb Brunelleschi's dome — 4:30pm sharp — Booked: two Brunelleschi Passes, dome entry at the Porta della Mandorla — 463 steps, no lift. The slot cannot be changed and names are checked against ID, so be there by 4:15. The pass also covers the Bell Tower, Baptistery, museum and crypt through 29 August.</t>
   </si>
   <si>
     <t>Duomo -&gt;</t>
@@ -460,7 +460,7 @@
     <t>8:15am</t>
   </si>
   <si>
-    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced and unshaded, and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
+    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced, unshaded and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
   </si>
   <si>
     <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs from the palace gates to the bridge. Stop halfway.</t>
@@ -475,7 +475,7 @@
     <t>Cross Ponte Vecchio, ~6 min</t>
   </si>
   <si>
-    <t>Late lunch — 'Ino — Two hours from 12:15 puts you out at 2:30, which is when Oltrarno kitchens stop serving — so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
+    <t>Late lunch — 'Ino — The Uffizi puts you out at 2:30, when Oltrarno kitchens stop serving, so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
   </si>
   <si>
     <t>Walk, ~2 min</t>
@@ -484,13 +484,13 @@
     <t>4:00pm</t>
   </si>
   <si>
-    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, then Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free. Moved here from Thursday evening, which had no daylight for it.</t>
+    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free.</t>
   </si>
   <si>
     <t>5:15pm</t>
   </si>
   <si>
-    <t>Opera del Duomo museum — Already paid — Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà. Entrance is Piazza del Duomo 9.</t>
+    <t>Opera del Duomo museum — Already paid: Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà, at Piazza del Duomo 9.</t>
   </si>
   <si>
     <t>6:30pm</t>
@@ -526,7 +526,7 @@
     <t>9:00am</t>
   </si>
   <si>
-    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, just outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton — taxi with the luggage. Have the IDP and licence ready.</t>
+    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
   </si>
   <si>
     <t>9:30am</t>
@@ -571,7 +571,7 @@
     <t>Self-drive</t>
   </si>
   <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st — which is why Monday starts at eight.</t>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st.</t>
   </si>
   <si>
     <t>Book -&gt;</t>
@@ -613,7 +613,7 @@
     <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
   </si>
   <si>
-    <t>Horseback riding, lunch and a winery — San Gimignano Experience: about an hour in the saddle through vineyards, olive groves and woods, then a Tuscan lunch (antipasti, truffle lasagna, bread soup), a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed. Three to four hours; book ahead. Backup operator: CET Experience, cetexperience.it.</t>
+    <t>Horseback riding, lunch and a winery — An hour in the saddle through vineyards and olive groves, then a Tuscan lunch, a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; three to four hours, and book ahead. Backup operator: CET Experience, cetexperience.it.</t>
   </si>
   <si>
     <t>Meet at the Bivio Volterra bus stop</t>
@@ -652,7 +652,7 @@
     <t>1:14pm</t>
   </si>
   <si>
-    <t>Frecciarossa 9587 to Naples — Booked. Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+    <t>Frecciarossa 9587 to Naples — Booked: Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
   </si>
   <si>
     <t>High-speed rail, 3h09</t>
@@ -667,7 +667,7 @@
     <t>5:26pm</t>
   </si>
   <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. The tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning, room for a suitcase, €18pp. An hour's wait after the Frecciarossa, but it leaves from the same building — no crossing Naples with the bags.</t>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct, €18pp. The tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning, room for a suitcase. An hour's wait after the Frecciarossa, but it leaves from the same building.</t>
   </si>
   <si>
     <t>Campania Express, 1h09</t>
@@ -685,7 +685,7 @@
     <t>6:50pm</t>
   </si>
   <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to arrange the room move on the 4th while you are out at Amalfi.</t>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to move the room on the 4th while you are out at Amalfi.</t>
   </si>
   <si>
     <t>7:15pm</t>
@@ -808,7 +808,7 @@
     <t>Ferry, ~35 min</t>
   </si>
   <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, and the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in, so have the camera out before you dock.</t>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, under the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in, so have the camera out before you dock.</t>
   </si>
   <si>
     <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, and unpretentious despite the address. La Tagliata up in the hills is the alternative if you would rather climb.</t>
@@ -913,7 +913,7 @@
     <t>10:20am</t>
   </si>
   <si>
-    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next one leaves.</t>
+    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next leaves.</t>
   </si>
   <si>
     <t>Campania Express, 1h14</t>
@@ -928,7 +928,7 @@
     <t>11:55am</t>
   </si>
   <si>
-    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city — Di Matteo and Sorbillo are both about twenty minutes up Via dei Tribunali. Naples came out of the itinerary altogether and this is the one window it gets back. If you would rather not risk it, there is good pizza in sight of the station.</t>
+    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city — Di Matteo and Sorbillo are twenty minutes up Via dei Tribunali. Naples came out of the itinerary altogether, and this is the one window it gets back. If you would rather not risk it, there is good pizza in sight of the station.</t>
   </si>
   <si>
     <t>Walk, ~20 min</t>
@@ -958,7 +958,7 @@
     <t>3:20pm</t>
   </si>
   <si>
-    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began. Superior Double. Nothing is prepaid — you settle €530 with the hotel.</t>
+    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began. Superior Double, and nothing is prepaid — you settle €530 with the hotel.</t>
   </si>
   <si>
     <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door, and the one corner of the centre you have not walked. Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -205,7 +205,7 @@
     <t>5:00pm</t>
   </si>
   <si>
-    <t>Shopping: Via del Corso up to the Spanish Steps — Aug 24 is a Monday, when Roman shops open late — most from 3:30 or 4pm until 7:30–8pm. Via del Corso is the chain high street, Piazza Venezia up to Piazza del Popolo; Via dei Condotti at the top is the luxury row. Small independents may still be shut for August, the chains not.</t>
+    <t>Shopping: Via del Corso up to the Spanish Steps — Via del Corso runs from Piazza Venezia to Piazza del Popolo; Via dei Condotti at the top is the luxury row. Monday hours, so shops open about 3:30–4pm and shut at 7:30–8pm. Small independents may still be closed for August.</t>
   </si>
   <si>
     <t>Walk, ~10 min from Trevi</t>
@@ -235,7 +235,7 @@
     <t>8:00am</t>
   </si>
   <si>
-    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Booked and paid, €90 for two: guided tour in English with earphones, entrance at Passageway 2. Show the voucher to Customer Care outside the Viale Vaticano entrance 30 minutes before, then collect tickets up the stairs at the far left of the hall, at the Guided Tours desk. Carry ID — both names are checked, it cannot be changed or refunded, and St Peter's is not included.</t>
+    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Show the voucher to Customer Care outside the Viale Vaticano entrance, 30 minutes before. After security, take the stairs at the far left of the hall to the Guided Tours desk for tickets, then on to the meeting point for earphones. Entrance is Passageway 2, and both names on the ticket are checked against ID.</t>
   </si>
   <si>
     <t>Taxi, ~15 min</t>
@@ -325,7 +325,7 @@
     <t>12:45pm</t>
   </si>
   <si>
-    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Booked: skip-the-line entry for two, English audioguide, two hours on the clock. Meet the host at the Fontana dei Mascheroni in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone; no large bags inside, but the cloakroom is free.</t>
+    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Meet the host at the Fontana dei Mascheroni, in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone. No large bags inside, but the cloakroom is free.</t>
   </si>
   <si>
     <t>Gallery -&gt;</t>
@@ -427,7 +427,7 @@
     <t>4:30pm</t>
   </si>
   <si>
-    <t>Climb Brunelleschi's dome — 4:30pm sharp — Booked: two Brunelleschi Passes, dome entry at the Porta della Mandorla — 463 steps, no lift. The slot cannot be changed and names are checked against ID, so be there by 4:15. The pass also covers the Bell Tower, Baptistery, museum and crypt through 29 August.</t>
+    <t>Climb Brunelleschi's dome — 4:30pm sharp — Entry is at the Porta della Mandorla — be there by 4:15 with ID, as the slot cannot be changed. 463 steps, no lift. The same pass covers the Bell Tower, Baptistery, museum and crypt through 29 August.</t>
   </si>
   <si>
     <t>Duomo -&gt;</t>
@@ -613,7 +613,7 @@
     <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
   </si>
   <si>
-    <t>Horseback riding, lunch and a winery — An hour in the saddle through vineyards and olive groves, then a Tuscan lunch, a cellar tour and tastings of Chianti Classico, Vernaccia and Super Tuscans. No riding experience needed; three to four hours, and book ahead. Backup operator: CET Experience, cetexperience.it.</t>
+    <t>Horseback riding, lunch and a winery — Meets at the Bivio Volterra bus stop, 11am to 3pm. An hour in the saddle, then lunch, a cellar tour and tastings. No riding experience needed; backup operator is CET Experience, cetexperience.it.</t>
   </si>
   <si>
     <t>Meet at the Bivio Volterra bus stop</t>
@@ -667,7 +667,7 @@
     <t>5:26pm</t>
   </si>
   <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct, €18pp. The tourist service, not the ordinary Circumvesuviana: reserved seats, air conditioning, room for a suitcase. An hour's wait after the Frecciarossa, but it leaves from the same building.</t>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. Platforms are downstairs from the Frecciarossa, signed EAV — no crossing Naples with the bags. Reserved seats, air conditioning and room for a suitcase.</t>
   </si>
   <si>
     <t>Campania Express, 1h09</t>
@@ -913,7 +913,7 @@
     <t>10:20am</t>
   </si>
   <si>
-    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct, €18pp. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next leaves.</t>
+    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next leaves.</t>
   </si>
   <si>
     <t>Campania Express, 1h14</t>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="510">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -409,7 +409,7 @@
     <t>2:25pm</t>
   </si>
   <si>
-    <t>Drop bags — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms from 2:00pm, and they will hold luggage until then. Checkout the 29th at noon, room-only, so breakfast is on you.</t>
+    <t>Check in — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms are ready from 2:00pm, so check in properly now rather than dropping bags and coming back for them. Checkout the 29th at noon, room-only, so breakfast is on you.</t>
   </si>
   <si>
     <t>Taxi, ~8 min</t>
@@ -418,7 +418,7 @@
     <t>Hotel site -&gt;</t>
   </si>
   <si>
-    <t>Accademia — David at the afternoon slot — Book the 3:00pm entry; the train lands at 2:11pm. Forty-five minutes is enough — go straight down the hall of the Prisoners.</t>
+    <t>Accademia — David, if the day allows — Optional, and the first thing to drop if the train runs late. Book the 3:00pm entry anyway, and be walking out by 4:15 or you are gambling with the dome. Forty-five minutes is enough — go straight down the hall of the Prisoners.</t>
   </si>
   <si>
     <t>Walk, ~6 min</t>
@@ -433,306 +433,309 @@
     <t>Duomo -&gt;</t>
   </si>
   <si>
+    <t>6:15pm</t>
+  </si>
+  <si>
+    <t>Back to the room to change — You checked in on arrival, so this is only a shower and a change before dinner. You will want it after 463 steps.</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is about 8:00pm and the hill is where to watch it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a few window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced, unshaded and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs from the palace gates to the bridge. Stop halfway.</t>
+  </si>
+  <si>
+    <t>12:15pm</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. About two hours with a guide.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Vecchio, ~6 min</t>
+  </si>
+  <si>
+    <t>Late lunch — 'Ino — The Uffizi puts you out at 2:30, when Oltrarno kitchens stop serving, so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
+  </si>
+  <si>
+    <t>Walk, ~2 min</t>
+  </si>
+  <si>
+    <t>4:00pm</t>
+  </si>
+  <si>
+    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free.</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Opera del Duomo museum — Already paid: Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà, at Piazza del Duomo 9.</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Fifteen minutes uphill from the centre — taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church, closer to the singers than an opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>Fiesole — Florence from the hill — Twenty-five minutes up for the view back over the city — roofs, river and dome from above. Go out along the viali to stay clear of the ZTL, and park at Piazza Mino.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~25 min</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Southwest to Certaldo — An hour and ten from Fiesole, against forty-five minutes driving straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~1h10</t>
+  </si>
+  <si>
+    <t>12:00pm</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace, a walled brick town. The funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>At the hotel</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand. Best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — Meets at the Bivio Volterra bus stop, 11am to 3pm. An hour in the saddle, then lunch, a cellar tour and tastings. No riding experience needed; backup operator is CET Experience, cetexperience.it.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so there is no need for a dawn start.</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Lunch by the station before the train — The later train buys an unhurried hour, and the next real meal is dinner in Sorrento</t>
+  </si>
+  <si>
+    <t>1:14pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9587 to Naples — Booked: Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 3h09</t>
+  </si>
+  <si>
+    <t>4:23pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
+  </si>
+  <si>
+    <t>5:26pm</t>
+  </si>
+  <si>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. Platforms are downstairs from the Frecciarossa, signed EAV — no crossing Naples with the bags. Reserved seats, air conditioning and room for a suitcase.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h09</t>
+  </si>
+  <si>
+    <t>EAV -&gt;</t>
+  </si>
+  <si>
+    <t>6:35pm</t>
+  </si>
+  <si>
+    <t>Arrive Sorrento station — The hotel is 480m away, six minutes on the flat. That is why this beats the ferry — Marina Piccola is the same distance uphill</t>
+  </si>
+  <si>
+    <t>6:50pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to move the room on the 4th while you are out at Amalfi.</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room — the easiest first night after three legs. Book before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees — the reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a fern-covered ruined mill in a gorge in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of town, free to walk through, with limoncello made on site</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Fibre in the rooms. The garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
     <t>6:00pm</t>
   </si>
   <si>
-    <t>Check in properly and change — Rooms open at 2:00pm, so this is a real stop, not a wait — and you will want it after 463 steps</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is about 8:00pm and the hill is where to watch it. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a few window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced, unshaded and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs from the palace gates to the bridge. Stop halfway.</t>
-  </si>
-  <si>
-    <t>12:15pm</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. About two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Vecchio, ~6 min</t>
-  </si>
-  <si>
-    <t>Late lunch — 'Ino — The Uffizi puts you out at 2:30, when Oltrarno kitchens stop serving, so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
-  </si>
-  <si>
-    <t>Walk, ~2 min</t>
-  </si>
-  <si>
-    <t>4:00pm</t>
-  </si>
-  <si>
-    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free.</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Opera del Duomo museum — Already paid: Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà, at Piazza del Duomo 9.</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Fifteen minutes uphill from the centre — taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church, closer to the singers than an opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>Fiesole — Florence from the hill — Twenty-five minutes up for the view back over the city — roofs, river and dome from above. Go out along the viali to stay clear of the ZTL, and park at Piazza Mino.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~25 min</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Southwest to Certaldo — An hour and ten from Fiesole, against forty-five minutes driving straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~1h10</t>
-  </si>
-  <si>
-    <t>12:00pm</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace, a walled brick town. The funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>At the hotel</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand. Best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — Meets at the Bivio Volterra bus stop, 11am to 3pm. An hour in the saddle, then lunch, a cellar tour and tastings. No riding experience needed; backup operator is CET Experience, cetexperience.it.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so there is no need for a dawn start.</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Lunch by the station before the train — The later train buys an unhurried hour, and the next real meal is dinner in Sorrento</t>
-  </si>
-  <si>
-    <t>1:14pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9587 to Naples — Booked: Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 3h09</t>
-  </si>
-  <si>
-    <t>4:23pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
-  </si>
-  <si>
-    <t>5:26pm</t>
-  </si>
-  <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. Platforms are downstairs from the Frecciarossa, signed EAV — no crossing Naples with the bags. Reserved seats, air conditioning and room for a suitcase.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h09</t>
-  </si>
-  <si>
-    <t>EAV -&gt;</t>
-  </si>
-  <si>
-    <t>6:35pm</t>
-  </si>
-  <si>
-    <t>Arrive Sorrento station — The hotel is 480m away, six minutes on the flat. That is why this beats the ferry — Marina Piccola is the same distance uphill</t>
-  </si>
-  <si>
-    <t>6:50pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to move the room on the 4th while you are out at Amalfi.</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>8:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room — the easiest first night after three legs. Book before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees — the reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a fern-covered ruined mill in a gorge in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of town, free to walk through, with limoncello made on site</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Fibre in the rooms. The garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
     <t>The pool, or the Thala Spa — No lift down to the water here. The hotel works with a beach club at the marina — ask the desk to book it the night before</t>
   </si>
   <si>
@@ -1294,10 +1297,10 @@
     <t>Two problems in one. The old reservation is still FCO Aug 24 → FCO Sep 6, so left alone it bills you for a fortnight's hire you will not take. And the car you do need — Borgo Ognissanti, Florence, Aug 29 to Aug 31 — is not booked at all. Re-quote before cancelling; the old €1,087.81 was a fourteen-day FCO round trip and will not carry over.</t>
   </si>
   <si>
-    <t>Accademia (Aug 27), then Pitti and the Uffizi (Aug 28)</t>
-  </si>
-  <si>
-    <t>Two Florence days means no second chance at any of them. The Accademia is the 3:00pm slot on arrival day, once the train is in — and it has to be out by 4:15pm, because the dome slot behind it cannot move. The next day opens at Pitti — book the 8:15am opening, which is what gets Boboli done before the heat — and the Uffizi is guided at 12:15pm, after the walk down from the palace.</t>
+    <t>Pitti and the Uffizi (Aug 28), and the Accademia (Aug 27) if you want it</t>
+  </si>
+  <si>
+    <t>Pitti and the Uffizi are the two with no second chance, so book those first: the 8:15am Pitti opening is what gets Boboli done before the heat, and the Uffizi is guided at 12:15pm after the walk down from the palace. The Accademia is now optional — it sits between a train that can be late and a 4:30pm dome slot that cannot move, and has to be out by 4:15pm. Book it anyway if you want the shot at David; at about €16 each it is cheap to write off.</t>
   </si>
   <si>
     <t>Horseback riding, lunch &amp; winery — San Gimignano, Aug 30</t>
@@ -3870,10 +3873,10 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E94" s="13" t="s">
         <v>189</v>
@@ -3893,7 +3896,7 @@
         <v>65</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E95" s="13" t="s">
         <v>134</v>
@@ -3907,10 +3910,10 @@
         <v>10</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,10 +3927,10 @@
         <v>71</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F98" t="s">
         <v>48</v>
@@ -3941,16 +3944,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3964,10 +3967,10 @@
         <v>205</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F100" t="s">
         <v>48</v>
@@ -3984,10 +3987,10 @@
         <v>179</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>68</v>
@@ -4004,7 +4007,7 @@
         <v>78</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>60</v>
@@ -4021,13 +4024,13 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -4044,7 +4047,7 @@
         <v>156</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>189</v>
@@ -4064,10 +4067,10 @@
         <v>225</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>68</v>
@@ -4078,10 +4081,10 @@
         <v>11</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,7 +4098,7 @@
         <v>231</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>189</v>
@@ -4115,13 +4118,13 @@
         <v>195</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4135,7 +4138,7 @@
         <v>121</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>57</v>
@@ -4155,7 +4158,7 @@
         <v>179</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E111" s="13" t="s">
         <v>85</v>
@@ -4175,10 +4178,10 @@
         <v>55</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -4195,10 +4198,10 @@
         <v>58</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
@@ -4215,7 +4218,7 @@
         <v>154</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>189</v>
@@ -4235,10 +4238,10 @@
         <v>158</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F115" t="s">
         <v>48</v>
@@ -4255,10 +4258,10 @@
         <v>65</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>68</v>
@@ -4269,10 +4272,10 @@
         <v>12</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4286,7 +4289,7 @@
         <v>146</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>131</v>
@@ -4306,13 +4309,13 @@
         <v>93</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4326,10 +4329,10 @@
         <v>195</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -4346,7 +4349,7 @@
         <v>98</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>85</v>
@@ -4366,7 +4369,7 @@
         <v>101</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E123" s="13" t="s">
         <v>85</v>
@@ -4383,13 +4386,13 @@
         <v>48</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F124" t="s">
         <v>48</v>
@@ -4403,13 +4406,13 @@
         <v>48</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>83</v>
@@ -4423,10 +4426,10 @@
         <v>48</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E126" s="13" t="s">
         <v>85</v>
@@ -4446,10 +4449,10 @@
         <v>61</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F127" t="s">
         <v>48</v>
@@ -4466,7 +4469,7 @@
         <v>225</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E128" s="13" t="s">
         <v>100</v>
@@ -4480,10 +4483,10 @@
         <v>13</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F130" s="14" t="s">
         <v>120</v>
@@ -4500,7 +4503,7 @@
         <v>93</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E131" s="13" t="s">
         <v>189</v>
@@ -4517,10 +4520,10 @@
         <v>48</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E132" s="13" t="s">
         <v>189</v>
@@ -4537,13 +4540,13 @@
         <v>48</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>218</v>
@@ -4557,10 +4560,10 @@
         <v>48</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>57</v>
@@ -4577,16 +4580,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4597,13 +4600,13 @@
         <v>48</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>126</v>
@@ -4617,13 +4620,13 @@
         <v>48</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F137" t="s">
         <v>48</v>
@@ -4637,10 +4640,10 @@
         <v>48</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>57</v>
@@ -4657,10 +4660,10 @@
         <v>48</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E139" s="13" t="s">
         <v>134</v>
@@ -4680,7 +4683,7 @@
         <v>156</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E140" s="13" t="s">
         <v>106</v>
@@ -4697,13 +4700,13 @@
         <v>48</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F141" t="s">
         <v>48</v>
@@ -4720,10 +4723,10 @@
         <v>223</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F142" t="s">
         <v>48</v>
@@ -4740,7 +4743,7 @@
         <v>227</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E143" s="13" t="s">
         <v>73</v>
@@ -4754,10 +4757,10 @@
         <v>14</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4768,10 +4771,10 @@
         <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E146" s="13" t="s">
         <v>80</v>
@@ -4788,13 +4791,13 @@
         <v>48</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F147" t="s">
         <v>48</v>
@@ -4808,13 +4811,13 @@
         <v>48</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F148" t="s">
         <v>48</v>
@@ -4891,42 +4894,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -4944,18 +4947,18 @@
         <v>1588</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D3" t="s">
         <v>118</v>
@@ -4973,18 +4976,18 @@
         <v>692.83</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D4" t="s">
         <v>166</v>
@@ -5002,24 +5005,24 @@
         <v>2132</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D5" t="s">
         <v>203</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5031,24 +5034,24 @@
         <v>6363.12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5060,7 +5063,7 @@
         <v>658</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -5077,7 +5080,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F7" s="16">
         <v>13</v>
@@ -5114,24 +5117,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B2" s="15">
         <v>11433.95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5142,51 +5145,51 @@
         <v>1850</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="15">
         <v>2115</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B5" s="15">
         <v>2400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B6" s="15">
         <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B7" s="17">
         <v>18198.95</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5211,220 +5214,220 @@
         <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="D3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>375</v>
-      </c>
-      <c r="B3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="D3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B5" t="s">
         <v>183</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B6" t="s">
         <v>183</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D12" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B13" t="s">
         <v>80</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5435,7 +5438,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5471,16 +5474,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>45</v>
@@ -5491,16 +5494,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5508,16 +5511,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>423</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5525,16 +5528,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5542,16 +5545,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5559,16 +5562,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5576,16 +5579,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>431</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5593,16 +5596,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5610,16 +5613,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5627,16 +5630,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5644,16 +5647,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5661,16 +5664,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5678,16 +5681,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>444</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5695,16 +5698,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5712,16 +5715,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5729,7 +5732,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,10 +5740,10 @@
         <v>48</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5748,10 +5751,10 @@
         <v>48</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,10 +5762,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,10 +5773,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5781,10 +5784,10 @@
         <v>48</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5792,10 +5795,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5806,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,10 +5817,10 @@
         <v>48</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5825,10 +5828,10 @@
         <v>48</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,10 +5839,10 @@
         <v>48</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -5880,158 +5883,158 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="E3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F3" t="s">
+        <v>485</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>487</v>
-      </c>
-      <c r="C3" t="s">
-        <v>488</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="E3" t="s">
-        <v>490</v>
-      </c>
-      <c r="F3" t="s">
-        <v>484</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6045,7 +6048,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/italy-2026/dist/Italy 2026 (revised).xlsx
+++ b/italy-2026/dist/Italy 2026 (revised).xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="512">
   <si>
     <t>ITALY 2026 PLAN</t>
   </si>
@@ -178,16 +178,16 @@
     <t>12:35pm</t>
   </si>
   <si>
-    <t>Private driver to Hotel Trame — Pre-booked NCC, meeting you inside arrivals with a name board; licensed cars may enter the ZTL, so you are dropped at the door. Italy has no UberX — the app offers only Uber Black, dearer than a taxi. Use itTaxi or FreeNow for a metered cab.</t>
-  </si>
-  <si>
-    <t>Private transfer, ~45 min</t>
+    <t>Uber to Hotel Trame — Uber it is, but know what that means here: Italy has no UberX, so the app books Uber Black and it runs dearer than a cab. The official FCO flat rate into the centre is €55 from the rank straight outside arrivals, and itTaxi or FreeNow call the same metered cars. Either way licensed cars may enter the ZTL, so you are dropped at the hotel door rather than a street away.</t>
+  </si>
+  <si>
+    <t>Uber or taxi, ~45 min</t>
   </si>
   <si>
     <t>2:00pm</t>
   </si>
   <si>
-    <t>Check in at Hotel Trame — A former Franciscan monastery a few streets off Campo de' Fiori</t>
+    <t>Check in at Hotel Trame — A former Franciscan monastery two streets off Campo de' Fiori, cloister still in the middle, rooms ready from 2:00pm. Put the street address from the Trip.com confirmation into your phone before you fly — these lanes are hard to find by name and the driver will want it. Everything else today is walkable from the door.</t>
   </si>
   <si>
     <t>Arrive</t>
@@ -196,804 +196,810 @@
     <t>3:00pm</t>
   </si>
   <si>
-    <t>First walk: Piazza Navona → Pantheon → Trevi — Piazza Navona, then the Pantheon, Piazza di Montecitorio and the Trevi Fountain. About two hours at an easy pace, all of it flat.</t>
+    <t>Heart of Rome Walk (1–3 hours) — Rick Steves' route, in order: Campo de' Fiori, Piazza Navona, the Pantheon, Piazza di Montecitorio, then the Trevi Fountain. It starts two streets from the hotel and ends five minutes from the shops, so the whole afternoon chains together on foot with no taxi. Take it at whatever pace the jet lag allows — an hour if you march it, three if you stop.</t>
+  </si>
+  <si>
+    <t>On foot from the hotel</t>
+  </si>
+  <si>
+    <t>5:00pm</t>
+  </si>
+  <si>
+    <t>Shopping: Via del Corso up to the Spanish Steps — Via del Corso runs from Piazza Venezia to Piazza del Popolo; Via dei Condotti at the top is the luxury row. Monday hours, so shops open about 3:30–4pm and shut at 7:30–8pm. Small independents may still be closed for August.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min from Trevi</t>
+  </si>
+  <si>
+    <t>Map -&gt;</t>
+  </si>
+  <si>
+    <t>7:30pm</t>
+  </si>
+  <si>
+    <t>Dinner in — food carried back to Trame — No restaurant on night one: one of you walks out and brings dinner back. Emma, the Roscioli family's pizzeria, is four minutes away and will box it up; the alimentari on Campo de' Fiori are closer still. Twenty hours awake is the whole reason.</t>
+  </si>
+  <si>
+    <t>At the hotel</t>
+  </si>
+  <si>
+    <t>Tue, Aug 25</t>
+  </si>
+  <si>
+    <t>ROME — Vatican Gardens &amp; Museums</t>
+  </si>
+  <si>
+    <t>8:00am</t>
+  </si>
+  <si>
+    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Show the voucher to Customer Care outside the Viale Vaticano entrance, 30 minutes before. After security, take the stairs at the far left of the hall to the Guided Tours desk for tickets, then on to the meeting point for earphones. Entrance is Passageway 2, and both names on the ticket are checked against ID.</t>
+  </si>
+  <si>
+    <t>Taxi, ~15 min</t>
+  </si>
+  <si>
+    <t>Vatican Museums -&gt;</t>
+  </si>
+  <si>
+    <t>12:30pm</t>
+  </si>
+  <si>
+    <t>Quick lunch in Borgo — Borgo Pio is the pedestrian lane between the Vatican walls and the castle, which is exactly where you need to be next. Anywhere with a free table will do — this is a stop, not an occasion.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min from the museum exit</t>
+  </si>
+  <si>
+    <t>Castel Sant'Angelo, then Ponte Sant'Angelo — Ten minutes from where you just ate, which is the point — the old plan sent you back to the hotel at half two and out again at five, crossing the city twice to reach somewhere you were already standing next to. Spiral ramp up to the roof terrace for the view back over St Peter's. Bernini's angels are on the bridge as you leave.</t>
+  </si>
+  <si>
+    <t>Walk, ~10 min</t>
+  </si>
+  <si>
+    <t>Tickets -&gt;</t>
+  </si>
+  <si>
+    <t>3:45pm</t>
+  </si>
+  <si>
+    <t>Back east on foot through the centro storico — Cross the river and walk home the long way — Via dei Coronari, Piazza Navona, whatever you missed yesterday. Half an hour direct, or all afternoon if you graze. It lands you near the hotel with time to change.</t>
+  </si>
+  <si>
+    <t>On foot, ~30 min</t>
+  </si>
+  <si>
+    <t>7:00pm</t>
+  </si>
+  <si>
+    <t>Rooftop aperitivo near Campo de' Fiori — Anywhere with a roof and a spritz — you are eating properly after the opera, so this is a drink and not a meal.</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>8:30pm</t>
+  </si>
+  <si>
+    <t>OPERA — arias at All Saints' Anglican Church — Via del Babuino, off Piazza di Spagna. The Aug 25 programme is still unconfirmed and nothing is booked — that is now top of the booking list, not a maybe.</t>
+  </si>
+  <si>
+    <t>10:00pm</t>
+  </si>
+  <si>
+    <t>Late dinner — Pierluigi — Seafood on Piazza de' Ricci, at a properly Roman hour. Six minutes from the hotel. The least fixed thing on the day — swap it for anywhere still serving if you would rather.</t>
+  </si>
+  <si>
+    <t>Walk, 6 min</t>
+  </si>
+  <si>
+    <t>Reserve -&gt;</t>
+  </si>
+  <si>
+    <t>Wed, Aug 26</t>
+  </si>
+  <si>
+    <t>ROME — Caracalla &amp; the Galleria Borghese</t>
+  </si>
+  <si>
+    <t>8:45am</t>
+  </si>
+  <si>
+    <t>Baths of Caracalla — Go first, while it is quiet — far emptier than anything else in ancient Rome at this hour. Brick vaults at full height, huge bathing halls, patches of the original mosaic floor.</t>
+  </si>
+  <si>
+    <t>10:30am</t>
+  </si>
+  <si>
+    <t>The Colosseum from outside, and the Arch of Constantine — The outside circuit from the Via dei Fori Imperiali side, then the Arch of Constantine. No interior ticket, so nothing to book and no queue.</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min from Caracalla</t>
+  </si>
+  <si>
+    <t>11:30am</t>
+  </si>
+  <si>
+    <t>Quick lunch in Monti — Quick by necessity: the Borghese meeting point is a fifteen-minute taxi away and will not hold, so eat by 12:10. Roscioli had this slot but wants two unhurried hours. Give it another lunch rather than rush it.</t>
+  </si>
+  <si>
+    <t>Walk, ~8 min</t>
+  </si>
+  <si>
+    <t>12:45pm</t>
+  </si>
+  <si>
+    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Meet the host at the Fontana dei Mascheroni, in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone. No large bags inside, but the cloakroom is free.</t>
+  </si>
+  <si>
+    <t>Gallery -&gt;</t>
+  </si>
+  <si>
+    <t>3:15pm</t>
+  </si>
+  <si>
+    <t>Villa Borghese Gardens — Straight out of the gallery into the park. Shaded avenues, the Fontana dei Cavalli Marini, and a bench under the pines through the worst of the heat.</t>
+  </si>
+  <si>
+    <t>Walk, ~5 min</t>
+  </si>
+  <si>
+    <t>5:30pm</t>
+  </si>
+  <si>
+    <t>The Pincio terrace, in the low sun — The terrace over Piazza del Popolo, St. Peter's dome on the skyline. This is the Rome photo session, timed for the low sun through the trees.</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min across the park</t>
+  </si>
+  <si>
+    <t>Info -&gt;</t>
+  </si>
+  <si>
+    <t>6:45pm</t>
+  </si>
+  <si>
+    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
+  </si>
+  <si>
+    <t>Walk down, ~10 min</t>
+  </si>
+  <si>
+    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
+  </si>
+  <si>
+    <t>9:00pm</t>
+  </si>
+  <si>
+    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
+  </si>
+  <si>
+    <t>Walk, ~12 min</t>
+  </si>
+  <si>
+    <t>Thu, Aug 27</t>
+  </si>
+  <si>
+    <t>ROME → FLORENCE — direct by Frecciarossa</t>
+  </si>
+  <si>
+    <t>TRAVEL DAY</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven and Termini is fifteen minutes away. No need to be up early — have a last coffee on the piazza.</t>
+  </si>
+  <si>
+    <t>12:10pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9420 to Florence — Booked: Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 2h01</t>
+  </si>
+  <si>
+    <t>Trenitalia -&gt;</t>
+  </si>
+  <si>
+    <t>2:11pm</t>
+  </si>
+  <si>
+    <t>Arrive Firenze S.M.N.</t>
+  </si>
+  <si>
+    <t>2:25pm</t>
+  </si>
+  <si>
+    <t>Check in — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms are ready from 2:00pm, so check in properly now rather than dropping bags and coming back for them. Checkout the 29th at noon, room-only, so breakfast is on you.</t>
+  </si>
+  <si>
+    <t>Taxi, ~8 min</t>
+  </si>
+  <si>
+    <t>Hotel site -&gt;</t>
+  </si>
+  <si>
+    <t>Accademia — David, if the day allows — Optional, and the first thing to drop if the train runs late. Book the 3:00pm entry anyway, and be walking out by 4:15 or you are gambling with the dome. Forty-five minutes is enough — go straight down the hall of the Prisoners.</t>
+  </si>
+  <si>
+    <t>Walk, ~6 min</t>
+  </si>
+  <si>
+    <t>4:30pm</t>
+  </si>
+  <si>
+    <t>Climb Brunelleschi's dome — 4:30pm sharp — Entry is at the Porta della Mandorla — be there by 4:15 with ID, as the slot cannot be changed. 463 steps, no lift. The same pass covers the Bell Tower, Baptistery, museum and crypt through 29 August.</t>
+  </si>
+  <si>
+    <t>Duomo -&gt;</t>
+  </si>
+  <si>
+    <t>6:15pm</t>
+  </si>
+  <si>
+    <t>Back to the room to change — You checked in on arrival, so this is only a shower and a change before dinner. You will want it after 463 steps.</t>
+  </si>
+  <si>
+    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is about 8:00pm and the hill is where to watch it. Taxi up, walk down through the rose garden.</t>
+  </si>
+  <si>
+    <t>Taxi up, ~10 min</t>
+  </si>
+  <si>
+    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a few window tables. Ask for one.</t>
+  </si>
+  <si>
+    <t>Walk down, ~15 min</t>
+  </si>
+  <si>
+    <t>Fri, Aug 28</t>
+  </si>
+  <si>
+    <t>FLORENCE — the full day</t>
+  </si>
+  <si>
+    <t>8:15am</t>
+  </si>
+  <si>
+    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced, unshaded and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
+  </si>
+  <si>
+    <t>Taxi, ~10 min</t>
+  </si>
+  <si>
+    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs from the palace gates to the bridge. Stop halfway.</t>
+  </si>
+  <si>
+    <t>12:15pm</t>
+  </si>
+  <si>
+    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. About two hours with a guide.</t>
+  </si>
+  <si>
+    <t>Cross Ponte Vecchio, ~6 min</t>
+  </si>
+  <si>
+    <t>2:30pm</t>
+  </si>
+  <si>
+    <t>Late lunch — 'Ino — The Uffizi puts you out at 2:30, when Oltrarno kitchens stop serving, so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
+  </si>
+  <si>
+    <t>Walk, ~2 min</t>
+  </si>
+  <si>
+    <t>4:00pm</t>
+  </si>
+  <si>
+    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free.</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>Opera del Duomo museum — Already paid: Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà, at Piazza del Duomo 9.</t>
+  </si>
+  <si>
+    <t>6:30pm</t>
+  </si>
+  <si>
+    <t>Back to the hotel to change — Fifteen minutes uphill from the centre — taxi if the day has run long</t>
+  </si>
+  <si>
+    <t>Walk, ~15 min</t>
+  </si>
+  <si>
+    <t>8:00pm</t>
+  </si>
+  <si>
+    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church, closer to the singers than an opera house puts you.</t>
+  </si>
+  <si>
+    <t>9:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
+  </si>
+  <si>
+    <t>Sat, Aug 29</t>
+  </si>
+  <si>
+    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>Fiesole — Florence from the hill — Twenty-five minutes up for the view back over the city — roofs, river and dome from above. Go out along the viali to stay clear of the ZTL, and park at Piazza Mino.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~25 min</t>
+  </si>
+  <si>
+    <t>10:45am</t>
+  </si>
+  <si>
+    <t>Southwest to Certaldo — An hour and ten from Fiesole, against forty-five minutes driving straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
+  </si>
+  <si>
+    <t>Self-drive, ~1h10</t>
+  </si>
+  <si>
+    <t>12:00pm</t>
+  </si>
+  <si>
+    <t>Certaldo Alto, by funicular — Boccaccio's birthplace, a walled brick town. The funicular climbs from Piazza Boccaccio in under two minutes</t>
+  </si>
+  <si>
+    <t>Arrive Certaldo</t>
+  </si>
+  <si>
+    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
+  </si>
+  <si>
+    <t>1:00pm</t>
+  </si>
+  <si>
+    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
+  </si>
+  <si>
+    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
+  </si>
+  <si>
+    <t>Self-drive</t>
+  </si>
+  <si>
+    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st.</t>
+  </si>
+  <si>
+    <t>Book -&gt;</t>
+  </si>
+  <si>
+    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
   </si>
   <si>
     <t>On foot</t>
   </si>
   <si>
-    <t>5:00pm</t>
-  </si>
-  <si>
-    <t>Shopping: Via del Corso up to the Spanish Steps — Via del Corso runs from Piazza Venezia to Piazza del Popolo; Via dei Condotti at the top is the luxury row. Monday hours, so shops open about 3:30–4pm and shut at 7:30–8pm. Small independents may still be closed for August.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min from Trevi</t>
-  </si>
-  <si>
-    <t>Map -&gt;</t>
-  </si>
-  <si>
-    <t>7:30pm</t>
-  </si>
-  <si>
-    <t>Dinner — Emma Pizzeria con Cucina — The Roscioli family's pizzeria — the same burrata and cured meats as Roscioli itself, on thin Roman bases. Four minutes from the hotel, which matters after twenty hours awake. Book the 7:30 sitting; it fills.</t>
-  </si>
-  <si>
-    <t>Walk, 4 min</t>
-  </si>
-  <si>
-    <t>Reserve -&gt;</t>
-  </si>
-  <si>
-    <t>Tue, Aug 25</t>
-  </si>
-  <si>
-    <t>ROME — Vatican Gardens &amp; Museums</t>
-  </si>
-  <si>
-    <t>8:00am</t>
-  </si>
-  <si>
-    <t>Vatican Gardens and Museums — arrive 8:00am, tour at 8:30am — Show the voucher to Customer Care outside the Viale Vaticano entrance, 30 minutes before. After security, take the stairs at the far left of the hall to the Guided Tours desk for tickets, then on to the meeting point for earphones. Entrance is Passageway 2, and both names on the ticket are checked against ID.</t>
-  </si>
-  <si>
-    <t>Taxi, ~15 min</t>
-  </si>
-  <si>
-    <t>Vatican Museums -&gt;</t>
-  </si>
-  <si>
-    <t>1:00pm</t>
-  </si>
-  <si>
-    <t>Lunch — Da Romolo or Hostaria Dino e Tony — Unfussy Roman cooking a short walk from the museum exit</t>
-  </si>
-  <si>
-    <t>Walk from the Vatican</t>
-  </si>
-  <si>
-    <t>2:30pm</t>
-  </si>
-  <si>
-    <t>Back to the hotel through the heat — Late August in Rome peaks around 3pm. Don't fight it.</t>
+    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
+  </si>
+  <si>
+    <t>Sun, Aug 30</t>
+  </si>
+  <si>
+    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
+  </si>
+  <si>
+    <t>Drive to San Gimignano — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand. Best seen from Piazza della Cisterna</t>
+  </si>
+  <si>
+    <t>10:15am</t>
+  </si>
+  <si>
+    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
+  </si>
+  <si>
+    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
+  </si>
+  <si>
+    <t>Horseback riding, lunch and a winery — Meets at the Bivio Volterra bus stop, 11am to 3pm. An hour in the saddle, then lunch, a cellar tour and tastings. No riding experience needed; backup operator is CET Experience, cetexperience.it.</t>
+  </si>
+  <si>
+    <t>Meet at the Bivio Volterra bus stop</t>
+  </si>
+  <si>
+    <t>Back to Castelfalfi — About twenty-five minutes</t>
+  </si>
+  <si>
+    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
+  </si>
+  <si>
+    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
+  </si>
+  <si>
+    <t>Mon, Aug 31</t>
+  </si>
+  <si>
+    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
+  </si>
+  <si>
+    <t>9:15am</t>
+  </si>
+  <si>
+    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so there is no need for a dawn start.</t>
+  </si>
+  <si>
+    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
+  </si>
+  <si>
+    <t>Rental desk</t>
+  </si>
+  <si>
+    <t>Lunch by the station before the train — The later train buys an unhurried hour, and the next real meal is dinner in Sorrento</t>
+  </si>
+  <si>
+    <t>1:14pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9587 to Naples — Booked: Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 3h09</t>
+  </si>
+  <si>
+    <t>4:23pm</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
+  </si>
+  <si>
+    <t>5:26pm</t>
+  </si>
+  <si>
+    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. Platforms are downstairs from the Frecciarossa, signed EAV — no crossing Naples with the bags. Reserved seats, air conditioning and room for a suitcase.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h09</t>
+  </si>
+  <si>
+    <t>EAV -&gt;</t>
+  </si>
+  <si>
+    <t>6:35pm</t>
+  </si>
+  <si>
+    <t>Arrive Sorrento station — The hotel is 480m away, six minutes on the flat. That is why this beats the ferry — Marina Piccola is the same distance uphill</t>
+  </si>
+  <si>
+    <t>6:50pm</t>
+  </si>
+  <si>
+    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to move the room on the 4th while you are out at Amalfi.</t>
+  </si>
+  <si>
+    <t>7:15pm</t>
+  </si>
+  <si>
+    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
+  </si>
+  <si>
+    <t>7:45pm</t>
+  </si>
+  <si>
+    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room — the easiest first night after three legs. Book before you arrive.</t>
+  </si>
+  <si>
+    <t>Tue, Sep 1</t>
+  </si>
+  <si>
+    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
+  </si>
+  <si>
+    <t>8:30am</t>
+  </si>
+  <si>
+    <t>Breakfast in the garden — Under the lemon and orange trees — the reason people book this hotel</t>
+  </si>
+  <si>
+    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a fern-covered ruined mill in a gorge in the middle of town</t>
+  </si>
+  <si>
+    <t>Walk from the door</t>
+  </si>
+  <si>
+    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of town, free to walk through, with limoncello made on site</t>
+  </si>
+  <si>
+    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
+  </si>
+  <si>
+    <t>Desk hours — Fibre in the rooms. The garden terrace is the quiet spot if the room feels small by day three.</t>
+  </si>
+  <si>
+    <t>6:00pm</t>
+  </si>
+  <si>
+    <t>The pool, or the Thala Spa — No lift down to the water here. The hotel works with a beach club at the marina — ask the desk to book it the night before</t>
+  </si>
+  <si>
+    <t>Dinner — O'Parrucchiano La Favorita — Tables among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the door.</t>
+  </si>
+  <si>
+    <t>Wed, Sep 2</t>
+  </si>
+  <si>
+    <t>SORRENTO — Capri day trip</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Twenty minutes on foot, and the last stretch is steep. The public lift from the Villa Comunale gardens skips it, or take a taxi</t>
+  </si>
+  <si>
+    <t>Walk ~20 min, or taxi</t>
+  </si>
+  <si>
+    <t>8:40am</t>
+  </si>
+  <si>
+    <t>Fast ferry — Sorrento → Capri — About 25 minutes. Up to forty crossings a day in season, but they sell out at the counter in August — book online the night before.</t>
+  </si>
+  <si>
+    <t>Fast ferry, ~25 min</t>
+  </si>
+  <si>
+    <t>Timetable -&gt;</t>
+  </si>
+  <si>
+    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves, plus the Blue Grotto if the sea is calm enough. About two hours.</t>
+  </si>
+  <si>
+    <t>Local boat</t>
+  </si>
+  <si>
+    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
+  </si>
+  <si>
+    <t>Funicular, then taxi</t>
+  </si>
+  <si>
+    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
+  </si>
+  <si>
+    <t>4:15pm</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento — Check the last sailing when you land. Missing it means a night on the island</t>
+  </si>
+  <si>
+    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
+  </si>
+  <si>
+    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
+  </si>
+  <si>
+    <t>Walk, ~7 min</t>
+  </si>
+  <si>
+    <t>Thu, Sep 3</t>
+  </si>
+  <si>
+    <t>SORRENTO → POSITANO — by ferry, there and back</t>
+  </si>
+  <si>
+    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
+  </si>
+  <si>
+    <t>Ferry to Positano — About 35 minutes down the peninsula. Mid-April to mid-October only; book the day before in August.</t>
+  </si>
+  <si>
+    <t>Ferry, ~35 min</t>
+  </si>
+  <si>
+    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, under the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in, so have the camera out before you dock.</t>
+  </si>
+  <si>
+    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, and unpretentious despite the address. La Tagliata up in the hills is the alternative if you would rather climb.</t>
+  </si>
+  <si>
+    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — the town's real local industry</t>
+  </si>
+  <si>
+    <t>Uphill on foot</t>
+  </si>
+  <si>
+    <t>Ferry back to Sorrento</t>
+  </si>
+  <si>
+    <t>Desk hours</t>
+  </si>
+  <si>
+    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
+  </si>
+  <si>
+    <t>Walk, ~3 min</t>
+  </si>
+  <si>
+    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia. The seafood is better than the theme suggests</t>
+  </si>
+  <si>
+    <t>Fri, Sep 4</t>
+  </si>
+  <si>
+    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
+  </si>
+  <si>
+    <t>Down to Marina Piccola — Taxi this one. It is the earliest start of the five and the walk is twenty minutes downhill</t>
+  </si>
+  <si>
+    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Mid-April to mid-October only.</t>
+  </si>
+  <si>
+    <t>Ferry, ~1h15</t>
+  </si>
+  <si>
+    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea, up sixty-two steps, with a 13th-century cloister of Arab-Norman arches behind it</t>
+  </si>
+  <si>
+    <t>Walk from the marina</t>
+  </si>
+  <si>
+    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path. Amalfi made paper here for six hundred years and the ruined mills are still in the gorge</t>
+  </si>
+  <si>
+    <t>Lunch — Da Gemma — Just off Piazza Duomo, on a terrace above the street. The best table in Amalfi</t>
+  </si>
+  <si>
+    <t>2:15pm</t>
+  </si>
+  <si>
+    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
+  </si>
+  <si>
+    <t>Private driver</t>
+  </si>
+  <si>
+    <t>2:45pm</t>
+  </si>
+  <si>
+    <t>Villa Cimbrone — The Terrace of Infinity: a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
+  </si>
+  <si>
+    <t>On foot; Ravello is car-free</t>
+  </si>
+  <si>
+    <t>3:50pm</t>
+  </si>
+  <si>
+    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
+  </si>
+  <si>
+    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving at five puts you back at the hotel by 6:30pm.</t>
+  </si>
+  <si>
+    <t>Private driver, ~1h30</t>
+  </si>
+  <si>
+    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town. The last proper dinner on the coast</t>
+  </si>
+  <si>
+    <t>Sat, Sep 5</t>
+  </si>
+  <si>
+    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
+  </si>
+  <si>
+    <t>Last breakfast on the roof</t>
+  </si>
+  <si>
+    <t>9:45am</t>
+  </si>
+  <si>
+    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice. It buys the Naples stop below</t>
+  </si>
+  <si>
+    <t>10:20am</t>
+  </si>
+  <si>
+    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next leaves.</t>
+  </si>
+  <si>
+    <t>Campania Express, 1h14</t>
+  </si>
+  <si>
+    <t>11:34am</t>
+  </si>
+  <si>
+    <t>Arrive Napoli Centrale — Nearly two hours before the Frecciarossa, and the point of the early start</t>
+  </si>
+  <si>
+    <t>11:55am</t>
+  </si>
+  <si>
+    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city — Di Matteo and Sorbillo are twenty minutes up Via dei Tribunali. Naples came out of the itinerary altogether, and this is the one window it gets back. If you would rather not risk it, there is good pizza in sight of the station.</t>
+  </si>
+  <si>
+    <t>Walk, ~20 min</t>
+  </si>
+  <si>
+    <t>Find -&gt;</t>
+  </si>
+  <si>
+    <t>1:30pm</t>
+  </si>
+  <si>
+    <t>Frecciarossa 9544 to Rome — Booked. Napoli Centrale 13:30 → Roma Termini 14:55, Executive, coach 1.</t>
+  </si>
+  <si>
+    <t>High-speed rail, 1h25</t>
+  </si>
+  <si>
+    <t>2:55pm</t>
+  </si>
+  <si>
+    <t>Arrive Roma Termini; taxi to the hotel</t>
+  </si>
+  <si>
+    <t>Taxi, ~12 min</t>
+  </si>
+  <si>
+    <t>3:20pm</t>
+  </si>
+  <si>
+    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began. Superior Double, and nothing is prepaid — you settle €530 with the hotel.</t>
+  </si>
+  <si>
+    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door, and the one corner of the centre you have not walked. Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
+  </si>
+  <si>
+    <t>Tiber Island and the Ponte Fabricio — The bridge has carried people since 62 BC, still on the original stone</t>
+  </si>
+  <si>
+    <t>Trevi Fountain, one last time — Twenty minutes up through the centre. Worth the crowd on a last evening</t>
+  </si>
+  <si>
+    <t>Aperitivo on Campo de' Fiori — The market stalls are packed away by now and the square turns over to drinking</t>
+  </si>
+  <si>
+    <t>Walk, ~4 min</t>
+  </si>
+  <si>
+    <t>Farewell dinner — Aroma, at Palazzo Manfredi — Michelin-starred, on a rooftop looking straight into the Colosseum. Book early — only a dozen tables have the view.</t>
+  </si>
+  <si>
+    <t>Sun, Sep 6</t>
+  </si>
+  <si>
+    <t>DEPART — FCO → IAH</t>
+  </si>
+  <si>
+    <t>6:40am</t>
+  </si>
+  <si>
+    <t>Taxi to FCO — About thirty-five minutes on an empty Sunday road. No rental to return; that ended in Florence on Aug 31.</t>
   </si>
   <si>
     <t>Taxi</t>
   </si>
   <si>
-    <t>Castel Sant'Angelo, then the bridge at sunset — Bernini's angels on Ponte Sant'Angelo catch the last light</t>
-  </si>
-  <si>
-    <t>Taxi, ~10 min</t>
-  </si>
-  <si>
-    <t>Tickets -&gt;</t>
-  </si>
-  <si>
-    <t>Rooftop aperitivo near Campo de' Fiori</t>
-  </si>
-  <si>
-    <t>Walk</t>
-  </si>
-  <si>
-    <t>8:30pm</t>
-  </si>
-  <si>
-    <t>OPERA — arias at All Saints' Anglican Church — Confirm the Aug 25 programme; Via del Babuino, off Piazza di Spagna</t>
-  </si>
-  <si>
-    <t>10:00pm</t>
-  </si>
-  <si>
-    <t>Late dinner — Pierluigi — Seafood on Piazza de' Ricci; a properly Roman hour to eat</t>
-  </si>
-  <si>
-    <t>Walk, 6 min</t>
-  </si>
-  <si>
-    <t>Wed, Aug 26</t>
-  </si>
-  <si>
-    <t>ROME — Caracalla &amp; the Galleria Borghese</t>
-  </si>
-  <si>
-    <t>8:45am</t>
-  </si>
-  <si>
-    <t>Baths of Caracalla — Go first, while it is quiet — far emptier than anything else in ancient Rome at this hour. Brick vaults at full height, huge bathing halls, patches of the original mosaic floor.</t>
-  </si>
-  <si>
-    <t>10:30am</t>
-  </si>
-  <si>
-    <t>The Colosseum from outside, and the Arch of Constantine — The outside circuit from the Via dei Fori Imperiali side, then the Arch of Constantine. No interior ticket, so nothing to book and no queue.</t>
-  </si>
-  <si>
-    <t>Walk, ~20 min from Caracalla</t>
-  </si>
-  <si>
-    <t>11:30am</t>
-  </si>
-  <si>
-    <t>Quick lunch in Monti — Quick by necessity: the Borghese meeting point is a fifteen-minute taxi away and will not hold, so eat by 12:10. Roscioli had this slot but wants two unhurried hours. Give it another lunch rather than rush it.</t>
-  </si>
-  <si>
-    <t>Walk, ~8 min</t>
-  </si>
-  <si>
-    <t>12:45pm</t>
-  </si>
-  <si>
-    <t>Galleria Borghese — meet 12:45pm, entry at 1:00pm — Meet the host at the Fontana dei Mascheroni, in front of the gallery — purple Crown Tours shirt and a flag. Bring ID, your own headphones and a charged phone. No large bags inside, but the cloakroom is free.</t>
-  </si>
-  <si>
-    <t>Gallery -&gt;</t>
-  </si>
-  <si>
-    <t>3:15pm</t>
-  </si>
-  <si>
-    <t>Villa Borghese Gardens — Straight out of the gallery into the park. Shaded avenues, the Fontana dei Cavalli Marini, and a bench under the pines through the worst of the heat.</t>
-  </si>
-  <si>
-    <t>Walk, ~5 min</t>
-  </si>
-  <si>
-    <t>5:30pm</t>
-  </si>
-  <si>
-    <t>The Pincio terrace, in the low sun — The terrace over Piazza del Popolo, St. Peter's dome on the skyline. This is the Rome photo session, timed for the low sun through the trees.</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min across the park</t>
-  </si>
-  <si>
-    <t>Info -&gt;</t>
-  </si>
-  <si>
-    <t>6:45pm</t>
-  </si>
-  <si>
-    <t>Down to Piazza del Popolo — The twin churches and the obelisk, down the Pincio steps</t>
-  </si>
-  <si>
-    <t>Walk down, ~10 min</t>
-  </si>
-  <si>
-    <t>Trastevere on foot — Cross the Tiber and wander to Piazza Santa Maria in Trastevere</t>
-  </si>
-  <si>
-    <t>9:00pm</t>
-  </si>
-  <si>
-    <t>Dinner — Da Enzo al 29 — Trastevere, twelve tables, no reservations after 9pm</t>
-  </si>
-  <si>
-    <t>Walk, ~12 min</t>
-  </si>
-  <si>
-    <t>Thu, Aug 27</t>
-  </si>
-  <si>
-    <t>ROME → FLORENCE — direct by Frecciarossa</t>
-  </si>
-  <si>
-    <t>TRAVEL DAY</t>
-  </si>
-  <si>
-    <t>11:00am</t>
-  </si>
-  <si>
-    <t>Check out — Hotel Trame; taxi to Termini — Checkout is eleven and Termini is fifteen minutes away. No need to be up early — have a last coffee on the piazza.</t>
-  </si>
-  <si>
-    <t>12:10pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9420 to Florence — Booked: Roma Termini 12:10 → Firenze S.M.N. 14:11, Executive, coach 1. Base fare, so it can be changed any number of times before departure.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 2h01</t>
-  </si>
-  <si>
-    <t>Trenitalia -&gt;</t>
-  </si>
-  <si>
-    <t>2:11pm</t>
-  </si>
-  <si>
-    <t>Arrive Firenze S.M.N.</t>
-  </si>
-  <si>
-    <t>2:25pm</t>
-  </si>
-  <si>
-    <t>Check in — The Hoxton — Via delle Mantellate 2, up by San Marco — 1.3km from the platform, so take a taxi with the bags. Rooms are ready from 2:00pm, so check in properly now rather than dropping bags and coming back for them. Checkout the 29th at noon, room-only, so breakfast is on you.</t>
-  </si>
-  <si>
-    <t>Taxi, ~8 min</t>
-  </si>
-  <si>
-    <t>Hotel site -&gt;</t>
-  </si>
-  <si>
-    <t>Accademia — David, if the day allows — Optional, and the first thing to drop if the train runs late. Book the 3:00pm entry anyway, and be walking out by 4:15 or you are gambling with the dome. Forty-five minutes is enough — go straight down the hall of the Prisoners.</t>
-  </si>
-  <si>
-    <t>Walk, ~6 min</t>
-  </si>
-  <si>
-    <t>4:30pm</t>
-  </si>
-  <si>
-    <t>Climb Brunelleschi's dome — 4:30pm sharp — Entry is at the Porta della Mandorla — be there by 4:15 with ID, as the slot cannot be changed. 463 steps, no lift. The same pass covers the Bell Tower, Baptistery, museum and crypt through 29 August.</t>
-  </si>
-  <si>
-    <t>Duomo -&gt;</t>
-  </si>
-  <si>
-    <t>6:15pm</t>
-  </si>
-  <si>
-    <t>Back to the room to change — You checked in on arrival, so this is only a shower and a change before dinner. You will want it after 463 steps.</t>
-  </si>
-  <si>
-    <t>Ponte Vecchio, then up to Piazzale Michelangelo — Sunset is about 8:00pm and the hill is where to watch it. Taxi up, walk down through the rose garden.</t>
-  </si>
-  <si>
-    <t>Taxi up, ~10 min</t>
-  </si>
-  <si>
-    <t>Dinner — Borgo San Jacopo — Michelin-starred, on the river, with a few window tables. Ask for one.</t>
-  </si>
-  <si>
-    <t>Walk down, ~15 min</t>
-  </si>
-  <si>
-    <t>Fri, Aug 28</t>
-  </si>
-  <si>
-    <t>FLORENCE — the full day</t>
-  </si>
-  <si>
-    <t>8:15am</t>
-  </si>
-  <si>
-    <t>Pitti Palace and the Boboli Gardens — 8:15 is when the gates open, and that is the point — Boboli is terraced, unshaded and unwalkable by mid-afternoon. The Palatine Gallery is hung floor to ceiling in the old manner. Climb to the top of the gardens for the view back over the city.</t>
-  </si>
-  <si>
-    <t>Coffee on the way down to Ponte Vecchio — Via de' Guicciardini runs from the palace gates to the bridge. Stop halfway.</t>
-  </si>
-  <si>
-    <t>12:15pm</t>
-  </si>
-  <si>
-    <t>Uffizi, guided — Botticelli, Leonardo, the Caravaggio room. About two hours with a guide.</t>
-  </si>
-  <si>
-    <t>Cross Ponte Vecchio, ~6 min</t>
-  </si>
-  <si>
-    <t>Late lunch — 'Ino — The Uffizi puts you out at 2:30, when Oltrarno kitchens stop serving, so lunch is thirty seconds from the gallery door. Panini made to order, Tuscan wine by the glass, open through the afternoon. Il Santo Bevitore is the sit-down alternative if the tour runs short.</t>
-  </si>
-  <si>
-    <t>Walk, ~2 min</t>
-  </si>
-  <si>
-    <t>4:00pm</t>
-  </si>
-  <si>
-    <t>Reverse Renaissance Walk — The centre backwards: Casa di Dante, Orsanmichele, then Piazza della Signoria and the Loggia dei Lanzi — an open-air sculpture hall, free.</t>
-  </si>
-  <si>
-    <t>5:15pm</t>
-  </si>
-  <si>
-    <t>Opera del Duomo museum — Already paid: Thursday's Brunelleschi Pass runs to the 29th. Ghiberti's original Gates of Paradise and Michelangelo's late Pietà, at Piazza del Duomo 9.</t>
-  </si>
-  <si>
-    <t>6:30pm</t>
-  </si>
-  <si>
-    <t>Back to the hotel to change — Fifteen minutes uphill from the centre — taxi if the day has run long</t>
-  </si>
-  <si>
-    <t>Walk, ~15 min</t>
-  </si>
-  <si>
-    <t>8:00pm</t>
-  </si>
-  <si>
-    <t>OPERA — La Traviata at St. Mark's Anglican — Via Maggio, across Ponte Santa Trinita. A chamber staging in a small church, closer to the singers than an opera house puts you.</t>
-  </si>
-  <si>
-    <t>9:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Trattoria Sostanza — Cash only. The butter chicken and the tortino. Alternative: Buca dell'Orafo.</t>
-  </si>
-  <si>
-    <t>Walk, ~10 min</t>
-  </si>
-  <si>
-    <t>Sat, Aug 29</t>
-  </si>
-  <si>
-    <t>FLORENCE → TUSCANY — Il Castelfalfi</t>
-  </si>
-  <si>
-    <t>9:00am</t>
-  </si>
-  <si>
-    <t>Check out; collect the rental car — The agencies are on Borgo Ognissanti, outside the ZTL, so you never drive into the centro storico. Twenty minutes downhill from the Hoxton, so taxi with the luggage. Have the IDP and licence ready.</t>
-  </si>
-  <si>
-    <t>9:30am</t>
-  </si>
-  <si>
-    <t>Fiesole — Florence from the hill — Twenty-five minutes up for the view back over the city — roofs, river and dome from above. Go out along the viali to stay clear of the ZTL, and park at Piazza Mino.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~25 min</t>
-  </si>
-  <si>
-    <t>10:45am</t>
-  </si>
-  <si>
-    <t>Southwest to Certaldo — An hour and ten from Fiesole, against forty-five minutes driving straight out. That is what the view costs, and Certaldo still gets an hour before lunch.</t>
-  </si>
-  <si>
-    <t>Self-drive, ~1h10</t>
-  </si>
-  <si>
-    <t>12:00pm</t>
-  </si>
-  <si>
-    <t>Certaldo Alto, by funicular — Boccaccio's birthplace, a walled brick town. The funicular climbs from Piazza Boccaccio in under two minutes</t>
-  </si>
-  <si>
-    <t>Arrive Certaldo</t>
-  </si>
-  <si>
-    <t>12:30pm</t>
-  </si>
-  <si>
-    <t>Casa Boccaccio — The Decameron's author was born here; the house is now a small, quiet museum</t>
-  </si>
-  <si>
-    <t>Lunch on Via Boccaccio — A terrace table in the upper town before the drive on</t>
-  </si>
-  <si>
-    <t>On to Castelfalfi — About twenty-five minutes further into the Val d'Elsa</t>
-  </si>
-  <si>
-    <t>Self-drive</t>
-  </si>
-  <si>
-    <t>Check in — Il Castelfalfi — A restored 14th-century hamlet on a 2,700-acre estate, with its own castle. Deluxe Room with breakfast. Rooms from 3:00pm, checkout 11:00am on the 31st.</t>
-  </si>
-  <si>
-    <t>Book -&gt;</t>
-  </si>
-  <si>
-    <t>The hamlet on foot — The piazza, the castle walls, the little church — all restored, none of it roped off</t>
-  </si>
-  <si>
-    <t>7:00pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at Ecrù — The estate's cocktail bar</t>
-  </si>
-  <si>
-    <t>At the hotel</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room; the vegetables and olive oil are grown on the property</t>
-  </si>
-  <si>
-    <t>Sun, Aug 30</t>
-  </si>
-  <si>
-    <t>TUSCANY — San Gimignano and a horseback vineyard tour</t>
-  </si>
-  <si>
-    <t>Drive to San Gimignano — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>The towers of San Gimignano — Fourteen of the original seventy-two medieval towers still stand. Best seen from Piazza della Cisterna</t>
-  </si>
-  <si>
-    <t>10:15am</t>
-  </si>
-  <si>
-    <t>The Collegiata — Ghirlandaio and Gozzoli frescoes wall to wall in a church the size of a chapel</t>
-  </si>
-  <si>
-    <t>Gelato at Dondoli — A two-time world gelato champion on Piazza della Cisterna. Quick, before the horses</t>
-  </si>
-  <si>
-    <t>Horseback riding, lunch and a winery — Meets at the Bivio Volterra bus stop, 11am to 3pm. An hour in the saddle, then lunch, a cellar tour and tastings. No riding experience needed; backup operator is CET Experience, cetexperience.it.</t>
-  </si>
-  <si>
-    <t>Meet at the Bivio Volterra bus stop</t>
-  </si>
-  <si>
-    <t>Back to Castelfalfi — About twenty-five minutes</t>
-  </si>
-  <si>
-    <t>Pool or spa terrace — You've earned it after a day in the saddle</t>
-  </si>
-  <si>
-    <t>Dinner — La Via del Sale — The estate's fine-dining room, on your last Tuscan night</t>
-  </si>
-  <si>
-    <t>Mon, Aug 31</t>
-  </si>
-  <si>
-    <t>TUSCANY → SORRENTO — car back to Florence, rail to Naples, driver over the peninsula</t>
-  </si>
-  <si>
-    <t>9:15am</t>
-  </si>
-  <si>
-    <t>Check out; on the road — Back toward Florence, retracing Saturday's route. The booked train is the 1:14pm, so there is no need for a dawn start.</t>
-  </si>
-  <si>
-    <t>Drop off the rental car — Borgo Ognissanti — the two-day rental ends where it started</t>
-  </si>
-  <si>
-    <t>Rental desk</t>
-  </si>
-  <si>
-    <t>Lunch by the station before the train — The later train buys an unhurried hour, and the next real meal is dinner in Sorrento</t>
-  </si>
-  <si>
-    <t>1:14pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9587 to Naples — Booked: Firenze S.M.N. 13:14 → Napoli Centrale 16:23, direct via Rome, Executive, coach 1. The longest leg of the trip.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 3h09</t>
-  </si>
-  <si>
-    <t>4:23pm</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Stay in the building — the Circumvesuviana platforms are downstairs, signed EAV</t>
-  </si>
-  <si>
-    <t>5:26pm</t>
-  </si>
-  <si>
-    <t>Campania Express to Sorrento — EAV 17:26 → Sorrento 18:35, direct. Platforms are downstairs from the Frecciarossa, signed EAV — no crossing Naples with the bags. Reserved seats, air conditioning and room for a suitcase.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h09</t>
-  </si>
-  <si>
-    <t>EAV -&gt;</t>
-  </si>
-  <si>
-    <t>6:35pm</t>
-  </si>
-  <si>
-    <t>Arrive Sorrento station — The hotel is 480m away, six minutes on the flat. That is why this beats the ferry — Marina Piccola is the same distance uphill</t>
-  </si>
-  <si>
-    <t>6:50pm</t>
-  </si>
-  <si>
-    <t>Check in — Ara Maris Hotel &amp; Spa — Via Correale 15, a few minutes east of Piazza Tasso. Deluxe Sea View for the first four nights. Ask the desk to move the room on the 4th while you are out at Amalfi.</t>
-  </si>
-  <si>
-    <t>7:15pm</t>
-  </si>
-  <si>
-    <t>Unpack — this is home for five nights — The gardens and the elliptical pool can wait for tomorrow; tonight is just arriving</t>
-  </si>
-  <si>
-    <t>7:45pm</t>
-  </si>
-  <si>
-    <t>Aperitivo at the Lumi Sky Lounge — The hotel's rooftop bar — Vesuvius on the far shore, and it goes pink at sunset</t>
-  </si>
-  <si>
-    <t>8:45pm</t>
-  </si>
-  <si>
-    <t>Dinner — Cora Bistrot — The hotel's own Mediterranean room — the easiest first night after three legs. Book before you arrive.</t>
-  </si>
-  <si>
-    <t>Tue, Sep 1</t>
-  </si>
-  <si>
-    <t>SORRENTO — the town, the lemon groves, and the first desk day</t>
-  </si>
-  <si>
-    <t>8:30am</t>
-  </si>
-  <si>
-    <t>Breakfast in the garden — Under the lemon and orange trees — the reason people book this hotel</t>
-  </si>
-  <si>
-    <t>Sorrento on foot — Piazza Tasso, the shopfronts of Via San Cesareo, and the Vallone dei Mulini — a fern-covered ruined mill in a gorge in the middle of town</t>
-  </si>
-  <si>
-    <t>Walk from the door</t>
-  </si>
-  <si>
-    <t>I Giardini di Cataldo — A working lemon and orange grove in the centre of town, free to walk through, with limoncello made on site</t>
-  </si>
-  <si>
-    <t>Lunch at Marina Grande — Bagni Delfino — A wooden deck over the water in the old fishing village below town. Fritto misto and a carafe of white.</t>
-  </si>
-  <si>
-    <t>Desk hours — Fibre in the rooms. The garden terrace is the quiet spot if the room feels small by day three.</t>
-  </si>
-  <si>
-    <t>6:00pm</t>
-  </si>
-  <si>
-    <t>The pool, or the Thala Spa — No lift down to the water here. The hotel works with a beach club at the marina — ask the desk to book it the night before</t>
-  </si>
-  <si>
-    <t>Dinner — O'Parrucchiano La Favorita — Tables among the lemon trees of a 19th-century greenhouse. Cannelloni was invented in this kitchen, so order it. Six minutes from the door.</t>
-  </si>
-  <si>
-    <t>Wed, Sep 2</t>
-  </si>
-  <si>
-    <t>SORRENTO — Capri day trip</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Twenty minutes on foot, and the last stretch is steep. The public lift from the Villa Comunale gardens skips it, or take a taxi</t>
-  </si>
-  <si>
-    <t>Walk ~20 min, or taxi</t>
-  </si>
-  <si>
-    <t>8:40am</t>
-  </si>
-  <si>
-    <t>Fast ferry — Sorrento → Capri — About 25 minutes. Up to forty crossings a day in season, but they sell out at the counter in August — book online the night before.</t>
-  </si>
-  <si>
-    <t>Fast ferry, ~25 min</t>
-  </si>
-  <si>
-    <t>Timetable -&gt;</t>
-  </si>
-  <si>
-    <t>Round-the-island boat from Marina Grande — The Faraglioni, the grottoes and the swim coves, plus the Blue Grotto if the sea is calm enough. About two hours.</t>
-  </si>
-  <si>
-    <t>Local boat</t>
-  </si>
-  <si>
-    <t>Lunch — Da Paolino — Under the lemon trees. Il Riccio is the Michelin alternative, on the cliff by the grotto.</t>
-  </si>
-  <si>
-    <t>Funicular, then taxi</t>
-  </si>
-  <si>
-    <t>The Piazzetta and the Gardens of Augustus — Gelato on the terrace above Via Krupp, looking straight down at the Faraglioni</t>
-  </si>
-  <si>
-    <t>4:15pm</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento — Check the last sailing when you land. Missing it means a night on the island</t>
-  </si>
-  <si>
-    <t>Desk hours — Back at the hotel with the US afternoon still ahead</t>
-  </si>
-  <si>
-    <t>Dinner — Il Buco — Michelin-starred, in the wine cellar of an old monastery just off Piazza Tasso</t>
-  </si>
-  <si>
-    <t>Walk, ~7 min</t>
-  </si>
-  <si>
-    <t>Thu, Sep 3</t>
-  </si>
-  <si>
-    <t>SORRENTO → POSITANO — by ferry, there and back</t>
-  </si>
-  <si>
-    <t>Slow morning — swim and breakfast — No ticket, no departure to make until mid-morning</t>
-  </si>
-  <si>
-    <t>Ferry to Positano — About 35 minutes down the peninsula. Mid-April to mid-October only; book the day before in August.</t>
-  </si>
-  <si>
-    <t>Ferry, ~35 min</t>
-  </si>
-  <si>
-    <t>Positano from the water, then from the stairs — The pastel town stacked straight up from Spiaggia Grande, under the majolica dome of Santa Maria Assunta. The best picture is from the boat coming in, so have the camera out before you dock.</t>
-  </si>
-  <si>
-    <t>Lunch — Chez Black, on the beach — Right on Spiaggia Grande, and unpretentious despite the address. La Tagliata up in the hills is the alternative if you would rather climb.</t>
-  </si>
-  <si>
-    <t>Via Pasitea and the boutiques — Linen and sandals made to measure while you wait — the town's real local industry</t>
-  </si>
-  <si>
-    <t>Uphill on foot</t>
-  </si>
-  <si>
-    <t>Ferry back to Sorrento</t>
-  </si>
-  <si>
-    <t>Desk hours</t>
-  </si>
-  <si>
-    <t>Golden hour on the Villa Comunale terrace — A public balcony on the cliff edge, three minutes from the hotel, over the Bay of Naples. The light goes gold about an hour before the sun drops behind Ischia.</t>
-  </si>
-  <si>
-    <t>Walk, ~3 min</t>
-  </si>
-  <si>
-    <t>Dinner — Ristorante Museo Caruso — A block off Piazza Tasso, walls covered in Caruso memorabilia. The seafood is better than the theme suggests</t>
-  </si>
-  <si>
-    <t>Fri, Sep 4</t>
-  </si>
-  <si>
-    <t>SORRENTO → AMALFI &amp; RAVELLO — ferry down, driver up, driver home</t>
-  </si>
-  <si>
-    <t>Down to Marina Piccola — Taxi this one. It is the earliest start of the five and the walk is twenty minutes downhill</t>
-  </si>
-  <si>
-    <t>Ferry to Amalfi, via Positano — About 40 minutes direct, a little over an hour with the Positano call. Mid-April to mid-October only.</t>
-  </si>
-  <si>
-    <t>Ferry, ~1h15</t>
-  </si>
-  <si>
-    <t>Amalfi's Duomo and the Cloister of Paradise — The striped façade of Sant'Andrea, up sixty-two steps, with a 13th-century cloister of Arab-Norman arches behind it</t>
-  </si>
-  <si>
-    <t>Walk from the marina</t>
-  </si>
-  <si>
-    <t>The lemon lanes behind the piazza — Up the Valle dei Mulini path. Amalfi made paper here for six hundred years and the ruined mills are still in the gorge</t>
-  </si>
-  <si>
-    <t>Lunch — Da Gemma — Just off Piazza Duomo, on a terrace above the street. The best table in Amalfi</t>
-  </si>
-  <si>
-    <t>2:15pm</t>
-  </si>
-  <si>
-    <t>Private driver up to Ravello — Thirty minutes of switchbacks, a thousand feet straight up from the coast</t>
-  </si>
-  <si>
-    <t>Private driver</t>
-  </si>
-  <si>
-    <t>2:45pm</t>
-  </si>
-  <si>
-    <t>Villa Cimbrone — The Terrace of Infinity: a marble balustrade lined with busts, and a thousand-foot drop to the sea</t>
-  </si>
-  <si>
-    <t>On foot; Ravello is car-free</t>
-  </si>
-  <si>
-    <t>3:50pm</t>
-  </si>
-  <si>
-    <t>Villa Rufolo's gardens — Wagner's Klingsor garden, and the festival stage cantilevered out over the drop</t>
-  </si>
-  <si>
-    <t>Driver back to Sorrento — Over the pass rather than around the coast — about an hour and a half either way. Leaving at five puts you back at the hotel by 6:30pm.</t>
-  </si>
-  <si>
-    <t>Private driver, ~1h30</t>
-  </si>
-  <si>
-    <t>Dinner — L'Antica Trattoria — Under a pergola in the old town. The last proper dinner on the coast</t>
-  </si>
-  <si>
-    <t>Sat, Sep 5</t>
-  </si>
-  <si>
-    <t>SORRENTO → ROME — driver to Naples, then the Frecciarossa</t>
-  </si>
-  <si>
-    <t>Last breakfast on the roof</t>
-  </si>
-  <si>
-    <t>9:45am</t>
-  </si>
-  <si>
-    <t>Check out — Ara Maris — Checkout is 11:00am, so this is early by choice. It buys the Naples stop below</t>
-  </si>
-  <si>
-    <t>10:20am</t>
-  </si>
-  <si>
-    <t>Campania Express to Naples — Sorrento 10:20 → Napoli Piazza Garibaldi 11:34, direct. Piazza Garibaldi is Napoli Centrale, so you step off one train where the next leaves.</t>
-  </si>
-  <si>
-    <t>Campania Express, 1h14</t>
-  </si>
-  <si>
-    <t>11:34am</t>
-  </si>
-  <si>
-    <t>Arrive Napoli Centrale — Nearly two hours before the Frecciarossa, and the point of the early start</t>
-  </si>
-  <si>
-    <t>11:55am</t>
-  </si>
-  <si>
-    <t>Pizza in Naples — the thing the replan took away — Bags into the station deposit, then the old city — Di Matteo and Sorbillo are twenty minutes up Via dei Tribunali. Naples came out of the itinerary altogether, and this is the one window it gets back. If you would rather not risk it, there is good pizza in sight of the station.</t>
-  </si>
-  <si>
-    <t>Walk, ~20 min</t>
-  </si>
-  <si>
-    <t>Find -&gt;</t>
-  </si>
-  <si>
-    <t>1:30pm</t>
-  </si>
-  <si>
-    <t>Frecciarossa 9544 to Rome — Booked. Napoli Centrale 13:30 → Roma Termini 14:55, Executive, coach 1.</t>
-  </si>
-  <si>
-    <t>High-speed rail, 1h25</t>
-  </si>
-  <si>
-    <t>2:55pm</t>
-  </si>
-  <si>
-    <t>Arrive Roma Termini; taxi to the hotel</t>
-  </si>
-  <si>
-    <t>Taxi, ~12 min</t>
-  </si>
-  <si>
-    <t>3:20pm</t>
-  </si>
-  <si>
-    <t>Check in — Nomos Hotel — Via di San Paolo alla Regola, four minutes from Campo de' Fiori and two streets from where the trip began. Superior Double, and nothing is prepaid — you settle €530 with the hotel.</t>
-  </si>
-  <si>
-    <t>The Jewish Ghetto and the Portico d'Ottavia — Six minutes from the door, and the one corner of the centre you have not walked. Europe's oldest standing Jewish quarter, with the ruined portico built into the street</t>
-  </si>
-  <si>
-    <t>Tiber Island and the Ponte Fabricio — The bridge has carried people since 62 BC, still on the original stone</t>
-  </si>
-  <si>
-    <t>Trevi Fountain, one last time — Twenty minutes up through the centre. Worth the crowd on a last evening</t>
-  </si>
-  <si>
-    <t>Aperitivo on Campo de' Fiori — The market stalls are packed away by now and the square turns over to drinking</t>
-  </si>
-  <si>
-    <t>Walk, ~4 min</t>
-  </si>
-  <si>
-    <t>Farewell dinner — Aroma, at Palazzo Manfredi — Michelin-starred, on a rooftop looking straight into the Colosseum. Book early — only a dozen tables have the view.</t>
-  </si>
-  <si>
-    <t>Sun, Sep 6</t>
-  </si>
-  <si>
-    <t>DEPART — FCO → IAH</t>
-  </si>
-  <si>
-    <t>6:40am</t>
-  </si>
-  <si>
-    <t>Taxi to FCO — About thirty-five minutes on an empty Sunday road. No rental to return; that ended in Florence on Aug 31.</t>
-  </si>
-  <si>
     <t>7:20am</t>
   </si>
   <si>
@@ -1309,6 +1315,12 @@
     <t>San Gimignano Experience, 11am–3pm, ~€120pp: an hour in the saddle through vineyards and olive groves, then lunch, a cellar tour and tastings. A small-group tour, so it fills. Meets at the Bivio Volterra bus stop.</t>
   </si>
   <si>
+    <t>Rome opera — All Saints' Anglican, Aug 25 — CONFIRM THE PROGRAMME</t>
+  </si>
+  <si>
+    <t>Still unconfirmed and still unbooked, and the whole evening of the 25th is built on it. Check the Aug 25 programme is actually posted, then book. If there is no concert that night, say so and the evening becomes a long dinner instead.</t>
+  </si>
+  <si>
     <t>Galleria Borghese — reserved, card charged Aug 23</t>
   </si>
   <si>
@@ -1318,12 +1330,6 @@
     <t>THIS WEEK</t>
   </si>
   <si>
-    <t>Private driver — FCO → Hotel Trame, Aug 24</t>
-  </si>
-  <si>
-    <t>Pre-booked NCC, meeting you inside arrivals with a name board — roughly €70–90 for the two of you, against a €55 flat-rate official taxi if you would rather just walk to the rank. Give them the ITA flight number so the driver tracks the landing.</t>
-  </si>
-  <si>
     <t>Campania Express — Naples ↔ Sorrento, Aug 31 and Sep 5</t>
   </si>
   <si>
@@ -1336,12 +1342,6 @@
     <t>A chamber staging in a small church, so the room is small too. Closes the single full Florence day, after the walk back through the centre.</t>
   </si>
   <si>
-    <t>Rome opera — All Saints' Anglican, Aug 25</t>
-  </si>
-  <si>
-    <t>Confirm the programme is posted before booking.</t>
-  </si>
-  <si>
     <t>Driver — Amalfi → Ravello → Sorrento, Sep 4</t>
   </si>
   <si>
@@ -1351,7 +1351,7 @@
     <t>Headline dinners on their dates</t>
   </si>
   <si>
-    <t>Emma Aug 24 · Pierluigi Aug 25 · Da Enzo Aug 26 · Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice.</t>
+    <t>Pierluigi Aug 25 · Da Enzo Aug 26 · Borgo San Jacopo Aug 27 · Sostanza Aug 28 · La Via del Sale Aug 29 &amp; 30 · Cora Bistrot Aug 31 · O'Parrucchiano Sep 1 · Il Buco Sep 2 · Da Gemma (lunch) Sep 4 · Aroma at Palazzo Manfredi Sep 5. Aroma and Il Buco are the two that need the most notice. Night one is takeaway from Emma, so there is nothing to reserve on the 24th.</t>
   </si>
   <si>
     <t>BEFORE YOU GO</t>
@@ -1373,6 +1373,12 @@
   </si>
   <si>
     <t>Both from Sorrento's Marina Piccola, seasonal but well inside the window. Two or three morning departures down the coast and two or three back in the afternoon — check the current timetable close to the date, the schedules shift with the season.</t>
+  </si>
+  <si>
+    <t>Pantheon entry — Aug 24, on the Heart of Rome walk</t>
+  </si>
+  <si>
+    <t>The Pantheon is no longer free: EUR5 a head, with timed reservations at busy times. Aug 24 is a Monday and the walk reaches it mid-afternoon, so a walk-up will probably be fine — but booking removes the only queue on an otherwise unticketed day.</t>
   </si>
   <si>
     <t>RULED OUT</t>
@@ -2384,8 +2390,8 @@
       <c r="E8" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>68</v>
+      <c r="F8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2393,10 +2399,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2407,16 +2413,16 @@
         <v>48</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="F11" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2427,16 +2433,16 @@
         <v>48</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>68</v>
+      <c r="F12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2447,16 +2453,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="F13" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2467,7 +2473,7 @@
         <v>48</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>81</v>
@@ -2475,8 +2481,8 @@
       <c r="E14" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>83</v>
+      <c r="F14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2487,7 +2493,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>84</v>
@@ -2513,10 +2519,10 @@
         <v>87</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2536,7 +2542,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2544,10 +2550,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,16 +2564,16 @@
         <v>48</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2578,13 +2584,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
         <v>48</v>
@@ -2598,13 +2604,13 @@
         <v>48</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
         <v>48</v>
@@ -2618,16 +2624,16 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2638,13 +2644,13 @@
         <v>48</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
         <v>48</v>
@@ -2658,16 +2664,16 @@
         <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2678,13 +2684,13 @@
         <v>48</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F26" t="s">
         <v>48</v>
@@ -2701,10 +2707,10 @@
         <v>65</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
         <v>48</v>
@@ -2718,16 +2724,16 @@
         <v>48</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2735,13 +2741,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2752,13 +2758,13 @@
         <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s">
         <v>48</v>
@@ -2772,16 +2778,16 @@
         <v>48</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2792,10 +2798,10 @@
         <v>48</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>57</v>
@@ -2812,16 +2818,16 @@
         <v>48</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2835,13 +2841,13 @@
         <v>58</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2852,16 +2858,16 @@
         <v>48</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2872,13 +2878,13 @@
         <v>48</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
@@ -2895,10 +2901,10 @@
         <v>65</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" t="s">
         <v>48</v>
@@ -2912,16 +2918,16 @@
         <v>48</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2929,10 +2935,10 @@
         <v>5</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,16 +2949,16 @@
         <v>48</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,13 +2969,13 @@
         <v>48</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F43" t="s">
         <v>48</v>
@@ -2983,16 +2989,16 @@
         <v>48</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3003,13 +3009,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F45" t="s">
         <v>48</v>
@@ -3023,13 +3029,13 @@
         <v>48</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
@@ -3043,13 +3049,13 @@
         <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>48</v>
@@ -3063,13 +3069,13 @@
         <v>48</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
@@ -3083,16 +3089,16 @@
         <v>48</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,16 +3109,16 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3120,13 +3126,13 @@
         <v>6</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3137,13 +3143,13 @@
         <v>48</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
@@ -3157,13 +3163,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -3177,13 +3183,13 @@
         <v>48</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -3197,16 +3203,16 @@
         <v>48</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3217,10 +3223,10 @@
         <v>48</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>85</v>
@@ -3237,10 +3243,10 @@
         <v>48</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>85</v>
@@ -3257,13 +3263,13 @@
         <v>48</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F59" t="s">
         <v>48</v>
@@ -3280,13 +3286,13 @@
         <v>58</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,10 +3306,10 @@
         <v>61</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="F61" t="s">
         <v>48</v>
@@ -3317,13 +3323,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F62" t="s">
         <v>48</v>
@@ -3340,10 +3346,10 @@
         <v>86</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F63" t="s">
         <v>48</v>
@@ -3354,10 +3360,10 @@
         <v>7</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3368,13 +3374,13 @@
         <v>48</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -3388,10 +3394,10 @@
         <v>48</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>57</v>
@@ -3408,10 +3414,10 @@
         <v>48</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E68" s="13" t="s">
         <v>85</v>
@@ -3428,10 +3434,10 @@
         <v>48</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>85</v>
@@ -3448,16 +3454,16 @@
         <v>48</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3468,13 +3474,13 @@
         <v>48</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
@@ -3488,13 +3494,13 @@
         <v>48</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
@@ -3511,10 +3517,10 @@
         <v>86</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F73" t="s">
         <v>48</v>
@@ -3525,13 +3531,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3542,13 +3548,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -3562,13 +3568,13 @@
         <v>48</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -3582,13 +3588,13 @@
         <v>48</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -3602,16 +3608,16 @@
         <v>48</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3622,10 +3628,10 @@
         <v>48</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>57</v>
@@ -3642,16 +3648,16 @@
         <v>48</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3662,10 +3668,10 @@
         <v>48</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>57</v>
@@ -3682,16 +3688,16 @@
         <v>48</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3702,13 +3708,13 @@
         <v>48</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F84" t="s">
         <v>48</v>
@@ -3722,13 +3728,13 @@
         <v>48</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F85" t="s">
         <v>48</v>
@@ -3742,16 +3748,16 @@
         <v>48</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3759,10 +3765,10 @@
         <v>9</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3773,13 +3779,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F89" t="s">
         <v>48</v>
@@ -3793,13 +3799,13 @@
         <v>48</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F90" t="s">
         <v>48</v>
@@ -3813,16 +3819,16 @@
         <v>48</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,16 +3839,16 @@
         <v>48</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,13 +3859,13 @@
         <v>48</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F93" t="s">
         <v>48</v>
@@ -3873,13 +3879,13 @@
         <v>48</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F94" t="s">
         <v>48</v>
@@ -3896,13 +3902,13 @@
         <v>65</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3910,10 +3916,10 @@
         <v>10</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,13 +3930,13 @@
         <v>48</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F98" t="s">
         <v>48</v>
@@ -3944,16 +3950,16 @@
         <v>48</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3964,13 +3970,13 @@
         <v>48</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F100" t="s">
         <v>48</v>
@@ -3984,16 +3990,16 @@
         <v>48</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4004,16 +4010,16 @@
         <v>48</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4024,13 +4030,13 @@
         <v>48</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F103" t="s">
         <v>48</v>
@@ -4044,13 +4050,13 @@
         <v>48</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="F104" t="s">
         <v>48</v>
@@ -4064,16 +4070,16 @@
         <v>48</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4081,10 +4087,10 @@
         <v>11</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,13 +4101,13 @@
         <v>48</v>
       </c>
       